--- a/DadosRomaneios.xlsx
+++ b/DadosRomaneios.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\pedro.andrade\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{01E987C0-B592-44A4-A9BC-66DDD4657C11}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1CE11EF9-5BEB-4AF9-B4B3-109DCC56BD26}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{B6976704-8E51-4052-B60A-5847F95A5AE5}"/>
   </bookViews>
@@ -4220,7 +4220,7 @@
     </row>
     <row r="89" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A89" s="1">
-        <v>46304</v>
+        <v>46303</v>
       </c>
       <c r="B89">
         <v>101</v>
@@ -4229,22 +4229,22 @@
         <v>46303</v>
       </c>
       <c r="D89" t="s">
-        <v>72</v>
+        <v>11</v>
       </c>
       <c r="E89" t="s">
-        <v>73</v>
+        <v>12</v>
       </c>
       <c r="F89">
-        <v>69829</v>
+        <v>69306</v>
       </c>
       <c r="G89">
-        <v>178883</v>
+        <v>178885</v>
       </c>
       <c r="H89" s="2">
-        <v>8832</v>
+        <v>6579.82</v>
       </c>
       <c r="I89" s="1">
-        <v>46304</v>
+        <v>46311</v>
       </c>
     </row>
     <row r="90" spans="1:9" x14ac:dyDescent="0.25">
@@ -4255,25 +4255,25 @@
         <v>101</v>
       </c>
       <c r="C90" s="1">
-        <v>46303</v>
+        <v>46293</v>
       </c>
       <c r="D90" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="E90" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="F90">
-        <v>69306</v>
+        <v>68061</v>
       </c>
       <c r="G90">
-        <v>178885</v>
+        <v>178140</v>
       </c>
       <c r="H90" s="2">
-        <v>6579.82</v>
+        <v>6791.6</v>
       </c>
       <c r="I90" s="1">
-        <v>46311</v>
+        <v>46294</v>
       </c>
     </row>
     <row r="91" spans="1:9" x14ac:dyDescent="0.25">
@@ -4284,7 +4284,7 @@
         <v>101</v>
       </c>
       <c r="C91" s="1">
-        <v>46293</v>
+        <v>46301</v>
       </c>
       <c r="D91" t="s">
         <v>15</v>
@@ -4293,13 +4293,13 @@
         <v>16</v>
       </c>
       <c r="F91">
-        <v>68061</v>
+        <v>69133</v>
       </c>
       <c r="G91">
-        <v>178140</v>
+        <v>178759</v>
       </c>
       <c r="H91" s="2">
-        <v>6791.6</v>
+        <v>13819.85</v>
       </c>
       <c r="I91" s="1">
         <v>46294</v>
@@ -4313,7 +4313,7 @@
         <v>101</v>
       </c>
       <c r="C92" s="1">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="D92" t="s">
         <v>15</v>
@@ -4322,13 +4322,13 @@
         <v>16</v>
       </c>
       <c r="F92">
-        <v>69133</v>
+        <v>68718</v>
       </c>
       <c r="G92">
-        <v>178759</v>
+        <v>178867</v>
       </c>
       <c r="H92" s="2">
-        <v>13819.85</v>
+        <v>8147.6</v>
       </c>
       <c r="I92" s="1">
         <v>46294</v>
@@ -4342,7 +4342,7 @@
         <v>101</v>
       </c>
       <c r="C93" s="1">
-        <v>46302</v>
+        <v>46292</v>
       </c>
       <c r="D93" t="s">
         <v>15</v>
@@ -4351,13 +4351,13 @@
         <v>16</v>
       </c>
       <c r="F93">
-        <v>68718</v>
+        <v>68717</v>
       </c>
       <c r="G93">
-        <v>178867</v>
+        <v>178106</v>
       </c>
       <c r="H93" s="2">
-        <v>8147.6</v>
+        <v>1645</v>
       </c>
       <c r="I93" s="1">
         <v>46294</v>
@@ -4371,7 +4371,7 @@
         <v>101</v>
       </c>
       <c r="C94" s="1">
-        <v>46292</v>
+        <v>46300</v>
       </c>
       <c r="D94" t="s">
         <v>15</v>
@@ -4380,13 +4380,13 @@
         <v>16</v>
       </c>
       <c r="F94">
-        <v>68717</v>
+        <v>67330</v>
       </c>
       <c r="G94">
-        <v>178106</v>
+        <v>178651</v>
       </c>
       <c r="H94" s="2">
-        <v>1645</v>
+        <v>467.6</v>
       </c>
       <c r="I94" s="1">
         <v>46294</v>
@@ -4400,22 +4400,22 @@
         <v>101</v>
       </c>
       <c r="C95" s="1">
-        <v>46300</v>
+        <v>46292</v>
       </c>
       <c r="D95" t="s">
-        <v>15</v>
+        <v>74</v>
       </c>
       <c r="E95" t="s">
-        <v>16</v>
+        <v>75</v>
       </c>
       <c r="F95">
-        <v>67330</v>
+        <v>68527</v>
       </c>
       <c r="G95">
-        <v>178651</v>
+        <v>178089</v>
       </c>
       <c r="H95" s="2">
-        <v>467.6</v>
+        <v>591.27</v>
       </c>
       <c r="I95" s="1">
         <v>46294</v>
@@ -4429,22 +4429,22 @@
         <v>101</v>
       </c>
       <c r="C96" s="1">
-        <v>46292</v>
+        <v>46295</v>
       </c>
       <c r="D96" t="s">
-        <v>74</v>
+        <v>17</v>
       </c>
       <c r="E96" t="s">
-        <v>75</v>
+        <v>18</v>
       </c>
       <c r="F96">
-        <v>68527</v>
+        <v>67970</v>
       </c>
       <c r="G96">
-        <v>178089</v>
+        <v>178369</v>
       </c>
       <c r="H96" s="2">
-        <v>591.27</v>
+        <v>585.55999999999995</v>
       </c>
       <c r="I96" s="1">
         <v>46294</v>
@@ -4458,22 +4458,22 @@
         <v>101</v>
       </c>
       <c r="C97" s="1">
-        <v>46295</v>
+        <v>46302</v>
       </c>
       <c r="D97" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="E97" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="F97">
-        <v>67970</v>
+        <v>68410</v>
       </c>
       <c r="G97">
-        <v>178369</v>
+        <v>178868</v>
       </c>
       <c r="H97" s="2">
-        <v>585.55999999999995</v>
+        <v>7873.96</v>
       </c>
       <c r="I97" s="1">
         <v>46294</v>
@@ -4487,30 +4487,30 @@
         <v>101</v>
       </c>
       <c r="C98" s="1">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="D98" t="s">
-        <v>19</v>
+        <v>76</v>
       </c>
       <c r="E98" t="s">
-        <v>20</v>
+        <v>77</v>
       </c>
       <c r="F98">
-        <v>68410</v>
+        <v>69685</v>
       </c>
       <c r="G98">
-        <v>178868</v>
+        <v>178871</v>
       </c>
       <c r="H98" s="2">
-        <v>7873.96</v>
+        <v>2569.75</v>
       </c>
       <c r="I98" s="1">
-        <v>46294</v>
+        <v>46308</v>
       </c>
     </row>
     <row r="99" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A99" s="1">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="B99">
         <v>101</v>
@@ -4519,22 +4519,22 @@
         <v>46303</v>
       </c>
       <c r="D99" t="s">
-        <v>76</v>
+        <v>72</v>
       </c>
       <c r="E99" t="s">
-        <v>77</v>
+        <v>73</v>
       </c>
       <c r="F99">
-        <v>69685</v>
+        <v>69829</v>
       </c>
       <c r="G99">
-        <v>178871</v>
+        <v>178883</v>
       </c>
       <c r="H99" s="2">
-        <v>2569.75</v>
+        <v>8832</v>
       </c>
       <c r="I99" s="1">
-        <v>46308</v>
+        <v>46304</v>
       </c>
     </row>
     <row r="100" spans="1:9" x14ac:dyDescent="0.25">
@@ -7652,7 +7652,7 @@
     </row>
     <row r="209" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A209" s="1">
-        <v>46305</v>
+        <v>46304</v>
       </c>
       <c r="B209">
         <v>101</v>
@@ -7661,27 +7661,27 @@
         <v>46304</v>
       </c>
       <c r="D209" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="E209" t="s">
-        <v>165</v>
+        <v>1</v>
       </c>
       <c r="F209">
-        <v>68675</v>
+        <v>69149</v>
       </c>
       <c r="G209">
-        <v>179045</v>
+        <v>178999</v>
       </c>
       <c r="H209" s="2">
-        <v>2764.8</v>
+        <v>305.2</v>
       </c>
       <c r="I209" s="1">
-        <v>46304</v>
+        <v>46302</v>
       </c>
     </row>
     <row r="210" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A210" s="1">
-        <v>46305</v>
+        <v>46304</v>
       </c>
       <c r="B210">
         <v>101</v>
@@ -7690,22 +7690,22 @@
         <v>46304</v>
       </c>
       <c r="D210" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="E210" t="s">
-        <v>165</v>
+        <v>1</v>
       </c>
       <c r="F210">
-        <v>69744</v>
+        <v>69351</v>
       </c>
       <c r="G210">
-        <v>179044</v>
+        <v>179015</v>
       </c>
       <c r="H210" s="2">
-        <v>35025.4</v>
+        <v>2600.4499999999998</v>
       </c>
       <c r="I210" s="1">
-        <v>46304</v>
+        <v>46301</v>
       </c>
     </row>
     <row r="211" spans="1:9" x14ac:dyDescent="0.25">
@@ -7725,16 +7725,16 @@
         <v>1</v>
       </c>
       <c r="F211">
-        <v>69149</v>
+        <v>69352</v>
       </c>
       <c r="G211">
-        <v>178999</v>
+        <v>178998</v>
       </c>
       <c r="H211" s="2">
-        <v>305.2</v>
+        <v>521.02</v>
       </c>
       <c r="I211" s="1">
-        <v>46302</v>
+        <v>46303</v>
       </c>
     </row>
     <row r="212" spans="1:9" x14ac:dyDescent="0.25">
@@ -7754,21 +7754,21 @@
         <v>1</v>
       </c>
       <c r="F212">
-        <v>69351</v>
+        <v>69437</v>
       </c>
       <c r="G212">
-        <v>179015</v>
+        <v>179039</v>
       </c>
       <c r="H212" s="2">
-        <v>2600.4499999999998</v>
+        <v>2078.34</v>
       </c>
       <c r="I212" s="1">
-        <v>46301</v>
+        <v>46303</v>
       </c>
     </row>
     <row r="213" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A213" s="1">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="B213">
         <v>101</v>
@@ -7777,27 +7777,27 @@
         <v>46304</v>
       </c>
       <c r="D213" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="E213" t="s">
-        <v>1</v>
+        <v>165</v>
       </c>
       <c r="F213">
-        <v>69352</v>
+        <v>68675</v>
       </c>
       <c r="G213">
-        <v>178998</v>
+        <v>179045</v>
       </c>
       <c r="H213" s="2">
-        <v>521.02</v>
+        <v>2764.8</v>
       </c>
       <c r="I213" s="1">
-        <v>46303</v>
+        <v>46304</v>
       </c>
     </row>
     <row r="214" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A214" s="1">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="B214">
         <v>101</v>
@@ -7806,22 +7806,22 @@
         <v>46304</v>
       </c>
       <c r="D214" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="E214" t="s">
-        <v>1</v>
+        <v>165</v>
       </c>
       <c r="F214">
-        <v>69437</v>
+        <v>69744</v>
       </c>
       <c r="G214">
-        <v>179039</v>
+        <v>179044</v>
       </c>
       <c r="H214" s="2">
-        <v>2078.34</v>
+        <v>35025.4</v>
       </c>
       <c r="I214" s="1">
-        <v>46303</v>
+        <v>46304</v>
       </c>
     </row>
     <row r="215" spans="1:9" x14ac:dyDescent="0.25">
@@ -13491,80 +13491,86 @@
     </row>
     <row r="412" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A412" s="1">
-        <v>46309</v>
+        <v>46308</v>
       </c>
       <c r="B412">
         <v>101</v>
       </c>
       <c r="C412" s="1">
-        <v>46308</v>
+        <v>46304</v>
       </c>
       <c r="D412" t="s">
-        <v>44</v>
+        <v>292</v>
       </c>
       <c r="E412" t="s">
-        <v>45</v>
+        <v>293</v>
+      </c>
+      <c r="F412">
+        <v>69392</v>
       </c>
       <c r="G412">
-        <v>179295</v>
+        <v>179006</v>
       </c>
       <c r="H412" s="2">
-        <v>15485.79</v>
+        <v>1983.9</v>
+      </c>
+      <c r="I412" s="1">
+        <v>46314</v>
       </c>
     </row>
     <row r="413" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A413" s="1">
-        <v>46309</v>
+        <v>46308</v>
       </c>
       <c r="B413">
         <v>101</v>
       </c>
       <c r="C413" s="1">
-        <v>46308</v>
+        <v>46304</v>
       </c>
       <c r="D413" t="s">
-        <v>44</v>
+        <v>294</v>
       </c>
       <c r="E413" t="s">
-        <v>45</v>
+        <v>295</v>
       </c>
       <c r="F413">
-        <v>69945</v>
+        <v>69310</v>
       </c>
       <c r="G413">
-        <v>179294</v>
+        <v>179035</v>
       </c>
       <c r="H413" s="2">
-        <v>2100</v>
+        <v>1271.0999999999999</v>
       </c>
       <c r="I413" s="1">
-        <v>46308</v>
+        <v>46311</v>
       </c>
     </row>
     <row r="414" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A414" s="1">
-        <v>46309</v>
+        <v>46308</v>
       </c>
       <c r="B414">
         <v>101</v>
       </c>
       <c r="C414" s="1">
-        <v>46308</v>
+        <v>46305</v>
       </c>
       <c r="D414" t="s">
-        <v>290</v>
+        <v>296</v>
       </c>
       <c r="E414" t="s">
-        <v>291</v>
+        <v>1</v>
       </c>
       <c r="F414">
-        <v>69656</v>
+        <v>69543</v>
       </c>
       <c r="G414">
-        <v>179270</v>
+        <v>179143</v>
       </c>
       <c r="H414" s="2">
-        <v>283.60000000000002</v>
+        <v>30712.720000000001</v>
       </c>
       <c r="I414" s="1">
         <v>46308</v>
@@ -13578,25 +13584,25 @@
         <v>101</v>
       </c>
       <c r="C415" s="1">
-        <v>46304</v>
+        <v>46306</v>
       </c>
       <c r="D415" t="s">
-        <v>292</v>
+        <v>11</v>
       </c>
       <c r="E415" t="s">
-        <v>293</v>
+        <v>12</v>
       </c>
       <c r="F415">
-        <v>69392</v>
+        <v>69343</v>
       </c>
       <c r="G415">
-        <v>179006</v>
+        <v>179180</v>
       </c>
       <c r="H415" s="2">
-        <v>1983.9</v>
+        <v>1281.22</v>
       </c>
       <c r="I415" s="1">
-        <v>46314</v>
+        <v>46311</v>
       </c>
     </row>
     <row r="416" spans="1:9" x14ac:dyDescent="0.25">
@@ -13607,25 +13613,25 @@
         <v>101</v>
       </c>
       <c r="C416" s="1">
-        <v>46304</v>
+        <v>46307</v>
       </c>
       <c r="D416" t="s">
-        <v>294</v>
+        <v>297</v>
       </c>
       <c r="E416" t="s">
-        <v>295</v>
+        <v>298</v>
       </c>
       <c r="F416">
-        <v>69310</v>
+        <v>69282</v>
       </c>
       <c r="G416">
-        <v>179035</v>
+        <v>179240</v>
       </c>
       <c r="H416" s="2">
-        <v>1271.0999999999999</v>
+        <v>6749.72</v>
       </c>
       <c r="I416" s="1">
-        <v>46311</v>
+        <v>46317</v>
       </c>
     </row>
     <row r="417" spans="1:9" x14ac:dyDescent="0.25">
@@ -13636,25 +13642,25 @@
         <v>101</v>
       </c>
       <c r="C417" s="1">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="D417" t="s">
-        <v>296</v>
+        <v>299</v>
       </c>
       <c r="E417" t="s">
-        <v>1</v>
+        <v>43</v>
       </c>
       <c r="F417">
-        <v>69543</v>
+        <v>67806</v>
       </c>
       <c r="G417">
-        <v>179143</v>
+        <v>179157</v>
       </c>
       <c r="H417" s="2">
-        <v>30712.720000000001</v>
+        <v>2556</v>
       </c>
       <c r="I417" s="1">
-        <v>46308</v>
+        <v>46300</v>
       </c>
     </row>
     <row r="418" spans="1:9" x14ac:dyDescent="0.25">
@@ -13665,25 +13671,25 @@
         <v>101</v>
       </c>
       <c r="C418" s="1">
-        <v>46306</v>
+        <v>46304</v>
       </c>
       <c r="D418" t="s">
-        <v>11</v>
+        <v>307</v>
       </c>
       <c r="E418" t="s">
-        <v>12</v>
+        <v>208</v>
       </c>
       <c r="F418">
-        <v>69343</v>
+        <v>69436</v>
       </c>
       <c r="G418">
-        <v>179180</v>
+        <v>179014</v>
       </c>
       <c r="H418" s="2">
-        <v>1281.22</v>
+        <v>804.72</v>
       </c>
       <c r="I418" s="1">
-        <v>46311</v>
+        <v>46303</v>
       </c>
     </row>
     <row r="419" spans="1:9" x14ac:dyDescent="0.25">
@@ -13694,25 +13700,25 @@
         <v>101</v>
       </c>
       <c r="C419" s="1">
-        <v>46307</v>
+        <v>46304</v>
       </c>
       <c r="D419" t="s">
-        <v>297</v>
+        <v>308</v>
       </c>
       <c r="E419" t="s">
-        <v>298</v>
+        <v>309</v>
       </c>
       <c r="F419">
-        <v>69282</v>
+        <v>68124</v>
       </c>
       <c r="G419">
-        <v>179240</v>
+        <v>179016</v>
       </c>
       <c r="H419" s="2">
-        <v>6749.72</v>
+        <v>5155</v>
       </c>
       <c r="I419" s="1">
-        <v>46317</v>
+        <v>46281</v>
       </c>
     </row>
     <row r="420" spans="1:9" x14ac:dyDescent="0.25">
@@ -13726,195 +13732,201 @@
         <v>46306</v>
       </c>
       <c r="D420" t="s">
-        <v>299</v>
+        <v>310</v>
       </c>
       <c r="E420" t="s">
         <v>43</v>
       </c>
       <c r="F420">
-        <v>67806</v>
+        <v>68499</v>
       </c>
       <c r="G420">
-        <v>179157</v>
+        <v>179177</v>
       </c>
       <c r="H420" s="2">
-        <v>2556</v>
+        <v>3763</v>
       </c>
       <c r="I420" s="1">
-        <v>46300</v>
+        <v>1</v>
       </c>
     </row>
     <row r="421" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A421" s="1">
-        <v>46309</v>
+        <v>46308</v>
       </c>
       <c r="B421">
         <v>101</v>
       </c>
       <c r="C421" s="1">
-        <v>46308</v>
+        <v>46306</v>
       </c>
       <c r="D421" t="s">
-        <v>300</v>
+        <v>310</v>
       </c>
       <c r="E421" t="s">
-        <v>301</v>
+        <v>43</v>
       </c>
       <c r="F421">
-        <v>69774</v>
+        <v>69315</v>
       </c>
       <c r="G421">
-        <v>179269</v>
+        <v>179171</v>
       </c>
       <c r="H421" s="2">
-        <v>833.92</v>
+        <v>417.6</v>
       </c>
       <c r="I421" s="1">
-        <v>46308</v>
+        <v>46300</v>
       </c>
     </row>
     <row r="422" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A422" s="1">
-        <v>46309</v>
+        <v>46308</v>
       </c>
       <c r="B422">
         <v>101</v>
       </c>
       <c r="C422" s="1">
-        <v>46308</v>
+        <v>46306</v>
       </c>
       <c r="D422" t="s">
-        <v>231</v>
+        <v>311</v>
       </c>
       <c r="E422" t="s">
-        <v>232</v>
+        <v>312</v>
+      </c>
+      <c r="F422">
+        <v>68459</v>
       </c>
       <c r="G422">
-        <v>179291</v>
+        <v>179159</v>
       </c>
       <c r="H422" s="2">
-        <v>1193.1099999999999</v>
+        <v>761.75</v>
+      </c>
+      <c r="I422" s="1">
+        <v>46287</v>
       </c>
     </row>
     <row r="423" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A423" s="1">
-        <v>46309</v>
+        <v>46308</v>
       </c>
       <c r="B423">
         <v>101</v>
       </c>
       <c r="C423" s="1">
-        <v>46308</v>
+        <v>46306</v>
       </c>
       <c r="D423" t="s">
-        <v>416</v>
+        <v>19</v>
       </c>
       <c r="E423" t="s">
-        <v>417</v>
+        <v>20</v>
       </c>
       <c r="F423">
-        <v>68800</v>
+        <v>69517</v>
       </c>
       <c r="G423">
-        <v>179271</v>
+        <v>179165</v>
       </c>
       <c r="H423" s="2">
-        <v>1414.25</v>
+        <v>13.2</v>
       </c>
       <c r="I423" s="1">
-        <v>46293</v>
+        <v>46301</v>
       </c>
     </row>
     <row r="424" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A424" s="1">
-        <v>46309</v>
+        <v>46308</v>
       </c>
       <c r="B424">
         <v>101</v>
       </c>
       <c r="C424" s="1">
-        <v>46308</v>
+        <v>46306</v>
       </c>
       <c r="D424" t="s">
-        <v>54</v>
+        <v>313</v>
       </c>
       <c r="E424" t="s">
-        <v>55</v>
+        <v>314</v>
       </c>
       <c r="F424">
-        <v>69781</v>
+        <v>66362</v>
       </c>
       <c r="G424">
-        <v>179275</v>
+        <v>179186</v>
       </c>
       <c r="H424" s="2">
-        <v>1074</v>
+        <v>440</v>
       </c>
       <c r="I424" s="1">
-        <v>46308</v>
+        <v>46295</v>
       </c>
     </row>
     <row r="425" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A425" s="1">
-        <v>46309</v>
+        <v>46308</v>
       </c>
       <c r="B425">
         <v>101</v>
       </c>
       <c r="C425" s="1">
-        <v>46303</v>
+        <v>46306</v>
       </c>
       <c r="D425" t="s">
-        <v>302</v>
+        <v>315</v>
       </c>
       <c r="E425" t="s">
-        <v>303</v>
+        <v>316</v>
       </c>
       <c r="F425">
-        <v>68896</v>
+        <v>66876</v>
       </c>
       <c r="G425">
-        <v>178889</v>
+        <v>179182</v>
       </c>
       <c r="H425" s="2">
-        <v>2700</v>
+        <v>2822.1</v>
       </c>
       <c r="I425" s="1">
-        <v>46294</v>
+        <v>46295</v>
       </c>
     </row>
     <row r="426" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A426" s="1">
-        <v>46309</v>
+        <v>46308</v>
       </c>
       <c r="B426">
         <v>101</v>
       </c>
       <c r="C426" s="1">
-        <v>46303</v>
+        <v>46306</v>
       </c>
       <c r="D426" t="s">
-        <v>302</v>
+        <v>317</v>
       </c>
       <c r="E426" t="s">
-        <v>303</v>
+        <v>318</v>
       </c>
       <c r="F426">
-        <v>68897</v>
+        <v>69258</v>
       </c>
       <c r="G426">
-        <v>178938</v>
+        <v>179161</v>
       </c>
       <c r="H426" s="2">
-        <v>2700</v>
+        <v>128.69999999999999</v>
       </c>
       <c r="I426" s="1">
-        <v>46294</v>
+        <v>46297</v>
       </c>
     </row>
     <row r="427" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A427" s="1">
-        <v>46309</v>
+        <v>46308</v>
       </c>
       <c r="B427">
         <v>101</v>
@@ -13923,114 +13935,114 @@
         <v>46307</v>
       </c>
       <c r="D427" t="s">
-        <v>5</v>
+        <v>319</v>
       </c>
       <c r="E427" t="s">
-        <v>6</v>
+        <v>320</v>
       </c>
       <c r="F427">
-        <v>69193</v>
+        <v>69318</v>
       </c>
       <c r="G427">
-        <v>179202</v>
+        <v>179210</v>
       </c>
       <c r="H427" s="2">
-        <v>891</v>
+        <v>1126.24</v>
       </c>
       <c r="I427" s="1">
-        <v>46308</v>
+        <v>46303</v>
       </c>
     </row>
     <row r="428" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A428" s="1">
-        <v>46309</v>
+        <v>46308</v>
       </c>
       <c r="B428">
         <v>101</v>
       </c>
       <c r="C428" s="1">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="D428" t="s">
-        <v>5</v>
+        <v>310</v>
       </c>
       <c r="E428" t="s">
-        <v>6</v>
+        <v>43</v>
       </c>
       <c r="F428">
-        <v>69291</v>
+        <v>68477</v>
       </c>
       <c r="G428">
-        <v>179203</v>
+        <v>179360</v>
       </c>
       <c r="H428" s="2">
-        <v>990</v>
+        <v>40740</v>
       </c>
       <c r="I428" s="1">
-        <v>46308</v>
+        <v>46287</v>
       </c>
     </row>
     <row r="429" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A429" s="1">
-        <v>46309</v>
+        <v>46308</v>
       </c>
       <c r="B429">
         <v>101</v>
       </c>
       <c r="C429" s="1">
-        <v>46304</v>
+        <v>46308</v>
       </c>
       <c r="D429" t="s">
-        <v>134</v>
+        <v>321</v>
       </c>
       <c r="E429" t="s">
-        <v>135</v>
+        <v>322</v>
       </c>
       <c r="F429">
-        <v>69539</v>
+        <v>67697</v>
       </c>
       <c r="G429">
-        <v>178991</v>
+        <v>179278</v>
       </c>
       <c r="H429" s="2">
-        <v>161.04</v>
+        <v>1965.6</v>
       </c>
       <c r="I429" s="1">
-        <v>46303</v>
+        <v>46279</v>
       </c>
     </row>
     <row r="430" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A430" s="1">
-        <v>46309</v>
+        <v>46308</v>
       </c>
       <c r="B430">
         <v>101</v>
       </c>
       <c r="C430" s="1">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="D430" t="s">
-        <v>304</v>
+        <v>315</v>
       </c>
       <c r="E430" t="s">
-        <v>305</v>
+        <v>316</v>
       </c>
       <c r="F430">
-        <v>69782</v>
+        <v>69468</v>
       </c>
       <c r="G430">
-        <v>179212</v>
+        <v>179340</v>
       </c>
       <c r="H430" s="2">
-        <v>1164.4000000000001</v>
+        <v>1531.16</v>
       </c>
       <c r="I430" s="1">
-        <v>46304</v>
+        <v>46311</v>
       </c>
     </row>
     <row r="431" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A431" s="1">
-        <v>46309</v>
+        <v>46308</v>
       </c>
       <c r="B431">
         <v>101</v>
@@ -14039,16 +14051,22 @@
         <v>46308</v>
       </c>
       <c r="D431" t="s">
-        <v>123</v>
+        <v>323</v>
       </c>
       <c r="E431" t="s">
-        <v>124</v>
+        <v>324</v>
+      </c>
+      <c r="F431">
+        <v>69587</v>
       </c>
       <c r="G431">
-        <v>179286</v>
+        <v>179285</v>
       </c>
       <c r="H431" s="2">
-        <v>5236.78</v>
+        <v>1165.2</v>
+      </c>
+      <c r="I431" s="1">
+        <v>46304</v>
       </c>
     </row>
     <row r="432" spans="1:9" x14ac:dyDescent="0.25">
@@ -14062,22 +14080,16 @@
         <v>46308</v>
       </c>
       <c r="D432" t="s">
-        <v>306</v>
+        <v>44</v>
       </c>
       <c r="E432" t="s">
-        <v>99</v>
-      </c>
-      <c r="F432">
-        <v>69477</v>
+        <v>45</v>
       </c>
       <c r="G432">
-        <v>179273</v>
+        <v>179295</v>
       </c>
       <c r="H432" s="2">
-        <v>7943.55</v>
-      </c>
-      <c r="I432" s="1">
-        <v>46307</v>
+        <v>15485.79</v>
       </c>
     </row>
     <row r="433" spans="1:9" x14ac:dyDescent="0.25">
@@ -14091,22 +14103,22 @@
         <v>46308</v>
       </c>
       <c r="D433" t="s">
-        <v>130</v>
+        <v>44</v>
       </c>
       <c r="E433" t="s">
-        <v>131</v>
+        <v>45</v>
       </c>
       <c r="F433">
-        <v>69691</v>
+        <v>69945</v>
       </c>
       <c r="G433">
-        <v>179365</v>
+        <v>179294</v>
       </c>
       <c r="H433" s="2">
-        <v>248.9</v>
+        <v>2100</v>
       </c>
       <c r="I433" s="1">
-        <v>46309</v>
+        <v>46308</v>
       </c>
     </row>
     <row r="434" spans="1:9" x14ac:dyDescent="0.25">
@@ -14120,288 +14132,282 @@
         <v>46308</v>
       </c>
       <c r="D434" t="s">
-        <v>134</v>
+        <v>290</v>
       </c>
       <c r="E434" t="s">
-        <v>135</v>
+        <v>291</v>
       </c>
       <c r="F434">
-        <v>68186</v>
+        <v>69656</v>
       </c>
       <c r="G434">
-        <v>179268</v>
+        <v>179270</v>
       </c>
       <c r="H434" s="2">
-        <v>5692.68</v>
+        <v>283.60000000000002</v>
       </c>
       <c r="I434" s="1">
-        <v>46296</v>
+        <v>46308</v>
       </c>
     </row>
     <row r="435" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A435" s="1">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="B435">
         <v>101</v>
       </c>
       <c r="C435" s="1">
-        <v>46304</v>
+        <v>46308</v>
       </c>
       <c r="D435" t="s">
-        <v>307</v>
+        <v>300</v>
       </c>
       <c r="E435" t="s">
-        <v>208</v>
+        <v>301</v>
       </c>
       <c r="F435">
-        <v>69436</v>
+        <v>69774</v>
       </c>
       <c r="G435">
-        <v>179014</v>
+        <v>179269</v>
       </c>
       <c r="H435" s="2">
-        <v>804.72</v>
+        <v>833.92</v>
       </c>
       <c r="I435" s="1">
-        <v>46303</v>
+        <v>46308</v>
       </c>
     </row>
     <row r="436" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A436" s="1">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="B436">
         <v>101</v>
       </c>
       <c r="C436" s="1">
-        <v>46304</v>
+        <v>46308</v>
       </c>
       <c r="D436" t="s">
-        <v>308</v>
+        <v>231</v>
       </c>
       <c r="E436" t="s">
-        <v>309</v>
-      </c>
-      <c r="F436">
-        <v>68124</v>
+        <v>232</v>
       </c>
       <c r="G436">
-        <v>179016</v>
+        <v>179291</v>
       </c>
       <c r="H436" s="2">
-        <v>5155</v>
-      </c>
-      <c r="I436" s="1">
-        <v>46281</v>
+        <v>1193.1099999999999</v>
       </c>
     </row>
     <row r="437" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A437" s="1">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="B437">
         <v>101</v>
       </c>
       <c r="C437" s="1">
-        <v>46306</v>
+        <v>46308</v>
       </c>
       <c r="D437" t="s">
-        <v>310</v>
+        <v>416</v>
       </c>
       <c r="E437" t="s">
-        <v>43</v>
+        <v>417</v>
       </c>
       <c r="F437">
-        <v>68499</v>
+        <v>68800</v>
       </c>
       <c r="G437">
-        <v>179177</v>
+        <v>179271</v>
       </c>
       <c r="H437" s="2">
-        <v>3763</v>
+        <v>1414.25</v>
       </c>
       <c r="I437" s="1">
-        <v>1</v>
+        <v>46293</v>
       </c>
     </row>
     <row r="438" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A438" s="1">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="B438">
         <v>101</v>
       </c>
       <c r="C438" s="1">
-        <v>46306</v>
+        <v>46308</v>
       </c>
       <c r="D438" t="s">
-        <v>310</v>
+        <v>54</v>
       </c>
       <c r="E438" t="s">
-        <v>43</v>
+        <v>55</v>
       </c>
       <c r="F438">
-        <v>69315</v>
+        <v>69781</v>
       </c>
       <c r="G438">
-        <v>179171</v>
+        <v>179275</v>
       </c>
       <c r="H438" s="2">
-        <v>417.6</v>
+        <v>1074</v>
       </c>
       <c r="I438" s="1">
-        <v>46300</v>
+        <v>46308</v>
       </c>
     </row>
     <row r="439" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A439" s="1">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="B439">
         <v>101</v>
       </c>
       <c r="C439" s="1">
-        <v>46306</v>
+        <v>46303</v>
       </c>
       <c r="D439" t="s">
-        <v>311</v>
+        <v>302</v>
       </c>
       <c r="E439" t="s">
-        <v>312</v>
+        <v>303</v>
       </c>
       <c r="F439">
-        <v>68459</v>
+        <v>68896</v>
       </c>
       <c r="G439">
-        <v>179159</v>
+        <v>178889</v>
       </c>
       <c r="H439" s="2">
-        <v>761.75</v>
+        <v>2700</v>
       </c>
       <c r="I439" s="1">
-        <v>46287</v>
+        <v>46294</v>
       </c>
     </row>
     <row r="440" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A440" s="1">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="B440">
         <v>101</v>
       </c>
       <c r="C440" s="1">
-        <v>46306</v>
+        <v>46303</v>
       </c>
       <c r="D440" t="s">
-        <v>19</v>
+        <v>302</v>
       </c>
       <c r="E440" t="s">
-        <v>20</v>
+        <v>303</v>
       </c>
       <c r="F440">
-        <v>69517</v>
+        <v>68897</v>
       </c>
       <c r="G440">
-        <v>179165</v>
+        <v>178938</v>
       </c>
       <c r="H440" s="2">
-        <v>13.2</v>
+        <v>2700</v>
       </c>
       <c r="I440" s="1">
-        <v>46301</v>
+        <v>46294</v>
       </c>
     </row>
     <row r="441" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A441" s="1">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="B441">
         <v>101</v>
       </c>
       <c r="C441" s="1">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="D441" t="s">
-        <v>313</v>
+        <v>5</v>
       </c>
       <c r="E441" t="s">
-        <v>314</v>
+        <v>6</v>
       </c>
       <c r="F441">
-        <v>66362</v>
+        <v>69193</v>
       </c>
       <c r="G441">
-        <v>179186</v>
+        <v>179202</v>
       </c>
       <c r="H441" s="2">
-        <v>440</v>
+        <v>891</v>
       </c>
       <c r="I441" s="1">
-        <v>46295</v>
+        <v>46308</v>
       </c>
     </row>
     <row r="442" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A442" s="1">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="B442">
         <v>101</v>
       </c>
       <c r="C442" s="1">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="D442" t="s">
-        <v>315</v>
+        <v>5</v>
       </c>
       <c r="E442" t="s">
-        <v>316</v>
+        <v>6</v>
       </c>
       <c r="F442">
-        <v>66876</v>
+        <v>69291</v>
       </c>
       <c r="G442">
-        <v>179182</v>
+        <v>179203</v>
       </c>
       <c r="H442" s="2">
-        <v>2822.1</v>
+        <v>990</v>
       </c>
       <c r="I442" s="1">
-        <v>46295</v>
+        <v>46308</v>
       </c>
     </row>
     <row r="443" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A443" s="1">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="B443">
         <v>101</v>
       </c>
       <c r="C443" s="1">
-        <v>46306</v>
+        <v>46304</v>
       </c>
       <c r="D443" t="s">
-        <v>317</v>
+        <v>134</v>
       </c>
       <c r="E443" t="s">
-        <v>318</v>
+        <v>135</v>
       </c>
       <c r="F443">
-        <v>69258</v>
+        <v>69539</v>
       </c>
       <c r="G443">
-        <v>179161</v>
+        <v>178991</v>
       </c>
       <c r="H443" s="2">
-        <v>128.69999999999999</v>
+        <v>161.04</v>
       </c>
       <c r="I443" s="1">
-        <v>46297</v>
+        <v>46303</v>
       </c>
     </row>
     <row r="444" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A444" s="1">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="B444">
         <v>101</v>
@@ -14410,27 +14416,27 @@
         <v>46307</v>
       </c>
       <c r="D444" t="s">
-        <v>319</v>
+        <v>304</v>
       </c>
       <c r="E444" t="s">
-        <v>320</v>
+        <v>305</v>
       </c>
       <c r="F444">
-        <v>69318</v>
+        <v>69782</v>
       </c>
       <c r="G444">
-        <v>179210</v>
+        <v>179212</v>
       </c>
       <c r="H444" s="2">
-        <v>1126.24</v>
+        <v>1164.4000000000001</v>
       </c>
       <c r="I444" s="1">
-        <v>46303</v>
+        <v>46304</v>
       </c>
     </row>
     <row r="445" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A445" s="1">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="B445">
         <v>101</v>
@@ -14439,27 +14445,21 @@
         <v>46308</v>
       </c>
       <c r="D445" t="s">
-        <v>310</v>
+        <v>123</v>
       </c>
       <c r="E445" t="s">
-        <v>43</v>
-      </c>
-      <c r="F445">
-        <v>68477</v>
+        <v>124</v>
       </c>
       <c r="G445">
-        <v>179360</v>
+        <v>179286</v>
       </c>
       <c r="H445" s="2">
-        <v>40740</v>
-      </c>
-      <c r="I445" s="1">
-        <v>46287</v>
+        <v>5236.78</v>
       </c>
     </row>
     <row r="446" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A446" s="1">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="B446">
         <v>101</v>
@@ -14468,27 +14468,27 @@
         <v>46308</v>
       </c>
       <c r="D446" t="s">
-        <v>321</v>
+        <v>306</v>
       </c>
       <c r="E446" t="s">
-        <v>322</v>
+        <v>99</v>
       </c>
       <c r="F446">
-        <v>67697</v>
+        <v>69477</v>
       </c>
       <c r="G446">
-        <v>179278</v>
+        <v>179273</v>
       </c>
       <c r="H446" s="2">
-        <v>1965.6</v>
+        <v>7943.55</v>
       </c>
       <c r="I446" s="1">
-        <v>46279</v>
+        <v>46307</v>
       </c>
     </row>
     <row r="447" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A447" s="1">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="B447">
         <v>101</v>
@@ -14497,27 +14497,27 @@
         <v>46308</v>
       </c>
       <c r="D447" t="s">
-        <v>315</v>
+        <v>130</v>
       </c>
       <c r="E447" t="s">
-        <v>316</v>
+        <v>131</v>
       </c>
       <c r="F447">
-        <v>69468</v>
+        <v>69691</v>
       </c>
       <c r="G447">
-        <v>179340</v>
+        <v>179365</v>
       </c>
       <c r="H447" s="2">
-        <v>1531.16</v>
+        <v>248.9</v>
       </c>
       <c r="I447" s="1">
-        <v>46311</v>
+        <v>46309</v>
       </c>
     </row>
     <row r="448" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A448" s="1">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="B448">
         <v>101</v>
@@ -14526,22 +14526,22 @@
         <v>46308</v>
       </c>
       <c r="D448" t="s">
-        <v>323</v>
+        <v>134</v>
       </c>
       <c r="E448" t="s">
-        <v>324</v>
+        <v>135</v>
       </c>
       <c r="F448">
-        <v>69587</v>
+        <v>68186</v>
       </c>
       <c r="G448">
-        <v>179285</v>
+        <v>179268</v>
       </c>
       <c r="H448" s="2">
-        <v>1165.2</v>
+        <v>5692.68</v>
       </c>
       <c r="I448" s="1">
-        <v>46304</v>
+        <v>46296</v>
       </c>
     </row>
     <row r="449" spans="1:9" x14ac:dyDescent="0.25">
@@ -17526,94 +17526,94 @@
     </row>
     <row r="553" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A553" s="1">
-        <v>46310</v>
+        <v>46309</v>
       </c>
       <c r="B553">
         <v>101</v>
       </c>
       <c r="C553" s="1">
-        <v>46301</v>
+        <v>46300</v>
       </c>
       <c r="D553" t="s">
-        <v>34</v>
+        <v>360</v>
       </c>
       <c r="E553" t="s">
-        <v>35</v>
+        <v>361</v>
       </c>
       <c r="F553">
-        <v>68369</v>
+        <v>67222</v>
       </c>
       <c r="G553">
-        <v>178768</v>
+        <v>178649</v>
       </c>
       <c r="H553" s="2">
-        <v>11873.92</v>
+        <v>3427.56</v>
       </c>
       <c r="I553" s="1">
-        <v>46289</v>
+        <v>46294</v>
       </c>
     </row>
     <row r="554" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A554" s="1">
-        <v>46310</v>
+        <v>46309</v>
       </c>
       <c r="B554">
         <v>101</v>
       </c>
       <c r="C554" s="1">
-        <v>46302</v>
+        <v>46300</v>
       </c>
       <c r="D554" t="s">
-        <v>337</v>
+        <v>280</v>
       </c>
       <c r="E554" t="s">
-        <v>338</v>
+        <v>281</v>
       </c>
       <c r="F554">
-        <v>69787</v>
+        <v>67280</v>
       </c>
       <c r="G554">
-        <v>178860</v>
+        <v>178693</v>
       </c>
       <c r="H554" s="2">
-        <v>4200</v>
+        <v>1228.6199999999999</v>
       </c>
       <c r="I554" s="1">
-        <v>46303</v>
+        <v>46294</v>
       </c>
     </row>
     <row r="555" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A555" s="1">
-        <v>46310</v>
+        <v>46309</v>
       </c>
       <c r="B555">
         <v>101</v>
       </c>
       <c r="C555" s="1">
-        <v>46303</v>
+        <v>46301</v>
       </c>
       <c r="D555" t="s">
-        <v>339</v>
+        <v>19</v>
       </c>
       <c r="E555" t="s">
-        <v>340</v>
+        <v>20</v>
       </c>
       <c r="F555">
-        <v>68666</v>
+        <v>69083</v>
       </c>
       <c r="G555">
-        <v>178879</v>
+        <v>178756</v>
       </c>
       <c r="H555" s="2">
-        <v>2016</v>
+        <v>1347.21</v>
       </c>
       <c r="I555" s="1">
-        <v>1</v>
+        <v>46294</v>
       </c>
     </row>
     <row r="556" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A556" s="1">
-        <v>46310</v>
+        <v>46309</v>
       </c>
       <c r="B556">
         <v>101</v>
@@ -17622,339 +17622,375 @@
         <v>46306</v>
       </c>
       <c r="D556" t="s">
-        <v>341</v>
+        <v>310</v>
       </c>
       <c r="E556" t="s">
-        <v>342</v>
+        <v>43</v>
       </c>
       <c r="F556">
-        <v>68724</v>
+        <v>69209</v>
       </c>
       <c r="G556">
-        <v>179158</v>
+        <v>179190</v>
       </c>
       <c r="H556" s="2">
-        <v>355</v>
+        <v>144</v>
       </c>
       <c r="I556" s="1">
-        <v>46300</v>
+        <v>46295</v>
       </c>
     </row>
     <row r="557" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A557" s="1">
-        <v>46310</v>
+        <v>46309</v>
       </c>
       <c r="B557">
         <v>101</v>
       </c>
       <c r="C557" s="1">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="D557" t="s">
-        <v>343</v>
+        <v>362</v>
       </c>
       <c r="E557" t="s">
-        <v>344</v>
+        <v>363</v>
       </c>
       <c r="F557">
-        <v>68287</v>
+        <v>69557</v>
       </c>
       <c r="G557">
-        <v>179160</v>
+        <v>179258</v>
       </c>
       <c r="H557" s="2">
-        <v>237.2</v>
+        <v>2750.5</v>
       </c>
       <c r="I557" s="1">
-        <v>1</v>
+        <v>46304</v>
       </c>
     </row>
     <row r="558" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A558" s="1">
-        <v>46310</v>
+        <v>46309</v>
       </c>
       <c r="B558">
         <v>101</v>
       </c>
       <c r="C558" s="1">
-        <v>46308</v>
+        <v>46307</v>
       </c>
       <c r="D558" t="s">
-        <v>345</v>
+        <v>364</v>
       </c>
       <c r="E558" t="s">
-        <v>346</v>
+        <v>32</v>
       </c>
       <c r="F558">
-        <v>69001</v>
+        <v>69221</v>
       </c>
       <c r="G558">
-        <v>179364</v>
+        <v>179257</v>
       </c>
       <c r="H558" s="2">
-        <v>578.1</v>
+        <v>1377.66</v>
       </c>
       <c r="I558" s="1">
-        <v>46309</v>
+        <v>46296</v>
       </c>
     </row>
     <row r="559" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A559" s="1">
-        <v>46310</v>
+        <v>46309</v>
       </c>
       <c r="B559">
         <v>101</v>
       </c>
       <c r="C559" s="1">
-        <v>46309</v>
+        <v>46307</v>
       </c>
       <c r="D559" t="s">
-        <v>34</v>
+        <v>365</v>
       </c>
       <c r="E559" t="s">
-        <v>35</v>
+        <v>32</v>
+      </c>
+      <c r="F559">
+        <v>69565</v>
       </c>
       <c r="G559">
-        <v>179393</v>
+        <v>179254</v>
       </c>
       <c r="H559" s="2">
-        <v>3131.08</v>
+        <v>1615.1</v>
+      </c>
+      <c r="I559" s="1">
+        <v>46304</v>
       </c>
     </row>
     <row r="560" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A560" s="1">
-        <v>46310</v>
+        <v>46309</v>
       </c>
       <c r="B560">
         <v>101</v>
       </c>
       <c r="C560" s="1">
-        <v>46309</v>
+        <v>46307</v>
       </c>
       <c r="D560" t="s">
-        <v>27</v>
+        <v>366</v>
       </c>
       <c r="E560" t="s">
-        <v>28</v>
+        <v>32</v>
+      </c>
+      <c r="F560">
+        <v>69568</v>
       </c>
       <c r="G560">
-        <v>179392</v>
+        <v>179256</v>
       </c>
       <c r="H560" s="2">
-        <v>4357.7700000000004</v>
+        <v>596.09</v>
+      </c>
+      <c r="I560" s="1">
+        <v>46304</v>
       </c>
     </row>
     <row r="561" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A561" s="1">
-        <v>46310</v>
+        <v>46309</v>
       </c>
       <c r="B561">
         <v>101</v>
       </c>
       <c r="C561" s="1">
-        <v>46309</v>
+        <v>46307</v>
       </c>
       <c r="D561" t="s">
-        <v>27</v>
+        <v>367</v>
       </c>
       <c r="E561" t="s">
-        <v>28</v>
+        <v>32</v>
+      </c>
+      <c r="F561">
+        <v>69675</v>
       </c>
       <c r="G561">
-        <v>179456</v>
+        <v>179253</v>
       </c>
       <c r="H561" s="2">
-        <v>35065.599999999999</v>
+        <v>646.72</v>
+      </c>
+      <c r="I561" s="1">
+        <v>46308</v>
       </c>
     </row>
     <row r="562" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A562" s="1">
-        <v>46310</v>
+        <v>46309</v>
       </c>
       <c r="B562">
         <v>101</v>
       </c>
       <c r="C562" s="1">
-        <v>46309</v>
+        <v>46307</v>
       </c>
       <c r="D562" t="s">
-        <v>27</v>
+        <v>368</v>
       </c>
       <c r="E562" t="s">
-        <v>28</v>
+        <v>369</v>
       </c>
       <c r="F562">
-        <v>68993</v>
+        <v>69644</v>
       </c>
       <c r="G562">
-        <v>179398</v>
+        <v>179246</v>
       </c>
       <c r="H562" s="2">
-        <v>141.94</v>
+        <v>667.2</v>
       </c>
       <c r="I562" s="1">
-        <v>46303</v>
+        <v>46308</v>
       </c>
     </row>
     <row r="563" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A563" s="1">
-        <v>46310</v>
+        <v>46309</v>
       </c>
       <c r="B563">
         <v>101</v>
       </c>
       <c r="C563" s="1">
-        <v>46309</v>
+        <v>46307</v>
       </c>
       <c r="D563" t="s">
-        <v>31</v>
+        <v>370</v>
       </c>
       <c r="E563" t="s">
-        <v>32</v>
+        <v>184</v>
+      </c>
+      <c r="F563">
+        <v>69558</v>
       </c>
       <c r="G563">
-        <v>179373</v>
+        <v>179255</v>
       </c>
       <c r="H563" s="2">
-        <v>1219.98</v>
+        <v>568.62</v>
+      </c>
+      <c r="I563" s="1">
+        <v>46304</v>
       </c>
     </row>
     <row r="564" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A564" s="1">
-        <v>46310</v>
+        <v>46309</v>
       </c>
       <c r="B564">
         <v>101</v>
       </c>
       <c r="C564" s="1">
-        <v>46309</v>
+        <v>46307</v>
       </c>
       <c r="D564" t="s">
-        <v>33</v>
+        <v>311</v>
       </c>
       <c r="E564" t="s">
-        <v>32</v>
+        <v>312</v>
       </c>
       <c r="F564">
-        <v>69275</v>
+        <v>68453</v>
       </c>
       <c r="G564">
-        <v>179399</v>
+        <v>179247</v>
       </c>
       <c r="H564" s="2">
-        <v>762.9</v>
+        <v>3241.96</v>
       </c>
       <c r="I564" s="1">
-        <v>46296</v>
+        <v>46286</v>
       </c>
     </row>
     <row r="565" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A565" s="1">
-        <v>46310</v>
+        <v>46309</v>
       </c>
       <c r="B565">
         <v>101</v>
       </c>
       <c r="C565" s="1">
-        <v>46309</v>
+        <v>46307</v>
       </c>
       <c r="D565" t="s">
-        <v>347</v>
+        <v>311</v>
       </c>
       <c r="E565" t="s">
-        <v>32</v>
+        <v>312</v>
+      </c>
+      <c r="F565">
+        <v>68454</v>
       </c>
       <c r="G565">
-        <v>179394</v>
+        <v>179248</v>
       </c>
       <c r="H565" s="2">
-        <v>1647.31</v>
+        <v>2480.21</v>
+      </c>
+      <c r="I565" s="1">
+        <v>46286</v>
       </c>
     </row>
     <row r="566" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A566" s="1">
-        <v>46310</v>
+        <v>46309</v>
       </c>
       <c r="B566">
         <v>101</v>
       </c>
       <c r="C566" s="1">
-        <v>46309</v>
+        <v>46307</v>
       </c>
       <c r="D566" t="s">
-        <v>341</v>
+        <v>371</v>
       </c>
       <c r="E566" t="s">
-        <v>342</v>
+        <v>372</v>
+      </c>
+      <c r="F566">
+        <v>67396</v>
       </c>
       <c r="G566">
-        <v>179377</v>
+        <v>179249</v>
       </c>
       <c r="H566" s="2">
-        <v>4762.8</v>
+        <v>1991.6</v>
+      </c>
+      <c r="I566" s="1">
+        <v>46287</v>
       </c>
     </row>
     <row r="567" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A567" s="1">
-        <v>46310</v>
+        <v>46309</v>
       </c>
       <c r="B567">
         <v>101</v>
       </c>
       <c r="C567" s="1">
-        <v>46309</v>
+        <v>46308</v>
       </c>
       <c r="D567" t="s">
-        <v>341</v>
+        <v>310</v>
       </c>
       <c r="E567" t="s">
-        <v>342</v>
+        <v>43</v>
       </c>
       <c r="F567">
-        <v>68902</v>
+        <v>69713</v>
       </c>
       <c r="G567">
-        <v>179414</v>
+        <v>179315</v>
       </c>
       <c r="H567" s="2">
-        <v>200</v>
+        <v>6683.04</v>
       </c>
       <c r="I567" s="1">
-        <v>46296</v>
+        <v>46303</v>
       </c>
     </row>
     <row r="568" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A568" s="1">
-        <v>46310</v>
+        <v>46309</v>
       </c>
       <c r="B568">
         <v>101</v>
       </c>
       <c r="C568" s="1">
-        <v>46309</v>
+        <v>46308</v>
       </c>
       <c r="D568" t="s">
-        <v>341</v>
+        <v>310</v>
       </c>
       <c r="E568" t="s">
-        <v>342</v>
+        <v>43</v>
       </c>
       <c r="F568">
-        <v>69316</v>
+        <v>69923</v>
       </c>
       <c r="G568">
-        <v>179375</v>
+        <v>179280</v>
       </c>
       <c r="H568" s="2">
-        <v>453.6</v>
+        <v>5800</v>
       </c>
       <c r="I568" s="1">
-        <v>46309</v>
+        <v>46308</v>
       </c>
     </row>
     <row r="569" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A569" s="1">
-        <v>46310</v>
+        <v>46309</v>
       </c>
       <c r="B569">
         <v>101</v>
@@ -17963,51 +17999,45 @@
         <v>46309</v>
       </c>
       <c r="D569" t="s">
-        <v>341</v>
+        <v>373</v>
       </c>
       <c r="E569" t="s">
-        <v>342</v>
-      </c>
-      <c r="F569">
-        <v>69498</v>
+        <v>374</v>
       </c>
       <c r="G569">
-        <v>179371</v>
+        <v>179397</v>
       </c>
       <c r="H569" s="2">
-        <v>850.4</v>
-      </c>
-      <c r="I569" s="1">
-        <v>46309</v>
+        <v>1668.01</v>
       </c>
     </row>
     <row r="570" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A570" s="1">
+        <v>46309</v>
+      </c>
+      <c r="B570">
+        <v>101</v>
+      </c>
+      <c r="C570" s="1">
+        <v>46309</v>
+      </c>
+      <c r="D570" t="s">
+        <v>375</v>
+      </c>
+      <c r="E570" t="s">
+        <v>376</v>
+      </c>
+      <c r="F570">
+        <v>69894</v>
+      </c>
+      <c r="G570">
+        <v>179395</v>
+      </c>
+      <c r="H570" s="2">
+        <v>3165</v>
+      </c>
+      <c r="I570" s="1">
         <v>46310</v>
-      </c>
-      <c r="B570">
-        <v>101</v>
-      </c>
-      <c r="C570" s="1">
-        <v>46309</v>
-      </c>
-      <c r="D570" t="s">
-        <v>341</v>
-      </c>
-      <c r="E570" t="s">
-        <v>342</v>
-      </c>
-      <c r="F570">
-        <v>69795</v>
-      </c>
-      <c r="G570">
-        <v>179389</v>
-      </c>
-      <c r="H570" s="2">
-        <v>284</v>
-      </c>
-      <c r="I570" s="1">
-        <v>46309</v>
       </c>
     </row>
     <row r="571" spans="1:9" x14ac:dyDescent="0.25">
@@ -18018,25 +18048,25 @@
         <v>101</v>
       </c>
       <c r="C571" s="1">
-        <v>46309</v>
+        <v>46301</v>
       </c>
       <c r="D571" t="s">
-        <v>341</v>
+        <v>34</v>
       </c>
       <c r="E571" t="s">
-        <v>342</v>
+        <v>35</v>
       </c>
       <c r="F571">
-        <v>69842</v>
+        <v>68369</v>
       </c>
       <c r="G571">
-        <v>179388</v>
+        <v>178768</v>
       </c>
       <c r="H571" s="2">
-        <v>84</v>
+        <v>11873.92</v>
       </c>
       <c r="I571" s="1">
-        <v>46309</v>
+        <v>46289</v>
       </c>
     </row>
     <row r="572" spans="1:9" x14ac:dyDescent="0.25">
@@ -18047,25 +18077,25 @@
         <v>101</v>
       </c>
       <c r="C572" s="1">
-        <v>46309</v>
+        <v>46302</v>
       </c>
       <c r="D572" t="s">
-        <v>348</v>
+        <v>337</v>
       </c>
       <c r="E572" t="s">
-        <v>349</v>
+        <v>338</v>
       </c>
       <c r="F572">
-        <v>69792</v>
+        <v>69787</v>
       </c>
       <c r="G572">
-        <v>179374</v>
+        <v>178860</v>
       </c>
       <c r="H572" s="2">
-        <v>4762.8</v>
+        <v>4200</v>
       </c>
       <c r="I572" s="1">
-        <v>46309</v>
+        <v>46303</v>
       </c>
     </row>
     <row r="573" spans="1:9" x14ac:dyDescent="0.25">
@@ -18076,19 +18106,25 @@
         <v>101</v>
       </c>
       <c r="C573" s="1">
-        <v>46309</v>
+        <v>46303</v>
       </c>
       <c r="D573" t="s">
-        <v>343</v>
+        <v>339</v>
       </c>
       <c r="E573" t="s">
-        <v>344</v>
+        <v>340</v>
+      </c>
+      <c r="F573">
+        <v>68666</v>
       </c>
       <c r="G573">
-        <v>179441</v>
+        <v>178879</v>
       </c>
       <c r="H573" s="2">
-        <v>1749.84</v>
+        <v>2016</v>
+      </c>
+      <c r="I573" s="1">
+        <v>1</v>
       </c>
     </row>
     <row r="574" spans="1:9" x14ac:dyDescent="0.25">
@@ -18099,19 +18135,25 @@
         <v>101</v>
       </c>
       <c r="C574" s="1">
-        <v>46309</v>
+        <v>46306</v>
       </c>
       <c r="D574" t="s">
-        <v>350</v>
+        <v>341</v>
       </c>
       <c r="E574" t="s">
-        <v>351</v>
+        <v>342</v>
+      </c>
+      <c r="F574">
+        <v>68724</v>
       </c>
       <c r="G574">
-        <v>179415</v>
+        <v>179158</v>
       </c>
       <c r="H574" s="2">
-        <v>4759.8999999999996</v>
+        <v>355</v>
+      </c>
+      <c r="I574" s="1">
+        <v>46300</v>
       </c>
     </row>
     <row r="575" spans="1:9" x14ac:dyDescent="0.25">
@@ -18122,25 +18164,25 @@
         <v>101</v>
       </c>
       <c r="C575" s="1">
-        <v>46309</v>
+        <v>46306</v>
       </c>
       <c r="D575" t="s">
-        <v>350</v>
+        <v>343</v>
       </c>
       <c r="E575" t="s">
-        <v>351</v>
+        <v>344</v>
       </c>
       <c r="F575">
-        <v>68807</v>
+        <v>68287</v>
       </c>
       <c r="G575">
-        <v>179413</v>
+        <v>179160</v>
       </c>
       <c r="H575" s="2">
-        <v>2147.5500000000002</v>
+        <v>237.2</v>
       </c>
       <c r="I575" s="1">
-        <v>46309</v>
+        <v>1</v>
       </c>
     </row>
     <row r="576" spans="1:9" x14ac:dyDescent="0.25">
@@ -18151,22 +18193,22 @@
         <v>101</v>
       </c>
       <c r="C576" s="1">
-        <v>46309</v>
+        <v>46308</v>
       </c>
       <c r="D576" t="s">
-        <v>350</v>
+        <v>345</v>
       </c>
       <c r="E576" t="s">
-        <v>351</v>
+        <v>346</v>
       </c>
       <c r="F576">
-        <v>68809</v>
+        <v>69001</v>
       </c>
       <c r="G576">
-        <v>179391</v>
+        <v>179364</v>
       </c>
       <c r="H576" s="2">
-        <v>923</v>
+        <v>578.1</v>
       </c>
       <c r="I576" s="1">
         <v>46309</v>
@@ -18183,22 +18225,16 @@
         <v>46309</v>
       </c>
       <c r="D577" t="s">
-        <v>350</v>
+        <v>34</v>
       </c>
       <c r="E577" t="s">
-        <v>351</v>
-      </c>
-      <c r="F577">
-        <v>69370</v>
+        <v>35</v>
       </c>
       <c r="G577">
-        <v>179400</v>
+        <v>179393</v>
       </c>
       <c r="H577" s="2">
-        <v>1903.5</v>
-      </c>
-      <c r="I577" s="1">
-        <v>46309</v>
+        <v>3131.08</v>
       </c>
     </row>
     <row r="578" spans="1:9" x14ac:dyDescent="0.25">
@@ -18212,22 +18248,16 @@
         <v>46309</v>
       </c>
       <c r="D578" t="s">
-        <v>350</v>
+        <v>27</v>
       </c>
       <c r="E578" t="s">
-        <v>351</v>
-      </c>
-      <c r="F578">
-        <v>69778</v>
+        <v>28</v>
       </c>
       <c r="G578">
-        <v>179433</v>
+        <v>179392</v>
       </c>
       <c r="H578" s="2">
-        <v>600</v>
-      </c>
-      <c r="I578" s="1">
-        <v>46309</v>
+        <v>4357.7700000000004</v>
       </c>
     </row>
     <row r="579" spans="1:9" x14ac:dyDescent="0.25">
@@ -18235,28 +18265,22 @@
         <v>46310</v>
       </c>
       <c r="B579">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="C579" s="1">
-        <v>45222</v>
+        <v>46309</v>
       </c>
       <c r="D579" t="s">
-        <v>352</v>
+        <v>27</v>
       </c>
       <c r="E579" t="s">
-        <v>353</v>
-      </c>
-      <c r="F579">
-        <v>450</v>
+        <v>28</v>
       </c>
       <c r="G579">
-        <v>514</v>
+        <v>179456</v>
       </c>
       <c r="H579" s="2">
-        <v>125.82</v>
-      </c>
-      <c r="I579" s="1">
-        <v>45222</v>
+        <v>35065.599999999999</v>
       </c>
     </row>
     <row r="580" spans="1:9" x14ac:dyDescent="0.25">
@@ -18264,28 +18288,28 @@
         <v>46310</v>
       </c>
       <c r="B580">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="C580" s="1">
-        <v>45222</v>
+        <v>46309</v>
       </c>
       <c r="D580" t="s">
-        <v>354</v>
+        <v>27</v>
       </c>
       <c r="E580" t="s">
-        <v>208</v>
+        <v>28</v>
       </c>
       <c r="F580">
-        <v>459</v>
+        <v>68993</v>
       </c>
       <c r="G580">
-        <v>516</v>
+        <v>179398</v>
       </c>
       <c r="H580" s="2">
-        <v>898.2</v>
+        <v>141.94</v>
       </c>
       <c r="I580" s="1">
-        <v>45222</v>
+        <v>46303</v>
       </c>
     </row>
     <row r="581" spans="1:9" x14ac:dyDescent="0.25">
@@ -18296,25 +18320,19 @@
         <v>101</v>
       </c>
       <c r="C581" s="1">
-        <v>46306</v>
+        <v>46309</v>
       </c>
       <c r="D581" t="s">
-        <v>271</v>
+        <v>31</v>
       </c>
       <c r="E581" t="s">
-        <v>272</v>
-      </c>
-      <c r="F581">
-        <v>68599</v>
+        <v>32</v>
       </c>
       <c r="G581">
-        <v>179200</v>
+        <v>179373</v>
       </c>
       <c r="H581" s="2">
-        <v>2384.5700000000002</v>
-      </c>
-      <c r="I581" s="1">
-        <v>46296</v>
+        <v>1219.98</v>
       </c>
     </row>
     <row r="582" spans="1:9" x14ac:dyDescent="0.25">
@@ -18328,22 +18346,22 @@
         <v>46309</v>
       </c>
       <c r="D582" t="s">
-        <v>355</v>
+        <v>33</v>
       </c>
       <c r="E582" t="s">
         <v>32</v>
       </c>
       <c r="F582">
-        <v>69955</v>
+        <v>69275</v>
       </c>
       <c r="G582">
-        <v>179430</v>
+        <v>179399</v>
       </c>
       <c r="H582" s="2">
-        <v>1594.8</v>
+        <v>762.9</v>
       </c>
       <c r="I582" s="1">
-        <v>46310</v>
+        <v>46296</v>
       </c>
     </row>
     <row r="583" spans="1:9" x14ac:dyDescent="0.25">
@@ -18357,22 +18375,16 @@
         <v>46309</v>
       </c>
       <c r="D583" t="s">
-        <v>356</v>
+        <v>347</v>
       </c>
       <c r="E583" t="s">
-        <v>357</v>
-      </c>
-      <c r="F583">
-        <v>69869</v>
+        <v>32</v>
       </c>
       <c r="G583">
-        <v>179384</v>
+        <v>179394</v>
       </c>
       <c r="H583" s="2">
-        <v>392.4</v>
-      </c>
-      <c r="I583" s="1">
-        <v>46309</v>
+        <v>1647.31</v>
       </c>
     </row>
     <row r="584" spans="1:9" x14ac:dyDescent="0.25">
@@ -18386,22 +18398,16 @@
         <v>46309</v>
       </c>
       <c r="D584" t="s">
-        <v>358</v>
+        <v>341</v>
       </c>
       <c r="E584" t="s">
-        <v>359</v>
-      </c>
-      <c r="F584">
-        <v>69663</v>
+        <v>342</v>
       </c>
       <c r="G584">
-        <v>179387</v>
+        <v>179377</v>
       </c>
       <c r="H584" s="2">
-        <v>1771.2</v>
-      </c>
-      <c r="I584" s="1">
-        <v>46309</v>
+        <v>4762.8</v>
       </c>
     </row>
     <row r="585" spans="1:9" x14ac:dyDescent="0.25">
@@ -18415,22 +18421,22 @@
         <v>46309</v>
       </c>
       <c r="D585" t="s">
-        <v>151</v>
+        <v>341</v>
       </c>
       <c r="E585" t="s">
-        <v>49</v>
+        <v>342</v>
       </c>
       <c r="F585">
-        <v>70060</v>
+        <v>68902</v>
       </c>
       <c r="G585">
-        <v>179435</v>
+        <v>179414</v>
       </c>
       <c r="H585" s="2">
-        <v>1406.66</v>
+        <v>200</v>
       </c>
       <c r="I585" s="1">
-        <v>46310</v>
+        <v>46296</v>
       </c>
     </row>
     <row r="586" spans="1:9" x14ac:dyDescent="0.25">
@@ -18441,488 +18447,482 @@
         <v>101</v>
       </c>
       <c r="C586" s="1">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="D586" t="s">
-        <v>58</v>
+        <v>341</v>
       </c>
       <c r="E586" t="s">
-        <v>59</v>
+        <v>342</v>
+      </c>
+      <c r="F586">
+        <v>69316</v>
       </c>
       <c r="G586">
-        <v>179369</v>
+        <v>179375</v>
       </c>
       <c r="H586" s="2">
-        <v>26935.55</v>
+        <v>453.6</v>
+      </c>
+      <c r="I586" s="1">
+        <v>46309</v>
       </c>
     </row>
     <row r="587" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A587" s="1">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="B587">
         <v>101</v>
       </c>
       <c r="C587" s="1">
-        <v>46300</v>
+        <v>46309</v>
       </c>
       <c r="D587" t="s">
-        <v>360</v>
+        <v>341</v>
       </c>
       <c r="E587" t="s">
-        <v>361</v>
+        <v>342</v>
       </c>
       <c r="F587">
-        <v>67222</v>
+        <v>69498</v>
       </c>
       <c r="G587">
-        <v>178649</v>
+        <v>179371</v>
       </c>
       <c r="H587" s="2">
-        <v>3427.56</v>
+        <v>850.4</v>
       </c>
       <c r="I587" s="1">
-        <v>46294</v>
+        <v>46309</v>
       </c>
     </row>
     <row r="588" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A588" s="1">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="B588">
         <v>101</v>
       </c>
       <c r="C588" s="1">
-        <v>46300</v>
+        <v>46309</v>
       </c>
       <c r="D588" t="s">
-        <v>280</v>
+        <v>341</v>
       </c>
       <c r="E588" t="s">
-        <v>281</v>
+        <v>342</v>
       </c>
       <c r="F588">
-        <v>67280</v>
+        <v>69795</v>
       </c>
       <c r="G588">
-        <v>178693</v>
+        <v>179389</v>
       </c>
       <c r="H588" s="2">
-        <v>1228.6199999999999</v>
+        <v>284</v>
       </c>
       <c r="I588" s="1">
-        <v>46294</v>
+        <v>46309</v>
       </c>
     </row>
     <row r="589" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A589" s="1">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="B589">
         <v>101</v>
       </c>
       <c r="C589" s="1">
-        <v>46301</v>
+        <v>46309</v>
       </c>
       <c r="D589" t="s">
-        <v>19</v>
+        <v>341</v>
       </c>
       <c r="E589" t="s">
-        <v>20</v>
+        <v>342</v>
       </c>
       <c r="F589">
-        <v>69083</v>
+        <v>69842</v>
       </c>
       <c r="G589">
-        <v>178756</v>
+        <v>179388</v>
       </c>
       <c r="H589" s="2">
-        <v>1347.21</v>
+        <v>84</v>
       </c>
       <c r="I589" s="1">
-        <v>46294</v>
+        <v>46309</v>
       </c>
     </row>
     <row r="590" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A590" s="1">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="B590">
         <v>101</v>
       </c>
       <c r="C590" s="1">
-        <v>46306</v>
+        <v>46309</v>
       </c>
       <c r="D590" t="s">
-        <v>310</v>
+        <v>348</v>
       </c>
       <c r="E590" t="s">
-        <v>43</v>
+        <v>349</v>
       </c>
       <c r="F590">
-        <v>69209</v>
+        <v>69792</v>
       </c>
       <c r="G590">
-        <v>179190</v>
+        <v>179374</v>
       </c>
       <c r="H590" s="2">
-        <v>144</v>
+        <v>4762.8</v>
       </c>
       <c r="I590" s="1">
-        <v>46295</v>
+        <v>46309</v>
       </c>
     </row>
     <row r="591" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A591" s="1">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="B591">
         <v>101</v>
       </c>
       <c r="C591" s="1">
-        <v>46307</v>
+        <v>46309</v>
       </c>
       <c r="D591" t="s">
-        <v>362</v>
+        <v>343</v>
       </c>
       <c r="E591" t="s">
-        <v>363</v>
-      </c>
-      <c r="F591">
-        <v>69557</v>
+        <v>344</v>
       </c>
       <c r="G591">
-        <v>179258</v>
+        <v>179441</v>
       </c>
       <c r="H591" s="2">
-        <v>2750.5</v>
-      </c>
-      <c r="I591" s="1">
-        <v>46304</v>
+        <v>1749.84</v>
       </c>
     </row>
     <row r="592" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A592" s="1">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="B592">
         <v>101</v>
       </c>
       <c r="C592" s="1">
-        <v>46307</v>
+        <v>46309</v>
       </c>
       <c r="D592" t="s">
-        <v>364</v>
+        <v>350</v>
       </c>
       <c r="E592" t="s">
-        <v>32</v>
-      </c>
-      <c r="F592">
-        <v>69221</v>
+        <v>351</v>
       </c>
       <c r="G592">
-        <v>179257</v>
+        <v>179415</v>
       </c>
       <c r="H592" s="2">
-        <v>1377.66</v>
-      </c>
-      <c r="I592" s="1">
-        <v>46296</v>
+        <v>4759.8999999999996</v>
       </c>
     </row>
     <row r="593" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A593" s="1">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="B593">
         <v>101</v>
       </c>
       <c r="C593" s="1">
-        <v>46307</v>
+        <v>46309</v>
       </c>
       <c r="D593" t="s">
-        <v>365</v>
+        <v>350</v>
       </c>
       <c r="E593" t="s">
-        <v>32</v>
+        <v>351</v>
       </c>
       <c r="F593">
-        <v>69565</v>
+        <v>68807</v>
       </c>
       <c r="G593">
-        <v>179254</v>
+        <v>179413</v>
       </c>
       <c r="H593" s="2">
-        <v>1615.1</v>
+        <v>2147.5500000000002</v>
       </c>
       <c r="I593" s="1">
-        <v>46304</v>
+        <v>46309</v>
       </c>
     </row>
     <row r="594" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A594" s="1">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="B594">
         <v>101</v>
       </c>
       <c r="C594" s="1">
-        <v>46307</v>
+        <v>46309</v>
       </c>
       <c r="D594" t="s">
-        <v>366</v>
+        <v>350</v>
       </c>
       <c r="E594" t="s">
-        <v>32</v>
+        <v>351</v>
       </c>
       <c r="F594">
-        <v>69568</v>
+        <v>68809</v>
       </c>
       <c r="G594">
-        <v>179256</v>
+        <v>179391</v>
       </c>
       <c r="H594" s="2">
-        <v>596.09</v>
+        <v>923</v>
       </c>
       <c r="I594" s="1">
-        <v>46304</v>
+        <v>46309</v>
       </c>
     </row>
     <row r="595" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A595" s="1">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="B595">
         <v>101</v>
       </c>
       <c r="C595" s="1">
-        <v>46307</v>
+        <v>46309</v>
       </c>
       <c r="D595" t="s">
-        <v>367</v>
+        <v>350</v>
       </c>
       <c r="E595" t="s">
-        <v>32</v>
+        <v>351</v>
       </c>
       <c r="F595">
-        <v>69675</v>
+        <v>69370</v>
       </c>
       <c r="G595">
-        <v>179253</v>
+        <v>179400</v>
       </c>
       <c r="H595" s="2">
-        <v>646.72</v>
+        <v>1903.5</v>
       </c>
       <c r="I595" s="1">
-        <v>46308</v>
+        <v>46309</v>
       </c>
     </row>
     <row r="596" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A596" s="1">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="B596">
         <v>101</v>
       </c>
       <c r="C596" s="1">
-        <v>46307</v>
+        <v>46309</v>
       </c>
       <c r="D596" t="s">
-        <v>368</v>
+        <v>350</v>
       </c>
       <c r="E596" t="s">
-        <v>369</v>
+        <v>351</v>
       </c>
       <c r="F596">
-        <v>69644</v>
+        <v>69778</v>
       </c>
       <c r="G596">
-        <v>179246</v>
+        <v>179433</v>
       </c>
       <c r="H596" s="2">
-        <v>667.2</v>
+        <v>600</v>
       </c>
       <c r="I596" s="1">
-        <v>46308</v>
+        <v>46309</v>
       </c>
     </row>
     <row r="597" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A597" s="1">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="B597">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="C597" s="1">
-        <v>46307</v>
+        <v>45222</v>
       </c>
       <c r="D597" t="s">
-        <v>370</v>
+        <v>352</v>
       </c>
       <c r="E597" t="s">
-        <v>184</v>
+        <v>353</v>
       </c>
       <c r="F597">
-        <v>69558</v>
+        <v>450</v>
       </c>
       <c r="G597">
-        <v>179255</v>
+        <v>514</v>
       </c>
       <c r="H597" s="2">
-        <v>568.62</v>
+        <v>125.82</v>
       </c>
       <c r="I597" s="1">
-        <v>46304</v>
+        <v>45222</v>
       </c>
     </row>
     <row r="598" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A598" s="1">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="B598">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="C598" s="1">
-        <v>46307</v>
+        <v>45222</v>
       </c>
       <c r="D598" t="s">
-        <v>311</v>
+        <v>354</v>
       </c>
       <c r="E598" t="s">
-        <v>312</v>
+        <v>208</v>
       </c>
       <c r="F598">
-        <v>68453</v>
+        <v>459</v>
       </c>
       <c r="G598">
-        <v>179247</v>
+        <v>516</v>
       </c>
       <c r="H598" s="2">
-        <v>3241.96</v>
+        <v>898.2</v>
       </c>
       <c r="I598" s="1">
-        <v>46286</v>
+        <v>45222</v>
       </c>
     </row>
     <row r="599" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A599" s="1">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="B599">
         <v>101</v>
       </c>
       <c r="C599" s="1">
-        <v>46307</v>
+        <v>46306</v>
       </c>
       <c r="D599" t="s">
-        <v>311</v>
+        <v>271</v>
       </c>
       <c r="E599" t="s">
-        <v>312</v>
+        <v>272</v>
       </c>
       <c r="F599">
-        <v>68454</v>
+        <v>68599</v>
       </c>
       <c r="G599">
-        <v>179248</v>
+        <v>179200</v>
       </c>
       <c r="H599" s="2">
-        <v>2480.21</v>
+        <v>2384.5700000000002</v>
       </c>
       <c r="I599" s="1">
-        <v>46286</v>
+        <v>46296</v>
       </c>
     </row>
     <row r="600" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A600" s="1">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="B600">
         <v>101</v>
       </c>
       <c r="C600" s="1">
-        <v>46307</v>
+        <v>46309</v>
       </c>
       <c r="D600" t="s">
-        <v>371</v>
+        <v>355</v>
       </c>
       <c r="E600" t="s">
-        <v>372</v>
+        <v>32</v>
       </c>
       <c r="F600">
-        <v>67396</v>
+        <v>69955</v>
       </c>
       <c r="G600">
-        <v>179249</v>
+        <v>179430</v>
       </c>
       <c r="H600" s="2">
-        <v>1991.6</v>
+        <v>1594.8</v>
       </c>
       <c r="I600" s="1">
-        <v>46287</v>
+        <v>46310</v>
       </c>
     </row>
     <row r="601" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A601" s="1">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="B601">
         <v>101</v>
       </c>
       <c r="C601" s="1">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="D601" t="s">
-        <v>310</v>
+        <v>356</v>
       </c>
       <c r="E601" t="s">
-        <v>43</v>
+        <v>357</v>
       </c>
       <c r="F601">
-        <v>69713</v>
+        <v>69869</v>
       </c>
       <c r="G601">
-        <v>179315</v>
+        <v>179384</v>
       </c>
       <c r="H601" s="2">
-        <v>6683.04</v>
+        <v>392.4</v>
       </c>
       <c r="I601" s="1">
-        <v>46303</v>
+        <v>46309</v>
       </c>
     </row>
     <row r="602" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A602" s="1">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="B602">
         <v>101</v>
       </c>
       <c r="C602" s="1">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="D602" t="s">
-        <v>310</v>
+        <v>358</v>
       </c>
       <c r="E602" t="s">
-        <v>43</v>
+        <v>359</v>
       </c>
       <c r="F602">
-        <v>69923</v>
+        <v>69663</v>
       </c>
       <c r="G602">
-        <v>179280</v>
+        <v>179387</v>
       </c>
       <c r="H602" s="2">
-        <v>5800</v>
+        <v>1771.2</v>
       </c>
       <c r="I602" s="1">
-        <v>46308</v>
+        <v>46309</v>
       </c>
     </row>
     <row r="603" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A603" s="1">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="B603">
         <v>101</v>
@@ -18931,45 +18931,45 @@
         <v>46309</v>
       </c>
       <c r="D603" t="s">
-        <v>373</v>
+        <v>151</v>
       </c>
       <c r="E603" t="s">
-        <v>374</v>
+        <v>49</v>
+      </c>
+      <c r="F603">
+        <v>70060</v>
       </c>
       <c r="G603">
-        <v>179397</v>
+        <v>179435</v>
       </c>
       <c r="H603" s="2">
-        <v>1668.01</v>
+        <v>1406.66</v>
+      </c>
+      <c r="I603" s="1">
+        <v>46310</v>
       </c>
     </row>
     <row r="604" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A604" s="1">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="B604">
         <v>101</v>
       </c>
       <c r="C604" s="1">
-        <v>46309</v>
+        <v>46308</v>
       </c>
       <c r="D604" t="s">
-        <v>375</v>
+        <v>58</v>
       </c>
       <c r="E604" t="s">
-        <v>376</v>
-      </c>
-      <c r="F604">
-        <v>69894</v>
+        <v>59</v>
       </c>
       <c r="G604">
-        <v>179395</v>
+        <v>179369</v>
       </c>
       <c r="H604" s="2">
-        <v>3165</v>
-      </c>
-      <c r="I604" s="1">
-        <v>46310</v>
+        <v>26935.55</v>
       </c>
     </row>
     <row r="605" spans="1:9" x14ac:dyDescent="0.25">
@@ -22242,6 +22242,9 @@
       </c>
     </row>
   </sheetData>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:I719">
+    <sortCondition ref="A703:A719"/>
+  </sortState>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
   <pageSetup orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
 </worksheet>

--- a/DadosRomaneios.xlsx
+++ b/DadosRomaneios.xlsx
@@ -8,12 +8,13 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\pedro.andrade\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1CE11EF9-5BEB-4AF9-B4B3-109DCC56BD26}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{60B97880-BCEF-486C-9ADF-DBCD7F7C6AF8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{B6976704-8E51-4052-B60A-5847F95A5AE5}"/>
+    <workbookView xWindow="16284" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{B6976704-8E51-4052-B60A-5847F95A5AE5}"/>
   </bookViews>
   <sheets>
     <sheet name="Romaneios" sheetId="2" r:id="rId1"/>
+    <sheet name="Planilha1" sheetId="3" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -38,8 +39,30 @@
 </workbook>
 </file>
 
+<file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
+<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
+  <metadataTypes count="1">
+    <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
+  </metadataTypes>
+  <futureMetadata name="XLDAPR" count="1">
+    <bk>
+      <extLst>
+        <ext uri="{bdbb8cdc-fa1e-496e-a857-3c3f30c029c3}">
+          <xda:dynamicArrayProperties fDynamic="1" fCollapsed="0"/>
+        </ext>
+      </extLst>
+    </bk>
+  </futureMetadata>
+  <cellMetadata count="1">
+    <bk>
+      <rc t="1" v="0"/>
+    </bk>
+  </cellMetadata>
+</metadata>
+</file>
+
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1445" uniqueCount="421">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1446" uniqueCount="422">
   <si>
     <t>000024 - 021</t>
   </si>
@@ -1302,6 +1325,9 @@
   </si>
   <si>
     <t>AFIP CLEMENTINO</t>
+  </si>
+  <si>
+    <t>Qtd. Expedição</t>
   </si>
 </sst>
 </file>
@@ -1311,13 +1337,19 @@
   <numFmts count="1">
     <numFmt numFmtId="8" formatCode="&quot;R$&quot;\ #,##0.00;[Red]\-&quot;R$&quot;\ #,##0.00"/>
   </numFmts>
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF242424"/>
+      <name val="Consolas"/>
+      <family val="3"/>
     </font>
   </fonts>
   <fills count="2">
@@ -1340,10 +1372,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="8" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -22248,4 +22281,118 @@
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
   <pageSetup orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5180BF9C-1943-4030-8A1B-6F86FE205C17}">
+  <dimension ref="A1:C11"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="12.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14.28515625" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="str" cm="1">
+        <f t="array" ref="A1:A11">_xlfn.UNIQUE(Romaneios!A1:A719)</f>
+        <v>Dt. Romaneio</v>
+      </c>
+      <c r="B1" t="s">
+        <v>421</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2" s="1">
+        <v>46302</v>
+      </c>
+      <c r="B2">
+        <f>COUNTIF(Romaneios!A:A,Planilha1!A2)</f>
+        <v>35</v>
+      </c>
+      <c r="C2" s="3"/>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3" s="1">
+        <v>46303</v>
+      </c>
+      <c r="B3">
+        <f>COUNTIF(Romaneios!A:A,Planilha1!A3)</f>
+        <v>62</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4" s="1">
+        <v>46304</v>
+      </c>
+      <c r="B4">
+        <f>COUNTIF(Romaneios!A:A,Planilha1!A4)</f>
+        <v>114</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A5" s="1">
+        <v>46305</v>
+      </c>
+      <c r="B5">
+        <f>COUNTIF(Romaneios!A:A,Planilha1!A5)</f>
+        <v>13</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A6" s="1">
+        <v>46306</v>
+      </c>
+      <c r="B6">
+        <f>COUNTIF(Romaneios!A:A,Planilha1!A6)</f>
+        <v>50</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A7" s="1">
+        <v>46307</v>
+      </c>
+      <c r="B7">
+        <f>COUNTIF(Romaneios!A:A,Planilha1!A7)</f>
+        <v>8</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A8" s="1">
+        <v>46308</v>
+      </c>
+      <c r="B8">
+        <f>COUNTIF(Romaneios!A:A,Planilha1!A8)</f>
+        <v>148</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A9" s="1">
+        <v>46309</v>
+      </c>
+      <c r="B9">
+        <f>COUNTIF(Romaneios!A:A,Planilha1!A9)</f>
+        <v>139</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A10" s="1">
+        <v>46310</v>
+      </c>
+      <c r="B10">
+        <f>COUNTIF(Romaneios!A:A,Planilha1!A10)</f>
+        <v>92</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A11" s="1">
+        <v>46311</v>
+      </c>
+      <c r="B11">
+        <f>COUNTIF(Romaneios!A:A,Planilha1!A11)</f>
+        <v>57</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
+</worksheet>
 </file>
--- a/DadosRomaneios.xlsx
+++ b/DadosRomaneios.xlsx
@@ -5,17 +5,21 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\pedro.andrade\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="U:\AcompanhamentoProducao\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8823DF78-14C9-4781-A0F0-B1C56FE2B6D2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C14689DD-72CB-4E34-B996-5F058AE252BF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" activeTab="1" xr2:uid="{B6976704-8E51-4052-B60A-5847F95A5AE5}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{B6976704-8E51-4052-B60A-5847F95A5AE5}"/>
   </bookViews>
   <sheets>
     <sheet name="Romaneios" sheetId="2" r:id="rId1"/>
     <sheet name="DadosRomaneios" sheetId="3" r:id="rId2"/>
+    <sheet name="Planilha1" sheetId="4" r:id="rId3"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">Planilha1!$A$1:$D$128</definedName>
+  </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -40,7 +44,7 @@
 </file>
 
 <file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
-<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xlrd="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
+<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
   <metadataTypes count="1">
     <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
   </metadataTypes>
@@ -62,7 +66,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="796" uniqueCount="190">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1054" uniqueCount="208">
   <si>
     <t>ALBERT EINSTEIN</t>
   </si>
@@ -632,6 +636,60 @@
   </si>
   <si>
     <t>CHS REG SOROCABA</t>
+  </si>
+  <si>
+    <t>DASA 61.486.650/0188</t>
+  </si>
+  <si>
+    <t>HOSP SAO CRISTOVAO</t>
+  </si>
+  <si>
+    <t>090181 DANTE PAZZANE</t>
+  </si>
+  <si>
+    <t>SEPACO</t>
+  </si>
+  <si>
+    <t>HOSP HELIOPOLIS</t>
+  </si>
+  <si>
+    <t>CLINICA SAO MARCOS</t>
+  </si>
+  <si>
+    <t>DASA BRONSTEIN</t>
+  </si>
+  <si>
+    <t>DASA TIJUCA</t>
+  </si>
+  <si>
+    <t>DASA 61.486.650/0112</t>
+  </si>
+  <si>
+    <t>DASA SERGIO FRANCO</t>
+  </si>
+  <si>
+    <t>DASA HOSP SAO LUCAS</t>
+  </si>
+  <si>
+    <t>CASA DE SAUDE S JOSE</t>
+  </si>
+  <si>
+    <t>MARBERG</t>
+  </si>
+  <si>
+    <t>DASA LAMINA</t>
+  </si>
+  <si>
+    <t>AME ITU</t>
+  </si>
+  <si>
+    <t>STA CASA DE OURINHOS</t>
+  </si>
+  <si>
+    <t>BIONOVIS</t>
+  </si>
+  <si>
+    <t>TJ RAJ 07</t>
   </si>
 </sst>
 </file>
@@ -673,11 +731,10 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1012,7 +1069,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BF29A37F-A1D1-4315-91AB-A952895E1E73}">
-  <dimension ref="A1:E791"/>
+  <dimension ref="A1:E918"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="12.85546875" bestFit="1" customWidth="1"/>
@@ -13144,7 +13201,7 @@
       </c>
     </row>
     <row r="723" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A723" s="3">
+      <c r="A723" s="1">
         <v>46314</v>
       </c>
       <c r="B723">
@@ -13161,7 +13218,7 @@
       </c>
     </row>
     <row r="724" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A724" s="3">
+      <c r="A724" s="1">
         <v>46314</v>
       </c>
       <c r="B724">
@@ -13178,7 +13235,7 @@
       </c>
     </row>
     <row r="725" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A725" s="3">
+      <c r="A725" s="1">
         <v>46314</v>
       </c>
       <c r="B725">
@@ -13192,7 +13249,7 @@
       </c>
     </row>
     <row r="726" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A726" s="3">
+      <c r="A726" s="1">
         <v>46314</v>
       </c>
       <c r="B726">
@@ -13206,7 +13263,7 @@
       </c>
     </row>
     <row r="727" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A727" s="3">
+      <c r="A727" s="1">
         <v>46314</v>
       </c>
       <c r="B727">
@@ -13223,7 +13280,7 @@
       </c>
     </row>
     <row r="728" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A728" s="3">
+      <c r="A728" s="1">
         <v>46314</v>
       </c>
       <c r="B728">
@@ -13240,7 +13297,7 @@
       </c>
     </row>
     <row r="729" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A729" s="3">
+      <c r="A729" s="1">
         <v>46314</v>
       </c>
       <c r="B729">
@@ -13254,7 +13311,7 @@
       </c>
     </row>
     <row r="730" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A730" s="3">
+      <c r="A730" s="1">
         <v>46314</v>
       </c>
       <c r="B730">
@@ -13271,7 +13328,7 @@
       </c>
     </row>
     <row r="731" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A731" s="3">
+      <c r="A731" s="1">
         <v>46314</v>
       </c>
       <c r="B731">
@@ -13288,7 +13345,7 @@
       </c>
     </row>
     <row r="732" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A732" s="3">
+      <c r="A732" s="1">
         <v>46314</v>
       </c>
       <c r="B732">
@@ -13305,7 +13362,7 @@
       </c>
     </row>
     <row r="733" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A733" s="3">
+      <c r="A733" s="1">
         <v>46314</v>
       </c>
       <c r="B733">
@@ -13319,7 +13376,7 @@
       </c>
     </row>
     <row r="734" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A734" s="3">
+      <c r="A734" s="1">
         <v>46314</v>
       </c>
       <c r="B734">
@@ -13336,7 +13393,7 @@
       </c>
     </row>
     <row r="735" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A735" s="3">
+      <c r="A735" s="1">
         <v>46314</v>
       </c>
       <c r="B735">
@@ -13353,7 +13410,7 @@
       </c>
     </row>
     <row r="736" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A736" s="3">
+      <c r="A736" s="1">
         <v>46314</v>
       </c>
       <c r="B736">
@@ -13370,7 +13427,7 @@
       </c>
     </row>
     <row r="737" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A737" s="3">
+      <c r="A737" s="1">
         <v>46314</v>
       </c>
       <c r="B737">
@@ -13387,7 +13444,7 @@
       </c>
     </row>
     <row r="738" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A738" s="3">
+      <c r="A738" s="1">
         <v>46314</v>
       </c>
       <c r="B738">
@@ -13404,7 +13461,7 @@
       </c>
     </row>
     <row r="739" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A739" s="3">
+      <c r="A739" s="1">
         <v>46314</v>
       </c>
       <c r="B739">
@@ -13421,7 +13478,7 @@
       </c>
     </row>
     <row r="740" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A740" s="3">
+      <c r="A740" s="1">
         <v>46314</v>
       </c>
       <c r="B740">
@@ -13438,7 +13495,7 @@
       </c>
     </row>
     <row r="741" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A741" s="3">
+      <c r="A741" s="1">
         <v>46314</v>
       </c>
       <c r="B741">
@@ -13455,7 +13512,7 @@
       </c>
     </row>
     <row r="742" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A742" s="3">
+      <c r="A742" s="1">
         <v>46314</v>
       </c>
       <c r="B742">
@@ -13472,7 +13529,7 @@
       </c>
     </row>
     <row r="743" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A743" s="3">
+      <c r="A743" s="1">
         <v>46314</v>
       </c>
       <c r="B743">
@@ -13489,7 +13546,7 @@
       </c>
     </row>
     <row r="744" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A744" s="3">
+      <c r="A744" s="1">
         <v>46314</v>
       </c>
       <c r="B744">
@@ -13503,7 +13560,7 @@
       </c>
     </row>
     <row r="745" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A745" s="3">
+      <c r="A745" s="1">
         <v>46314</v>
       </c>
       <c r="B745">
@@ -13517,7 +13574,7 @@
       </c>
     </row>
     <row r="746" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A746" s="3">
+      <c r="A746" s="1">
         <v>46314</v>
       </c>
       <c r="B746">
@@ -13534,7 +13591,7 @@
       </c>
     </row>
     <row r="747" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A747" s="3">
+      <c r="A747" s="1">
         <v>46314</v>
       </c>
       <c r="B747">
@@ -13551,7 +13608,7 @@
       </c>
     </row>
     <row r="748" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A748" s="3">
+      <c r="A748" s="1">
         <v>46314</v>
       </c>
       <c r="B748">
@@ -13568,7 +13625,7 @@
       </c>
     </row>
     <row r="749" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A749" s="3">
+      <c r="A749" s="1">
         <v>46314</v>
       </c>
       <c r="B749">
@@ -13585,7 +13642,7 @@
       </c>
     </row>
     <row r="750" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A750" s="3">
+      <c r="A750" s="1">
         <v>46314</v>
       </c>
       <c r="B750">
@@ -13602,7 +13659,7 @@
       </c>
     </row>
     <row r="751" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A751" s="3">
+      <c r="A751" s="1">
         <v>46314</v>
       </c>
       <c r="B751">
@@ -13619,7 +13676,7 @@
       </c>
     </row>
     <row r="752" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A752" s="3">
+      <c r="A752" s="1">
         <v>46314</v>
       </c>
       <c r="B752">
@@ -13636,7 +13693,7 @@
       </c>
     </row>
     <row r="753" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A753" s="3">
+      <c r="A753" s="1">
         <v>46314</v>
       </c>
       <c r="B753">
@@ -13653,7 +13710,7 @@
       </c>
     </row>
     <row r="754" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A754" s="3">
+      <c r="A754" s="1">
         <v>46314</v>
       </c>
       <c r="B754">
@@ -13670,7 +13727,7 @@
       </c>
     </row>
     <row r="755" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A755" s="3">
+      <c r="A755" s="1">
         <v>46314</v>
       </c>
       <c r="B755">
@@ -13687,7 +13744,7 @@
       </c>
     </row>
     <row r="756" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A756" s="3">
+      <c r="A756" s="1">
         <v>46314</v>
       </c>
       <c r="B756">
@@ -13704,7 +13761,7 @@
       </c>
     </row>
     <row r="757" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A757" s="3">
+      <c r="A757" s="1">
         <v>46314</v>
       </c>
       <c r="B757">
@@ -13721,7 +13778,7 @@
       </c>
     </row>
     <row r="758" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A758" s="3">
+      <c r="A758" s="1">
         <v>46314</v>
       </c>
       <c r="B758">
@@ -13738,7 +13795,7 @@
       </c>
     </row>
     <row r="759" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A759" s="3">
+      <c r="A759" s="1">
         <v>46314</v>
       </c>
       <c r="B759">
@@ -13755,7 +13812,7 @@
       </c>
     </row>
     <row r="760" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A760" s="3">
+      <c r="A760" s="1">
         <v>46314</v>
       </c>
       <c r="B760">
@@ -13772,7 +13829,7 @@
       </c>
     </row>
     <row r="761" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A761" s="3">
+      <c r="A761" s="1">
         <v>46314</v>
       </c>
       <c r="B761">
@@ -13789,7 +13846,7 @@
       </c>
     </row>
     <row r="762" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A762" s="3">
+      <c r="A762" s="1">
         <v>46314</v>
       </c>
       <c r="B762">
@@ -13803,7 +13860,7 @@
       </c>
     </row>
     <row r="763" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A763" s="3">
+      <c r="A763" s="1">
         <v>46314</v>
       </c>
       <c r="B763">
@@ -13820,7 +13877,7 @@
       </c>
     </row>
     <row r="764" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A764" s="3">
+      <c r="A764" s="1">
         <v>46314</v>
       </c>
       <c r="B764">
@@ -13837,7 +13894,7 @@
       </c>
     </row>
     <row r="765" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A765" s="3">
+      <c r="A765" s="1">
         <v>46314</v>
       </c>
       <c r="B765">
@@ -13854,7 +13911,7 @@
       </c>
     </row>
     <row r="766" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A766" s="3">
+      <c r="A766" s="1">
         <v>46314</v>
       </c>
       <c r="B766">
@@ -13871,7 +13928,7 @@
       </c>
     </row>
     <row r="767" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A767" s="3">
+      <c r="A767" s="1">
         <v>46314</v>
       </c>
       <c r="B767">
@@ -13888,7 +13945,7 @@
       </c>
     </row>
     <row r="768" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A768" s="3">
+      <c r="A768" s="1">
         <v>46314</v>
       </c>
       <c r="B768">
@@ -13905,7 +13962,7 @@
       </c>
     </row>
     <row r="769" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A769" s="3">
+      <c r="A769" s="1">
         <v>46314</v>
       </c>
       <c r="B769">
@@ -13922,7 +13979,7 @@
       </c>
     </row>
     <row r="770" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A770" s="3">
+      <c r="A770" s="1">
         <v>46314</v>
       </c>
       <c r="B770">
@@ -13939,7 +13996,7 @@
       </c>
     </row>
     <row r="771" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A771" s="3">
+      <c r="A771" s="1">
         <v>46314</v>
       </c>
       <c r="B771">
@@ -13956,7 +14013,7 @@
       </c>
     </row>
     <row r="772" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A772" s="3">
+      <c r="A772" s="1">
         <v>46314</v>
       </c>
       <c r="B772">
@@ -13973,7 +14030,7 @@
       </c>
     </row>
     <row r="773" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A773" s="3">
+      <c r="A773" s="1">
         <v>46314</v>
       </c>
       <c r="B773">
@@ -13987,7 +14044,7 @@
       </c>
     </row>
     <row r="774" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A774" s="3">
+      <c r="A774" s="1">
         <v>46314</v>
       </c>
       <c r="B774">
@@ -14004,7 +14061,7 @@
       </c>
     </row>
     <row r="775" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A775" s="3">
+      <c r="A775" s="1">
         <v>46314</v>
       </c>
       <c r="B775">
@@ -14021,7 +14078,7 @@
       </c>
     </row>
     <row r="776" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A776" s="3">
+      <c r="A776" s="1">
         <v>46314</v>
       </c>
       <c r="B776">
@@ -14038,7 +14095,7 @@
       </c>
     </row>
     <row r="777" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A777" s="3">
+      <c r="A777" s="1">
         <v>46314</v>
       </c>
       <c r="B777">
@@ -14055,7 +14112,7 @@
       </c>
     </row>
     <row r="778" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A778" s="3">
+      <c r="A778" s="1">
         <v>46314</v>
       </c>
       <c r="B778">
@@ -14069,7 +14126,7 @@
       </c>
     </row>
     <row r="779" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A779" s="3">
+      <c r="A779" s="1">
         <v>46314</v>
       </c>
       <c r="B779">
@@ -14086,7 +14143,7 @@
       </c>
     </row>
     <row r="780" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A780" s="3">
+      <c r="A780" s="1">
         <v>46314</v>
       </c>
       <c r="B780">
@@ -14103,7 +14160,7 @@
       </c>
     </row>
     <row r="781" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A781" s="3">
+      <c r="A781" s="1">
         <v>46314</v>
       </c>
       <c r="B781">
@@ -14117,7 +14174,7 @@
       </c>
     </row>
     <row r="782" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A782" s="3">
+      <c r="A782" s="1">
         <v>46314</v>
       </c>
       <c r="B782">
@@ -14134,7 +14191,7 @@
       </c>
     </row>
     <row r="783" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A783" s="3">
+      <c r="A783" s="1">
         <v>46314</v>
       </c>
       <c r="B783">
@@ -14151,7 +14208,7 @@
       </c>
     </row>
     <row r="784" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A784" s="3">
+      <c r="A784" s="1">
         <v>46314</v>
       </c>
       <c r="B784">
@@ -14168,7 +14225,7 @@
       </c>
     </row>
     <row r="785" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A785" s="3">
+      <c r="A785" s="1">
         <v>46314</v>
       </c>
       <c r="B785">
@@ -14185,7 +14242,7 @@
       </c>
     </row>
     <row r="786" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A786" s="3">
+      <c r="A786" s="1">
         <v>46314</v>
       </c>
       <c r="B786">
@@ -14202,7 +14259,7 @@
       </c>
     </row>
     <row r="787" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A787" s="3">
+      <c r="A787" s="1">
         <v>46314</v>
       </c>
       <c r="B787">
@@ -14216,7 +14273,7 @@
       </c>
     </row>
     <row r="788" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A788" s="3">
+      <c r="A788" s="1">
         <v>46314</v>
       </c>
       <c r="B788">
@@ -14230,7 +14287,7 @@
       </c>
     </row>
     <row r="789" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A789" s="3">
+      <c r="A789" s="1">
         <v>46314</v>
       </c>
       <c r="B789">
@@ -14247,7 +14304,7 @@
       </c>
     </row>
     <row r="790" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A790" s="3">
+      <c r="A790" s="1">
         <v>46314</v>
       </c>
       <c r="B790">
@@ -14264,7 +14321,7 @@
       </c>
     </row>
     <row r="791" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A791" s="3">
+      <c r="A791" s="1">
         <v>46314</v>
       </c>
       <c r="B791">
@@ -14278,6 +14335,2120 @@
       </c>
       <c r="E791">
         <v>179607</v>
+      </c>
+    </row>
+    <row r="792" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A792" s="1">
+        <v>46315</v>
+      </c>
+      <c r="B792">
+        <v>101</v>
+      </c>
+      <c r="C792" t="s">
+        <v>15</v>
+      </c>
+      <c r="D792">
+        <v>70278</v>
+      </c>
+      <c r="E792">
+        <v>179693</v>
+      </c>
+    </row>
+    <row r="793" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A793" s="1">
+        <v>46315</v>
+      </c>
+      <c r="B793">
+        <v>101</v>
+      </c>
+      <c r="C793" t="s">
+        <v>0</v>
+      </c>
+      <c r="E793">
+        <v>179705</v>
+      </c>
+    </row>
+    <row r="794" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A794" s="1">
+        <v>46315</v>
+      </c>
+      <c r="B794">
+        <v>101</v>
+      </c>
+      <c r="C794" t="s">
+        <v>115</v>
+      </c>
+      <c r="D794">
+        <v>70279</v>
+      </c>
+      <c r="E794">
+        <v>179692</v>
+      </c>
+    </row>
+    <row r="795" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A795" s="1">
+        <v>46315</v>
+      </c>
+      <c r="B795">
+        <v>101</v>
+      </c>
+      <c r="C795" t="s">
+        <v>0</v>
+      </c>
+      <c r="D795">
+        <v>70298</v>
+      </c>
+      <c r="E795">
+        <v>179680</v>
+      </c>
+    </row>
+    <row r="796" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A796" s="1">
+        <v>46315</v>
+      </c>
+      <c r="B796">
+        <v>101</v>
+      </c>
+      <c r="C796" t="s">
+        <v>94</v>
+      </c>
+      <c r="E796">
+        <v>179646</v>
+      </c>
+    </row>
+    <row r="797" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A797" s="1">
+        <v>46315</v>
+      </c>
+      <c r="B797">
+        <v>101</v>
+      </c>
+      <c r="C797" t="s">
+        <v>190</v>
+      </c>
+      <c r="D797">
+        <v>70059</v>
+      </c>
+      <c r="E797">
+        <v>179565</v>
+      </c>
+    </row>
+    <row r="798" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A798" s="1">
+        <v>46315</v>
+      </c>
+      <c r="B798">
+        <v>101</v>
+      </c>
+      <c r="C798" t="s">
+        <v>40</v>
+      </c>
+      <c r="D798">
+        <v>69908</v>
+      </c>
+      <c r="E798">
+        <v>179712</v>
+      </c>
+    </row>
+    <row r="799" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A799" s="1">
+        <v>46315</v>
+      </c>
+      <c r="B799">
+        <v>101</v>
+      </c>
+      <c r="C799" t="s">
+        <v>191</v>
+      </c>
+      <c r="D799">
+        <v>68978</v>
+      </c>
+      <c r="E799">
+        <v>179645</v>
+      </c>
+    </row>
+    <row r="800" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A800" s="1">
+        <v>46315</v>
+      </c>
+      <c r="B800">
+        <v>101</v>
+      </c>
+      <c r="C800" t="s">
+        <v>48</v>
+      </c>
+      <c r="D800">
+        <v>70201</v>
+      </c>
+      <c r="E800">
+        <v>179653</v>
+      </c>
+    </row>
+    <row r="801" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A801" s="1">
+        <v>46315</v>
+      </c>
+      <c r="B801">
+        <v>101</v>
+      </c>
+      <c r="C801" t="s">
+        <v>40</v>
+      </c>
+      <c r="D801">
+        <v>70088</v>
+      </c>
+      <c r="E801">
+        <v>179713</v>
+      </c>
+    </row>
+    <row r="802" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A802" s="1">
+        <v>46315</v>
+      </c>
+      <c r="B802">
+        <v>101</v>
+      </c>
+      <c r="C802" t="s">
+        <v>123</v>
+      </c>
+      <c r="D802">
+        <v>69737</v>
+      </c>
+      <c r="E802">
+        <v>179728</v>
+      </c>
+    </row>
+    <row r="803" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A803" s="1">
+        <v>46315</v>
+      </c>
+      <c r="B803">
+        <v>101</v>
+      </c>
+      <c r="C803" t="s">
+        <v>69</v>
+      </c>
+      <c r="D803">
+        <v>67824</v>
+      </c>
+      <c r="E803">
+        <v>179694</v>
+      </c>
+    </row>
+    <row r="804" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A804" s="1">
+        <v>46315</v>
+      </c>
+      <c r="B804">
+        <v>101</v>
+      </c>
+      <c r="C804" t="s">
+        <v>25</v>
+      </c>
+      <c r="D804">
+        <v>70390</v>
+      </c>
+      <c r="E804">
+        <v>179689</v>
+      </c>
+    </row>
+    <row r="805" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A805" s="1">
+        <v>46315</v>
+      </c>
+      <c r="B805">
+        <v>101</v>
+      </c>
+      <c r="C805" t="s">
+        <v>0</v>
+      </c>
+      <c r="E805">
+        <v>179647</v>
+      </c>
+    </row>
+    <row r="806" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A806" s="1">
+        <v>46315</v>
+      </c>
+      <c r="B806">
+        <v>101</v>
+      </c>
+      <c r="C806" t="s">
+        <v>69</v>
+      </c>
+      <c r="D806">
+        <v>68147</v>
+      </c>
+      <c r="E806">
+        <v>179695</v>
+      </c>
+    </row>
+    <row r="807" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A807" s="1">
+        <v>46315</v>
+      </c>
+      <c r="B807">
+        <v>101</v>
+      </c>
+      <c r="C807" t="s">
+        <v>25</v>
+      </c>
+      <c r="D807">
+        <v>69469</v>
+      </c>
+      <c r="E807">
+        <v>179723</v>
+      </c>
+    </row>
+    <row r="808" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A808" s="1">
+        <v>46315</v>
+      </c>
+      <c r="B808">
+        <v>101</v>
+      </c>
+      <c r="C808" t="s">
+        <v>29</v>
+      </c>
+      <c r="D808">
+        <v>66980</v>
+      </c>
+      <c r="E808">
+        <v>176367</v>
+      </c>
+    </row>
+    <row r="809" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A809" s="1">
+        <v>46315</v>
+      </c>
+      <c r="B809">
+        <v>101</v>
+      </c>
+      <c r="C809" t="s">
+        <v>187</v>
+      </c>
+      <c r="D809">
+        <v>70197</v>
+      </c>
+      <c r="E809">
+        <v>179658</v>
+      </c>
+    </row>
+    <row r="810" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A810" s="1">
+        <v>46315</v>
+      </c>
+      <c r="B810">
+        <v>101</v>
+      </c>
+      <c r="C810" t="s">
+        <v>29</v>
+      </c>
+      <c r="D810">
+        <v>69806</v>
+      </c>
+      <c r="E810">
+        <v>179657</v>
+      </c>
+    </row>
+    <row r="811" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A811" s="1">
+        <v>46315</v>
+      </c>
+      <c r="B811">
+        <v>101</v>
+      </c>
+      <c r="C811" t="s">
+        <v>86</v>
+      </c>
+      <c r="E811">
+        <v>179263</v>
+      </c>
+    </row>
+    <row r="812" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A812" s="1">
+        <v>46315</v>
+      </c>
+      <c r="B812">
+        <v>101</v>
+      </c>
+      <c r="C812" t="s">
+        <v>29</v>
+      </c>
+      <c r="D812">
+        <v>69802</v>
+      </c>
+      <c r="E812">
+        <v>179674</v>
+      </c>
+    </row>
+    <row r="813" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A813" s="1">
+        <v>46315</v>
+      </c>
+      <c r="B813">
+        <v>101</v>
+      </c>
+      <c r="C813" t="s">
+        <v>74</v>
+      </c>
+      <c r="D813">
+        <v>69767</v>
+      </c>
+      <c r="E813">
+        <v>179688</v>
+      </c>
+    </row>
+    <row r="814" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A814" s="1">
+        <v>46315</v>
+      </c>
+      <c r="B814">
+        <v>101</v>
+      </c>
+      <c r="C814" t="s">
+        <v>29</v>
+      </c>
+      <c r="D814">
+        <v>69814</v>
+      </c>
+      <c r="E814">
+        <v>179659</v>
+      </c>
+    </row>
+    <row r="815" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A815" s="1">
+        <v>46315</v>
+      </c>
+      <c r="B815">
+        <v>101</v>
+      </c>
+      <c r="C815" t="s">
+        <v>29</v>
+      </c>
+      <c r="E815">
+        <v>179707</v>
+      </c>
+    </row>
+    <row r="816" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A816" s="1">
+        <v>46315</v>
+      </c>
+      <c r="B816">
+        <v>101</v>
+      </c>
+      <c r="C816" t="s">
+        <v>29</v>
+      </c>
+      <c r="D816">
+        <v>69803</v>
+      </c>
+      <c r="E816">
+        <v>179671</v>
+      </c>
+    </row>
+    <row r="817" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A817" s="1">
+        <v>46315</v>
+      </c>
+      <c r="B817">
+        <v>101</v>
+      </c>
+      <c r="C817" t="s">
+        <v>86</v>
+      </c>
+      <c r="E817">
+        <v>179703</v>
+      </c>
+    </row>
+    <row r="818" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A818" s="1">
+        <v>46315</v>
+      </c>
+      <c r="B818">
+        <v>101</v>
+      </c>
+      <c r="C818" t="s">
+        <v>117</v>
+      </c>
+      <c r="E818">
+        <v>179679</v>
+      </c>
+    </row>
+    <row r="819" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A819" s="1">
+        <v>46315</v>
+      </c>
+      <c r="B819">
+        <v>101</v>
+      </c>
+      <c r="C819" t="s">
+        <v>29</v>
+      </c>
+      <c r="D819">
+        <v>70192</v>
+      </c>
+      <c r="E819">
+        <v>179716</v>
+      </c>
+    </row>
+    <row r="820" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A820" s="1">
+        <v>46315</v>
+      </c>
+      <c r="B820">
+        <v>101</v>
+      </c>
+      <c r="C820" t="s">
+        <v>117</v>
+      </c>
+      <c r="D820">
+        <v>70157</v>
+      </c>
+      <c r="E820">
+        <v>179690</v>
+      </c>
+    </row>
+    <row r="821" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A821" s="1">
+        <v>46315</v>
+      </c>
+      <c r="B821">
+        <v>101</v>
+      </c>
+      <c r="C821" t="s">
+        <v>86</v>
+      </c>
+      <c r="D821">
+        <v>69757</v>
+      </c>
+      <c r="E821">
+        <v>179638</v>
+      </c>
+    </row>
+    <row r="822" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A822" s="1">
+        <v>46315</v>
+      </c>
+      <c r="B822">
+        <v>101</v>
+      </c>
+      <c r="C822" t="s">
+        <v>117</v>
+      </c>
+      <c r="D822">
+        <v>69764</v>
+      </c>
+      <c r="E822">
+        <v>179650</v>
+      </c>
+    </row>
+    <row r="823" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A823" s="1">
+        <v>46315</v>
+      </c>
+      <c r="B823">
+        <v>101</v>
+      </c>
+      <c r="C823" t="s">
+        <v>29</v>
+      </c>
+      <c r="D823">
+        <v>70288</v>
+      </c>
+      <c r="E823">
+        <v>179655</v>
+      </c>
+    </row>
+    <row r="824" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A824" s="1">
+        <v>46315</v>
+      </c>
+      <c r="B824">
+        <v>101</v>
+      </c>
+      <c r="C824" t="s">
+        <v>187</v>
+      </c>
+      <c r="D824">
+        <v>68888</v>
+      </c>
+      <c r="E824">
+        <v>179636</v>
+      </c>
+    </row>
+    <row r="825" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A825" s="1">
+        <v>46315</v>
+      </c>
+      <c r="B825">
+        <v>101</v>
+      </c>
+      <c r="C825" t="s">
+        <v>86</v>
+      </c>
+      <c r="D825">
+        <v>70160</v>
+      </c>
+      <c r="E825">
+        <v>179673</v>
+      </c>
+    </row>
+    <row r="826" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A826" s="1">
+        <v>46315</v>
+      </c>
+      <c r="B826">
+        <v>101</v>
+      </c>
+      <c r="C826" t="s">
+        <v>187</v>
+      </c>
+      <c r="D826">
+        <v>69391</v>
+      </c>
+      <c r="E826">
+        <v>179639</v>
+      </c>
+    </row>
+    <row r="827" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A827" s="1">
+        <v>46315</v>
+      </c>
+      <c r="B827">
+        <v>101</v>
+      </c>
+      <c r="C827" t="s">
+        <v>74</v>
+      </c>
+      <c r="D827">
+        <v>69768</v>
+      </c>
+      <c r="E827">
+        <v>179660</v>
+      </c>
+    </row>
+    <row r="828" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A828" s="1">
+        <v>46315</v>
+      </c>
+      <c r="B828">
+        <v>101</v>
+      </c>
+      <c r="C828" t="s">
+        <v>86</v>
+      </c>
+      <c r="E828">
+        <v>179702</v>
+      </c>
+    </row>
+    <row r="829" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A829" s="1">
+        <v>46315</v>
+      </c>
+      <c r="B829">
+        <v>101</v>
+      </c>
+      <c r="C829" t="s">
+        <v>118</v>
+      </c>
+      <c r="E829">
+        <v>179706</v>
+      </c>
+    </row>
+    <row r="830" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A830" s="1">
+        <v>46315</v>
+      </c>
+      <c r="B830">
+        <v>101</v>
+      </c>
+      <c r="C830" t="s">
+        <v>74</v>
+      </c>
+      <c r="D830">
+        <v>69769</v>
+      </c>
+      <c r="E830">
+        <v>179640</v>
+      </c>
+    </row>
+    <row r="831" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A831" s="1">
+        <v>46315</v>
+      </c>
+      <c r="B831">
+        <v>101</v>
+      </c>
+      <c r="C831" t="s">
+        <v>86</v>
+      </c>
+      <c r="D831">
+        <v>69369</v>
+      </c>
+      <c r="E831">
+        <v>179641</v>
+      </c>
+    </row>
+    <row r="832" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A832" s="1">
+        <v>46315</v>
+      </c>
+      <c r="B832">
+        <v>101</v>
+      </c>
+      <c r="C832" t="s">
+        <v>86</v>
+      </c>
+      <c r="D832">
+        <v>70154</v>
+      </c>
+      <c r="E832">
+        <v>179637</v>
+      </c>
+    </row>
+    <row r="833" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A833" s="1">
+        <v>46315</v>
+      </c>
+      <c r="B833">
+        <v>101</v>
+      </c>
+      <c r="C833" t="s">
+        <v>86</v>
+      </c>
+      <c r="D833">
+        <v>69756</v>
+      </c>
+      <c r="E833">
+        <v>179701</v>
+      </c>
+    </row>
+    <row r="834" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A834" s="1">
+        <v>46315</v>
+      </c>
+      <c r="B834">
+        <v>101</v>
+      </c>
+      <c r="C834" t="s">
+        <v>118</v>
+      </c>
+      <c r="D834">
+        <v>69762</v>
+      </c>
+      <c r="E834">
+        <v>179661</v>
+      </c>
+    </row>
+    <row r="835" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A835" s="1">
+        <v>46315</v>
+      </c>
+      <c r="B835">
+        <v>101</v>
+      </c>
+      <c r="C835" t="s">
+        <v>86</v>
+      </c>
+      <c r="D835">
+        <v>69754</v>
+      </c>
+      <c r="E835">
+        <v>179722</v>
+      </c>
+    </row>
+    <row r="836" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A836" s="1">
+        <v>46315</v>
+      </c>
+      <c r="B836">
+        <v>101</v>
+      </c>
+      <c r="C836" t="s">
+        <v>86</v>
+      </c>
+      <c r="D836">
+        <v>70153</v>
+      </c>
+      <c r="E836">
+        <v>179656</v>
+      </c>
+    </row>
+    <row r="837" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A837" s="1">
+        <v>46315</v>
+      </c>
+      <c r="B837">
+        <v>101</v>
+      </c>
+      <c r="C837" t="s">
+        <v>158</v>
+      </c>
+      <c r="D837">
+        <v>539</v>
+      </c>
+      <c r="E837">
+        <v>534</v>
+      </c>
+    </row>
+    <row r="838" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A838" s="1">
+        <v>46315</v>
+      </c>
+      <c r="B838">
+        <v>101</v>
+      </c>
+      <c r="C838" t="s">
+        <v>40</v>
+      </c>
+      <c r="D838">
+        <v>549</v>
+      </c>
+      <c r="E838">
+        <v>540</v>
+      </c>
+    </row>
+    <row r="839" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A839" s="1">
+        <v>46315</v>
+      </c>
+      <c r="B839">
+        <v>101</v>
+      </c>
+      <c r="C839" t="s">
+        <v>24</v>
+      </c>
+      <c r="D839">
+        <v>546</v>
+      </c>
+      <c r="E839">
+        <v>539</v>
+      </c>
+    </row>
+    <row r="840" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A840" s="1">
+        <v>46315</v>
+      </c>
+      <c r="B840">
+        <v>101</v>
+      </c>
+      <c r="C840" t="s">
+        <v>24</v>
+      </c>
+      <c r="D840">
+        <v>547</v>
+      </c>
+      <c r="E840">
+        <v>538</v>
+      </c>
+    </row>
+    <row r="841" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A841" s="1">
+        <v>46315</v>
+      </c>
+      <c r="B841">
+        <v>101</v>
+      </c>
+      <c r="C841" t="s">
+        <v>40</v>
+      </c>
+      <c r="D841">
+        <v>548</v>
+      </c>
+      <c r="E841">
+        <v>541</v>
+      </c>
+    </row>
+    <row r="842" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A842" s="1">
+        <v>46315</v>
+      </c>
+      <c r="B842">
+        <v>101</v>
+      </c>
+      <c r="C842" t="s">
+        <v>192</v>
+      </c>
+      <c r="D842">
+        <v>70163</v>
+      </c>
+      <c r="E842">
+        <v>179642</v>
+      </c>
+    </row>
+    <row r="843" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A843" s="1">
+        <v>46315</v>
+      </c>
+      <c r="B843">
+        <v>101</v>
+      </c>
+      <c r="C843" t="s">
+        <v>193</v>
+      </c>
+      <c r="D843">
+        <v>69943</v>
+      </c>
+      <c r="E843">
+        <v>179662</v>
+      </c>
+    </row>
+    <row r="844" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A844" s="1">
+        <v>46315</v>
+      </c>
+      <c r="B844">
+        <v>101</v>
+      </c>
+      <c r="C844" t="s">
+        <v>166</v>
+      </c>
+      <c r="D844">
+        <v>69738</v>
+      </c>
+      <c r="E844">
+        <v>179751</v>
+      </c>
+    </row>
+    <row r="845" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A845" s="1">
+        <v>46315</v>
+      </c>
+      <c r="B845">
+        <v>101</v>
+      </c>
+      <c r="C845" t="s">
+        <v>194</v>
+      </c>
+      <c r="D845">
+        <v>70464</v>
+      </c>
+      <c r="E845">
+        <v>179779</v>
+      </c>
+    </row>
+    <row r="846" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A846" s="1">
+        <v>46315</v>
+      </c>
+      <c r="B846">
+        <v>101</v>
+      </c>
+      <c r="C846" t="s">
+        <v>19</v>
+      </c>
+      <c r="D846">
+        <v>69704</v>
+      </c>
+      <c r="E846">
+        <v>179780</v>
+      </c>
+    </row>
+    <row r="847" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A847" s="1">
+        <v>46315</v>
+      </c>
+      <c r="B847">
+        <v>101</v>
+      </c>
+      <c r="C847" t="s">
+        <v>7</v>
+      </c>
+      <c r="D847">
+        <v>70076</v>
+      </c>
+      <c r="E847">
+        <v>179556</v>
+      </c>
+    </row>
+    <row r="848" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A848" s="1">
+        <v>46315</v>
+      </c>
+      <c r="B848">
+        <v>101</v>
+      </c>
+      <c r="C848" t="s">
+        <v>19</v>
+      </c>
+      <c r="D848">
+        <v>70128</v>
+      </c>
+      <c r="E848">
+        <v>179616</v>
+      </c>
+    </row>
+    <row r="849" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A849" s="1">
+        <v>46315</v>
+      </c>
+      <c r="B849">
+        <v>101</v>
+      </c>
+      <c r="C849" t="s">
+        <v>19</v>
+      </c>
+      <c r="D849">
+        <v>70321</v>
+      </c>
+      <c r="E849">
+        <v>179675</v>
+      </c>
+    </row>
+    <row r="850" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A850" s="1">
+        <v>46315</v>
+      </c>
+      <c r="B850">
+        <v>101</v>
+      </c>
+      <c r="C850" t="s">
+        <v>19</v>
+      </c>
+      <c r="D850">
+        <v>69389</v>
+      </c>
+      <c r="E850">
+        <v>179785</v>
+      </c>
+    </row>
+    <row r="851" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A851" s="1">
+        <v>46315</v>
+      </c>
+      <c r="B851">
+        <v>101</v>
+      </c>
+      <c r="C851" t="s">
+        <v>19</v>
+      </c>
+      <c r="D851">
+        <v>68822</v>
+      </c>
+      <c r="E851">
+        <v>179783</v>
+      </c>
+    </row>
+    <row r="852" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A852" s="1">
+        <v>46315</v>
+      </c>
+      <c r="B852">
+        <v>101</v>
+      </c>
+      <c r="C852" t="s">
+        <v>19</v>
+      </c>
+      <c r="D852">
+        <v>69687</v>
+      </c>
+      <c r="E852">
+        <v>179782</v>
+      </c>
+    </row>
+    <row r="853" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A853" s="1">
+        <v>46315</v>
+      </c>
+      <c r="B853">
+        <v>101</v>
+      </c>
+      <c r="C853" t="s">
+        <v>19</v>
+      </c>
+      <c r="D853">
+        <v>70241</v>
+      </c>
+      <c r="E853">
+        <v>179781</v>
+      </c>
+    </row>
+    <row r="854" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A854" s="1">
+        <v>46315</v>
+      </c>
+      <c r="B854">
+        <v>101</v>
+      </c>
+      <c r="C854" t="s">
+        <v>89</v>
+      </c>
+      <c r="D854">
+        <v>70072</v>
+      </c>
+      <c r="E854">
+        <v>179681</v>
+      </c>
+    </row>
+    <row r="855" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A855" s="1">
+        <v>46315</v>
+      </c>
+      <c r="B855">
+        <v>101</v>
+      </c>
+      <c r="C855" t="s">
+        <v>121</v>
+      </c>
+      <c r="D855">
+        <v>70144</v>
+      </c>
+      <c r="E855">
+        <v>179676</v>
+      </c>
+    </row>
+    <row r="856" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A856" s="1">
+        <v>46315</v>
+      </c>
+      <c r="B856">
+        <v>101</v>
+      </c>
+      <c r="C856" t="s">
+        <v>121</v>
+      </c>
+      <c r="D856">
+        <v>70203</v>
+      </c>
+      <c r="E856">
+        <v>179685</v>
+      </c>
+    </row>
+    <row r="857" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A857" s="1">
+        <v>46315</v>
+      </c>
+      <c r="B857">
+        <v>101</v>
+      </c>
+      <c r="C857" t="s">
+        <v>121</v>
+      </c>
+      <c r="D857">
+        <v>70236</v>
+      </c>
+      <c r="E857">
+        <v>179684</v>
+      </c>
+    </row>
+    <row r="858" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A858" s="1">
+        <v>46315</v>
+      </c>
+      <c r="B858">
+        <v>101</v>
+      </c>
+      <c r="C858" t="s">
+        <v>122</v>
+      </c>
+      <c r="D858">
+        <v>70235</v>
+      </c>
+      <c r="E858">
+        <v>179726</v>
+      </c>
+    </row>
+    <row r="859" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A859" s="1">
+        <v>46315</v>
+      </c>
+      <c r="B859">
+        <v>101</v>
+      </c>
+      <c r="C859" t="s">
+        <v>195</v>
+      </c>
+      <c r="D859">
+        <v>70078</v>
+      </c>
+      <c r="E859">
+        <v>179677</v>
+      </c>
+    </row>
+    <row r="860" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A860" s="1">
+        <v>46315</v>
+      </c>
+      <c r="B860">
+        <v>101</v>
+      </c>
+      <c r="C860" t="s">
+        <v>122</v>
+      </c>
+      <c r="D860">
+        <v>69839</v>
+      </c>
+      <c r="E860">
+        <v>179678</v>
+      </c>
+    </row>
+    <row r="861" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A861" s="1">
+        <v>46315</v>
+      </c>
+      <c r="B861">
+        <v>101</v>
+      </c>
+      <c r="C861" t="s">
+        <v>18</v>
+      </c>
+      <c r="E861">
+        <v>18624</v>
+      </c>
+    </row>
+    <row r="862" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A862" s="1">
+        <v>46315</v>
+      </c>
+      <c r="B862">
+        <v>101</v>
+      </c>
+      <c r="C862" t="s">
+        <v>196</v>
+      </c>
+      <c r="D862">
+        <v>16289</v>
+      </c>
+      <c r="E862">
+        <v>18608</v>
+      </c>
+    </row>
+    <row r="863" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A863" s="1">
+        <v>46315</v>
+      </c>
+      <c r="B863">
+        <v>101</v>
+      </c>
+      <c r="C863" t="s">
+        <v>196</v>
+      </c>
+      <c r="D863">
+        <v>16293</v>
+      </c>
+      <c r="E863">
+        <v>18612</v>
+      </c>
+    </row>
+    <row r="864" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A864" s="1">
+        <v>46315</v>
+      </c>
+      <c r="B864">
+        <v>101</v>
+      </c>
+      <c r="C864" t="s">
+        <v>15</v>
+      </c>
+      <c r="D864">
+        <v>16305</v>
+      </c>
+      <c r="E864">
+        <v>18625</v>
+      </c>
+    </row>
+    <row r="865" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A865" s="1">
+        <v>46315</v>
+      </c>
+      <c r="B865">
+        <v>101</v>
+      </c>
+      <c r="C865" t="s">
+        <v>197</v>
+      </c>
+      <c r="D865">
+        <v>16299</v>
+      </c>
+      <c r="E865">
+        <v>18616</v>
+      </c>
+    </row>
+    <row r="866" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A866" s="1">
+        <v>46315</v>
+      </c>
+      <c r="B866">
+        <v>101</v>
+      </c>
+      <c r="C866" t="s">
+        <v>15</v>
+      </c>
+      <c r="D866">
+        <v>16300</v>
+      </c>
+      <c r="E866">
+        <v>18621</v>
+      </c>
+    </row>
+    <row r="867" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A867" s="1">
+        <v>46315</v>
+      </c>
+      <c r="B867">
+        <v>101</v>
+      </c>
+      <c r="C867" t="s">
+        <v>197</v>
+      </c>
+      <c r="E867">
+        <v>18617</v>
+      </c>
+    </row>
+    <row r="868" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A868" s="1">
+        <v>46315</v>
+      </c>
+      <c r="B868">
+        <v>101</v>
+      </c>
+      <c r="C868" t="s">
+        <v>198</v>
+      </c>
+      <c r="D868">
+        <v>16291</v>
+      </c>
+      <c r="E868">
+        <v>18610</v>
+      </c>
+    </row>
+    <row r="869" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A869" s="1">
+        <v>46315</v>
+      </c>
+      <c r="B869">
+        <v>101</v>
+      </c>
+      <c r="C869" t="s">
+        <v>196</v>
+      </c>
+      <c r="D869">
+        <v>16292</v>
+      </c>
+      <c r="E869">
+        <v>18611</v>
+      </c>
+    </row>
+    <row r="870" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A870" s="1">
+        <v>46315</v>
+      </c>
+      <c r="B870">
+        <v>101</v>
+      </c>
+      <c r="C870" t="s">
+        <v>199</v>
+      </c>
+      <c r="D870">
+        <v>16288</v>
+      </c>
+      <c r="E870">
+        <v>18607</v>
+      </c>
+    </row>
+    <row r="871" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A871" s="1">
+        <v>46315</v>
+      </c>
+      <c r="B871">
+        <v>101</v>
+      </c>
+      <c r="C871" t="s">
+        <v>200</v>
+      </c>
+      <c r="D871">
+        <v>16306</v>
+      </c>
+      <c r="E871">
+        <v>18618</v>
+      </c>
+    </row>
+    <row r="872" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A872" s="1">
+        <v>46315</v>
+      </c>
+      <c r="B872">
+        <v>101</v>
+      </c>
+      <c r="C872" t="s">
+        <v>15</v>
+      </c>
+      <c r="D872">
+        <v>16302</v>
+      </c>
+      <c r="E872">
+        <v>18622</v>
+      </c>
+    </row>
+    <row r="873" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A873" s="1">
+        <v>46315</v>
+      </c>
+      <c r="B873">
+        <v>101</v>
+      </c>
+      <c r="C873" t="s">
+        <v>201</v>
+      </c>
+      <c r="D873">
+        <v>16272</v>
+      </c>
+      <c r="E873">
+        <v>18603</v>
+      </c>
+    </row>
+    <row r="874" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A874" s="1">
+        <v>46315</v>
+      </c>
+      <c r="B874">
+        <v>101</v>
+      </c>
+      <c r="C874" t="s">
+        <v>202</v>
+      </c>
+      <c r="D874">
+        <v>16246</v>
+      </c>
+      <c r="E874">
+        <v>18605</v>
+      </c>
+    </row>
+    <row r="875" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A875" s="1">
+        <v>46315</v>
+      </c>
+      <c r="B875">
+        <v>101</v>
+      </c>
+      <c r="C875" t="s">
+        <v>203</v>
+      </c>
+      <c r="D875">
+        <v>16295</v>
+      </c>
+      <c r="E875">
+        <v>18614</v>
+      </c>
+    </row>
+    <row r="876" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A876" s="1">
+        <v>46315</v>
+      </c>
+      <c r="B876">
+        <v>101</v>
+      </c>
+      <c r="C876" t="s">
+        <v>201</v>
+      </c>
+      <c r="D876">
+        <v>16273</v>
+      </c>
+      <c r="E876">
+        <v>18606</v>
+      </c>
+    </row>
+    <row r="877" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A877" s="1">
+        <v>46315</v>
+      </c>
+      <c r="B877">
+        <v>101</v>
+      </c>
+      <c r="C877" t="s">
+        <v>201</v>
+      </c>
+      <c r="D877">
+        <v>16274</v>
+      </c>
+      <c r="E877">
+        <v>18601</v>
+      </c>
+    </row>
+    <row r="878" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A878" s="1">
+        <v>46315</v>
+      </c>
+      <c r="B878">
+        <v>101</v>
+      </c>
+      <c r="C878" t="s">
+        <v>15</v>
+      </c>
+      <c r="D878">
+        <v>16294</v>
+      </c>
+      <c r="E878">
+        <v>18613</v>
+      </c>
+    </row>
+    <row r="879" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A879" s="1">
+        <v>46315</v>
+      </c>
+      <c r="B879">
+        <v>101</v>
+      </c>
+      <c r="C879" t="s">
+        <v>15</v>
+      </c>
+      <c r="D879">
+        <v>16296</v>
+      </c>
+      <c r="E879">
+        <v>18615</v>
+      </c>
+    </row>
+    <row r="880" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A880" s="1">
+        <v>46315</v>
+      </c>
+      <c r="B880">
+        <v>101</v>
+      </c>
+      <c r="C880" t="s">
+        <v>15</v>
+      </c>
+      <c r="D880">
+        <v>16297</v>
+      </c>
+      <c r="E880">
+        <v>18619</v>
+      </c>
+    </row>
+    <row r="881" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A881" s="1">
+        <v>46315</v>
+      </c>
+      <c r="B881">
+        <v>101</v>
+      </c>
+      <c r="C881" t="s">
+        <v>23</v>
+      </c>
+      <c r="D881">
+        <v>68823</v>
+      </c>
+      <c r="E881">
+        <v>179790</v>
+      </c>
+    </row>
+    <row r="882" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A882" s="1">
+        <v>46315</v>
+      </c>
+      <c r="B882">
+        <v>101</v>
+      </c>
+      <c r="C882" t="s">
+        <v>23</v>
+      </c>
+      <c r="E882">
+        <v>179596</v>
+      </c>
+    </row>
+    <row r="883" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A883" s="1">
+        <v>46315</v>
+      </c>
+      <c r="B883">
+        <v>101</v>
+      </c>
+      <c r="C883" t="s">
+        <v>33</v>
+      </c>
+      <c r="D883">
+        <v>70315</v>
+      </c>
+      <c r="E883">
+        <v>179798</v>
+      </c>
+    </row>
+    <row r="884" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A884" s="1">
+        <v>46315</v>
+      </c>
+      <c r="B884">
+        <v>101</v>
+      </c>
+      <c r="C884" t="s">
+        <v>69</v>
+      </c>
+      <c r="D884">
+        <v>70453</v>
+      </c>
+      <c r="E884">
+        <v>179753</v>
+      </c>
+    </row>
+    <row r="885" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A885" s="1">
+        <v>46315</v>
+      </c>
+      <c r="B885">
+        <v>101</v>
+      </c>
+      <c r="C885" t="s">
+        <v>15</v>
+      </c>
+      <c r="D885">
+        <v>69645</v>
+      </c>
+      <c r="E885">
+        <v>179604</v>
+      </c>
+    </row>
+    <row r="886" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A886" s="1">
+        <v>46315</v>
+      </c>
+      <c r="B886">
+        <v>101</v>
+      </c>
+      <c r="C886" t="s">
+        <v>204</v>
+      </c>
+      <c r="D886">
+        <v>69840</v>
+      </c>
+      <c r="E886">
+        <v>179602</v>
+      </c>
+    </row>
+    <row r="887" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A887" s="1">
+        <v>46315</v>
+      </c>
+      <c r="B887">
+        <v>101</v>
+      </c>
+      <c r="C887" t="s">
+        <v>205</v>
+      </c>
+      <c r="E887">
+        <v>179368</v>
+      </c>
+    </row>
+    <row r="888" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A888" s="1">
+        <v>46315</v>
+      </c>
+      <c r="B888">
+        <v>101</v>
+      </c>
+      <c r="C888" t="s">
+        <v>19</v>
+      </c>
+      <c r="E888">
+        <v>179643</v>
+      </c>
+    </row>
+    <row r="889" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A889" s="1">
+        <v>46315</v>
+      </c>
+      <c r="B889">
+        <v>101</v>
+      </c>
+      <c r="C889" t="s">
+        <v>206</v>
+      </c>
+      <c r="D889">
+        <v>69551</v>
+      </c>
+      <c r="E889">
+        <v>179635</v>
+      </c>
+    </row>
+    <row r="890" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A890" s="1">
+        <v>46315</v>
+      </c>
+      <c r="B890">
+        <v>101</v>
+      </c>
+      <c r="C890" t="s">
+        <v>19</v>
+      </c>
+      <c r="E890">
+        <v>179767</v>
+      </c>
+    </row>
+    <row r="891" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A891" s="1">
+        <v>46315</v>
+      </c>
+      <c r="B891">
+        <v>101</v>
+      </c>
+      <c r="C891" t="s">
+        <v>15</v>
+      </c>
+      <c r="D891">
+        <v>70012</v>
+      </c>
+      <c r="E891">
+        <v>179608</v>
+      </c>
+    </row>
+    <row r="892" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A892" s="1">
+        <v>46315</v>
+      </c>
+      <c r="B892">
+        <v>101</v>
+      </c>
+      <c r="C892" t="s">
+        <v>12</v>
+      </c>
+      <c r="D892">
+        <v>69420</v>
+      </c>
+      <c r="E892">
+        <v>179625</v>
+      </c>
+    </row>
+    <row r="893" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A893" s="1">
+        <v>46315</v>
+      </c>
+      <c r="B893">
+        <v>101</v>
+      </c>
+      <c r="C893" t="s">
+        <v>19</v>
+      </c>
+      <c r="D893">
+        <v>70456</v>
+      </c>
+      <c r="E893">
+        <v>179784</v>
+      </c>
+    </row>
+    <row r="894" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A894" s="1">
+        <v>46315</v>
+      </c>
+      <c r="B894">
+        <v>101</v>
+      </c>
+      <c r="C894" t="s">
+        <v>207</v>
+      </c>
+      <c r="D894">
+        <v>70215</v>
+      </c>
+      <c r="E894">
+        <v>179696</v>
+      </c>
+    </row>
+    <row r="895" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A895" s="1">
+        <v>46315</v>
+      </c>
+      <c r="B895">
+        <v>101</v>
+      </c>
+      <c r="C895" t="s">
+        <v>207</v>
+      </c>
+      <c r="D895">
+        <v>70326</v>
+      </c>
+      <c r="E895">
+        <v>179700</v>
+      </c>
+    </row>
+    <row r="896" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A896" s="1">
+        <v>46315</v>
+      </c>
+      <c r="B896">
+        <v>101</v>
+      </c>
+      <c r="C896" t="s">
+        <v>8</v>
+      </c>
+      <c r="D896">
+        <v>70406</v>
+      </c>
+      <c r="E896">
+        <v>179826</v>
+      </c>
+    </row>
+    <row r="897" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A897" s="1">
+        <v>46315</v>
+      </c>
+      <c r="B897">
+        <v>101</v>
+      </c>
+      <c r="C897" t="s">
+        <v>207</v>
+      </c>
+      <c r="D897">
+        <v>70329</v>
+      </c>
+      <c r="E897">
+        <v>179717</v>
+      </c>
+    </row>
+    <row r="898" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A898" s="1">
+        <v>46315</v>
+      </c>
+      <c r="B898">
+        <v>101</v>
+      </c>
+      <c r="C898" t="s">
+        <v>207</v>
+      </c>
+      <c r="D898">
+        <v>70324</v>
+      </c>
+      <c r="E898">
+        <v>179698</v>
+      </c>
+    </row>
+    <row r="899" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A899" s="1">
+        <v>46315</v>
+      </c>
+      <c r="B899">
+        <v>101</v>
+      </c>
+      <c r="C899" t="s">
+        <v>207</v>
+      </c>
+      <c r="D899">
+        <v>70328</v>
+      </c>
+      <c r="E899">
+        <v>179714</v>
+      </c>
+    </row>
+    <row r="900" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A900" s="1">
+        <v>46315</v>
+      </c>
+      <c r="B900">
+        <v>101</v>
+      </c>
+      <c r="C900" t="s">
+        <v>8</v>
+      </c>
+      <c r="D900">
+        <v>70411</v>
+      </c>
+      <c r="E900">
+        <v>179831</v>
+      </c>
+    </row>
+    <row r="901" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A901" s="1">
+        <v>46315</v>
+      </c>
+      <c r="B901">
+        <v>101</v>
+      </c>
+      <c r="C901" t="s">
+        <v>207</v>
+      </c>
+      <c r="D901">
+        <v>70330</v>
+      </c>
+      <c r="E901">
+        <v>179719</v>
+      </c>
+    </row>
+    <row r="902" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A902" s="1">
+        <v>46315</v>
+      </c>
+      <c r="B902">
+        <v>101</v>
+      </c>
+      <c r="C902" t="s">
+        <v>207</v>
+      </c>
+      <c r="D902">
+        <v>70325</v>
+      </c>
+      <c r="E902">
+        <v>179699</v>
+      </c>
+    </row>
+    <row r="903" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A903" s="1">
+        <v>46315</v>
+      </c>
+      <c r="B903">
+        <v>101</v>
+      </c>
+      <c r="C903" t="s">
+        <v>8</v>
+      </c>
+      <c r="D903">
+        <v>70396</v>
+      </c>
+      <c r="E903">
+        <v>179787</v>
+      </c>
+    </row>
+    <row r="904" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A904" s="1">
+        <v>46315</v>
+      </c>
+      <c r="B904">
+        <v>101</v>
+      </c>
+      <c r="C904" t="s">
+        <v>8</v>
+      </c>
+      <c r="D904">
+        <v>70414</v>
+      </c>
+      <c r="E904">
+        <v>179834</v>
+      </c>
+    </row>
+    <row r="905" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A905" s="1">
+        <v>46315</v>
+      </c>
+      <c r="B905">
+        <v>101</v>
+      </c>
+      <c r="C905" t="s">
+        <v>8</v>
+      </c>
+      <c r="D905">
+        <v>70400</v>
+      </c>
+      <c r="E905">
+        <v>179819</v>
+      </c>
+    </row>
+    <row r="906" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A906" s="1">
+        <v>46315</v>
+      </c>
+      <c r="B906">
+        <v>101</v>
+      </c>
+      <c r="C906" t="s">
+        <v>207</v>
+      </c>
+      <c r="D906">
+        <v>70327</v>
+      </c>
+      <c r="E906">
+        <v>179709</v>
+      </c>
+    </row>
+    <row r="907" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A907" s="1">
+        <v>46315</v>
+      </c>
+      <c r="B907">
+        <v>101</v>
+      </c>
+      <c r="C907" t="s">
+        <v>11</v>
+      </c>
+      <c r="D907">
+        <v>70419</v>
+      </c>
+      <c r="E907">
+        <v>179841</v>
+      </c>
+    </row>
+    <row r="908" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A908" s="1">
+        <v>46315</v>
+      </c>
+      <c r="B908">
+        <v>101</v>
+      </c>
+      <c r="C908" t="s">
+        <v>8</v>
+      </c>
+      <c r="D908">
+        <v>70416</v>
+      </c>
+      <c r="E908">
+        <v>179836</v>
+      </c>
+    </row>
+    <row r="909" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A909" s="1">
+        <v>46315</v>
+      </c>
+      <c r="B909">
+        <v>101</v>
+      </c>
+      <c r="C909" t="s">
+        <v>8</v>
+      </c>
+      <c r="D909">
+        <v>70415</v>
+      </c>
+      <c r="E909">
+        <v>179835</v>
+      </c>
+    </row>
+    <row r="910" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A910" s="1">
+        <v>46315</v>
+      </c>
+      <c r="B910">
+        <v>101</v>
+      </c>
+      <c r="C910" t="s">
+        <v>8</v>
+      </c>
+      <c r="D910">
+        <v>70423</v>
+      </c>
+      <c r="E910">
+        <v>179845</v>
+      </c>
+    </row>
+    <row r="911" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A911" s="1">
+        <v>46315</v>
+      </c>
+      <c r="B911">
+        <v>101</v>
+      </c>
+      <c r="C911" t="s">
+        <v>11</v>
+      </c>
+      <c r="D911">
+        <v>70421</v>
+      </c>
+      <c r="E911">
+        <v>179838</v>
+      </c>
+    </row>
+    <row r="912" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A912" s="1">
+        <v>46315</v>
+      </c>
+      <c r="B912">
+        <v>101</v>
+      </c>
+      <c r="C912" t="s">
+        <v>8</v>
+      </c>
+      <c r="D912">
+        <v>70417</v>
+      </c>
+      <c r="E912">
+        <v>179837</v>
+      </c>
+    </row>
+    <row r="913" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A913" s="1">
+        <v>46315</v>
+      </c>
+      <c r="B913">
+        <v>101</v>
+      </c>
+      <c r="C913" t="s">
+        <v>11</v>
+      </c>
+      <c r="D913">
+        <v>70399</v>
+      </c>
+      <c r="E913">
+        <v>179810</v>
+      </c>
+    </row>
+    <row r="914" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A914" s="1">
+        <v>46315</v>
+      </c>
+      <c r="B914">
+        <v>101</v>
+      </c>
+      <c r="C914" t="s">
+        <v>11</v>
+      </c>
+      <c r="D914">
+        <v>70348</v>
+      </c>
+      <c r="E914">
+        <v>179774</v>
+      </c>
+    </row>
+    <row r="915" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A915" s="1">
+        <v>46315</v>
+      </c>
+      <c r="B915">
+        <v>101</v>
+      </c>
+      <c r="C915" t="s">
+        <v>11</v>
+      </c>
+      <c r="D915">
+        <v>70422</v>
+      </c>
+      <c r="E915">
+        <v>179843</v>
+      </c>
+    </row>
+    <row r="916" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A916" s="1">
+        <v>46315</v>
+      </c>
+      <c r="B916">
+        <v>101</v>
+      </c>
+      <c r="C916" t="s">
+        <v>8</v>
+      </c>
+      <c r="D916">
+        <v>70431</v>
+      </c>
+      <c r="E916">
+        <v>179861</v>
+      </c>
+    </row>
+    <row r="917" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A917" s="1">
+        <v>46315</v>
+      </c>
+      <c r="B917">
+        <v>101</v>
+      </c>
+      <c r="C917" t="s">
+        <v>11</v>
+      </c>
+      <c r="D917">
+        <v>70436</v>
+      </c>
+      <c r="E917">
+        <v>179839</v>
+      </c>
+    </row>
+    <row r="918" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A918" s="1">
+        <v>46315</v>
+      </c>
+      <c r="B918">
+        <v>101</v>
+      </c>
+      <c r="C918" t="s">
+        <v>11</v>
+      </c>
+      <c r="D918">
+        <v>70334</v>
+      </c>
+      <c r="E918">
+        <v>179732</v>
       </c>
     </row>
   </sheetData>
@@ -14428,4 +16599,1765 @@
   </sheetData>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3CCA1778-A08A-4BBC-894B-FE6DC9B4E104}">
+  <dimension ref="A1:D128"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="15.140625" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>168</v>
+      </c>
+      <c r="B1" t="s">
+        <v>170</v>
+      </c>
+      <c r="C1" t="s">
+        <v>171</v>
+      </c>
+      <c r="D1" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A2" s="1">
+        <v>46315</v>
+      </c>
+      <c r="B2" t="s">
+        <v>15</v>
+      </c>
+      <c r="C2">
+        <v>70278</v>
+      </c>
+      <c r="D2">
+        <v>179693</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A3" s="1">
+        <v>46315</v>
+      </c>
+      <c r="B3" t="s">
+        <v>0</v>
+      </c>
+      <c r="D3">
+        <v>179705</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A4" s="1">
+        <v>46315</v>
+      </c>
+      <c r="B4" t="s">
+        <v>115</v>
+      </c>
+      <c r="C4">
+        <v>70279</v>
+      </c>
+      <c r="D4">
+        <v>179692</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A5" s="1">
+        <v>46315</v>
+      </c>
+      <c r="B5" t="s">
+        <v>0</v>
+      </c>
+      <c r="C5">
+        <v>70298</v>
+      </c>
+      <c r="D5">
+        <v>179680</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A6" s="1">
+        <v>46315</v>
+      </c>
+      <c r="B6" t="s">
+        <v>94</v>
+      </c>
+      <c r="D6">
+        <v>179646</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A7" s="1">
+        <v>46315</v>
+      </c>
+      <c r="B7" t="s">
+        <v>190</v>
+      </c>
+      <c r="C7">
+        <v>70059</v>
+      </c>
+      <c r="D7">
+        <v>179565</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A8" s="1">
+        <v>46315</v>
+      </c>
+      <c r="B8" t="s">
+        <v>40</v>
+      </c>
+      <c r="C8">
+        <v>69908</v>
+      </c>
+      <c r="D8">
+        <v>179712</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A9" s="1">
+        <v>46315</v>
+      </c>
+      <c r="B9" t="s">
+        <v>191</v>
+      </c>
+      <c r="C9">
+        <v>68978</v>
+      </c>
+      <c r="D9">
+        <v>179645</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A10" s="1">
+        <v>46315</v>
+      </c>
+      <c r="B10" t="s">
+        <v>48</v>
+      </c>
+      <c r="C10">
+        <v>70201</v>
+      </c>
+      <c r="D10">
+        <v>179653</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A11" s="1">
+        <v>46315</v>
+      </c>
+      <c r="B11" t="s">
+        <v>40</v>
+      </c>
+      <c r="C11">
+        <v>70088</v>
+      </c>
+      <c r="D11">
+        <v>179713</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A12" s="1">
+        <v>46315</v>
+      </c>
+      <c r="B12" t="s">
+        <v>123</v>
+      </c>
+      <c r="C12">
+        <v>69737</v>
+      </c>
+      <c r="D12">
+        <v>179728</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A13" s="1">
+        <v>46315</v>
+      </c>
+      <c r="B13" t="s">
+        <v>69</v>
+      </c>
+      <c r="C13">
+        <v>67824</v>
+      </c>
+      <c r="D13">
+        <v>179694</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A14" s="1">
+        <v>46315</v>
+      </c>
+      <c r="B14" t="s">
+        <v>25</v>
+      </c>
+      <c r="C14">
+        <v>70390</v>
+      </c>
+      <c r="D14">
+        <v>179689</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A15" s="1">
+        <v>46315</v>
+      </c>
+      <c r="B15" t="s">
+        <v>0</v>
+      </c>
+      <c r="D15">
+        <v>179647</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A16" s="1">
+        <v>46315</v>
+      </c>
+      <c r="B16" t="s">
+        <v>69</v>
+      </c>
+      <c r="C16">
+        <v>68147</v>
+      </c>
+      <c r="D16">
+        <v>179695</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A17" s="1">
+        <v>46315</v>
+      </c>
+      <c r="B17" t="s">
+        <v>25</v>
+      </c>
+      <c r="C17">
+        <v>69469</v>
+      </c>
+      <c r="D17">
+        <v>179723</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A18" s="1">
+        <v>46315</v>
+      </c>
+      <c r="B18" t="s">
+        <v>29</v>
+      </c>
+      <c r="C18">
+        <v>66980</v>
+      </c>
+      <c r="D18">
+        <v>176367</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A19" s="1">
+        <v>46315</v>
+      </c>
+      <c r="B19" t="s">
+        <v>187</v>
+      </c>
+      <c r="C19">
+        <v>70197</v>
+      </c>
+      <c r="D19">
+        <v>179658</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A20" s="1">
+        <v>46315</v>
+      </c>
+      <c r="B20" t="s">
+        <v>29</v>
+      </c>
+      <c r="C20">
+        <v>69806</v>
+      </c>
+      <c r="D20">
+        <v>179657</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A21" s="1">
+        <v>46315</v>
+      </c>
+      <c r="B21" t="s">
+        <v>86</v>
+      </c>
+      <c r="D21">
+        <v>179263</v>
+      </c>
+    </row>
+    <row r="22" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A22" s="1">
+        <v>46315</v>
+      </c>
+      <c r="B22" t="s">
+        <v>29</v>
+      </c>
+      <c r="C22">
+        <v>69802</v>
+      </c>
+      <c r="D22">
+        <v>179674</v>
+      </c>
+    </row>
+    <row r="23" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A23" s="1">
+        <v>46315</v>
+      </c>
+      <c r="B23" t="s">
+        <v>74</v>
+      </c>
+      <c r="C23">
+        <v>69767</v>
+      </c>
+      <c r="D23">
+        <v>179688</v>
+      </c>
+    </row>
+    <row r="24" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A24" s="1">
+        <v>46315</v>
+      </c>
+      <c r="B24" t="s">
+        <v>29</v>
+      </c>
+      <c r="C24">
+        <v>69814</v>
+      </c>
+      <c r="D24">
+        <v>179659</v>
+      </c>
+    </row>
+    <row r="25" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A25" s="1">
+        <v>46315</v>
+      </c>
+      <c r="B25" t="s">
+        <v>29</v>
+      </c>
+      <c r="D25">
+        <v>179707</v>
+      </c>
+    </row>
+    <row r="26" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A26" s="1">
+        <v>46315</v>
+      </c>
+      <c r="B26" t="s">
+        <v>29</v>
+      </c>
+      <c r="C26">
+        <v>69803</v>
+      </c>
+      <c r="D26">
+        <v>179671</v>
+      </c>
+    </row>
+    <row r="27" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A27" s="1">
+        <v>46315</v>
+      </c>
+      <c r="B27" t="s">
+        <v>86</v>
+      </c>
+      <c r="D27">
+        <v>179703</v>
+      </c>
+    </row>
+    <row r="28" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A28" s="1">
+        <v>46315</v>
+      </c>
+      <c r="B28" t="s">
+        <v>117</v>
+      </c>
+      <c r="D28">
+        <v>179679</v>
+      </c>
+    </row>
+    <row r="29" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A29" s="1">
+        <v>46315</v>
+      </c>
+      <c r="B29" t="s">
+        <v>29</v>
+      </c>
+      <c r="C29">
+        <v>70192</v>
+      </c>
+      <c r="D29">
+        <v>179716</v>
+      </c>
+    </row>
+    <row r="30" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A30" s="1">
+        <v>46315</v>
+      </c>
+      <c r="B30" t="s">
+        <v>117</v>
+      </c>
+      <c r="C30">
+        <v>70157</v>
+      </c>
+      <c r="D30">
+        <v>179690</v>
+      </c>
+    </row>
+    <row r="31" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A31" s="1">
+        <v>46315</v>
+      </c>
+      <c r="B31" t="s">
+        <v>86</v>
+      </c>
+      <c r="C31">
+        <v>69757</v>
+      </c>
+      <c r="D31">
+        <v>179638</v>
+      </c>
+    </row>
+    <row r="32" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A32" s="1">
+        <v>46315</v>
+      </c>
+      <c r="B32" t="s">
+        <v>117</v>
+      </c>
+      <c r="C32">
+        <v>69764</v>
+      </c>
+      <c r="D32">
+        <v>179650</v>
+      </c>
+    </row>
+    <row r="33" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A33" s="1">
+        <v>46315</v>
+      </c>
+      <c r="B33" t="s">
+        <v>29</v>
+      </c>
+      <c r="C33">
+        <v>70288</v>
+      </c>
+      <c r="D33">
+        <v>179655</v>
+      </c>
+    </row>
+    <row r="34" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A34" s="1">
+        <v>46315</v>
+      </c>
+      <c r="B34" t="s">
+        <v>187</v>
+      </c>
+      <c r="C34">
+        <v>68888</v>
+      </c>
+      <c r="D34">
+        <v>179636</v>
+      </c>
+    </row>
+    <row r="35" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A35" s="1">
+        <v>46315</v>
+      </c>
+      <c r="B35" t="s">
+        <v>86</v>
+      </c>
+      <c r="C35">
+        <v>70160</v>
+      </c>
+      <c r="D35">
+        <v>179673</v>
+      </c>
+    </row>
+    <row r="36" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A36" s="1">
+        <v>46315</v>
+      </c>
+      <c r="B36" t="s">
+        <v>187</v>
+      </c>
+      <c r="C36">
+        <v>69391</v>
+      </c>
+      <c r="D36">
+        <v>179639</v>
+      </c>
+    </row>
+    <row r="37" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A37" s="1">
+        <v>46315</v>
+      </c>
+      <c r="B37" t="s">
+        <v>74</v>
+      </c>
+      <c r="C37">
+        <v>69768</v>
+      </c>
+      <c r="D37">
+        <v>179660</v>
+      </c>
+    </row>
+    <row r="38" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A38" s="1">
+        <v>46315</v>
+      </c>
+      <c r="B38" t="s">
+        <v>86</v>
+      </c>
+      <c r="D38">
+        <v>179702</v>
+      </c>
+    </row>
+    <row r="39" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A39" s="1">
+        <v>46315</v>
+      </c>
+      <c r="B39" t="s">
+        <v>118</v>
+      </c>
+      <c r="D39">
+        <v>179706</v>
+      </c>
+    </row>
+    <row r="40" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A40" s="1">
+        <v>46315</v>
+      </c>
+      <c r="B40" t="s">
+        <v>74</v>
+      </c>
+      <c r="C40">
+        <v>69769</v>
+      </c>
+      <c r="D40">
+        <v>179640</v>
+      </c>
+    </row>
+    <row r="41" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A41" s="1">
+        <v>46315</v>
+      </c>
+      <c r="B41" t="s">
+        <v>86</v>
+      </c>
+      <c r="C41">
+        <v>69369</v>
+      </c>
+      <c r="D41">
+        <v>179641</v>
+      </c>
+    </row>
+    <row r="42" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A42" s="1">
+        <v>46315</v>
+      </c>
+      <c r="B42" t="s">
+        <v>86</v>
+      </c>
+      <c r="C42">
+        <v>70154</v>
+      </c>
+      <c r="D42">
+        <v>179637</v>
+      </c>
+    </row>
+    <row r="43" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A43" s="1">
+        <v>46315</v>
+      </c>
+      <c r="B43" t="s">
+        <v>86</v>
+      </c>
+      <c r="C43">
+        <v>69756</v>
+      </c>
+      <c r="D43">
+        <v>179701</v>
+      </c>
+    </row>
+    <row r="44" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A44" s="1">
+        <v>46315</v>
+      </c>
+      <c r="B44" t="s">
+        <v>118</v>
+      </c>
+      <c r="C44">
+        <v>69762</v>
+      </c>
+      <c r="D44">
+        <v>179661</v>
+      </c>
+    </row>
+    <row r="45" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A45" s="1">
+        <v>46315</v>
+      </c>
+      <c r="B45" t="s">
+        <v>86</v>
+      </c>
+      <c r="C45">
+        <v>69754</v>
+      </c>
+      <c r="D45">
+        <v>179722</v>
+      </c>
+    </row>
+    <row r="46" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A46" s="1">
+        <v>46315</v>
+      </c>
+      <c r="B46" t="s">
+        <v>86</v>
+      </c>
+      <c r="C46">
+        <v>70153</v>
+      </c>
+      <c r="D46">
+        <v>179656</v>
+      </c>
+    </row>
+    <row r="47" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A47" s="1">
+        <v>46315</v>
+      </c>
+      <c r="B47" t="s">
+        <v>158</v>
+      </c>
+      <c r="C47">
+        <v>539</v>
+      </c>
+      <c r="D47">
+        <v>534</v>
+      </c>
+    </row>
+    <row r="48" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A48" s="1">
+        <v>46315</v>
+      </c>
+      <c r="B48" t="s">
+        <v>40</v>
+      </c>
+      <c r="C48">
+        <v>549</v>
+      </c>
+      <c r="D48">
+        <v>540</v>
+      </c>
+    </row>
+    <row r="49" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A49" s="1">
+        <v>46315</v>
+      </c>
+      <c r="B49" t="s">
+        <v>24</v>
+      </c>
+      <c r="C49">
+        <v>546</v>
+      </c>
+      <c r="D49">
+        <v>539</v>
+      </c>
+    </row>
+    <row r="50" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A50" s="1">
+        <v>46315</v>
+      </c>
+      <c r="B50" t="s">
+        <v>24</v>
+      </c>
+      <c r="C50">
+        <v>547</v>
+      </c>
+      <c r="D50">
+        <v>538</v>
+      </c>
+    </row>
+    <row r="51" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A51" s="1">
+        <v>46315</v>
+      </c>
+      <c r="B51" t="s">
+        <v>40</v>
+      </c>
+      <c r="C51">
+        <v>548</v>
+      </c>
+      <c r="D51">
+        <v>541</v>
+      </c>
+    </row>
+    <row r="52" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A52" s="1">
+        <v>46315</v>
+      </c>
+      <c r="B52" t="s">
+        <v>192</v>
+      </c>
+      <c r="C52">
+        <v>70163</v>
+      </c>
+      <c r="D52">
+        <v>179642</v>
+      </c>
+    </row>
+    <row r="53" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A53" s="1">
+        <v>46315</v>
+      </c>
+      <c r="B53" t="s">
+        <v>193</v>
+      </c>
+      <c r="C53">
+        <v>69943</v>
+      </c>
+      <c r="D53">
+        <v>179662</v>
+      </c>
+    </row>
+    <row r="54" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A54" s="1">
+        <v>46315</v>
+      </c>
+      <c r="B54" t="s">
+        <v>166</v>
+      </c>
+      <c r="C54">
+        <v>69738</v>
+      </c>
+      <c r="D54">
+        <v>179751</v>
+      </c>
+    </row>
+    <row r="55" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A55" s="1">
+        <v>46315</v>
+      </c>
+      <c r="B55" t="s">
+        <v>194</v>
+      </c>
+      <c r="C55">
+        <v>70464</v>
+      </c>
+      <c r="D55">
+        <v>179779</v>
+      </c>
+    </row>
+    <row r="56" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A56" s="1">
+        <v>46315</v>
+      </c>
+      <c r="B56" t="s">
+        <v>19</v>
+      </c>
+      <c r="C56">
+        <v>69704</v>
+      </c>
+      <c r="D56">
+        <v>179780</v>
+      </c>
+    </row>
+    <row r="57" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A57" s="1">
+        <v>46315</v>
+      </c>
+      <c r="B57" t="s">
+        <v>7</v>
+      </c>
+      <c r="C57">
+        <v>70076</v>
+      </c>
+      <c r="D57">
+        <v>179556</v>
+      </c>
+    </row>
+    <row r="58" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A58" s="1">
+        <v>46315</v>
+      </c>
+      <c r="B58" t="s">
+        <v>19</v>
+      </c>
+      <c r="C58">
+        <v>70128</v>
+      </c>
+      <c r="D58">
+        <v>179616</v>
+      </c>
+    </row>
+    <row r="59" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A59" s="1">
+        <v>46315</v>
+      </c>
+      <c r="B59" t="s">
+        <v>19</v>
+      </c>
+      <c r="C59">
+        <v>70321</v>
+      </c>
+      <c r="D59">
+        <v>179675</v>
+      </c>
+    </row>
+    <row r="60" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A60" s="1">
+        <v>46315</v>
+      </c>
+      <c r="B60" t="s">
+        <v>19</v>
+      </c>
+      <c r="C60">
+        <v>69389</v>
+      </c>
+      <c r="D60">
+        <v>179785</v>
+      </c>
+    </row>
+    <row r="61" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A61" s="1">
+        <v>46315</v>
+      </c>
+      <c r="B61" t="s">
+        <v>19</v>
+      </c>
+      <c r="C61">
+        <v>68822</v>
+      </c>
+      <c r="D61">
+        <v>179783</v>
+      </c>
+    </row>
+    <row r="62" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A62" s="1">
+        <v>46315</v>
+      </c>
+      <c r="B62" t="s">
+        <v>19</v>
+      </c>
+      <c r="C62">
+        <v>69687</v>
+      </c>
+      <c r="D62">
+        <v>179782</v>
+      </c>
+    </row>
+    <row r="63" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A63" s="1">
+        <v>46315</v>
+      </c>
+      <c r="B63" t="s">
+        <v>19</v>
+      </c>
+      <c r="C63">
+        <v>70241</v>
+      </c>
+      <c r="D63">
+        <v>179781</v>
+      </c>
+    </row>
+    <row r="64" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A64" s="1">
+        <v>46315</v>
+      </c>
+      <c r="B64" t="s">
+        <v>89</v>
+      </c>
+      <c r="C64">
+        <v>70072</v>
+      </c>
+      <c r="D64">
+        <v>179681</v>
+      </c>
+    </row>
+    <row r="65" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A65" s="1">
+        <v>46315</v>
+      </c>
+      <c r="B65" t="s">
+        <v>121</v>
+      </c>
+      <c r="C65">
+        <v>70144</v>
+      </c>
+      <c r="D65">
+        <v>179676</v>
+      </c>
+    </row>
+    <row r="66" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A66" s="1">
+        <v>46315</v>
+      </c>
+      <c r="B66" t="s">
+        <v>121</v>
+      </c>
+      <c r="C66">
+        <v>70203</v>
+      </c>
+      <c r="D66">
+        <v>179685</v>
+      </c>
+    </row>
+    <row r="67" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A67" s="1">
+        <v>46315</v>
+      </c>
+      <c r="B67" t="s">
+        <v>121</v>
+      </c>
+      <c r="C67">
+        <v>70236</v>
+      </c>
+      <c r="D67">
+        <v>179684</v>
+      </c>
+    </row>
+    <row r="68" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A68" s="1">
+        <v>46315</v>
+      </c>
+      <c r="B68" t="s">
+        <v>122</v>
+      </c>
+      <c r="C68">
+        <v>70235</v>
+      </c>
+      <c r="D68">
+        <v>179726</v>
+      </c>
+    </row>
+    <row r="69" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A69" s="1">
+        <v>46315</v>
+      </c>
+      <c r="B69" t="s">
+        <v>195</v>
+      </c>
+      <c r="C69">
+        <v>70078</v>
+      </c>
+      <c r="D69">
+        <v>179677</v>
+      </c>
+    </row>
+    <row r="70" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A70" s="1">
+        <v>46315</v>
+      </c>
+      <c r="B70" t="s">
+        <v>122</v>
+      </c>
+      <c r="C70">
+        <v>69839</v>
+      </c>
+      <c r="D70">
+        <v>179678</v>
+      </c>
+    </row>
+    <row r="71" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A71" s="1">
+        <v>46315</v>
+      </c>
+      <c r="B71" t="s">
+        <v>18</v>
+      </c>
+      <c r="D71">
+        <v>18624</v>
+      </c>
+    </row>
+    <row r="72" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A72" s="1">
+        <v>46315</v>
+      </c>
+      <c r="B72" t="s">
+        <v>196</v>
+      </c>
+      <c r="C72">
+        <v>16289</v>
+      </c>
+      <c r="D72">
+        <v>18608</v>
+      </c>
+    </row>
+    <row r="73" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A73" s="1">
+        <v>46315</v>
+      </c>
+      <c r="B73" t="s">
+        <v>196</v>
+      </c>
+      <c r="C73">
+        <v>16293</v>
+      </c>
+      <c r="D73">
+        <v>18612</v>
+      </c>
+    </row>
+    <row r="74" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A74" s="1">
+        <v>46315</v>
+      </c>
+      <c r="B74" t="s">
+        <v>15</v>
+      </c>
+      <c r="C74">
+        <v>16305</v>
+      </c>
+      <c r="D74">
+        <v>18625</v>
+      </c>
+    </row>
+    <row r="75" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A75" s="1">
+        <v>46315</v>
+      </c>
+      <c r="B75" t="s">
+        <v>197</v>
+      </c>
+      <c r="C75">
+        <v>16299</v>
+      </c>
+      <c r="D75">
+        <v>18616</v>
+      </c>
+    </row>
+    <row r="76" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A76" s="1">
+        <v>46315</v>
+      </c>
+      <c r="B76" t="s">
+        <v>15</v>
+      </c>
+      <c r="C76">
+        <v>16300</v>
+      </c>
+      <c r="D76">
+        <v>18621</v>
+      </c>
+    </row>
+    <row r="77" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A77" s="1">
+        <v>46315</v>
+      </c>
+      <c r="B77" t="s">
+        <v>197</v>
+      </c>
+      <c r="D77">
+        <v>18617</v>
+      </c>
+    </row>
+    <row r="78" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A78" s="1">
+        <v>46315</v>
+      </c>
+      <c r="B78" t="s">
+        <v>198</v>
+      </c>
+      <c r="C78">
+        <v>16291</v>
+      </c>
+      <c r="D78">
+        <v>18610</v>
+      </c>
+    </row>
+    <row r="79" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A79" s="1">
+        <v>46315</v>
+      </c>
+      <c r="B79" t="s">
+        <v>196</v>
+      </c>
+      <c r="C79">
+        <v>16292</v>
+      </c>
+      <c r="D79">
+        <v>18611</v>
+      </c>
+    </row>
+    <row r="80" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A80" s="1">
+        <v>46315</v>
+      </c>
+      <c r="B80" t="s">
+        <v>199</v>
+      </c>
+      <c r="C80">
+        <v>16288</v>
+      </c>
+      <c r="D80">
+        <v>18607</v>
+      </c>
+    </row>
+    <row r="81" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A81" s="1">
+        <v>46315</v>
+      </c>
+      <c r="B81" t="s">
+        <v>200</v>
+      </c>
+      <c r="C81">
+        <v>16306</v>
+      </c>
+      <c r="D81">
+        <v>18618</v>
+      </c>
+    </row>
+    <row r="82" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A82" s="1">
+        <v>46315</v>
+      </c>
+      <c r="B82" t="s">
+        <v>15</v>
+      </c>
+      <c r="C82">
+        <v>16302</v>
+      </c>
+      <c r="D82">
+        <v>18622</v>
+      </c>
+    </row>
+    <row r="83" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A83" s="1">
+        <v>46315</v>
+      </c>
+      <c r="B83" t="s">
+        <v>201</v>
+      </c>
+      <c r="C83">
+        <v>16272</v>
+      </c>
+      <c r="D83">
+        <v>18603</v>
+      </c>
+    </row>
+    <row r="84" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A84" s="1">
+        <v>46315</v>
+      </c>
+      <c r="B84" t="s">
+        <v>202</v>
+      </c>
+      <c r="C84">
+        <v>16246</v>
+      </c>
+      <c r="D84">
+        <v>18605</v>
+      </c>
+    </row>
+    <row r="85" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A85" s="1">
+        <v>46315</v>
+      </c>
+      <c r="B85" t="s">
+        <v>203</v>
+      </c>
+      <c r="C85">
+        <v>16295</v>
+      </c>
+      <c r="D85">
+        <v>18614</v>
+      </c>
+    </row>
+    <row r="86" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A86" s="1">
+        <v>46315</v>
+      </c>
+      <c r="B86" t="s">
+        <v>201</v>
+      </c>
+      <c r="C86">
+        <v>16273</v>
+      </c>
+      <c r="D86">
+        <v>18606</v>
+      </c>
+    </row>
+    <row r="87" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A87" s="1">
+        <v>46315</v>
+      </c>
+      <c r="B87" t="s">
+        <v>201</v>
+      </c>
+      <c r="C87">
+        <v>16274</v>
+      </c>
+      <c r="D87">
+        <v>18601</v>
+      </c>
+    </row>
+    <row r="88" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A88" s="1">
+        <v>46315</v>
+      </c>
+      <c r="B88" t="s">
+        <v>15</v>
+      </c>
+      <c r="C88">
+        <v>16294</v>
+      </c>
+      <c r="D88">
+        <v>18613</v>
+      </c>
+    </row>
+    <row r="89" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A89" s="1">
+        <v>46315</v>
+      </c>
+      <c r="B89" t="s">
+        <v>15</v>
+      </c>
+      <c r="C89">
+        <v>16296</v>
+      </c>
+      <c r="D89">
+        <v>18615</v>
+      </c>
+    </row>
+    <row r="90" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A90" s="1">
+        <v>46315</v>
+      </c>
+      <c r="B90" t="s">
+        <v>15</v>
+      </c>
+      <c r="C90">
+        <v>16297</v>
+      </c>
+      <c r="D90">
+        <v>18619</v>
+      </c>
+    </row>
+    <row r="91" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A91" s="1">
+        <v>46315</v>
+      </c>
+      <c r="B91" t="s">
+        <v>23</v>
+      </c>
+      <c r="C91">
+        <v>68823</v>
+      </c>
+      <c r="D91">
+        <v>179790</v>
+      </c>
+    </row>
+    <row r="92" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A92" s="1">
+        <v>46315</v>
+      </c>
+      <c r="B92" t="s">
+        <v>23</v>
+      </c>
+      <c r="D92">
+        <v>179596</v>
+      </c>
+    </row>
+    <row r="93" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A93" s="1">
+        <v>46315</v>
+      </c>
+      <c r="B93" t="s">
+        <v>33</v>
+      </c>
+      <c r="C93">
+        <v>70315</v>
+      </c>
+      <c r="D93">
+        <v>179798</v>
+      </c>
+    </row>
+    <row r="94" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A94" s="1">
+        <v>46315</v>
+      </c>
+      <c r="B94" t="s">
+        <v>69</v>
+      </c>
+      <c r="C94">
+        <v>70453</v>
+      </c>
+      <c r="D94">
+        <v>179753</v>
+      </c>
+    </row>
+    <row r="95" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A95" s="1">
+        <v>46315</v>
+      </c>
+      <c r="B95" t="s">
+        <v>15</v>
+      </c>
+      <c r="C95">
+        <v>69645</v>
+      </c>
+      <c r="D95">
+        <v>179604</v>
+      </c>
+    </row>
+    <row r="96" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A96" s="1">
+        <v>46315</v>
+      </c>
+      <c r="B96" t="s">
+        <v>204</v>
+      </c>
+      <c r="C96">
+        <v>69840</v>
+      </c>
+      <c r="D96">
+        <v>179602</v>
+      </c>
+    </row>
+    <row r="97" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A97" s="1">
+        <v>46315</v>
+      </c>
+      <c r="B97" t="s">
+        <v>205</v>
+      </c>
+      <c r="D97">
+        <v>179368</v>
+      </c>
+    </row>
+    <row r="98" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A98" s="1">
+        <v>46315</v>
+      </c>
+      <c r="B98" t="s">
+        <v>19</v>
+      </c>
+      <c r="D98">
+        <v>179643</v>
+      </c>
+    </row>
+    <row r="99" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A99" s="1">
+        <v>46315</v>
+      </c>
+      <c r="B99" t="s">
+        <v>206</v>
+      </c>
+      <c r="C99">
+        <v>69551</v>
+      </c>
+      <c r="D99">
+        <v>179635</v>
+      </c>
+    </row>
+    <row r="100" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A100" s="1">
+        <v>46315</v>
+      </c>
+      <c r="B100" t="s">
+        <v>19</v>
+      </c>
+      <c r="D100">
+        <v>179767</v>
+      </c>
+    </row>
+    <row r="101" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A101" s="1">
+        <v>46315</v>
+      </c>
+      <c r="B101" t="s">
+        <v>15</v>
+      </c>
+      <c r="C101">
+        <v>70012</v>
+      </c>
+      <c r="D101">
+        <v>179608</v>
+      </c>
+    </row>
+    <row r="102" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A102" s="1">
+        <v>46315</v>
+      </c>
+      <c r="B102" t="s">
+        <v>12</v>
+      </c>
+      <c r="C102">
+        <v>69420</v>
+      </c>
+      <c r="D102">
+        <v>179625</v>
+      </c>
+    </row>
+    <row r="103" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A103" s="1">
+        <v>46315</v>
+      </c>
+      <c r="B103" t="s">
+        <v>19</v>
+      </c>
+      <c r="C103">
+        <v>70456</v>
+      </c>
+      <c r="D103">
+        <v>179784</v>
+      </c>
+    </row>
+    <row r="104" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A104" s="1">
+        <v>46315</v>
+      </c>
+      <c r="B104" t="s">
+        <v>207</v>
+      </c>
+      <c r="C104">
+        <v>70215</v>
+      </c>
+      <c r="D104">
+        <v>179696</v>
+      </c>
+    </row>
+    <row r="105" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A105" s="1">
+        <v>46315</v>
+      </c>
+      <c r="B105" t="s">
+        <v>207</v>
+      </c>
+      <c r="C105">
+        <v>70326</v>
+      </c>
+      <c r="D105">
+        <v>179700</v>
+      </c>
+    </row>
+    <row r="106" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A106" s="1">
+        <v>46315</v>
+      </c>
+      <c r="B106" t="s">
+        <v>8</v>
+      </c>
+      <c r="C106">
+        <v>70406</v>
+      </c>
+      <c r="D106">
+        <v>179826</v>
+      </c>
+    </row>
+    <row r="107" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A107" s="1">
+        <v>46315</v>
+      </c>
+      <c r="B107" t="s">
+        <v>207</v>
+      </c>
+      <c r="C107">
+        <v>70329</v>
+      </c>
+      <c r="D107">
+        <v>179717</v>
+      </c>
+    </row>
+    <row r="108" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A108" s="1">
+        <v>46315</v>
+      </c>
+      <c r="B108" t="s">
+        <v>207</v>
+      </c>
+      <c r="C108">
+        <v>70324</v>
+      </c>
+      <c r="D108">
+        <v>179698</v>
+      </c>
+    </row>
+    <row r="109" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A109" s="1">
+        <v>46315</v>
+      </c>
+      <c r="B109" t="s">
+        <v>207</v>
+      </c>
+      <c r="C109">
+        <v>70328</v>
+      </c>
+      <c r="D109">
+        <v>179714</v>
+      </c>
+    </row>
+    <row r="110" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A110" s="1">
+        <v>46315</v>
+      </c>
+      <c r="B110" t="s">
+        <v>8</v>
+      </c>
+      <c r="C110">
+        <v>70411</v>
+      </c>
+      <c r="D110">
+        <v>179831</v>
+      </c>
+    </row>
+    <row r="111" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A111" s="1">
+        <v>46315</v>
+      </c>
+      <c r="B111" t="s">
+        <v>207</v>
+      </c>
+      <c r="C111">
+        <v>70330</v>
+      </c>
+      <c r="D111">
+        <v>179719</v>
+      </c>
+    </row>
+    <row r="112" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A112" s="1">
+        <v>46315</v>
+      </c>
+      <c r="B112" t="s">
+        <v>207</v>
+      </c>
+      <c r="C112">
+        <v>70325</v>
+      </c>
+      <c r="D112">
+        <v>179699</v>
+      </c>
+    </row>
+    <row r="113" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A113" s="1">
+        <v>46315</v>
+      </c>
+      <c r="B113" t="s">
+        <v>8</v>
+      </c>
+      <c r="C113">
+        <v>70396</v>
+      </c>
+      <c r="D113">
+        <v>179787</v>
+      </c>
+    </row>
+    <row r="114" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A114" s="1">
+        <v>46315</v>
+      </c>
+      <c r="B114" t="s">
+        <v>8</v>
+      </c>
+      <c r="C114">
+        <v>70414</v>
+      </c>
+      <c r="D114">
+        <v>179834</v>
+      </c>
+    </row>
+    <row r="115" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A115" s="1">
+        <v>46315</v>
+      </c>
+      <c r="B115" t="s">
+        <v>8</v>
+      </c>
+      <c r="C115">
+        <v>70400</v>
+      </c>
+      <c r="D115">
+        <v>179819</v>
+      </c>
+    </row>
+    <row r="116" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A116" s="1">
+        <v>46315</v>
+      </c>
+      <c r="B116" t="s">
+        <v>207</v>
+      </c>
+      <c r="C116">
+        <v>70327</v>
+      </c>
+      <c r="D116">
+        <v>179709</v>
+      </c>
+    </row>
+    <row r="117" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A117" s="1">
+        <v>46315</v>
+      </c>
+      <c r="B117" t="s">
+        <v>11</v>
+      </c>
+      <c r="C117">
+        <v>70419</v>
+      </c>
+      <c r="D117">
+        <v>179841</v>
+      </c>
+    </row>
+    <row r="118" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A118" s="1">
+        <v>46315</v>
+      </c>
+      <c r="B118" t="s">
+        <v>8</v>
+      </c>
+      <c r="C118">
+        <v>70416</v>
+      </c>
+      <c r="D118">
+        <v>179836</v>
+      </c>
+    </row>
+    <row r="119" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A119" s="1">
+        <v>46315</v>
+      </c>
+      <c r="B119" t="s">
+        <v>8</v>
+      </c>
+      <c r="C119">
+        <v>70415</v>
+      </c>
+      <c r="D119">
+        <v>179835</v>
+      </c>
+    </row>
+    <row r="120" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A120" s="1">
+        <v>46315</v>
+      </c>
+      <c r="B120" t="s">
+        <v>8</v>
+      </c>
+      <c r="C120">
+        <v>70423</v>
+      </c>
+      <c r="D120">
+        <v>179845</v>
+      </c>
+    </row>
+    <row r="121" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A121" s="1">
+        <v>46315</v>
+      </c>
+      <c r="B121" t="s">
+        <v>11</v>
+      </c>
+      <c r="C121">
+        <v>70421</v>
+      </c>
+      <c r="D121">
+        <v>179838</v>
+      </c>
+    </row>
+    <row r="122" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A122" s="1">
+        <v>46315</v>
+      </c>
+      <c r="B122" t="s">
+        <v>8</v>
+      </c>
+      <c r="C122">
+        <v>70417</v>
+      </c>
+      <c r="D122">
+        <v>179837</v>
+      </c>
+    </row>
+    <row r="123" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A123" s="1">
+        <v>46315</v>
+      </c>
+      <c r="B123" t="s">
+        <v>11</v>
+      </c>
+      <c r="C123">
+        <v>70399</v>
+      </c>
+      <c r="D123">
+        <v>179810</v>
+      </c>
+    </row>
+    <row r="124" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A124" s="1">
+        <v>46315</v>
+      </c>
+      <c r="B124" t="s">
+        <v>11</v>
+      </c>
+      <c r="C124">
+        <v>70348</v>
+      </c>
+      <c r="D124">
+        <v>179774</v>
+      </c>
+    </row>
+    <row r="125" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A125" s="1">
+        <v>46315</v>
+      </c>
+      <c r="B125" t="s">
+        <v>11</v>
+      </c>
+      <c r="C125">
+        <v>70422</v>
+      </c>
+      <c r="D125">
+        <v>179843</v>
+      </c>
+    </row>
+    <row r="126" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A126" s="1">
+        <v>46315</v>
+      </c>
+      <c r="B126" t="s">
+        <v>8</v>
+      </c>
+      <c r="C126">
+        <v>70431</v>
+      </c>
+      <c r="D126">
+        <v>179861</v>
+      </c>
+    </row>
+    <row r="127" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A127" s="1">
+        <v>46315</v>
+      </c>
+      <c r="B127" t="s">
+        <v>11</v>
+      </c>
+      <c r="C127">
+        <v>70436</v>
+      </c>
+      <c r="D127">
+        <v>179839</v>
+      </c>
+    </row>
+    <row r="128" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A128" s="1">
+        <v>46315</v>
+      </c>
+      <c r="B128" t="s">
+        <v>11</v>
+      </c>
+      <c r="C128">
+        <v>70334</v>
+      </c>
+      <c r="D128">
+        <v>179732</v>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:D128" xr:uid="{3CCA1778-A08A-4BBC-894B-FE6DC9B4E104}"/>
+  <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
+</worksheet>
 </file>
--- a/DadosRomaneios.xlsx
+++ b/DadosRomaneios.xlsx
@@ -8,18 +8,14 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="U:\AcompanhamentoProducao\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C14689DD-72CB-4E34-B996-5F058AE252BF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2022B6CC-C9D8-4A70-A37C-2BF50ED79ADB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{B6976704-8E51-4052-B60A-5847F95A5AE5}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" activeTab="1" xr2:uid="{B6976704-8E51-4052-B60A-5847F95A5AE5}"/>
   </bookViews>
   <sheets>
     <sheet name="Romaneios" sheetId="2" r:id="rId1"/>
     <sheet name="DadosRomaneios" sheetId="3" r:id="rId2"/>
-    <sheet name="Planilha1" sheetId="4" r:id="rId3"/>
   </sheets>
-  <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">Planilha1!$A$1:$D$128</definedName>
-  </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -44,7 +40,7 @@
 </file>
 
 <file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
-<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
+<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xlrd="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
   <metadataTypes count="1">
     <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
   </metadataTypes>
@@ -66,7 +62,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1054" uniqueCount="208">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="923" uniqueCount="208">
   <si>
     <t>ALBERT EINSTEIN</t>
   </si>
@@ -16462,7 +16458,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5180BF9C-1943-4030-8A1B-6F86FE205C17}">
-  <dimension ref="A1:C14"/>
+  <dimension ref="A1:C15"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="12.85546875" style="1" bestFit="1" customWidth="1"/>
@@ -16471,7 +16467,7 @@
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="str" cm="1">
-        <f t="array" ref="A1:A14">_xlfn.UNIQUE(Romaneios!A1:A791)</f>
+        <f t="array" ref="A1:A15">_xlfn.UNIQUE(Romaneios!A1:A918)</f>
         <v>Dt. Romaneio</v>
       </c>
       <c r="B1" t="s">
@@ -16596,1768 +16592,16 @@
         <v>69</v>
       </c>
     </row>
+    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A15" s="1">
+        <v>46315</v>
+      </c>
+      <c r="B15">
+        <f>COUNTIF(Romaneios!A:A,DadosRomaneios!A15)</f>
+        <v>127</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3CCA1778-A08A-4BBC-894B-FE6DC9B4E104}">
-  <dimension ref="A1:D128"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="1" max="1" width="15.140625" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A1" t="s">
-        <v>168</v>
-      </c>
-      <c r="B1" t="s">
-        <v>170</v>
-      </c>
-      <c r="C1" t="s">
-        <v>171</v>
-      </c>
-      <c r="D1" t="s">
-        <v>172</v>
-      </c>
-    </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A2" s="1">
-        <v>46315</v>
-      </c>
-      <c r="B2" t="s">
-        <v>15</v>
-      </c>
-      <c r="C2">
-        <v>70278</v>
-      </c>
-      <c r="D2">
-        <v>179693</v>
-      </c>
-    </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A3" s="1">
-        <v>46315</v>
-      </c>
-      <c r="B3" t="s">
-        <v>0</v>
-      </c>
-      <c r="D3">
-        <v>179705</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A4" s="1">
-        <v>46315</v>
-      </c>
-      <c r="B4" t="s">
-        <v>115</v>
-      </c>
-      <c r="C4">
-        <v>70279</v>
-      </c>
-      <c r="D4">
-        <v>179692</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A5" s="1">
-        <v>46315</v>
-      </c>
-      <c r="B5" t="s">
-        <v>0</v>
-      </c>
-      <c r="C5">
-        <v>70298</v>
-      </c>
-      <c r="D5">
-        <v>179680</v>
-      </c>
-    </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A6" s="1">
-        <v>46315</v>
-      </c>
-      <c r="B6" t="s">
-        <v>94</v>
-      </c>
-      <c r="D6">
-        <v>179646</v>
-      </c>
-    </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A7" s="1">
-        <v>46315</v>
-      </c>
-      <c r="B7" t="s">
-        <v>190</v>
-      </c>
-      <c r="C7">
-        <v>70059</v>
-      </c>
-      <c r="D7">
-        <v>179565</v>
-      </c>
-    </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A8" s="1">
-        <v>46315</v>
-      </c>
-      <c r="B8" t="s">
-        <v>40</v>
-      </c>
-      <c r="C8">
-        <v>69908</v>
-      </c>
-      <c r="D8">
-        <v>179712</v>
-      </c>
-    </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A9" s="1">
-        <v>46315</v>
-      </c>
-      <c r="B9" t="s">
-        <v>191</v>
-      </c>
-      <c r="C9">
-        <v>68978</v>
-      </c>
-      <c r="D9">
-        <v>179645</v>
-      </c>
-    </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A10" s="1">
-        <v>46315</v>
-      </c>
-      <c r="B10" t="s">
-        <v>48</v>
-      </c>
-      <c r="C10">
-        <v>70201</v>
-      </c>
-      <c r="D10">
-        <v>179653</v>
-      </c>
-    </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A11" s="1">
-        <v>46315</v>
-      </c>
-      <c r="B11" t="s">
-        <v>40</v>
-      </c>
-      <c r="C11">
-        <v>70088</v>
-      </c>
-      <c r="D11">
-        <v>179713</v>
-      </c>
-    </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A12" s="1">
-        <v>46315</v>
-      </c>
-      <c r="B12" t="s">
-        <v>123</v>
-      </c>
-      <c r="C12">
-        <v>69737</v>
-      </c>
-      <c r="D12">
-        <v>179728</v>
-      </c>
-    </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A13" s="1">
-        <v>46315</v>
-      </c>
-      <c r="B13" t="s">
-        <v>69</v>
-      </c>
-      <c r="C13">
-        <v>67824</v>
-      </c>
-      <c r="D13">
-        <v>179694</v>
-      </c>
-    </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A14" s="1">
-        <v>46315</v>
-      </c>
-      <c r="B14" t="s">
-        <v>25</v>
-      </c>
-      <c r="C14">
-        <v>70390</v>
-      </c>
-      <c r="D14">
-        <v>179689</v>
-      </c>
-    </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A15" s="1">
-        <v>46315</v>
-      </c>
-      <c r="B15" t="s">
-        <v>0</v>
-      </c>
-      <c r="D15">
-        <v>179647</v>
-      </c>
-    </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A16" s="1">
-        <v>46315</v>
-      </c>
-      <c r="B16" t="s">
-        <v>69</v>
-      </c>
-      <c r="C16">
-        <v>68147</v>
-      </c>
-      <c r="D16">
-        <v>179695</v>
-      </c>
-    </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A17" s="1">
-        <v>46315</v>
-      </c>
-      <c r="B17" t="s">
-        <v>25</v>
-      </c>
-      <c r="C17">
-        <v>69469</v>
-      </c>
-      <c r="D17">
-        <v>179723</v>
-      </c>
-    </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A18" s="1">
-        <v>46315</v>
-      </c>
-      <c r="B18" t="s">
-        <v>29</v>
-      </c>
-      <c r="C18">
-        <v>66980</v>
-      </c>
-      <c r="D18">
-        <v>176367</v>
-      </c>
-    </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A19" s="1">
-        <v>46315</v>
-      </c>
-      <c r="B19" t="s">
-        <v>187</v>
-      </c>
-      <c r="C19">
-        <v>70197</v>
-      </c>
-      <c r="D19">
-        <v>179658</v>
-      </c>
-    </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A20" s="1">
-        <v>46315</v>
-      </c>
-      <c r="B20" t="s">
-        <v>29</v>
-      </c>
-      <c r="C20">
-        <v>69806</v>
-      </c>
-      <c r="D20">
-        <v>179657</v>
-      </c>
-    </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A21" s="1">
-        <v>46315</v>
-      </c>
-      <c r="B21" t="s">
-        <v>86</v>
-      </c>
-      <c r="D21">
-        <v>179263</v>
-      </c>
-    </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A22" s="1">
-        <v>46315</v>
-      </c>
-      <c r="B22" t="s">
-        <v>29</v>
-      </c>
-      <c r="C22">
-        <v>69802</v>
-      </c>
-      <c r="D22">
-        <v>179674</v>
-      </c>
-    </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A23" s="1">
-        <v>46315</v>
-      </c>
-      <c r="B23" t="s">
-        <v>74</v>
-      </c>
-      <c r="C23">
-        <v>69767</v>
-      </c>
-      <c r="D23">
-        <v>179688</v>
-      </c>
-    </row>
-    <row r="24" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A24" s="1">
-        <v>46315</v>
-      </c>
-      <c r="B24" t="s">
-        <v>29</v>
-      </c>
-      <c r="C24">
-        <v>69814</v>
-      </c>
-      <c r="D24">
-        <v>179659</v>
-      </c>
-    </row>
-    <row r="25" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A25" s="1">
-        <v>46315</v>
-      </c>
-      <c r="B25" t="s">
-        <v>29</v>
-      </c>
-      <c r="D25">
-        <v>179707</v>
-      </c>
-    </row>
-    <row r="26" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A26" s="1">
-        <v>46315</v>
-      </c>
-      <c r="B26" t="s">
-        <v>29</v>
-      </c>
-      <c r="C26">
-        <v>69803</v>
-      </c>
-      <c r="D26">
-        <v>179671</v>
-      </c>
-    </row>
-    <row r="27" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A27" s="1">
-        <v>46315</v>
-      </c>
-      <c r="B27" t="s">
-        <v>86</v>
-      </c>
-      <c r="D27">
-        <v>179703</v>
-      </c>
-    </row>
-    <row r="28" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A28" s="1">
-        <v>46315</v>
-      </c>
-      <c r="B28" t="s">
-        <v>117</v>
-      </c>
-      <c r="D28">
-        <v>179679</v>
-      </c>
-    </row>
-    <row r="29" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A29" s="1">
-        <v>46315</v>
-      </c>
-      <c r="B29" t="s">
-        <v>29</v>
-      </c>
-      <c r="C29">
-        <v>70192</v>
-      </c>
-      <c r="D29">
-        <v>179716</v>
-      </c>
-    </row>
-    <row r="30" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A30" s="1">
-        <v>46315</v>
-      </c>
-      <c r="B30" t="s">
-        <v>117</v>
-      </c>
-      <c r="C30">
-        <v>70157</v>
-      </c>
-      <c r="D30">
-        <v>179690</v>
-      </c>
-    </row>
-    <row r="31" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A31" s="1">
-        <v>46315</v>
-      </c>
-      <c r="B31" t="s">
-        <v>86</v>
-      </c>
-      <c r="C31">
-        <v>69757</v>
-      </c>
-      <c r="D31">
-        <v>179638</v>
-      </c>
-    </row>
-    <row r="32" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A32" s="1">
-        <v>46315</v>
-      </c>
-      <c r="B32" t="s">
-        <v>117</v>
-      </c>
-      <c r="C32">
-        <v>69764</v>
-      </c>
-      <c r="D32">
-        <v>179650</v>
-      </c>
-    </row>
-    <row r="33" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A33" s="1">
-        <v>46315</v>
-      </c>
-      <c r="B33" t="s">
-        <v>29</v>
-      </c>
-      <c r="C33">
-        <v>70288</v>
-      </c>
-      <c r="D33">
-        <v>179655</v>
-      </c>
-    </row>
-    <row r="34" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A34" s="1">
-        <v>46315</v>
-      </c>
-      <c r="B34" t="s">
-        <v>187</v>
-      </c>
-      <c r="C34">
-        <v>68888</v>
-      </c>
-      <c r="D34">
-        <v>179636</v>
-      </c>
-    </row>
-    <row r="35" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A35" s="1">
-        <v>46315</v>
-      </c>
-      <c r="B35" t="s">
-        <v>86</v>
-      </c>
-      <c r="C35">
-        <v>70160</v>
-      </c>
-      <c r="D35">
-        <v>179673</v>
-      </c>
-    </row>
-    <row r="36" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A36" s="1">
-        <v>46315</v>
-      </c>
-      <c r="B36" t="s">
-        <v>187</v>
-      </c>
-      <c r="C36">
-        <v>69391</v>
-      </c>
-      <c r="D36">
-        <v>179639</v>
-      </c>
-    </row>
-    <row r="37" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A37" s="1">
-        <v>46315</v>
-      </c>
-      <c r="B37" t="s">
-        <v>74</v>
-      </c>
-      <c r="C37">
-        <v>69768</v>
-      </c>
-      <c r="D37">
-        <v>179660</v>
-      </c>
-    </row>
-    <row r="38" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A38" s="1">
-        <v>46315</v>
-      </c>
-      <c r="B38" t="s">
-        <v>86</v>
-      </c>
-      <c r="D38">
-        <v>179702</v>
-      </c>
-    </row>
-    <row r="39" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A39" s="1">
-        <v>46315</v>
-      </c>
-      <c r="B39" t="s">
-        <v>118</v>
-      </c>
-      <c r="D39">
-        <v>179706</v>
-      </c>
-    </row>
-    <row r="40" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A40" s="1">
-        <v>46315</v>
-      </c>
-      <c r="B40" t="s">
-        <v>74</v>
-      </c>
-      <c r="C40">
-        <v>69769</v>
-      </c>
-      <c r="D40">
-        <v>179640</v>
-      </c>
-    </row>
-    <row r="41" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A41" s="1">
-        <v>46315</v>
-      </c>
-      <c r="B41" t="s">
-        <v>86</v>
-      </c>
-      <c r="C41">
-        <v>69369</v>
-      </c>
-      <c r="D41">
-        <v>179641</v>
-      </c>
-    </row>
-    <row r="42" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A42" s="1">
-        <v>46315</v>
-      </c>
-      <c r="B42" t="s">
-        <v>86</v>
-      </c>
-      <c r="C42">
-        <v>70154</v>
-      </c>
-      <c r="D42">
-        <v>179637</v>
-      </c>
-    </row>
-    <row r="43" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A43" s="1">
-        <v>46315</v>
-      </c>
-      <c r="B43" t="s">
-        <v>86</v>
-      </c>
-      <c r="C43">
-        <v>69756</v>
-      </c>
-      <c r="D43">
-        <v>179701</v>
-      </c>
-    </row>
-    <row r="44" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A44" s="1">
-        <v>46315</v>
-      </c>
-      <c r="B44" t="s">
-        <v>118</v>
-      </c>
-      <c r="C44">
-        <v>69762</v>
-      </c>
-      <c r="D44">
-        <v>179661</v>
-      </c>
-    </row>
-    <row r="45" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A45" s="1">
-        <v>46315</v>
-      </c>
-      <c r="B45" t="s">
-        <v>86</v>
-      </c>
-      <c r="C45">
-        <v>69754</v>
-      </c>
-      <c r="D45">
-        <v>179722</v>
-      </c>
-    </row>
-    <row r="46" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A46" s="1">
-        <v>46315</v>
-      </c>
-      <c r="B46" t="s">
-        <v>86</v>
-      </c>
-      <c r="C46">
-        <v>70153</v>
-      </c>
-      <c r="D46">
-        <v>179656</v>
-      </c>
-    </row>
-    <row r="47" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A47" s="1">
-        <v>46315</v>
-      </c>
-      <c r="B47" t="s">
-        <v>158</v>
-      </c>
-      <c r="C47">
-        <v>539</v>
-      </c>
-      <c r="D47">
-        <v>534</v>
-      </c>
-    </row>
-    <row r="48" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A48" s="1">
-        <v>46315</v>
-      </c>
-      <c r="B48" t="s">
-        <v>40</v>
-      </c>
-      <c r="C48">
-        <v>549</v>
-      </c>
-      <c r="D48">
-        <v>540</v>
-      </c>
-    </row>
-    <row r="49" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A49" s="1">
-        <v>46315</v>
-      </c>
-      <c r="B49" t="s">
-        <v>24</v>
-      </c>
-      <c r="C49">
-        <v>546</v>
-      </c>
-      <c r="D49">
-        <v>539</v>
-      </c>
-    </row>
-    <row r="50" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A50" s="1">
-        <v>46315</v>
-      </c>
-      <c r="B50" t="s">
-        <v>24</v>
-      </c>
-      <c r="C50">
-        <v>547</v>
-      </c>
-      <c r="D50">
-        <v>538</v>
-      </c>
-    </row>
-    <row r="51" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A51" s="1">
-        <v>46315</v>
-      </c>
-      <c r="B51" t="s">
-        <v>40</v>
-      </c>
-      <c r="C51">
-        <v>548</v>
-      </c>
-      <c r="D51">
-        <v>541</v>
-      </c>
-    </row>
-    <row r="52" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A52" s="1">
-        <v>46315</v>
-      </c>
-      <c r="B52" t="s">
-        <v>192</v>
-      </c>
-      <c r="C52">
-        <v>70163</v>
-      </c>
-      <c r="D52">
-        <v>179642</v>
-      </c>
-    </row>
-    <row r="53" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A53" s="1">
-        <v>46315</v>
-      </c>
-      <c r="B53" t="s">
-        <v>193</v>
-      </c>
-      <c r="C53">
-        <v>69943</v>
-      </c>
-      <c r="D53">
-        <v>179662</v>
-      </c>
-    </row>
-    <row r="54" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A54" s="1">
-        <v>46315</v>
-      </c>
-      <c r="B54" t="s">
-        <v>166</v>
-      </c>
-      <c r="C54">
-        <v>69738</v>
-      </c>
-      <c r="D54">
-        <v>179751</v>
-      </c>
-    </row>
-    <row r="55" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A55" s="1">
-        <v>46315</v>
-      </c>
-      <c r="B55" t="s">
-        <v>194</v>
-      </c>
-      <c r="C55">
-        <v>70464</v>
-      </c>
-      <c r="D55">
-        <v>179779</v>
-      </c>
-    </row>
-    <row r="56" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A56" s="1">
-        <v>46315</v>
-      </c>
-      <c r="B56" t="s">
-        <v>19</v>
-      </c>
-      <c r="C56">
-        <v>69704</v>
-      </c>
-      <c r="D56">
-        <v>179780</v>
-      </c>
-    </row>
-    <row r="57" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A57" s="1">
-        <v>46315</v>
-      </c>
-      <c r="B57" t="s">
-        <v>7</v>
-      </c>
-      <c r="C57">
-        <v>70076</v>
-      </c>
-      <c r="D57">
-        <v>179556</v>
-      </c>
-    </row>
-    <row r="58" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A58" s="1">
-        <v>46315</v>
-      </c>
-      <c r="B58" t="s">
-        <v>19</v>
-      </c>
-      <c r="C58">
-        <v>70128</v>
-      </c>
-      <c r="D58">
-        <v>179616</v>
-      </c>
-    </row>
-    <row r="59" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A59" s="1">
-        <v>46315</v>
-      </c>
-      <c r="B59" t="s">
-        <v>19</v>
-      </c>
-      <c r="C59">
-        <v>70321</v>
-      </c>
-      <c r="D59">
-        <v>179675</v>
-      </c>
-    </row>
-    <row r="60" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A60" s="1">
-        <v>46315</v>
-      </c>
-      <c r="B60" t="s">
-        <v>19</v>
-      </c>
-      <c r="C60">
-        <v>69389</v>
-      </c>
-      <c r="D60">
-        <v>179785</v>
-      </c>
-    </row>
-    <row r="61" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A61" s="1">
-        <v>46315</v>
-      </c>
-      <c r="B61" t="s">
-        <v>19</v>
-      </c>
-      <c r="C61">
-        <v>68822</v>
-      </c>
-      <c r="D61">
-        <v>179783</v>
-      </c>
-    </row>
-    <row r="62" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A62" s="1">
-        <v>46315</v>
-      </c>
-      <c r="B62" t="s">
-        <v>19</v>
-      </c>
-      <c r="C62">
-        <v>69687</v>
-      </c>
-      <c r="D62">
-        <v>179782</v>
-      </c>
-    </row>
-    <row r="63" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A63" s="1">
-        <v>46315</v>
-      </c>
-      <c r="B63" t="s">
-        <v>19</v>
-      </c>
-      <c r="C63">
-        <v>70241</v>
-      </c>
-      <c r="D63">
-        <v>179781</v>
-      </c>
-    </row>
-    <row r="64" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A64" s="1">
-        <v>46315</v>
-      </c>
-      <c r="B64" t="s">
-        <v>89</v>
-      </c>
-      <c r="C64">
-        <v>70072</v>
-      </c>
-      <c r="D64">
-        <v>179681</v>
-      </c>
-    </row>
-    <row r="65" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A65" s="1">
-        <v>46315</v>
-      </c>
-      <c r="B65" t="s">
-        <v>121</v>
-      </c>
-      <c r="C65">
-        <v>70144</v>
-      </c>
-      <c r="D65">
-        <v>179676</v>
-      </c>
-    </row>
-    <row r="66" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A66" s="1">
-        <v>46315</v>
-      </c>
-      <c r="B66" t="s">
-        <v>121</v>
-      </c>
-      <c r="C66">
-        <v>70203</v>
-      </c>
-      <c r="D66">
-        <v>179685</v>
-      </c>
-    </row>
-    <row r="67" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A67" s="1">
-        <v>46315</v>
-      </c>
-      <c r="B67" t="s">
-        <v>121</v>
-      </c>
-      <c r="C67">
-        <v>70236</v>
-      </c>
-      <c r="D67">
-        <v>179684</v>
-      </c>
-    </row>
-    <row r="68" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A68" s="1">
-        <v>46315</v>
-      </c>
-      <c r="B68" t="s">
-        <v>122</v>
-      </c>
-      <c r="C68">
-        <v>70235</v>
-      </c>
-      <c r="D68">
-        <v>179726</v>
-      </c>
-    </row>
-    <row r="69" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A69" s="1">
-        <v>46315</v>
-      </c>
-      <c r="B69" t="s">
-        <v>195</v>
-      </c>
-      <c r="C69">
-        <v>70078</v>
-      </c>
-      <c r="D69">
-        <v>179677</v>
-      </c>
-    </row>
-    <row r="70" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A70" s="1">
-        <v>46315</v>
-      </c>
-      <c r="B70" t="s">
-        <v>122</v>
-      </c>
-      <c r="C70">
-        <v>69839</v>
-      </c>
-      <c r="D70">
-        <v>179678</v>
-      </c>
-    </row>
-    <row r="71" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A71" s="1">
-        <v>46315</v>
-      </c>
-      <c r="B71" t="s">
-        <v>18</v>
-      </c>
-      <c r="D71">
-        <v>18624</v>
-      </c>
-    </row>
-    <row r="72" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A72" s="1">
-        <v>46315</v>
-      </c>
-      <c r="B72" t="s">
-        <v>196</v>
-      </c>
-      <c r="C72">
-        <v>16289</v>
-      </c>
-      <c r="D72">
-        <v>18608</v>
-      </c>
-    </row>
-    <row r="73" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A73" s="1">
-        <v>46315</v>
-      </c>
-      <c r="B73" t="s">
-        <v>196</v>
-      </c>
-      <c r="C73">
-        <v>16293</v>
-      </c>
-      <c r="D73">
-        <v>18612</v>
-      </c>
-    </row>
-    <row r="74" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A74" s="1">
-        <v>46315</v>
-      </c>
-      <c r="B74" t="s">
-        <v>15</v>
-      </c>
-      <c r="C74">
-        <v>16305</v>
-      </c>
-      <c r="D74">
-        <v>18625</v>
-      </c>
-    </row>
-    <row r="75" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A75" s="1">
-        <v>46315</v>
-      </c>
-      <c r="B75" t="s">
-        <v>197</v>
-      </c>
-      <c r="C75">
-        <v>16299</v>
-      </c>
-      <c r="D75">
-        <v>18616</v>
-      </c>
-    </row>
-    <row r="76" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A76" s="1">
-        <v>46315</v>
-      </c>
-      <c r="B76" t="s">
-        <v>15</v>
-      </c>
-      <c r="C76">
-        <v>16300</v>
-      </c>
-      <c r="D76">
-        <v>18621</v>
-      </c>
-    </row>
-    <row r="77" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A77" s="1">
-        <v>46315</v>
-      </c>
-      <c r="B77" t="s">
-        <v>197</v>
-      </c>
-      <c r="D77">
-        <v>18617</v>
-      </c>
-    </row>
-    <row r="78" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A78" s="1">
-        <v>46315</v>
-      </c>
-      <c r="B78" t="s">
-        <v>198</v>
-      </c>
-      <c r="C78">
-        <v>16291</v>
-      </c>
-      <c r="D78">
-        <v>18610</v>
-      </c>
-    </row>
-    <row r="79" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A79" s="1">
-        <v>46315</v>
-      </c>
-      <c r="B79" t="s">
-        <v>196</v>
-      </c>
-      <c r="C79">
-        <v>16292</v>
-      </c>
-      <c r="D79">
-        <v>18611</v>
-      </c>
-    </row>
-    <row r="80" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A80" s="1">
-        <v>46315</v>
-      </c>
-      <c r="B80" t="s">
-        <v>199</v>
-      </c>
-      <c r="C80">
-        <v>16288</v>
-      </c>
-      <c r="D80">
-        <v>18607</v>
-      </c>
-    </row>
-    <row r="81" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A81" s="1">
-        <v>46315</v>
-      </c>
-      <c r="B81" t="s">
-        <v>200</v>
-      </c>
-      <c r="C81">
-        <v>16306</v>
-      </c>
-      <c r="D81">
-        <v>18618</v>
-      </c>
-    </row>
-    <row r="82" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A82" s="1">
-        <v>46315</v>
-      </c>
-      <c r="B82" t="s">
-        <v>15</v>
-      </c>
-      <c r="C82">
-        <v>16302</v>
-      </c>
-      <c r="D82">
-        <v>18622</v>
-      </c>
-    </row>
-    <row r="83" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A83" s="1">
-        <v>46315</v>
-      </c>
-      <c r="B83" t="s">
-        <v>201</v>
-      </c>
-      <c r="C83">
-        <v>16272</v>
-      </c>
-      <c r="D83">
-        <v>18603</v>
-      </c>
-    </row>
-    <row r="84" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A84" s="1">
-        <v>46315</v>
-      </c>
-      <c r="B84" t="s">
-        <v>202</v>
-      </c>
-      <c r="C84">
-        <v>16246</v>
-      </c>
-      <c r="D84">
-        <v>18605</v>
-      </c>
-    </row>
-    <row r="85" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A85" s="1">
-        <v>46315</v>
-      </c>
-      <c r="B85" t="s">
-        <v>203</v>
-      </c>
-      <c r="C85">
-        <v>16295</v>
-      </c>
-      <c r="D85">
-        <v>18614</v>
-      </c>
-    </row>
-    <row r="86" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A86" s="1">
-        <v>46315</v>
-      </c>
-      <c r="B86" t="s">
-        <v>201</v>
-      </c>
-      <c r="C86">
-        <v>16273</v>
-      </c>
-      <c r="D86">
-        <v>18606</v>
-      </c>
-    </row>
-    <row r="87" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A87" s="1">
-        <v>46315</v>
-      </c>
-      <c r="B87" t="s">
-        <v>201</v>
-      </c>
-      <c r="C87">
-        <v>16274</v>
-      </c>
-      <c r="D87">
-        <v>18601</v>
-      </c>
-    </row>
-    <row r="88" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A88" s="1">
-        <v>46315</v>
-      </c>
-      <c r="B88" t="s">
-        <v>15</v>
-      </c>
-      <c r="C88">
-        <v>16294</v>
-      </c>
-      <c r="D88">
-        <v>18613</v>
-      </c>
-    </row>
-    <row r="89" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A89" s="1">
-        <v>46315</v>
-      </c>
-      <c r="B89" t="s">
-        <v>15</v>
-      </c>
-      <c r="C89">
-        <v>16296</v>
-      </c>
-      <c r="D89">
-        <v>18615</v>
-      </c>
-    </row>
-    <row r="90" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A90" s="1">
-        <v>46315</v>
-      </c>
-      <c r="B90" t="s">
-        <v>15</v>
-      </c>
-      <c r="C90">
-        <v>16297</v>
-      </c>
-      <c r="D90">
-        <v>18619</v>
-      </c>
-    </row>
-    <row r="91" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A91" s="1">
-        <v>46315</v>
-      </c>
-      <c r="B91" t="s">
-        <v>23</v>
-      </c>
-      <c r="C91">
-        <v>68823</v>
-      </c>
-      <c r="D91">
-        <v>179790</v>
-      </c>
-    </row>
-    <row r="92" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A92" s="1">
-        <v>46315</v>
-      </c>
-      <c r="B92" t="s">
-        <v>23</v>
-      </c>
-      <c r="D92">
-        <v>179596</v>
-      </c>
-    </row>
-    <row r="93" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A93" s="1">
-        <v>46315</v>
-      </c>
-      <c r="B93" t="s">
-        <v>33</v>
-      </c>
-      <c r="C93">
-        <v>70315</v>
-      </c>
-      <c r="D93">
-        <v>179798</v>
-      </c>
-    </row>
-    <row r="94" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A94" s="1">
-        <v>46315</v>
-      </c>
-      <c r="B94" t="s">
-        <v>69</v>
-      </c>
-      <c r="C94">
-        <v>70453</v>
-      </c>
-      <c r="D94">
-        <v>179753</v>
-      </c>
-    </row>
-    <row r="95" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A95" s="1">
-        <v>46315</v>
-      </c>
-      <c r="B95" t="s">
-        <v>15</v>
-      </c>
-      <c r="C95">
-        <v>69645</v>
-      </c>
-      <c r="D95">
-        <v>179604</v>
-      </c>
-    </row>
-    <row r="96" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A96" s="1">
-        <v>46315</v>
-      </c>
-      <c r="B96" t="s">
-        <v>204</v>
-      </c>
-      <c r="C96">
-        <v>69840</v>
-      </c>
-      <c r="D96">
-        <v>179602</v>
-      </c>
-    </row>
-    <row r="97" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A97" s="1">
-        <v>46315</v>
-      </c>
-      <c r="B97" t="s">
-        <v>205</v>
-      </c>
-      <c r="D97">
-        <v>179368</v>
-      </c>
-    </row>
-    <row r="98" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A98" s="1">
-        <v>46315</v>
-      </c>
-      <c r="B98" t="s">
-        <v>19</v>
-      </c>
-      <c r="D98">
-        <v>179643</v>
-      </c>
-    </row>
-    <row r="99" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A99" s="1">
-        <v>46315</v>
-      </c>
-      <c r="B99" t="s">
-        <v>206</v>
-      </c>
-      <c r="C99">
-        <v>69551</v>
-      </c>
-      <c r="D99">
-        <v>179635</v>
-      </c>
-    </row>
-    <row r="100" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A100" s="1">
-        <v>46315</v>
-      </c>
-      <c r="B100" t="s">
-        <v>19</v>
-      </c>
-      <c r="D100">
-        <v>179767</v>
-      </c>
-    </row>
-    <row r="101" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A101" s="1">
-        <v>46315</v>
-      </c>
-      <c r="B101" t="s">
-        <v>15</v>
-      </c>
-      <c r="C101">
-        <v>70012</v>
-      </c>
-      <c r="D101">
-        <v>179608</v>
-      </c>
-    </row>
-    <row r="102" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A102" s="1">
-        <v>46315</v>
-      </c>
-      <c r="B102" t="s">
-        <v>12</v>
-      </c>
-      <c r="C102">
-        <v>69420</v>
-      </c>
-      <c r="D102">
-        <v>179625</v>
-      </c>
-    </row>
-    <row r="103" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A103" s="1">
-        <v>46315</v>
-      </c>
-      <c r="B103" t="s">
-        <v>19</v>
-      </c>
-      <c r="C103">
-        <v>70456</v>
-      </c>
-      <c r="D103">
-        <v>179784</v>
-      </c>
-    </row>
-    <row r="104" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A104" s="1">
-        <v>46315</v>
-      </c>
-      <c r="B104" t="s">
-        <v>207</v>
-      </c>
-      <c r="C104">
-        <v>70215</v>
-      </c>
-      <c r="D104">
-        <v>179696</v>
-      </c>
-    </row>
-    <row r="105" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A105" s="1">
-        <v>46315</v>
-      </c>
-      <c r="B105" t="s">
-        <v>207</v>
-      </c>
-      <c r="C105">
-        <v>70326</v>
-      </c>
-      <c r="D105">
-        <v>179700</v>
-      </c>
-    </row>
-    <row r="106" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A106" s="1">
-        <v>46315</v>
-      </c>
-      <c r="B106" t="s">
-        <v>8</v>
-      </c>
-      <c r="C106">
-        <v>70406</v>
-      </c>
-      <c r="D106">
-        <v>179826</v>
-      </c>
-    </row>
-    <row r="107" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A107" s="1">
-        <v>46315</v>
-      </c>
-      <c r="B107" t="s">
-        <v>207</v>
-      </c>
-      <c r="C107">
-        <v>70329</v>
-      </c>
-      <c r="D107">
-        <v>179717</v>
-      </c>
-    </row>
-    <row r="108" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A108" s="1">
-        <v>46315</v>
-      </c>
-      <c r="B108" t="s">
-        <v>207</v>
-      </c>
-      <c r="C108">
-        <v>70324</v>
-      </c>
-      <c r="D108">
-        <v>179698</v>
-      </c>
-    </row>
-    <row r="109" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A109" s="1">
-        <v>46315</v>
-      </c>
-      <c r="B109" t="s">
-        <v>207</v>
-      </c>
-      <c r="C109">
-        <v>70328</v>
-      </c>
-      <c r="D109">
-        <v>179714</v>
-      </c>
-    </row>
-    <row r="110" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A110" s="1">
-        <v>46315</v>
-      </c>
-      <c r="B110" t="s">
-        <v>8</v>
-      </c>
-      <c r="C110">
-        <v>70411</v>
-      </c>
-      <c r="D110">
-        <v>179831</v>
-      </c>
-    </row>
-    <row r="111" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A111" s="1">
-        <v>46315</v>
-      </c>
-      <c r="B111" t="s">
-        <v>207</v>
-      </c>
-      <c r="C111">
-        <v>70330</v>
-      </c>
-      <c r="D111">
-        <v>179719</v>
-      </c>
-    </row>
-    <row r="112" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A112" s="1">
-        <v>46315</v>
-      </c>
-      <c r="B112" t="s">
-        <v>207</v>
-      </c>
-      <c r="C112">
-        <v>70325</v>
-      </c>
-      <c r="D112">
-        <v>179699</v>
-      </c>
-    </row>
-    <row r="113" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A113" s="1">
-        <v>46315</v>
-      </c>
-      <c r="B113" t="s">
-        <v>8</v>
-      </c>
-      <c r="C113">
-        <v>70396</v>
-      </c>
-      <c r="D113">
-        <v>179787</v>
-      </c>
-    </row>
-    <row r="114" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A114" s="1">
-        <v>46315</v>
-      </c>
-      <c r="B114" t="s">
-        <v>8</v>
-      </c>
-      <c r="C114">
-        <v>70414</v>
-      </c>
-      <c r="D114">
-        <v>179834</v>
-      </c>
-    </row>
-    <row r="115" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A115" s="1">
-        <v>46315</v>
-      </c>
-      <c r="B115" t="s">
-        <v>8</v>
-      </c>
-      <c r="C115">
-        <v>70400</v>
-      </c>
-      <c r="D115">
-        <v>179819</v>
-      </c>
-    </row>
-    <row r="116" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A116" s="1">
-        <v>46315</v>
-      </c>
-      <c r="B116" t="s">
-        <v>207</v>
-      </c>
-      <c r="C116">
-        <v>70327</v>
-      </c>
-      <c r="D116">
-        <v>179709</v>
-      </c>
-    </row>
-    <row r="117" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A117" s="1">
-        <v>46315</v>
-      </c>
-      <c r="B117" t="s">
-        <v>11</v>
-      </c>
-      <c r="C117">
-        <v>70419</v>
-      </c>
-      <c r="D117">
-        <v>179841</v>
-      </c>
-    </row>
-    <row r="118" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A118" s="1">
-        <v>46315</v>
-      </c>
-      <c r="B118" t="s">
-        <v>8</v>
-      </c>
-      <c r="C118">
-        <v>70416</v>
-      </c>
-      <c r="D118">
-        <v>179836</v>
-      </c>
-    </row>
-    <row r="119" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A119" s="1">
-        <v>46315</v>
-      </c>
-      <c r="B119" t="s">
-        <v>8</v>
-      </c>
-      <c r="C119">
-        <v>70415</v>
-      </c>
-      <c r="D119">
-        <v>179835</v>
-      </c>
-    </row>
-    <row r="120" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A120" s="1">
-        <v>46315</v>
-      </c>
-      <c r="B120" t="s">
-        <v>8</v>
-      </c>
-      <c r="C120">
-        <v>70423</v>
-      </c>
-      <c r="D120">
-        <v>179845</v>
-      </c>
-    </row>
-    <row r="121" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A121" s="1">
-        <v>46315</v>
-      </c>
-      <c r="B121" t="s">
-        <v>11</v>
-      </c>
-      <c r="C121">
-        <v>70421</v>
-      </c>
-      <c r="D121">
-        <v>179838</v>
-      </c>
-    </row>
-    <row r="122" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A122" s="1">
-        <v>46315</v>
-      </c>
-      <c r="B122" t="s">
-        <v>8</v>
-      </c>
-      <c r="C122">
-        <v>70417</v>
-      </c>
-      <c r="D122">
-        <v>179837</v>
-      </c>
-    </row>
-    <row r="123" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A123" s="1">
-        <v>46315</v>
-      </c>
-      <c r="B123" t="s">
-        <v>11</v>
-      </c>
-      <c r="C123">
-        <v>70399</v>
-      </c>
-      <c r="D123">
-        <v>179810</v>
-      </c>
-    </row>
-    <row r="124" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A124" s="1">
-        <v>46315</v>
-      </c>
-      <c r="B124" t="s">
-        <v>11</v>
-      </c>
-      <c r="C124">
-        <v>70348</v>
-      </c>
-      <c r="D124">
-        <v>179774</v>
-      </c>
-    </row>
-    <row r="125" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A125" s="1">
-        <v>46315</v>
-      </c>
-      <c r="B125" t="s">
-        <v>11</v>
-      </c>
-      <c r="C125">
-        <v>70422</v>
-      </c>
-      <c r="D125">
-        <v>179843</v>
-      </c>
-    </row>
-    <row r="126" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A126" s="1">
-        <v>46315</v>
-      </c>
-      <c r="B126" t="s">
-        <v>8</v>
-      </c>
-      <c r="C126">
-        <v>70431</v>
-      </c>
-      <c r="D126">
-        <v>179861</v>
-      </c>
-    </row>
-    <row r="127" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A127" s="1">
-        <v>46315</v>
-      </c>
-      <c r="B127" t="s">
-        <v>11</v>
-      </c>
-      <c r="C127">
-        <v>70436</v>
-      </c>
-      <c r="D127">
-        <v>179839</v>
-      </c>
-    </row>
-    <row r="128" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A128" s="1">
-        <v>46315</v>
-      </c>
-      <c r="B128" t="s">
-        <v>11</v>
-      </c>
-      <c r="C128">
-        <v>70334</v>
-      </c>
-      <c r="D128">
-        <v>179732</v>
-      </c>
-    </row>
-  </sheetData>
-  <autoFilter ref="A1:D128" xr:uid="{3CCA1778-A08A-4BBC-894B-FE6DC9B4E104}"/>
-  <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
-</worksheet>
 </file>
--- a/DadosRomaneios.xlsx
+++ b/DadosRomaneios.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="U:\AcompanhamentoProducao\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2022B6CC-C9D8-4A70-A37C-2BF50ED79ADB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{812A5EDB-2CF6-446C-BA0D-2A38DEB7C0F1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" activeTab="1" xr2:uid="{B6976704-8E51-4052-B60A-5847F95A5AE5}"/>
   </bookViews>
@@ -62,7 +62,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="923" uniqueCount="208">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1046" uniqueCount="214">
   <si>
     <t>ALBERT EINSTEIN</t>
   </si>
@@ -686,6 +686,24 @@
   </si>
   <si>
     <t>TJ RAJ 07</t>
+  </si>
+  <si>
+    <t>AFIP SANTANA</t>
+  </si>
+  <si>
+    <t>CAMINHO DE DAMASCO</t>
+  </si>
+  <si>
+    <t>ARS ENSINO SUPERIOR</t>
+  </si>
+  <si>
+    <t>HORIBA MEDICAL</t>
+  </si>
+  <si>
+    <t>SYNGENTA INDAIATUBA</t>
+  </si>
+  <si>
+    <t>DASA 12.857.736/0001</t>
   </si>
 </sst>
 </file>
@@ -1065,11 +1083,14 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BF29A37F-A1D1-4315-91AB-A952895E1E73}">
-  <dimension ref="A1:E918"/>
+  <dimension ref="A1:E1041"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="12.85546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="5.42578125" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="23.85546875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="8.140625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="8.28515625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -16445,6 +16466,2019 @@
       </c>
       <c r="E918">
         <v>179732</v>
+      </c>
+    </row>
+    <row r="919" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A919" s="1">
+        <v>46316</v>
+      </c>
+      <c r="B919">
+        <v>101</v>
+      </c>
+      <c r="C919" t="s">
+        <v>3</v>
+      </c>
+      <c r="E919">
+        <v>179727</v>
+      </c>
+    </row>
+    <row r="920" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A920" s="1">
+        <v>46316</v>
+      </c>
+      <c r="B920">
+        <v>101</v>
+      </c>
+      <c r="C920" t="s">
+        <v>208</v>
+      </c>
+      <c r="D920">
+        <v>69216</v>
+      </c>
+      <c r="E920">
+        <v>179128</v>
+      </c>
+    </row>
+    <row r="921" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A921" s="1">
+        <v>46316</v>
+      </c>
+      <c r="B921">
+        <v>101</v>
+      </c>
+      <c r="C921" t="s">
+        <v>2</v>
+      </c>
+      <c r="D921">
+        <v>70054</v>
+      </c>
+      <c r="E921">
+        <v>179725</v>
+      </c>
+    </row>
+    <row r="922" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A922" s="1">
+        <v>46316</v>
+      </c>
+      <c r="B922">
+        <v>101</v>
+      </c>
+      <c r="C922" t="s">
+        <v>208</v>
+      </c>
+      <c r="D922">
+        <v>66483</v>
+      </c>
+      <c r="E922">
+        <v>179127</v>
+      </c>
+    </row>
+    <row r="923" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A923" s="1">
+        <v>46316</v>
+      </c>
+      <c r="B923">
+        <v>101</v>
+      </c>
+      <c r="C923" t="s">
+        <v>3</v>
+      </c>
+      <c r="D923">
+        <v>69050</v>
+      </c>
+      <c r="E923">
+        <v>179876</v>
+      </c>
+    </row>
+    <row r="924" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A924" s="1">
+        <v>46316</v>
+      </c>
+      <c r="B924">
+        <v>101</v>
+      </c>
+      <c r="C924" t="s">
+        <v>3</v>
+      </c>
+      <c r="E924">
+        <v>179583</v>
+      </c>
+    </row>
+    <row r="925" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A925" s="1">
+        <v>46316</v>
+      </c>
+      <c r="B925">
+        <v>101</v>
+      </c>
+      <c r="C925" t="s">
+        <v>208</v>
+      </c>
+      <c r="D925">
+        <v>69874</v>
+      </c>
+      <c r="E925">
+        <v>179141</v>
+      </c>
+    </row>
+    <row r="926" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A926" s="1">
+        <v>46316</v>
+      </c>
+      <c r="B926">
+        <v>101</v>
+      </c>
+      <c r="C926" t="s">
+        <v>2</v>
+      </c>
+      <c r="E926">
+        <v>179724</v>
+      </c>
+    </row>
+    <row r="927" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A927" s="1">
+        <v>46316</v>
+      </c>
+      <c r="B927">
+        <v>101</v>
+      </c>
+      <c r="C927" t="s">
+        <v>2</v>
+      </c>
+      <c r="D927">
+        <v>69414</v>
+      </c>
+      <c r="E927">
+        <v>179708</v>
+      </c>
+    </row>
+    <row r="928" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A928" s="1">
+        <v>46316</v>
+      </c>
+      <c r="B928">
+        <v>101</v>
+      </c>
+      <c r="C928" t="s">
+        <v>2</v>
+      </c>
+      <c r="D928">
+        <v>69448</v>
+      </c>
+      <c r="E928">
+        <v>179710</v>
+      </c>
+    </row>
+    <row r="929" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A929" s="1">
+        <v>46316</v>
+      </c>
+      <c r="B929">
+        <v>101</v>
+      </c>
+      <c r="C929" t="s">
+        <v>3</v>
+      </c>
+      <c r="D929">
+        <v>69959</v>
+      </c>
+      <c r="E929">
+        <v>179748</v>
+      </c>
+    </row>
+    <row r="930" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A930" s="1">
+        <v>46316</v>
+      </c>
+      <c r="B930">
+        <v>101</v>
+      </c>
+      <c r="C930" t="s">
+        <v>23</v>
+      </c>
+      <c r="E930">
+        <v>179596</v>
+      </c>
+    </row>
+    <row r="931" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A931" s="1">
+        <v>46316</v>
+      </c>
+      <c r="B931">
+        <v>101</v>
+      </c>
+      <c r="C931" t="s">
+        <v>33</v>
+      </c>
+      <c r="D931">
+        <v>70315</v>
+      </c>
+      <c r="E931">
+        <v>179798</v>
+      </c>
+    </row>
+    <row r="932" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A932" s="1">
+        <v>46316</v>
+      </c>
+      <c r="B932">
+        <v>101</v>
+      </c>
+      <c r="C932" t="s">
+        <v>69</v>
+      </c>
+      <c r="D932">
+        <v>70453</v>
+      </c>
+      <c r="E932">
+        <v>179753</v>
+      </c>
+    </row>
+    <row r="933" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A933" s="1">
+        <v>46316</v>
+      </c>
+      <c r="B933">
+        <v>101</v>
+      </c>
+      <c r="C933" t="s">
+        <v>23</v>
+      </c>
+      <c r="D933">
+        <v>68823</v>
+      </c>
+      <c r="E933">
+        <v>179790</v>
+      </c>
+    </row>
+    <row r="934" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A934" s="1">
+        <v>46316</v>
+      </c>
+      <c r="B934">
+        <v>101</v>
+      </c>
+      <c r="C934" t="s">
+        <v>40</v>
+      </c>
+      <c r="D934">
+        <v>69053</v>
+      </c>
+      <c r="E934">
+        <v>179749</v>
+      </c>
+    </row>
+    <row r="935" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A935" s="1">
+        <v>46316</v>
+      </c>
+      <c r="B935">
+        <v>101</v>
+      </c>
+      <c r="C935" t="s">
+        <v>15</v>
+      </c>
+      <c r="D935">
+        <v>70276</v>
+      </c>
+      <c r="E935">
+        <v>179792</v>
+      </c>
+    </row>
+    <row r="936" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A936" s="1">
+        <v>46316</v>
+      </c>
+      <c r="B936">
+        <v>101</v>
+      </c>
+      <c r="C936" t="s">
+        <v>90</v>
+      </c>
+      <c r="D936">
+        <v>70161</v>
+      </c>
+      <c r="E936">
+        <v>179750</v>
+      </c>
+    </row>
+    <row r="937" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A937" s="1">
+        <v>46316</v>
+      </c>
+      <c r="B937">
+        <v>101</v>
+      </c>
+      <c r="C937" t="s">
+        <v>24</v>
+      </c>
+      <c r="D937">
+        <v>70259</v>
+      </c>
+      <c r="E937">
+        <v>179885</v>
+      </c>
+    </row>
+    <row r="938" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A938" s="1">
+        <v>46316</v>
+      </c>
+      <c r="B938">
+        <v>101</v>
+      </c>
+      <c r="C938" t="s">
+        <v>25</v>
+      </c>
+      <c r="D938">
+        <v>69470</v>
+      </c>
+      <c r="E938">
+        <v>179863</v>
+      </c>
+    </row>
+    <row r="939" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A939" s="1">
+        <v>46316</v>
+      </c>
+      <c r="B939">
+        <v>101</v>
+      </c>
+      <c r="C939" t="s">
+        <v>209</v>
+      </c>
+      <c r="D939">
+        <v>70226</v>
+      </c>
+      <c r="E939">
+        <v>179743</v>
+      </c>
+    </row>
+    <row r="940" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A940" s="1">
+        <v>46316</v>
+      </c>
+      <c r="B940">
+        <v>101</v>
+      </c>
+      <c r="C940" t="s">
+        <v>111</v>
+      </c>
+      <c r="D940">
+        <v>69297</v>
+      </c>
+      <c r="E940">
+        <v>179220</v>
+      </c>
+    </row>
+    <row r="941" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A941" s="1">
+        <v>46316</v>
+      </c>
+      <c r="B941">
+        <v>101</v>
+      </c>
+      <c r="C941" t="s">
+        <v>180</v>
+      </c>
+      <c r="D941">
+        <v>70234</v>
+      </c>
+      <c r="E941">
+        <v>179851</v>
+      </c>
+    </row>
+    <row r="942" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A942" s="1">
+        <v>46316</v>
+      </c>
+      <c r="B942">
+        <v>101</v>
+      </c>
+      <c r="C942" t="s">
+        <v>180</v>
+      </c>
+      <c r="E942">
+        <v>179820</v>
+      </c>
+    </row>
+    <row r="943" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A943" s="1">
+        <v>46316</v>
+      </c>
+      <c r="B943">
+        <v>101</v>
+      </c>
+      <c r="C943" t="s">
+        <v>111</v>
+      </c>
+      <c r="E943">
+        <v>179800</v>
+      </c>
+    </row>
+    <row r="944" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A944" s="1">
+        <v>46316</v>
+      </c>
+      <c r="B944">
+        <v>101</v>
+      </c>
+      <c r="C944" t="s">
+        <v>111</v>
+      </c>
+      <c r="D944">
+        <v>70371</v>
+      </c>
+      <c r="E944">
+        <v>179856</v>
+      </c>
+    </row>
+    <row r="945" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A945" s="1">
+        <v>46316</v>
+      </c>
+      <c r="B945">
+        <v>101</v>
+      </c>
+      <c r="C945" t="s">
+        <v>56</v>
+      </c>
+      <c r="D945">
+        <v>68470</v>
+      </c>
+      <c r="E945">
+        <v>179745</v>
+      </c>
+    </row>
+    <row r="946" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A946" s="1">
+        <v>46316</v>
+      </c>
+      <c r="B946">
+        <v>101</v>
+      </c>
+      <c r="C946" t="s">
+        <v>26</v>
+      </c>
+      <c r="E946">
+        <v>179865</v>
+      </c>
+    </row>
+    <row r="947" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A947" s="1">
+        <v>46316</v>
+      </c>
+      <c r="B947">
+        <v>101</v>
+      </c>
+      <c r="C947" t="s">
+        <v>26</v>
+      </c>
+      <c r="D947">
+        <v>70225</v>
+      </c>
+      <c r="E947">
+        <v>179747</v>
+      </c>
+    </row>
+    <row r="948" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A948" s="1">
+        <v>46316</v>
+      </c>
+      <c r="B948">
+        <v>101</v>
+      </c>
+      <c r="C948" t="s">
+        <v>23</v>
+      </c>
+      <c r="D948">
+        <v>69838</v>
+      </c>
+      <c r="E948">
+        <v>179886</v>
+      </c>
+    </row>
+    <row r="949" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A949" s="1">
+        <v>46316</v>
+      </c>
+      <c r="B949">
+        <v>101</v>
+      </c>
+      <c r="C949" t="s">
+        <v>26</v>
+      </c>
+      <c r="D949">
+        <v>70319</v>
+      </c>
+      <c r="E949">
+        <v>179864</v>
+      </c>
+    </row>
+    <row r="950" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A950" s="1">
+        <v>46316</v>
+      </c>
+      <c r="B950">
+        <v>101</v>
+      </c>
+      <c r="C950" t="s">
+        <v>45</v>
+      </c>
+      <c r="D950">
+        <v>68793</v>
+      </c>
+      <c r="E950">
+        <v>179744</v>
+      </c>
+    </row>
+    <row r="951" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A951" s="1">
+        <v>46316</v>
+      </c>
+      <c r="B951">
+        <v>101</v>
+      </c>
+      <c r="C951" t="s">
+        <v>44</v>
+      </c>
+      <c r="E951">
+        <v>179853</v>
+      </c>
+    </row>
+    <row r="952" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A952" s="1">
+        <v>46316</v>
+      </c>
+      <c r="B952">
+        <v>101</v>
+      </c>
+      <c r="C952" t="s">
+        <v>0</v>
+      </c>
+      <c r="D952">
+        <v>70065</v>
+      </c>
+      <c r="E952">
+        <v>179524</v>
+      </c>
+    </row>
+    <row r="953" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A953" s="1">
+        <v>46316</v>
+      </c>
+      <c r="B953">
+        <v>101</v>
+      </c>
+      <c r="C953" t="s">
+        <v>15</v>
+      </c>
+      <c r="E953">
+        <v>179883</v>
+      </c>
+    </row>
+    <row r="954" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A954" s="1">
+        <v>46316</v>
+      </c>
+      <c r="B954">
+        <v>101</v>
+      </c>
+      <c r="C954" t="s">
+        <v>15</v>
+      </c>
+      <c r="D954">
+        <v>68923</v>
+      </c>
+      <c r="E954">
+        <v>179742</v>
+      </c>
+    </row>
+    <row r="955" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A955" s="1">
+        <v>46316</v>
+      </c>
+      <c r="B955">
+        <v>101</v>
+      </c>
+      <c r="C955" t="s">
+        <v>0</v>
+      </c>
+      <c r="D955">
+        <v>70284</v>
+      </c>
+      <c r="E955">
+        <v>179888</v>
+      </c>
+    </row>
+    <row r="956" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A956" s="1">
+        <v>46316</v>
+      </c>
+      <c r="B956">
+        <v>101</v>
+      </c>
+      <c r="C956" t="s">
+        <v>0</v>
+      </c>
+      <c r="D956">
+        <v>70108</v>
+      </c>
+      <c r="E956">
+        <v>179880</v>
+      </c>
+    </row>
+    <row r="957" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A957" s="1">
+        <v>46316</v>
+      </c>
+      <c r="B957">
+        <v>101</v>
+      </c>
+      <c r="C957" t="s">
+        <v>0</v>
+      </c>
+      <c r="D957">
+        <v>70117</v>
+      </c>
+      <c r="E957">
+        <v>179889</v>
+      </c>
+    </row>
+    <row r="958" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A958" s="1">
+        <v>46316</v>
+      </c>
+      <c r="B958">
+        <v>101</v>
+      </c>
+      <c r="C958" t="s">
+        <v>0</v>
+      </c>
+      <c r="D958">
+        <v>70282</v>
+      </c>
+      <c r="E958">
+        <v>179882</v>
+      </c>
+    </row>
+    <row r="959" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A959" s="1">
+        <v>46316</v>
+      </c>
+      <c r="B959">
+        <v>101</v>
+      </c>
+      <c r="C959" t="s">
+        <v>32</v>
+      </c>
+      <c r="E959">
+        <v>179802</v>
+      </c>
+    </row>
+    <row r="960" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A960" s="1">
+        <v>46316</v>
+      </c>
+      <c r="B960">
+        <v>101</v>
+      </c>
+      <c r="C960" t="s">
+        <v>15</v>
+      </c>
+      <c r="E960">
+        <v>179893</v>
+      </c>
+    </row>
+    <row r="961" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A961" s="1">
+        <v>46316</v>
+      </c>
+      <c r="B961">
+        <v>101</v>
+      </c>
+      <c r="C961" t="s">
+        <v>15</v>
+      </c>
+      <c r="D961">
+        <v>70380</v>
+      </c>
+      <c r="E961">
+        <v>179795</v>
+      </c>
+    </row>
+    <row r="962" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A962" s="1">
+        <v>46316</v>
+      </c>
+      <c r="B962">
+        <v>101</v>
+      </c>
+      <c r="C962" t="s">
+        <v>15</v>
+      </c>
+      <c r="D962">
+        <v>70367</v>
+      </c>
+      <c r="E962">
+        <v>179754</v>
+      </c>
+    </row>
+    <row r="963" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A963" s="1">
+        <v>46316</v>
+      </c>
+      <c r="B963">
+        <v>101</v>
+      </c>
+      <c r="C963" t="s">
+        <v>210</v>
+      </c>
+      <c r="D963">
+        <v>70309</v>
+      </c>
+      <c r="E963">
+        <v>179849</v>
+      </c>
+    </row>
+    <row r="964" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A964" s="1">
+        <v>46316</v>
+      </c>
+      <c r="B964">
+        <v>101</v>
+      </c>
+      <c r="C964" t="s">
+        <v>177</v>
+      </c>
+      <c r="D964">
+        <v>70369</v>
+      </c>
+      <c r="E964">
+        <v>179801</v>
+      </c>
+    </row>
+    <row r="965" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A965" s="1">
+        <v>46316</v>
+      </c>
+      <c r="B965">
+        <v>101</v>
+      </c>
+      <c r="C965" t="s">
+        <v>181</v>
+      </c>
+      <c r="D965">
+        <v>70239</v>
+      </c>
+      <c r="E965">
+        <v>179796</v>
+      </c>
+    </row>
+    <row r="966" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A966" s="1">
+        <v>46316</v>
+      </c>
+      <c r="B966">
+        <v>101</v>
+      </c>
+      <c r="C966" t="s">
+        <v>15</v>
+      </c>
+      <c r="E966">
+        <v>179852</v>
+      </c>
+    </row>
+    <row r="967" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A967" s="1">
+        <v>46316</v>
+      </c>
+      <c r="B967">
+        <v>101</v>
+      </c>
+      <c r="C967" t="s">
+        <v>20</v>
+      </c>
+      <c r="D967">
+        <v>70246</v>
+      </c>
+      <c r="E967">
+        <v>179901</v>
+      </c>
+    </row>
+    <row r="968" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A968" s="1">
+        <v>46316</v>
+      </c>
+      <c r="B968">
+        <v>101</v>
+      </c>
+      <c r="C968" t="s">
+        <v>28</v>
+      </c>
+      <c r="D968">
+        <v>70368</v>
+      </c>
+      <c r="E968">
+        <v>179737</v>
+      </c>
+    </row>
+    <row r="969" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A969" s="1">
+        <v>46316</v>
+      </c>
+      <c r="B969">
+        <v>101</v>
+      </c>
+      <c r="C969" t="s">
+        <v>28</v>
+      </c>
+      <c r="D969">
+        <v>70366</v>
+      </c>
+      <c r="E969">
+        <v>179738</v>
+      </c>
+    </row>
+    <row r="970" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A970" s="1">
+        <v>46316</v>
+      </c>
+      <c r="B970">
+        <v>101</v>
+      </c>
+      <c r="C970" t="s">
+        <v>28</v>
+      </c>
+      <c r="D970">
+        <v>70364</v>
+      </c>
+      <c r="E970">
+        <v>179887</v>
+      </c>
+    </row>
+    <row r="971" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A971" s="1">
+        <v>46316</v>
+      </c>
+      <c r="B971">
+        <v>101</v>
+      </c>
+      <c r="C971" t="s">
+        <v>28</v>
+      </c>
+      <c r="D971">
+        <v>70375</v>
+      </c>
+      <c r="E971">
+        <v>179740</v>
+      </c>
+    </row>
+    <row r="972" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A972" s="1">
+        <v>46316</v>
+      </c>
+      <c r="B972">
+        <v>101</v>
+      </c>
+      <c r="C972" t="s">
+        <v>28</v>
+      </c>
+      <c r="D972">
+        <v>70365</v>
+      </c>
+      <c r="E972">
+        <v>179752</v>
+      </c>
+    </row>
+    <row r="973" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A973" s="1">
+        <v>46316</v>
+      </c>
+      <c r="B973">
+        <v>101</v>
+      </c>
+      <c r="C973" t="s">
+        <v>28</v>
+      </c>
+      <c r="D973">
+        <v>70378</v>
+      </c>
+      <c r="E973">
+        <v>179741</v>
+      </c>
+    </row>
+    <row r="974" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A974" s="1">
+        <v>46316</v>
+      </c>
+      <c r="B974">
+        <v>101</v>
+      </c>
+      <c r="C974" t="s">
+        <v>28</v>
+      </c>
+      <c r="D974">
+        <v>70370</v>
+      </c>
+      <c r="E974">
+        <v>179736</v>
+      </c>
+    </row>
+    <row r="975" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A975" s="1">
+        <v>46316</v>
+      </c>
+      <c r="B975">
+        <v>101</v>
+      </c>
+      <c r="C975" t="s">
+        <v>28</v>
+      </c>
+      <c r="D975">
+        <v>70372</v>
+      </c>
+      <c r="E975">
+        <v>179734</v>
+      </c>
+    </row>
+    <row r="976" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A976" s="1">
+        <v>46316</v>
+      </c>
+      <c r="B976">
+        <v>101</v>
+      </c>
+      <c r="C976" t="s">
+        <v>28</v>
+      </c>
+      <c r="D976">
+        <v>70373</v>
+      </c>
+      <c r="E976">
+        <v>179739</v>
+      </c>
+    </row>
+    <row r="977" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A977" s="1">
+        <v>46316</v>
+      </c>
+      <c r="B977">
+        <v>101</v>
+      </c>
+      <c r="C977" t="s">
+        <v>28</v>
+      </c>
+      <c r="D977">
+        <v>70374</v>
+      </c>
+      <c r="E977">
+        <v>179733</v>
+      </c>
+    </row>
+    <row r="978" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A978" s="1">
+        <v>46316</v>
+      </c>
+      <c r="B978">
+        <v>101</v>
+      </c>
+      <c r="C978" t="s">
+        <v>0</v>
+      </c>
+      <c r="D978">
+        <v>66212</v>
+      </c>
+      <c r="E978">
+        <v>179111</v>
+      </c>
+    </row>
+    <row r="979" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A979" s="1">
+        <v>46316</v>
+      </c>
+      <c r="B979">
+        <v>101</v>
+      </c>
+      <c r="C979" t="s">
+        <v>0</v>
+      </c>
+      <c r="D979">
+        <v>69725</v>
+      </c>
+      <c r="E979">
+        <v>179867</v>
+      </c>
+    </row>
+    <row r="980" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A980" s="1">
+        <v>46316</v>
+      </c>
+      <c r="B980">
+        <v>101</v>
+      </c>
+      <c r="C980" t="s">
+        <v>0</v>
+      </c>
+      <c r="D980">
+        <v>69048</v>
+      </c>
+      <c r="E980">
+        <v>179550</v>
+      </c>
+    </row>
+    <row r="981" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A981" s="1">
+        <v>46316</v>
+      </c>
+      <c r="B981">
+        <v>101</v>
+      </c>
+      <c r="C981" t="s">
+        <v>0</v>
+      </c>
+      <c r="E981">
+        <v>179758</v>
+      </c>
+    </row>
+    <row r="982" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A982" s="1">
+        <v>46316</v>
+      </c>
+      <c r="B982">
+        <v>101</v>
+      </c>
+      <c r="C982" t="s">
+        <v>0</v>
+      </c>
+      <c r="E982">
+        <v>179559</v>
+      </c>
+    </row>
+    <row r="983" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A983" s="1">
+        <v>46316</v>
+      </c>
+      <c r="B983">
+        <v>101</v>
+      </c>
+      <c r="C983" t="s">
+        <v>0</v>
+      </c>
+      <c r="D983">
+        <v>69866</v>
+      </c>
+      <c r="E983">
+        <v>179869</v>
+      </c>
+    </row>
+    <row r="984" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A984" s="1">
+        <v>46316</v>
+      </c>
+      <c r="B984">
+        <v>101</v>
+      </c>
+      <c r="C984" t="s">
+        <v>0</v>
+      </c>
+      <c r="E984">
+        <v>179804</v>
+      </c>
+    </row>
+    <row r="985" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A985" s="1">
+        <v>46316</v>
+      </c>
+      <c r="B985">
+        <v>101</v>
+      </c>
+      <c r="C985" t="s">
+        <v>0</v>
+      </c>
+      <c r="E985">
+        <v>179815</v>
+      </c>
+    </row>
+    <row r="986" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A986" s="1">
+        <v>46316</v>
+      </c>
+      <c r="B986">
+        <v>101</v>
+      </c>
+      <c r="C986" t="s">
+        <v>0</v>
+      </c>
+      <c r="E986">
+        <v>179764</v>
+      </c>
+    </row>
+    <row r="987" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A987" s="1">
+        <v>46316</v>
+      </c>
+      <c r="B987">
+        <v>101</v>
+      </c>
+      <c r="C987" t="s">
+        <v>0</v>
+      </c>
+      <c r="D987">
+        <v>70097</v>
+      </c>
+      <c r="E987">
+        <v>179760</v>
+      </c>
+    </row>
+    <row r="988" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A988" s="1">
+        <v>46316</v>
+      </c>
+      <c r="B988">
+        <v>101</v>
+      </c>
+      <c r="C988" t="s">
+        <v>0</v>
+      </c>
+      <c r="E988">
+        <v>179814</v>
+      </c>
+    </row>
+    <row r="989" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A989" s="1">
+        <v>46316</v>
+      </c>
+      <c r="B989">
+        <v>101</v>
+      </c>
+      <c r="C989" t="s">
+        <v>0</v>
+      </c>
+      <c r="D989">
+        <v>70095</v>
+      </c>
+      <c r="E989">
+        <v>179761</v>
+      </c>
+    </row>
+    <row r="990" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A990" s="1">
+        <v>46316</v>
+      </c>
+      <c r="B990">
+        <v>101</v>
+      </c>
+      <c r="C990" t="s">
+        <v>0</v>
+      </c>
+      <c r="E990">
+        <v>179816</v>
+      </c>
+    </row>
+    <row r="991" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A991" s="1">
+        <v>46316</v>
+      </c>
+      <c r="B991">
+        <v>101</v>
+      </c>
+      <c r="C991" t="s">
+        <v>0</v>
+      </c>
+      <c r="D991">
+        <v>70126</v>
+      </c>
+      <c r="E991">
+        <v>179762</v>
+      </c>
+    </row>
+    <row r="992" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A992" s="1">
+        <v>46316</v>
+      </c>
+      <c r="B992">
+        <v>101</v>
+      </c>
+      <c r="C992" t="s">
+        <v>0</v>
+      </c>
+      <c r="D992">
+        <v>69845</v>
+      </c>
+      <c r="E992">
+        <v>179868</v>
+      </c>
+    </row>
+    <row r="993" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A993" s="1">
+        <v>46316</v>
+      </c>
+      <c r="B993">
+        <v>101</v>
+      </c>
+      <c r="C993" t="s">
+        <v>0</v>
+      </c>
+      <c r="D993">
+        <v>70287</v>
+      </c>
+      <c r="E993">
+        <v>179813</v>
+      </c>
+    </row>
+    <row r="994" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A994" s="1">
+        <v>46316</v>
+      </c>
+      <c r="B994">
+        <v>101</v>
+      </c>
+      <c r="C994" t="s">
+        <v>0</v>
+      </c>
+      <c r="D994">
+        <v>70100</v>
+      </c>
+      <c r="E994">
+        <v>179763</v>
+      </c>
+    </row>
+    <row r="995" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A995" s="1">
+        <v>46316</v>
+      </c>
+      <c r="B995">
+        <v>101</v>
+      </c>
+      <c r="C995" t="s">
+        <v>0</v>
+      </c>
+      <c r="D995">
+        <v>70179</v>
+      </c>
+      <c r="E995">
+        <v>179817</v>
+      </c>
+    </row>
+    <row r="996" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A996" s="1">
+        <v>46316</v>
+      </c>
+      <c r="B996">
+        <v>101</v>
+      </c>
+      <c r="C996" t="s">
+        <v>0</v>
+      </c>
+      <c r="D996">
+        <v>69882</v>
+      </c>
+      <c r="E996">
+        <v>179866</v>
+      </c>
+    </row>
+    <row r="997" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A997" s="1">
+        <v>46316</v>
+      </c>
+      <c r="B997">
+        <v>101</v>
+      </c>
+      <c r="C997" t="s">
+        <v>0</v>
+      </c>
+      <c r="D997">
+        <v>70290</v>
+      </c>
+      <c r="E997">
+        <v>179809</v>
+      </c>
+    </row>
+    <row r="998" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A998" s="1">
+        <v>46316</v>
+      </c>
+      <c r="B998">
+        <v>101</v>
+      </c>
+      <c r="C998" t="s">
+        <v>0</v>
+      </c>
+      <c r="D998">
+        <v>70124</v>
+      </c>
+      <c r="E998">
+        <v>179812</v>
+      </c>
+    </row>
+    <row r="999" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A999" s="1">
+        <v>46316</v>
+      </c>
+      <c r="B999">
+        <v>101</v>
+      </c>
+      <c r="C999" t="s">
+        <v>0</v>
+      </c>
+      <c r="D999">
+        <v>70098</v>
+      </c>
+      <c r="E999">
+        <v>179759</v>
+      </c>
+    </row>
+    <row r="1000" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1000" s="1">
+        <v>46316</v>
+      </c>
+      <c r="B1000">
+        <v>101</v>
+      </c>
+      <c r="C1000" t="s">
+        <v>0</v>
+      </c>
+      <c r="D1000">
+        <v>70222</v>
+      </c>
+      <c r="E1000">
+        <v>179806</v>
+      </c>
+    </row>
+    <row r="1001" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1001" s="1">
+        <v>46316</v>
+      </c>
+      <c r="B1001">
+        <v>101</v>
+      </c>
+      <c r="C1001" t="s">
+        <v>0</v>
+      </c>
+      <c r="D1001">
+        <v>70101</v>
+      </c>
+      <c r="E1001">
+        <v>179811</v>
+      </c>
+    </row>
+    <row r="1002" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1002" s="1">
+        <v>46316</v>
+      </c>
+      <c r="B1002">
+        <v>101</v>
+      </c>
+      <c r="C1002" t="s">
+        <v>0</v>
+      </c>
+      <c r="D1002">
+        <v>70224</v>
+      </c>
+      <c r="E1002">
+        <v>179805</v>
+      </c>
+    </row>
+    <row r="1003" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1003" s="1">
+        <v>46316</v>
+      </c>
+      <c r="B1003">
+        <v>101</v>
+      </c>
+      <c r="C1003" t="s">
+        <v>2</v>
+      </c>
+      <c r="E1003">
+        <v>179720</v>
+      </c>
+    </row>
+    <row r="1004" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1004" s="1">
+        <v>46316</v>
+      </c>
+      <c r="B1004">
+        <v>101</v>
+      </c>
+      <c r="C1004" t="s">
+        <v>85</v>
+      </c>
+      <c r="D1004">
+        <v>69930</v>
+      </c>
+      <c r="E1004">
+        <v>179919</v>
+      </c>
+    </row>
+    <row r="1005" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1005" s="1">
+        <v>46316</v>
+      </c>
+      <c r="B1005">
+        <v>101</v>
+      </c>
+      <c r="C1005" t="s">
+        <v>85</v>
+      </c>
+      <c r="D1005">
+        <v>70320</v>
+      </c>
+      <c r="E1005">
+        <v>179916</v>
+      </c>
+    </row>
+    <row r="1006" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1006" s="1">
+        <v>46316</v>
+      </c>
+      <c r="B1006">
+        <v>101</v>
+      </c>
+      <c r="C1006" t="s">
+        <v>71</v>
+      </c>
+      <c r="D1006">
+        <v>70457</v>
+      </c>
+      <c r="E1006">
+        <v>179799</v>
+      </c>
+    </row>
+    <row r="1007" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1007" s="1">
+        <v>46316</v>
+      </c>
+      <c r="B1007">
+        <v>101</v>
+      </c>
+      <c r="C1007" t="s">
+        <v>71</v>
+      </c>
+      <c r="E1007">
+        <v>179943</v>
+      </c>
+    </row>
+    <row r="1008" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1008" s="1">
+        <v>46316</v>
+      </c>
+      <c r="B1008">
+        <v>101</v>
+      </c>
+      <c r="C1008" t="s">
+        <v>183</v>
+      </c>
+      <c r="E1008">
+        <v>179721</v>
+      </c>
+    </row>
+    <row r="1009" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1009" s="1">
+        <v>46316</v>
+      </c>
+      <c r="B1009">
+        <v>101</v>
+      </c>
+      <c r="C1009" t="s">
+        <v>62</v>
+      </c>
+      <c r="D1009">
+        <v>70185</v>
+      </c>
+      <c r="E1009">
+        <v>179945</v>
+      </c>
+    </row>
+    <row r="1010" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1010" s="1">
+        <v>46316</v>
+      </c>
+      <c r="B1010">
+        <v>101</v>
+      </c>
+      <c r="C1010" t="s">
+        <v>211</v>
+      </c>
+      <c r="D1010">
+        <v>70090</v>
+      </c>
+      <c r="E1010">
+        <v>179793</v>
+      </c>
+    </row>
+    <row r="1011" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1011" s="1">
+        <v>46316</v>
+      </c>
+      <c r="B1011">
+        <v>101</v>
+      </c>
+      <c r="C1011" t="s">
+        <v>75</v>
+      </c>
+      <c r="D1011">
+        <v>70384</v>
+      </c>
+      <c r="E1011">
+        <v>179879</v>
+      </c>
+    </row>
+    <row r="1012" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1012" s="1">
+        <v>46316</v>
+      </c>
+      <c r="B1012">
+        <v>101</v>
+      </c>
+      <c r="C1012" t="s">
+        <v>19</v>
+      </c>
+      <c r="D1012">
+        <v>68434</v>
+      </c>
+      <c r="E1012">
+        <v>178274</v>
+      </c>
+    </row>
+    <row r="1013" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1013" s="1">
+        <v>46316</v>
+      </c>
+      <c r="B1013">
+        <v>101</v>
+      </c>
+      <c r="C1013" t="s">
+        <v>156</v>
+      </c>
+      <c r="E1013">
+        <v>179871</v>
+      </c>
+    </row>
+    <row r="1014" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1014" s="1">
+        <v>46316</v>
+      </c>
+      <c r="B1014">
+        <v>101</v>
+      </c>
+      <c r="C1014" t="s">
+        <v>212</v>
+      </c>
+      <c r="D1014">
+        <v>67672</v>
+      </c>
+      <c r="E1014">
+        <v>179547</v>
+      </c>
+    </row>
+    <row r="1015" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1015" s="1">
+        <v>46316</v>
+      </c>
+      <c r="B1015">
+        <v>101</v>
+      </c>
+      <c r="C1015" t="s">
+        <v>74</v>
+      </c>
+      <c r="D1015">
+        <v>70280</v>
+      </c>
+      <c r="E1015">
+        <v>179926</v>
+      </c>
+    </row>
+    <row r="1016" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1016" s="1">
+        <v>46316</v>
+      </c>
+      <c r="B1016">
+        <v>101</v>
+      </c>
+      <c r="C1016" t="s">
+        <v>0</v>
+      </c>
+      <c r="D1016">
+        <v>66744</v>
+      </c>
+      <c r="E1016">
+        <v>178891</v>
+      </c>
+    </row>
+    <row r="1017" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1017" s="1">
+        <v>46316</v>
+      </c>
+      <c r="B1017">
+        <v>101</v>
+      </c>
+      <c r="C1017" t="s">
+        <v>0</v>
+      </c>
+      <c r="D1017">
+        <v>69650</v>
+      </c>
+      <c r="E1017">
+        <v>179599</v>
+      </c>
+    </row>
+    <row r="1018" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1018" s="1">
+        <v>46316</v>
+      </c>
+      <c r="B1018">
+        <v>101</v>
+      </c>
+      <c r="C1018" t="s">
+        <v>0</v>
+      </c>
+      <c r="D1018">
+        <v>68821</v>
+      </c>
+      <c r="E1018">
+        <v>179551</v>
+      </c>
+    </row>
+    <row r="1019" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1019" s="1">
+        <v>46316</v>
+      </c>
+      <c r="B1019">
+        <v>101</v>
+      </c>
+      <c r="C1019" t="s">
+        <v>34</v>
+      </c>
+      <c r="D1019">
+        <v>70338</v>
+      </c>
+      <c r="E1019">
+        <v>179766</v>
+      </c>
+    </row>
+    <row r="1020" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1020" s="1">
+        <v>46316</v>
+      </c>
+      <c r="B1020">
+        <v>101</v>
+      </c>
+      <c r="C1020" t="s">
+        <v>152</v>
+      </c>
+      <c r="D1020">
+        <v>70425</v>
+      </c>
+      <c r="E1020">
+        <v>179847</v>
+      </c>
+    </row>
+    <row r="1021" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1021" s="1">
+        <v>46316</v>
+      </c>
+      <c r="B1021">
+        <v>101</v>
+      </c>
+      <c r="C1021" t="s">
+        <v>34</v>
+      </c>
+      <c r="D1021">
+        <v>70438</v>
+      </c>
+      <c r="E1021">
+        <v>179875</v>
+      </c>
+    </row>
+    <row r="1022" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1022" s="1">
+        <v>46316</v>
+      </c>
+      <c r="B1022">
+        <v>101</v>
+      </c>
+      <c r="C1022" t="s">
+        <v>7</v>
+      </c>
+      <c r="D1022">
+        <v>70446</v>
+      </c>
+      <c r="E1022">
+        <v>179898</v>
+      </c>
+    </row>
+    <row r="1023" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1023" s="1">
+        <v>46316</v>
+      </c>
+      <c r="B1023">
+        <v>101</v>
+      </c>
+      <c r="C1023" t="s">
+        <v>152</v>
+      </c>
+      <c r="D1023">
+        <v>70401</v>
+      </c>
+      <c r="E1023">
+        <v>179821</v>
+      </c>
+    </row>
+    <row r="1024" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1024" s="1">
+        <v>46316</v>
+      </c>
+      <c r="B1024">
+        <v>101</v>
+      </c>
+      <c r="C1024" t="s">
+        <v>9</v>
+      </c>
+      <c r="D1024">
+        <v>70429</v>
+      </c>
+      <c r="E1024">
+        <v>179858</v>
+      </c>
+    </row>
+    <row r="1025" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1025" s="1">
+        <v>46316</v>
+      </c>
+      <c r="B1025">
+        <v>101</v>
+      </c>
+      <c r="C1025" t="s">
+        <v>152</v>
+      </c>
+      <c r="D1025">
+        <v>70407</v>
+      </c>
+      <c r="E1025">
+        <v>179827</v>
+      </c>
+    </row>
+    <row r="1026" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1026" s="1">
+        <v>46316</v>
+      </c>
+      <c r="B1026">
+        <v>101</v>
+      </c>
+      <c r="C1026" t="s">
+        <v>34</v>
+      </c>
+      <c r="D1026">
+        <v>70343</v>
+      </c>
+      <c r="E1026">
+        <v>179769</v>
+      </c>
+    </row>
+    <row r="1027" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1027" s="1">
+        <v>46316</v>
+      </c>
+      <c r="B1027">
+        <v>101</v>
+      </c>
+      <c r="C1027" t="s">
+        <v>9</v>
+      </c>
+      <c r="D1027">
+        <v>70392</v>
+      </c>
+      <c r="E1027">
+        <v>179776</v>
+      </c>
+    </row>
+    <row r="1028" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1028" s="1">
+        <v>46316</v>
+      </c>
+      <c r="B1028">
+        <v>101</v>
+      </c>
+      <c r="C1028" t="s">
+        <v>152</v>
+      </c>
+      <c r="D1028">
+        <v>70424</v>
+      </c>
+      <c r="E1028">
+        <v>179846</v>
+      </c>
+    </row>
+    <row r="1029" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1029" s="1">
+        <v>46316</v>
+      </c>
+      <c r="B1029">
+        <v>101</v>
+      </c>
+      <c r="C1029" t="s">
+        <v>9</v>
+      </c>
+      <c r="D1029">
+        <v>70409</v>
+      </c>
+      <c r="E1029">
+        <v>179830</v>
+      </c>
+    </row>
+    <row r="1030" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1030" s="1">
+        <v>46316</v>
+      </c>
+      <c r="B1030">
+        <v>101</v>
+      </c>
+      <c r="C1030" t="s">
+        <v>119</v>
+      </c>
+      <c r="D1030">
+        <v>70394</v>
+      </c>
+      <c r="E1030">
+        <v>179786</v>
+      </c>
+    </row>
+    <row r="1031" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1031" s="1">
+        <v>46316</v>
+      </c>
+      <c r="B1031">
+        <v>101</v>
+      </c>
+      <c r="C1031" t="s">
+        <v>119</v>
+      </c>
+      <c r="D1031">
+        <v>70395</v>
+      </c>
+      <c r="E1031">
+        <v>179778</v>
+      </c>
+    </row>
+    <row r="1032" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1032" s="1">
+        <v>46316</v>
+      </c>
+      <c r="B1032">
+        <v>101</v>
+      </c>
+      <c r="C1032" t="s">
+        <v>121</v>
+      </c>
+      <c r="D1032">
+        <v>70236</v>
+      </c>
+      <c r="E1032">
+        <v>179684</v>
+      </c>
+    </row>
+    <row r="1033" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1033" s="1">
+        <v>46316</v>
+      </c>
+      <c r="B1033">
+        <v>101</v>
+      </c>
+      <c r="C1033" t="s">
+        <v>89</v>
+      </c>
+      <c r="E1033">
+        <v>179857</v>
+      </c>
+    </row>
+    <row r="1034" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1034" s="1">
+        <v>46316</v>
+      </c>
+      <c r="B1034">
+        <v>101</v>
+      </c>
+      <c r="C1034" t="s">
+        <v>70</v>
+      </c>
+      <c r="D1034">
+        <v>70152</v>
+      </c>
+      <c r="E1034">
+        <v>179715</v>
+      </c>
+    </row>
+    <row r="1035" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1035" s="1">
+        <v>46316</v>
+      </c>
+      <c r="B1035">
+        <v>101</v>
+      </c>
+      <c r="C1035" t="s">
+        <v>120</v>
+      </c>
+      <c r="E1035">
+        <v>179711</v>
+      </c>
+    </row>
+    <row r="1036" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1036" s="1">
+        <v>46316</v>
+      </c>
+      <c r="B1036">
+        <v>101</v>
+      </c>
+      <c r="C1036" t="s">
+        <v>159</v>
+      </c>
+      <c r="E1036">
+        <v>179704</v>
+      </c>
+    </row>
+    <row r="1037" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1037" s="1">
+        <v>46316</v>
+      </c>
+      <c r="B1037">
+        <v>101</v>
+      </c>
+      <c r="C1037" t="s">
+        <v>159</v>
+      </c>
+      <c r="D1037">
+        <v>69860</v>
+      </c>
+      <c r="E1037">
+        <v>179789</v>
+      </c>
+    </row>
+    <row r="1038" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1038" s="1">
+        <v>46316</v>
+      </c>
+      <c r="B1038">
+        <v>101</v>
+      </c>
+      <c r="C1038" t="s">
+        <v>159</v>
+      </c>
+      <c r="D1038">
+        <v>70277</v>
+      </c>
+      <c r="E1038">
+        <v>179788</v>
+      </c>
+    </row>
+    <row r="1039" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1039" s="1">
+        <v>46316</v>
+      </c>
+      <c r="B1039">
+        <v>101</v>
+      </c>
+      <c r="C1039" t="s">
+        <v>159</v>
+      </c>
+      <c r="D1039">
+        <v>68224</v>
+      </c>
+      <c r="E1039">
+        <v>179931</v>
+      </c>
+    </row>
+    <row r="1040" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1040" s="1">
+        <v>46316</v>
+      </c>
+      <c r="B1040">
+        <v>101</v>
+      </c>
+      <c r="C1040" t="s">
+        <v>158</v>
+      </c>
+      <c r="D1040">
+        <v>70188</v>
+      </c>
+      <c r="E1040">
+        <v>179906</v>
+      </c>
+    </row>
+    <row r="1041" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1041" s="1">
+        <v>46316</v>
+      </c>
+      <c r="B1041">
+        <v>101</v>
+      </c>
+      <c r="C1041" t="s">
+        <v>213</v>
+      </c>
+      <c r="D1041">
+        <v>70386</v>
+      </c>
+      <c r="E1041">
+        <v>179890</v>
       </c>
     </row>
   </sheetData>
@@ -16458,7 +18492,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5180BF9C-1943-4030-8A1B-6F86FE205C17}">
-  <dimension ref="A1:C15"/>
+  <dimension ref="A1:C16"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="12.85546875" style="1" bestFit="1" customWidth="1"/>
@@ -16467,7 +18501,7 @@
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="str" cm="1">
-        <f t="array" ref="A1:A15">_xlfn.UNIQUE(Romaneios!A1:A918)</f>
+        <f t="array" ref="A1:A16">_xlfn.UNIQUE(Romaneios!A1:A1041)</f>
         <v>Dt. Romaneio</v>
       </c>
       <c r="B1" t="s">
@@ -16599,6 +18633,15 @@
       <c r="B15">
         <f>COUNTIF(Romaneios!A:A,DadosRomaneios!A15)</f>
         <v>127</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A16" s="1">
+        <v>46316</v>
+      </c>
+      <c r="B16">
+        <f>COUNTIF(Romaneios!A:A,DadosRomaneios!A16)</f>
+        <v>123</v>
       </c>
     </row>
   </sheetData>

--- a/DadosRomaneios.xlsx
+++ b/DadosRomaneios.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="U:\AcompanhamentoProducao\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{812A5EDB-2CF6-446C-BA0D-2A38DEB7C0F1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1320ED70-5104-45CE-8E00-A8C7073D0C1F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" activeTab="1" xr2:uid="{B6976704-8E51-4052-B60A-5847F95A5AE5}"/>
   </bookViews>
@@ -62,7 +62,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1046" uniqueCount="214">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1232" uniqueCount="233">
   <si>
     <t>ALBERT EINSTEIN</t>
   </si>
@@ -704,6 +704,63 @@
   </si>
   <si>
     <t>DASA 12.857.736/0001</t>
+  </si>
+  <si>
+    <t>PA ZONA OESTE</t>
+  </si>
+  <si>
+    <t>COI CLINICA 39.086.1</t>
+  </si>
+  <si>
+    <t>NOTRE DAME</t>
+  </si>
+  <si>
+    <t>LAPA TERCEIRIZACOES</t>
+  </si>
+  <si>
+    <t>HOSP BARRA DOR I</t>
+  </si>
+  <si>
+    <t>TOPIX 4.587.125/0001</t>
+  </si>
+  <si>
+    <t>ATTIMO SERVICOS</t>
+  </si>
+  <si>
+    <t>090171-PE.BENTO</t>
+  </si>
+  <si>
+    <t>SECRETARIA DE ESTADO</t>
+  </si>
+  <si>
+    <t>SECONCI LORENA</t>
+  </si>
+  <si>
+    <t>DASA LAB VALECLIN</t>
+  </si>
+  <si>
+    <t>UNIMED DE CAPIVARI</t>
+  </si>
+  <si>
+    <t>SECONCI VL ALPINA</t>
+  </si>
+  <si>
+    <t>SECONCI HELIOPOLIS</t>
+  </si>
+  <si>
+    <t>DASA 45.796.554/0018</t>
+  </si>
+  <si>
+    <t>SECONCI ITAPECERICA</t>
+  </si>
+  <si>
+    <t>SECONCI SAPOPEMBA</t>
+  </si>
+  <si>
+    <t>CHAPEL SCHOOL</t>
+  </si>
+  <si>
+    <t>TEC LAB 51.131.969/0</t>
   </si>
 </sst>
 </file>
@@ -1083,7 +1140,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BF29A37F-A1D1-4315-91AB-A952895E1E73}">
-  <dimension ref="A1:E1041"/>
+  <dimension ref="A1:E1227"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="12.85546875" bestFit="1" customWidth="1"/>
@@ -18481,6 +18538,3075 @@
         <v>179890</v>
       </c>
     </row>
+    <row r="1042" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1042" s="1">
+        <v>46317</v>
+      </c>
+      <c r="B1042">
+        <v>101</v>
+      </c>
+      <c r="C1042" t="s">
+        <v>13</v>
+      </c>
+      <c r="D1042">
+        <v>69799</v>
+      </c>
+      <c r="E1042">
+        <v>179960</v>
+      </c>
+    </row>
+    <row r="1043" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1043" s="1">
+        <v>46317</v>
+      </c>
+      <c r="B1043">
+        <v>101</v>
+      </c>
+      <c r="C1043" t="s">
+        <v>214</v>
+      </c>
+      <c r="D1043">
+        <v>69591</v>
+      </c>
+      <c r="E1043">
+        <v>179477</v>
+      </c>
+    </row>
+    <row r="1044" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1044" s="1">
+        <v>46317</v>
+      </c>
+      <c r="B1044">
+        <v>101</v>
+      </c>
+      <c r="C1044" t="s">
+        <v>214</v>
+      </c>
+      <c r="D1044">
+        <v>69590</v>
+      </c>
+      <c r="E1044">
+        <v>179475</v>
+      </c>
+    </row>
+    <row r="1045" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1045" s="1">
+        <v>46317</v>
+      </c>
+      <c r="B1045">
+        <v>101</v>
+      </c>
+      <c r="C1045" t="s">
+        <v>13</v>
+      </c>
+      <c r="E1045">
+        <v>179376</v>
+      </c>
+    </row>
+    <row r="1046" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1046" s="1">
+        <v>46317</v>
+      </c>
+      <c r="B1046">
+        <v>101</v>
+      </c>
+      <c r="C1046" t="s">
+        <v>13</v>
+      </c>
+      <c r="D1046">
+        <v>69817</v>
+      </c>
+      <c r="E1046">
+        <v>179972</v>
+      </c>
+    </row>
+    <row r="1047" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1047" s="1">
+        <v>46317</v>
+      </c>
+      <c r="B1047">
+        <v>101</v>
+      </c>
+      <c r="C1047" t="s">
+        <v>33</v>
+      </c>
+      <c r="D1047">
+        <v>70206</v>
+      </c>
+      <c r="E1047">
+        <v>179612</v>
+      </c>
+    </row>
+    <row r="1048" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1048" s="1">
+        <v>46317</v>
+      </c>
+      <c r="B1048">
+        <v>101</v>
+      </c>
+      <c r="C1048" t="s">
+        <v>215</v>
+      </c>
+      <c r="D1048">
+        <v>70233</v>
+      </c>
+      <c r="E1048">
+        <v>179921</v>
+      </c>
+    </row>
+    <row r="1049" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1049" s="1">
+        <v>46317</v>
+      </c>
+      <c r="B1049">
+        <v>101</v>
+      </c>
+      <c r="C1049" t="s">
+        <v>216</v>
+      </c>
+      <c r="D1049">
+        <v>70045</v>
+      </c>
+      <c r="E1049">
+        <v>179476</v>
+      </c>
+    </row>
+    <row r="1050" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1050" s="1">
+        <v>46317</v>
+      </c>
+      <c r="B1050">
+        <v>102</v>
+      </c>
+      <c r="C1050" t="s">
+        <v>217</v>
+      </c>
+      <c r="E1050">
+        <v>546</v>
+      </c>
+    </row>
+    <row r="1051" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1051" s="1">
+        <v>46317</v>
+      </c>
+      <c r="B1051">
+        <v>101</v>
+      </c>
+      <c r="C1051" t="s">
+        <v>13</v>
+      </c>
+      <c r="D1051">
+        <v>69816</v>
+      </c>
+      <c r="E1051">
+        <v>179891</v>
+      </c>
+    </row>
+    <row r="1052" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1052" s="1">
+        <v>46317</v>
+      </c>
+      <c r="B1052">
+        <v>101</v>
+      </c>
+      <c r="C1052" t="s">
+        <v>16</v>
+      </c>
+      <c r="D1052">
+        <v>70323</v>
+      </c>
+      <c r="E1052">
+        <v>179621</v>
+      </c>
+    </row>
+    <row r="1053" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1053" s="1">
+        <v>46317</v>
+      </c>
+      <c r="B1053">
+        <v>101</v>
+      </c>
+      <c r="C1053" t="s">
+        <v>13</v>
+      </c>
+      <c r="D1053">
+        <v>69798</v>
+      </c>
+      <c r="E1053">
+        <v>179918</v>
+      </c>
+    </row>
+    <row r="1054" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1054" s="1">
+        <v>46317</v>
+      </c>
+      <c r="B1054">
+        <v>101</v>
+      </c>
+      <c r="C1054" t="s">
+        <v>13</v>
+      </c>
+      <c r="E1054">
+        <v>179925</v>
+      </c>
+    </row>
+    <row r="1055" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1055" s="1">
+        <v>46317</v>
+      </c>
+      <c r="B1055">
+        <v>101</v>
+      </c>
+      <c r="C1055" t="s">
+        <v>142</v>
+      </c>
+      <c r="D1055">
+        <v>68642</v>
+      </c>
+      <c r="E1055">
+        <v>179984</v>
+      </c>
+    </row>
+    <row r="1056" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1056" s="1">
+        <v>46317</v>
+      </c>
+      <c r="B1056">
+        <v>101</v>
+      </c>
+      <c r="C1056" t="s">
+        <v>13</v>
+      </c>
+      <c r="E1056">
+        <v>179996</v>
+      </c>
+    </row>
+    <row r="1057" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1057" s="1">
+        <v>46317</v>
+      </c>
+      <c r="B1057">
+        <v>101</v>
+      </c>
+      <c r="C1057" t="s">
+        <v>13</v>
+      </c>
+      <c r="E1057">
+        <v>179997</v>
+      </c>
+    </row>
+    <row r="1058" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1058" s="1">
+        <v>46317</v>
+      </c>
+      <c r="B1058">
+        <v>101</v>
+      </c>
+      <c r="C1058" t="s">
+        <v>13</v>
+      </c>
+      <c r="E1058">
+        <v>180001</v>
+      </c>
+    </row>
+    <row r="1059" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1059" s="1">
+        <v>46317</v>
+      </c>
+      <c r="B1059">
+        <v>101</v>
+      </c>
+      <c r="C1059" t="s">
+        <v>218</v>
+      </c>
+      <c r="D1059">
+        <v>68654</v>
+      </c>
+      <c r="E1059">
+        <v>179985</v>
+      </c>
+    </row>
+    <row r="1060" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1060" s="1">
+        <v>46317</v>
+      </c>
+      <c r="B1060">
+        <v>101</v>
+      </c>
+      <c r="C1060" t="s">
+        <v>215</v>
+      </c>
+      <c r="E1060">
+        <v>179920</v>
+      </c>
+    </row>
+    <row r="1061" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1061" s="1">
+        <v>46317</v>
+      </c>
+      <c r="B1061">
+        <v>102</v>
+      </c>
+      <c r="C1061" t="s">
+        <v>219</v>
+      </c>
+      <c r="E1061">
+        <v>548</v>
+      </c>
+    </row>
+    <row r="1062" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1062" s="1">
+        <v>46317</v>
+      </c>
+      <c r="B1062">
+        <v>102</v>
+      </c>
+      <c r="C1062" t="s">
+        <v>220</v>
+      </c>
+      <c r="D1062">
+        <v>520</v>
+      </c>
+      <c r="E1062">
+        <v>547</v>
+      </c>
+    </row>
+    <row r="1063" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1063" s="1">
+        <v>46317</v>
+      </c>
+      <c r="B1063">
+        <v>101</v>
+      </c>
+      <c r="C1063" t="s">
+        <v>23</v>
+      </c>
+      <c r="D1063">
+        <v>68325</v>
+      </c>
+      <c r="E1063">
+        <v>179953</v>
+      </c>
+    </row>
+    <row r="1064" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1064" s="1">
+        <v>46317</v>
+      </c>
+      <c r="B1064">
+        <v>101</v>
+      </c>
+      <c r="C1064" t="s">
+        <v>89</v>
+      </c>
+      <c r="D1064">
+        <v>69893</v>
+      </c>
+      <c r="E1064">
+        <v>179912</v>
+      </c>
+    </row>
+    <row r="1065" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1065" s="1">
+        <v>46317</v>
+      </c>
+      <c r="B1065">
+        <v>101</v>
+      </c>
+      <c r="C1065" t="s">
+        <v>60</v>
+      </c>
+      <c r="D1065">
+        <v>70058</v>
+      </c>
+      <c r="E1065">
+        <v>179966</v>
+      </c>
+    </row>
+    <row r="1066" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1066" s="1">
+        <v>46317</v>
+      </c>
+      <c r="B1066">
+        <v>101</v>
+      </c>
+      <c r="C1066" t="s">
+        <v>60</v>
+      </c>
+      <c r="D1066">
+        <v>70116</v>
+      </c>
+      <c r="E1066">
+        <v>179989</v>
+      </c>
+    </row>
+    <row r="1067" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1067" s="1">
+        <v>46317</v>
+      </c>
+      <c r="B1067">
+        <v>101</v>
+      </c>
+      <c r="C1067" t="s">
+        <v>60</v>
+      </c>
+      <c r="D1067">
+        <v>69466</v>
+      </c>
+      <c r="E1067">
+        <v>178988</v>
+      </c>
+    </row>
+    <row r="1068" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1068" s="1">
+        <v>46317</v>
+      </c>
+      <c r="B1068">
+        <v>101</v>
+      </c>
+      <c r="C1068" t="s">
+        <v>60</v>
+      </c>
+      <c r="D1068">
+        <v>69467</v>
+      </c>
+      <c r="E1068">
+        <v>178996</v>
+      </c>
+    </row>
+    <row r="1069" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1069" s="1">
+        <v>46317</v>
+      </c>
+      <c r="B1069">
+        <v>101</v>
+      </c>
+      <c r="C1069" t="s">
+        <v>60</v>
+      </c>
+      <c r="E1069">
+        <v>179967</v>
+      </c>
+    </row>
+    <row r="1070" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1070" s="1">
+        <v>46317</v>
+      </c>
+      <c r="B1070">
+        <v>101</v>
+      </c>
+      <c r="C1070" t="s">
+        <v>60</v>
+      </c>
+      <c r="D1070">
+        <v>70057</v>
+      </c>
+      <c r="E1070">
+        <v>179991</v>
+      </c>
+    </row>
+    <row r="1071" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1071" s="1">
+        <v>46317</v>
+      </c>
+      <c r="B1071">
+        <v>101</v>
+      </c>
+      <c r="C1071" t="s">
+        <v>60</v>
+      </c>
+      <c r="D1071">
+        <v>70066</v>
+      </c>
+      <c r="E1071">
+        <v>179990</v>
+      </c>
+    </row>
+    <row r="1072" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1072" s="1">
+        <v>46317</v>
+      </c>
+      <c r="B1072">
+        <v>101</v>
+      </c>
+      <c r="C1072" t="s">
+        <v>60</v>
+      </c>
+      <c r="D1072">
+        <v>70588</v>
+      </c>
+      <c r="E1072">
+        <v>180000</v>
+      </c>
+    </row>
+    <row r="1073" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1073" s="1">
+        <v>46317</v>
+      </c>
+      <c r="B1073">
+        <v>101</v>
+      </c>
+      <c r="C1073" t="s">
+        <v>151</v>
+      </c>
+      <c r="D1073">
+        <v>70549</v>
+      </c>
+      <c r="E1073">
+        <v>179975</v>
+      </c>
+    </row>
+    <row r="1074" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1074" s="1">
+        <v>46317</v>
+      </c>
+      <c r="B1074">
+        <v>101</v>
+      </c>
+      <c r="C1074" t="s">
+        <v>27</v>
+      </c>
+      <c r="D1074">
+        <v>67000</v>
+      </c>
+      <c r="E1074">
+        <v>179756</v>
+      </c>
+    </row>
+    <row r="1075" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1075" s="1">
+        <v>46317</v>
+      </c>
+      <c r="B1075">
+        <v>101</v>
+      </c>
+      <c r="C1075" t="s">
+        <v>27</v>
+      </c>
+      <c r="D1075">
+        <v>67939</v>
+      </c>
+      <c r="E1075">
+        <v>179746</v>
+      </c>
+    </row>
+    <row r="1076" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1076" s="1">
+        <v>46317</v>
+      </c>
+      <c r="B1076">
+        <v>101</v>
+      </c>
+      <c r="C1076" t="s">
+        <v>111</v>
+      </c>
+      <c r="D1076">
+        <v>69298</v>
+      </c>
+      <c r="E1076">
+        <v>179913</v>
+      </c>
+    </row>
+    <row r="1077" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1077" s="1">
+        <v>46317</v>
+      </c>
+      <c r="B1077">
+        <v>101</v>
+      </c>
+      <c r="C1077" t="s">
+        <v>27</v>
+      </c>
+      <c r="E1077">
+        <v>179941</v>
+      </c>
+    </row>
+    <row r="1078" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1078" s="1">
+        <v>46317</v>
+      </c>
+      <c r="B1078">
+        <v>101</v>
+      </c>
+      <c r="C1078" t="s">
+        <v>27</v>
+      </c>
+      <c r="D1078">
+        <v>70462</v>
+      </c>
+      <c r="E1078">
+        <v>179939</v>
+      </c>
+    </row>
+    <row r="1079" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1079" s="1">
+        <v>46317</v>
+      </c>
+      <c r="B1079">
+        <v>101</v>
+      </c>
+      <c r="C1079" t="s">
+        <v>193</v>
+      </c>
+      <c r="D1079">
+        <v>69627</v>
+      </c>
+      <c r="E1079">
+        <v>179654</v>
+      </c>
+    </row>
+    <row r="1080" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1080" s="1">
+        <v>46317</v>
+      </c>
+      <c r="B1080">
+        <v>101</v>
+      </c>
+      <c r="C1080" t="s">
+        <v>193</v>
+      </c>
+      <c r="D1080">
+        <v>70238</v>
+      </c>
+      <c r="E1080">
+        <v>179663</v>
+      </c>
+    </row>
+    <row r="1081" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1081" s="1">
+        <v>46317</v>
+      </c>
+      <c r="B1081">
+        <v>101</v>
+      </c>
+      <c r="C1081" t="s">
+        <v>180</v>
+      </c>
+      <c r="D1081">
+        <v>69349</v>
+      </c>
+      <c r="E1081">
+        <v>179917</v>
+      </c>
+    </row>
+    <row r="1082" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1082" s="1">
+        <v>46317</v>
+      </c>
+      <c r="B1082">
+        <v>101</v>
+      </c>
+      <c r="C1082" t="s">
+        <v>58</v>
+      </c>
+      <c r="D1082">
+        <v>70137</v>
+      </c>
+      <c r="E1082">
+        <v>179958</v>
+      </c>
+    </row>
+    <row r="1083" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1083" s="1">
+        <v>46317</v>
+      </c>
+      <c r="B1083">
+        <v>101</v>
+      </c>
+      <c r="C1083" t="s">
+        <v>58</v>
+      </c>
+      <c r="D1083">
+        <v>70040</v>
+      </c>
+      <c r="E1083">
+        <v>179968</v>
+      </c>
+    </row>
+    <row r="1084" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1084" s="1">
+        <v>46317</v>
+      </c>
+      <c r="B1084">
+        <v>101</v>
+      </c>
+      <c r="C1084" t="s">
+        <v>58</v>
+      </c>
+      <c r="D1084">
+        <v>69951</v>
+      </c>
+      <c r="E1084">
+        <v>179944</v>
+      </c>
+    </row>
+    <row r="1085" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1085" s="1">
+        <v>46317</v>
+      </c>
+      <c r="B1085">
+        <v>101</v>
+      </c>
+      <c r="C1085" t="s">
+        <v>39</v>
+      </c>
+      <c r="D1085">
+        <v>70450</v>
+      </c>
+      <c r="E1085">
+        <v>179954</v>
+      </c>
+    </row>
+    <row r="1086" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1086" s="1">
+        <v>46317</v>
+      </c>
+      <c r="B1086">
+        <v>101</v>
+      </c>
+      <c r="C1086" t="s">
+        <v>24</v>
+      </c>
+      <c r="D1086">
+        <v>70261</v>
+      </c>
+      <c r="E1086">
+        <v>179961</v>
+      </c>
+    </row>
+    <row r="1087" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1087" s="1">
+        <v>46317</v>
+      </c>
+      <c r="B1087">
+        <v>101</v>
+      </c>
+      <c r="C1087" t="s">
+        <v>0</v>
+      </c>
+      <c r="E1087">
+        <v>179982</v>
+      </c>
+    </row>
+    <row r="1088" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1088" s="1">
+        <v>46317</v>
+      </c>
+      <c r="B1088">
+        <v>101</v>
+      </c>
+      <c r="C1088" t="s">
+        <v>20</v>
+      </c>
+      <c r="D1088">
+        <v>69967</v>
+      </c>
+      <c r="E1088">
+        <v>179942</v>
+      </c>
+    </row>
+    <row r="1089" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1089" s="1">
+        <v>46317</v>
+      </c>
+      <c r="B1089">
+        <v>101</v>
+      </c>
+      <c r="C1089" t="s">
+        <v>15</v>
+      </c>
+      <c r="D1089">
+        <v>70381</v>
+      </c>
+      <c r="E1089">
+        <v>179797</v>
+      </c>
+    </row>
+    <row r="1090" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1090" s="1">
+        <v>46317</v>
+      </c>
+      <c r="B1090">
+        <v>101</v>
+      </c>
+      <c r="C1090" t="s">
+        <v>81</v>
+      </c>
+      <c r="D1090">
+        <v>70229</v>
+      </c>
+      <c r="E1090">
+        <v>179905</v>
+      </c>
+    </row>
+    <row r="1091" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1091" s="1">
+        <v>46317</v>
+      </c>
+      <c r="B1091">
+        <v>101</v>
+      </c>
+      <c r="C1091" t="s">
+        <v>221</v>
+      </c>
+      <c r="E1091">
+        <v>179908</v>
+      </c>
+    </row>
+    <row r="1092" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1092" s="1">
+        <v>46317</v>
+      </c>
+      <c r="B1092">
+        <v>101</v>
+      </c>
+      <c r="C1092" t="s">
+        <v>0</v>
+      </c>
+      <c r="D1092">
+        <v>70289</v>
+      </c>
+      <c r="E1092">
+        <v>179987</v>
+      </c>
+    </row>
+    <row r="1093" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1093" s="1">
+        <v>46317</v>
+      </c>
+      <c r="B1093">
+        <v>101</v>
+      </c>
+      <c r="C1093" t="s">
+        <v>69</v>
+      </c>
+      <c r="D1093">
+        <v>70118</v>
+      </c>
+      <c r="E1093">
+        <v>179929</v>
+      </c>
+    </row>
+    <row r="1094" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1094" s="1">
+        <v>46317</v>
+      </c>
+      <c r="B1094">
+        <v>101</v>
+      </c>
+      <c r="C1094" t="s">
+        <v>0</v>
+      </c>
+      <c r="D1094">
+        <v>70142</v>
+      </c>
+      <c r="E1094">
+        <v>179998</v>
+      </c>
+    </row>
+    <row r="1095" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1095" s="1">
+        <v>46317</v>
+      </c>
+      <c r="B1095">
+        <v>101</v>
+      </c>
+      <c r="C1095" t="s">
+        <v>23</v>
+      </c>
+      <c r="E1095">
+        <v>179911</v>
+      </c>
+    </row>
+    <row r="1096" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1096" s="1">
+        <v>46317</v>
+      </c>
+      <c r="B1096">
+        <v>101</v>
+      </c>
+      <c r="C1096" t="s">
+        <v>69</v>
+      </c>
+      <c r="D1096">
+        <v>68248</v>
+      </c>
+      <c r="E1096">
+        <v>179940</v>
+      </c>
+    </row>
+    <row r="1097" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1097" s="1">
+        <v>46317</v>
+      </c>
+      <c r="B1097">
+        <v>101</v>
+      </c>
+      <c r="C1097" t="s">
+        <v>23</v>
+      </c>
+      <c r="D1097">
+        <v>70317</v>
+      </c>
+      <c r="E1097">
+        <v>179947</v>
+      </c>
+    </row>
+    <row r="1098" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1098" s="1">
+        <v>46317</v>
+      </c>
+      <c r="B1098">
+        <v>101</v>
+      </c>
+      <c r="C1098" t="s">
+        <v>0</v>
+      </c>
+      <c r="D1098">
+        <v>70220</v>
+      </c>
+      <c r="E1098">
+        <v>179909</v>
+      </c>
+    </row>
+    <row r="1099" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1099" s="1">
+        <v>46317</v>
+      </c>
+      <c r="B1099">
+        <v>101</v>
+      </c>
+      <c r="C1099" t="s">
+        <v>23</v>
+      </c>
+      <c r="D1099">
+        <v>68361</v>
+      </c>
+      <c r="E1099">
+        <v>179930</v>
+      </c>
+    </row>
+    <row r="1100" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1100" s="1">
+        <v>46317</v>
+      </c>
+      <c r="B1100">
+        <v>101</v>
+      </c>
+      <c r="C1100" t="s">
+        <v>0</v>
+      </c>
+      <c r="E1100">
+        <v>179988</v>
+      </c>
+    </row>
+    <row r="1101" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1101" s="1">
+        <v>46317</v>
+      </c>
+      <c r="B1101">
+        <v>101</v>
+      </c>
+      <c r="C1101" t="s">
+        <v>69</v>
+      </c>
+      <c r="D1101">
+        <v>69521</v>
+      </c>
+      <c r="E1101">
+        <v>179956</v>
+      </c>
+    </row>
+    <row r="1102" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1102" s="1">
+        <v>46317</v>
+      </c>
+      <c r="B1102">
+        <v>101</v>
+      </c>
+      <c r="C1102" t="s">
+        <v>101</v>
+      </c>
+      <c r="D1102">
+        <v>70488</v>
+      </c>
+      <c r="E1102">
+        <v>179928</v>
+      </c>
+    </row>
+    <row r="1103" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1103" s="1">
+        <v>46317</v>
+      </c>
+      <c r="B1103">
+        <v>101</v>
+      </c>
+      <c r="C1103" t="s">
+        <v>73</v>
+      </c>
+      <c r="D1103">
+        <v>70480</v>
+      </c>
+      <c r="E1103">
+        <v>179933</v>
+      </c>
+    </row>
+    <row r="1104" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1104" s="1">
+        <v>46317</v>
+      </c>
+      <c r="B1104">
+        <v>101</v>
+      </c>
+      <c r="C1104" t="s">
+        <v>99</v>
+      </c>
+      <c r="D1104">
+        <v>70479</v>
+      </c>
+      <c r="E1104">
+        <v>179959</v>
+      </c>
+    </row>
+    <row r="1105" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1105" s="1">
+        <v>46317</v>
+      </c>
+      <c r="B1105">
+        <v>101</v>
+      </c>
+      <c r="C1105" t="s">
+        <v>128</v>
+      </c>
+      <c r="D1105">
+        <v>69910</v>
+      </c>
+      <c r="E1105">
+        <v>179383</v>
+      </c>
+    </row>
+    <row r="1106" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1106" s="1">
+        <v>46317</v>
+      </c>
+      <c r="B1106">
+        <v>101</v>
+      </c>
+      <c r="C1106" t="s">
+        <v>100</v>
+      </c>
+      <c r="D1106">
+        <v>70487</v>
+      </c>
+      <c r="E1106">
+        <v>179934</v>
+      </c>
+    </row>
+    <row r="1107" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1107" s="1">
+        <v>46317</v>
+      </c>
+      <c r="B1107">
+        <v>101</v>
+      </c>
+      <c r="C1107" t="s">
+        <v>72</v>
+      </c>
+      <c r="D1107">
+        <v>70467</v>
+      </c>
+      <c r="E1107">
+        <v>179927</v>
+      </c>
+    </row>
+    <row r="1108" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1108" s="1">
+        <v>46317</v>
+      </c>
+      <c r="B1108">
+        <v>101</v>
+      </c>
+      <c r="C1108" t="s">
+        <v>180</v>
+      </c>
+      <c r="E1108">
+        <v>179970</v>
+      </c>
+    </row>
+    <row r="1109" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1109" s="1">
+        <v>46317</v>
+      </c>
+      <c r="B1109">
+        <v>101</v>
+      </c>
+      <c r="C1109" t="s">
+        <v>23</v>
+      </c>
+      <c r="D1109">
+        <v>68612</v>
+      </c>
+      <c r="E1109">
+        <v>179444</v>
+      </c>
+    </row>
+    <row r="1110" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1110" s="1">
+        <v>46317</v>
+      </c>
+      <c r="B1110">
+        <v>101</v>
+      </c>
+      <c r="C1110" t="s">
+        <v>180</v>
+      </c>
+      <c r="E1110">
+        <v>179969</v>
+      </c>
+    </row>
+    <row r="1111" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1111" s="1">
+        <v>46317</v>
+      </c>
+      <c r="B1111">
+        <v>101</v>
+      </c>
+      <c r="C1111" t="s">
+        <v>180</v>
+      </c>
+      <c r="D1111">
+        <v>69520</v>
+      </c>
+      <c r="E1111">
+        <v>179971</v>
+      </c>
+    </row>
+    <row r="1112" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1112" s="1">
+        <v>46317</v>
+      </c>
+      <c r="B1112">
+        <v>101</v>
+      </c>
+      <c r="C1112" t="s">
+        <v>26</v>
+      </c>
+      <c r="D1112">
+        <v>70209</v>
+      </c>
+      <c r="E1112">
+        <v>179962</v>
+      </c>
+    </row>
+    <row r="1113" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1113" s="1">
+        <v>46317</v>
+      </c>
+      <c r="B1113">
+        <v>101</v>
+      </c>
+      <c r="C1113" t="s">
+        <v>0</v>
+      </c>
+      <c r="E1113">
+        <v>179983</v>
+      </c>
+    </row>
+    <row r="1114" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1114" s="1">
+        <v>46317</v>
+      </c>
+      <c r="B1114">
+        <v>101</v>
+      </c>
+      <c r="C1114" t="s">
+        <v>85</v>
+      </c>
+      <c r="D1114">
+        <v>69735</v>
+      </c>
+      <c r="E1114">
+        <v>179981</v>
+      </c>
+    </row>
+    <row r="1115" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1115" s="1">
+        <v>46317</v>
+      </c>
+      <c r="B1115">
+        <v>101</v>
+      </c>
+      <c r="C1115" t="s">
+        <v>69</v>
+      </c>
+      <c r="D1115">
+        <v>69823</v>
+      </c>
+      <c r="E1115">
+        <v>179923</v>
+      </c>
+    </row>
+    <row r="1116" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1116" s="1">
+        <v>46317</v>
+      </c>
+      <c r="B1116">
+        <v>101</v>
+      </c>
+      <c r="C1116" t="s">
+        <v>6</v>
+      </c>
+      <c r="E1116">
+        <v>179935</v>
+      </c>
+    </row>
+    <row r="1117" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1117" s="1">
+        <v>46317</v>
+      </c>
+      <c r="B1117">
+        <v>101</v>
+      </c>
+      <c r="C1117" t="s">
+        <v>6</v>
+      </c>
+      <c r="E1117">
+        <v>179979</v>
+      </c>
+    </row>
+    <row r="1118" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1118" s="1">
+        <v>46317</v>
+      </c>
+      <c r="B1118">
+        <v>101</v>
+      </c>
+      <c r="C1118" t="s">
+        <v>6</v>
+      </c>
+      <c r="D1118">
+        <v>68157</v>
+      </c>
+      <c r="E1118">
+        <v>179980</v>
+      </c>
+    </row>
+    <row r="1119" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1119" s="1">
+        <v>46317</v>
+      </c>
+      <c r="B1119">
+        <v>101</v>
+      </c>
+      <c r="C1119" t="s">
+        <v>6</v>
+      </c>
+      <c r="D1119">
+        <v>69418</v>
+      </c>
+      <c r="E1119">
+        <v>179965</v>
+      </c>
+    </row>
+    <row r="1120" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1120" s="1">
+        <v>46317</v>
+      </c>
+      <c r="B1120">
+        <v>101</v>
+      </c>
+      <c r="C1120" t="s">
+        <v>6</v>
+      </c>
+      <c r="D1120">
+        <v>66413</v>
+      </c>
+      <c r="E1120">
+        <v>179937</v>
+      </c>
+    </row>
+    <row r="1121" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1121" s="1">
+        <v>46317</v>
+      </c>
+      <c r="B1121">
+        <v>101</v>
+      </c>
+      <c r="C1121" t="s">
+        <v>6</v>
+      </c>
+      <c r="D1121">
+        <v>66252</v>
+      </c>
+      <c r="E1121">
+        <v>179936</v>
+      </c>
+    </row>
+    <row r="1122" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1122" s="1">
+        <v>46317</v>
+      </c>
+      <c r="B1122">
+        <v>101</v>
+      </c>
+      <c r="C1122" t="s">
+        <v>6</v>
+      </c>
+      <c r="D1122">
+        <v>68673</v>
+      </c>
+      <c r="E1122">
+        <v>179978</v>
+      </c>
+    </row>
+    <row r="1123" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1123" s="1">
+        <v>46317</v>
+      </c>
+      <c r="B1123">
+        <v>101</v>
+      </c>
+      <c r="C1123" t="s">
+        <v>6</v>
+      </c>
+      <c r="D1123">
+        <v>69237</v>
+      </c>
+      <c r="E1123">
+        <v>179915</v>
+      </c>
+    </row>
+    <row r="1124" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1124" s="1">
+        <v>46317</v>
+      </c>
+      <c r="B1124">
+        <v>101</v>
+      </c>
+      <c r="C1124" t="s">
+        <v>22</v>
+      </c>
+      <c r="D1124">
+        <v>70180</v>
+      </c>
+      <c r="E1124">
+        <v>180018</v>
+      </c>
+    </row>
+    <row r="1125" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1125" s="1">
+        <v>46317</v>
+      </c>
+      <c r="B1125">
+        <v>101</v>
+      </c>
+      <c r="C1125" t="s">
+        <v>222</v>
+      </c>
+      <c r="D1125">
+        <v>69983</v>
+      </c>
+      <c r="E1125">
+        <v>180020</v>
+      </c>
+    </row>
+    <row r="1126" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1126" s="1">
+        <v>46317</v>
+      </c>
+      <c r="B1126">
+        <v>101</v>
+      </c>
+      <c r="C1126" t="s">
+        <v>222</v>
+      </c>
+      <c r="D1126">
+        <v>69995</v>
+      </c>
+      <c r="E1126">
+        <v>180021</v>
+      </c>
+    </row>
+    <row r="1127" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1127" s="1">
+        <v>46317</v>
+      </c>
+      <c r="B1127">
+        <v>101</v>
+      </c>
+      <c r="C1127" t="s">
+        <v>125</v>
+      </c>
+      <c r="D1127">
+        <v>70313</v>
+      </c>
+      <c r="E1127">
+        <v>180039</v>
+      </c>
+    </row>
+    <row r="1128" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1128" s="1">
+        <v>46317</v>
+      </c>
+      <c r="B1128">
+        <v>101</v>
+      </c>
+      <c r="C1128" t="s">
+        <v>159</v>
+      </c>
+      <c r="D1128">
+        <v>68604</v>
+      </c>
+      <c r="E1128">
+        <v>179582</v>
+      </c>
+    </row>
+    <row r="1129" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1129" s="1">
+        <v>46317</v>
+      </c>
+      <c r="B1129">
+        <v>101</v>
+      </c>
+      <c r="C1129" t="s">
+        <v>141</v>
+      </c>
+      <c r="D1129">
+        <v>70469</v>
+      </c>
+      <c r="E1129">
+        <v>180017</v>
+      </c>
+    </row>
+    <row r="1130" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1130" s="1">
+        <v>46317</v>
+      </c>
+      <c r="B1130">
+        <v>101</v>
+      </c>
+      <c r="C1130" t="s">
+        <v>89</v>
+      </c>
+      <c r="D1130">
+        <v>70471</v>
+      </c>
+      <c r="E1130">
+        <v>180012</v>
+      </c>
+    </row>
+    <row r="1131" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1131" s="1">
+        <v>46317</v>
+      </c>
+      <c r="B1131">
+        <v>101</v>
+      </c>
+      <c r="C1131" t="s">
+        <v>89</v>
+      </c>
+      <c r="D1131">
+        <v>70472</v>
+      </c>
+      <c r="E1131">
+        <v>180013</v>
+      </c>
+    </row>
+    <row r="1132" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1132" s="1">
+        <v>46317</v>
+      </c>
+      <c r="B1132">
+        <v>101</v>
+      </c>
+      <c r="C1132" t="s">
+        <v>121</v>
+      </c>
+      <c r="D1132">
+        <v>70527</v>
+      </c>
+      <c r="E1132">
+        <v>180025</v>
+      </c>
+    </row>
+    <row r="1133" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1133" s="1">
+        <v>46317</v>
+      </c>
+      <c r="B1133">
+        <v>101</v>
+      </c>
+      <c r="C1133" t="s">
+        <v>11</v>
+      </c>
+      <c r="D1133">
+        <v>70336</v>
+      </c>
+      <c r="E1133">
+        <v>179765</v>
+      </c>
+    </row>
+    <row r="1134" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1134" s="1">
+        <v>46317</v>
+      </c>
+      <c r="B1134">
+        <v>101</v>
+      </c>
+      <c r="C1134" t="s">
+        <v>7</v>
+      </c>
+      <c r="D1134">
+        <v>70418</v>
+      </c>
+      <c r="E1134">
+        <v>179840</v>
+      </c>
+    </row>
+    <row r="1135" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1135" s="1">
+        <v>46317</v>
+      </c>
+      <c r="B1135">
+        <v>101</v>
+      </c>
+      <c r="C1135" t="s">
+        <v>7</v>
+      </c>
+      <c r="D1135">
+        <v>70432</v>
+      </c>
+      <c r="E1135">
+        <v>179862</v>
+      </c>
+    </row>
+    <row r="1136" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1136" s="1">
+        <v>46317</v>
+      </c>
+      <c r="B1136">
+        <v>101</v>
+      </c>
+      <c r="C1136" t="s">
+        <v>152</v>
+      </c>
+      <c r="D1136">
+        <v>70398</v>
+      </c>
+      <c r="E1136">
+        <v>179808</v>
+      </c>
+    </row>
+    <row r="1137" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1137" s="1">
+        <v>46317</v>
+      </c>
+      <c r="B1137">
+        <v>101</v>
+      </c>
+      <c r="C1137" t="s">
+        <v>8</v>
+      </c>
+      <c r="D1137">
+        <v>70333</v>
+      </c>
+      <c r="E1137">
+        <v>179730</v>
+      </c>
+    </row>
+    <row r="1138" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1138" s="1">
+        <v>46317</v>
+      </c>
+      <c r="B1138">
+        <v>101</v>
+      </c>
+      <c r="C1138" t="s">
+        <v>152</v>
+      </c>
+      <c r="D1138">
+        <v>70397</v>
+      </c>
+      <c r="E1138">
+        <v>179803</v>
+      </c>
+    </row>
+    <row r="1139" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1139" s="1">
+        <v>46317</v>
+      </c>
+      <c r="B1139">
+        <v>101</v>
+      </c>
+      <c r="C1139" t="s">
+        <v>8</v>
+      </c>
+      <c r="D1139">
+        <v>70428</v>
+      </c>
+      <c r="E1139">
+        <v>179855</v>
+      </c>
+    </row>
+    <row r="1140" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1140" s="1">
+        <v>46317</v>
+      </c>
+      <c r="B1140">
+        <v>101</v>
+      </c>
+      <c r="C1140" t="s">
+        <v>8</v>
+      </c>
+      <c r="D1140">
+        <v>70415</v>
+      </c>
+      <c r="E1140">
+        <v>179835</v>
+      </c>
+    </row>
+    <row r="1141" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1141" s="1">
+        <v>46317</v>
+      </c>
+      <c r="B1141">
+        <v>101</v>
+      </c>
+      <c r="C1141" t="s">
+        <v>11</v>
+      </c>
+      <c r="D1141">
+        <v>70345</v>
+      </c>
+      <c r="E1141">
+        <v>179772</v>
+      </c>
+    </row>
+    <row r="1142" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1142" s="1">
+        <v>46317</v>
+      </c>
+      <c r="B1142">
+        <v>101</v>
+      </c>
+      <c r="C1142" t="s">
+        <v>11</v>
+      </c>
+      <c r="D1142">
+        <v>70427</v>
+      </c>
+      <c r="E1142">
+        <v>179854</v>
+      </c>
+    </row>
+    <row r="1143" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1143" s="1">
+        <v>46317</v>
+      </c>
+      <c r="B1143">
+        <v>101</v>
+      </c>
+      <c r="C1143" t="s">
+        <v>19</v>
+      </c>
+      <c r="D1143">
+        <v>69683</v>
+      </c>
+      <c r="E1143">
+        <v>179338</v>
+      </c>
+    </row>
+    <row r="1144" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1144" s="1">
+        <v>46317</v>
+      </c>
+      <c r="B1144">
+        <v>101</v>
+      </c>
+      <c r="C1144" t="s">
+        <v>223</v>
+      </c>
+      <c r="D1144">
+        <v>70546</v>
+      </c>
+      <c r="E1144">
+        <v>180023</v>
+      </c>
+    </row>
+    <row r="1145" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1145" s="1">
+        <v>46317</v>
+      </c>
+      <c r="B1145">
+        <v>101</v>
+      </c>
+      <c r="C1145" t="s">
+        <v>224</v>
+      </c>
+      <c r="D1145">
+        <v>70461</v>
+      </c>
+      <c r="E1145">
+        <v>180009</v>
+      </c>
+    </row>
+    <row r="1146" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1146" s="1">
+        <v>46317</v>
+      </c>
+      <c r="B1146">
+        <v>101</v>
+      </c>
+      <c r="C1146" t="s">
+        <v>225</v>
+      </c>
+      <c r="D1146">
+        <v>70558</v>
+      </c>
+      <c r="E1146">
+        <v>180047</v>
+      </c>
+    </row>
+    <row r="1147" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1147" s="1">
+        <v>46317</v>
+      </c>
+      <c r="B1147">
+        <v>101</v>
+      </c>
+      <c r="C1147" t="s">
+        <v>19</v>
+      </c>
+      <c r="D1147">
+        <v>69076</v>
+      </c>
+      <c r="E1147">
+        <v>180037</v>
+      </c>
+    </row>
+    <row r="1148" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1148" s="1">
+        <v>46317</v>
+      </c>
+      <c r="B1148">
+        <v>101</v>
+      </c>
+      <c r="C1148" t="s">
+        <v>19</v>
+      </c>
+      <c r="E1148">
+        <v>180036</v>
+      </c>
+    </row>
+    <row r="1149" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1149" s="1">
+        <v>46317</v>
+      </c>
+      <c r="B1149">
+        <v>101</v>
+      </c>
+      <c r="C1149" t="s">
+        <v>19</v>
+      </c>
+      <c r="D1149">
+        <v>69220</v>
+      </c>
+      <c r="E1149">
+        <v>180053</v>
+      </c>
+    </row>
+    <row r="1150" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1150" s="1">
+        <v>46317</v>
+      </c>
+      <c r="B1150">
+        <v>101</v>
+      </c>
+      <c r="C1150" t="s">
+        <v>19</v>
+      </c>
+      <c r="D1150">
+        <v>70016</v>
+      </c>
+      <c r="E1150">
+        <v>180008</v>
+      </c>
+    </row>
+    <row r="1151" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1151" s="1">
+        <v>46317</v>
+      </c>
+      <c r="B1151">
+        <v>101</v>
+      </c>
+      <c r="C1151" t="s">
+        <v>19</v>
+      </c>
+      <c r="D1151">
+        <v>70491</v>
+      </c>
+      <c r="E1151">
+        <v>180031</v>
+      </c>
+    </row>
+    <row r="1152" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1152" s="1">
+        <v>46318</v>
+      </c>
+      <c r="B1152">
+        <v>101</v>
+      </c>
+      <c r="C1152" t="s">
+        <v>226</v>
+      </c>
+      <c r="D1152">
+        <v>70251</v>
+      </c>
+      <c r="E1152">
+        <v>179735</v>
+      </c>
+    </row>
+    <row r="1153" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1153" s="1">
+        <v>46318</v>
+      </c>
+      <c r="B1153">
+        <v>101</v>
+      </c>
+      <c r="C1153" t="s">
+        <v>227</v>
+      </c>
+      <c r="D1153">
+        <v>67458</v>
+      </c>
+      <c r="E1153">
+        <v>179484</v>
+      </c>
+    </row>
+    <row r="1154" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1154" s="1">
+        <v>46318</v>
+      </c>
+      <c r="B1154">
+        <v>101</v>
+      </c>
+      <c r="C1154" t="s">
+        <v>227</v>
+      </c>
+      <c r="D1154">
+        <v>65934</v>
+      </c>
+      <c r="E1154">
+        <v>179995</v>
+      </c>
+    </row>
+    <row r="1155" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1155" s="1">
+        <v>46318</v>
+      </c>
+      <c r="B1155">
+        <v>101</v>
+      </c>
+      <c r="C1155" t="s">
+        <v>228</v>
+      </c>
+      <c r="D1155">
+        <v>70476</v>
+      </c>
+      <c r="E1155">
+        <v>180026</v>
+      </c>
+    </row>
+    <row r="1156" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1156" s="1">
+        <v>46318</v>
+      </c>
+      <c r="B1156">
+        <v>101</v>
+      </c>
+      <c r="C1156" t="s">
+        <v>227</v>
+      </c>
+      <c r="D1156">
+        <v>67001</v>
+      </c>
+      <c r="E1156">
+        <v>179932</v>
+      </c>
+    </row>
+    <row r="1157" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1157" s="1">
+        <v>46318</v>
+      </c>
+      <c r="B1157">
+        <v>101</v>
+      </c>
+      <c r="C1157" t="s">
+        <v>229</v>
+      </c>
+      <c r="E1157">
+        <v>179791</v>
+      </c>
+    </row>
+    <row r="1158" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1158" s="1">
+        <v>46318</v>
+      </c>
+      <c r="B1158">
+        <v>101</v>
+      </c>
+      <c r="C1158" t="s">
+        <v>230</v>
+      </c>
+      <c r="D1158">
+        <v>70244</v>
+      </c>
+      <c r="E1158">
+        <v>180097</v>
+      </c>
+    </row>
+    <row r="1159" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1159" s="1">
+        <v>46318</v>
+      </c>
+      <c r="B1159">
+        <v>101</v>
+      </c>
+      <c r="C1159" t="s">
+        <v>15</v>
+      </c>
+      <c r="D1159">
+        <v>69957</v>
+      </c>
+      <c r="E1159">
+        <v>180076</v>
+      </c>
+    </row>
+    <row r="1160" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1160" s="1">
+        <v>46318</v>
+      </c>
+      <c r="B1160">
+        <v>101</v>
+      </c>
+      <c r="C1160" t="s">
+        <v>229</v>
+      </c>
+      <c r="D1160">
+        <v>68450</v>
+      </c>
+      <c r="E1160">
+        <v>180015</v>
+      </c>
+    </row>
+    <row r="1161" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1161" s="1">
+        <v>46318</v>
+      </c>
+      <c r="B1161">
+        <v>101</v>
+      </c>
+      <c r="C1161" t="s">
+        <v>20</v>
+      </c>
+      <c r="E1161">
+        <v>180007</v>
+      </c>
+    </row>
+    <row r="1162" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1162" s="1">
+        <v>46318</v>
+      </c>
+      <c r="B1162">
+        <v>101</v>
+      </c>
+      <c r="C1162" t="s">
+        <v>177</v>
+      </c>
+      <c r="D1162">
+        <v>70202</v>
+      </c>
+      <c r="E1162">
+        <v>180079</v>
+      </c>
+    </row>
+    <row r="1163" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1163" s="1">
+        <v>46318</v>
+      </c>
+      <c r="B1163">
+        <v>101</v>
+      </c>
+      <c r="C1163" t="s">
+        <v>20</v>
+      </c>
+      <c r="D1163">
+        <v>70547</v>
+      </c>
+      <c r="E1163">
+        <v>180029</v>
+      </c>
+    </row>
+    <row r="1164" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1164" s="1">
+        <v>46318</v>
+      </c>
+      <c r="B1164">
+        <v>101</v>
+      </c>
+      <c r="C1164" t="s">
+        <v>20</v>
+      </c>
+      <c r="D1164">
+        <v>69205</v>
+      </c>
+      <c r="E1164">
+        <v>180033</v>
+      </c>
+    </row>
+    <row r="1165" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1165" s="1">
+        <v>46318</v>
+      </c>
+      <c r="B1165">
+        <v>101</v>
+      </c>
+      <c r="C1165" t="s">
+        <v>27</v>
+      </c>
+      <c r="D1165">
+        <v>69541</v>
+      </c>
+      <c r="E1165">
+        <v>180040</v>
+      </c>
+    </row>
+    <row r="1166" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1166" s="1">
+        <v>46318</v>
+      </c>
+      <c r="B1166">
+        <v>101</v>
+      </c>
+      <c r="C1166" t="s">
+        <v>27</v>
+      </c>
+      <c r="D1166">
+        <v>70539</v>
+      </c>
+      <c r="E1166">
+        <v>180032</v>
+      </c>
+    </row>
+    <row r="1167" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1167" s="1">
+        <v>46318</v>
+      </c>
+      <c r="B1167">
+        <v>101</v>
+      </c>
+      <c r="C1167" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1167">
+        <v>69190</v>
+      </c>
+      <c r="E1167">
+        <v>179986</v>
+      </c>
+    </row>
+    <row r="1168" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1168" s="1">
+        <v>46318</v>
+      </c>
+      <c r="B1168">
+        <v>101</v>
+      </c>
+      <c r="C1168" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1168">
+        <v>68053</v>
+      </c>
+      <c r="E1168">
+        <v>177772</v>
+      </c>
+    </row>
+    <row r="1169" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1169" s="1">
+        <v>46318</v>
+      </c>
+      <c r="B1169">
+        <v>101</v>
+      </c>
+      <c r="C1169" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1169">
+        <v>67487</v>
+      </c>
+      <c r="E1169">
+        <v>178428</v>
+      </c>
+    </row>
+    <row r="1170" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1170" s="1">
+        <v>46318</v>
+      </c>
+      <c r="B1170">
+        <v>101</v>
+      </c>
+      <c r="C1170" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1170">
+        <v>70052</v>
+      </c>
+      <c r="E1170">
+        <v>179910</v>
+      </c>
+    </row>
+    <row r="1171" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1171" s="1">
+        <v>46318</v>
+      </c>
+      <c r="B1171">
+        <v>101</v>
+      </c>
+      <c r="C1171" t="s">
+        <v>26</v>
+      </c>
+      <c r="D1171">
+        <v>69580</v>
+      </c>
+      <c r="E1171">
+        <v>180102</v>
+      </c>
+    </row>
+    <row r="1172" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1172" s="1">
+        <v>46318</v>
+      </c>
+      <c r="B1172">
+        <v>101</v>
+      </c>
+      <c r="C1172" t="s">
+        <v>26</v>
+      </c>
+      <c r="D1172">
+        <v>70551</v>
+      </c>
+      <c r="E1172">
+        <v>180083</v>
+      </c>
+    </row>
+    <row r="1173" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1173" s="1">
+        <v>46318</v>
+      </c>
+      <c r="B1173">
+        <v>101</v>
+      </c>
+      <c r="C1173" t="s">
+        <v>112</v>
+      </c>
+      <c r="D1173">
+        <v>70212</v>
+      </c>
+      <c r="E1173">
+        <v>180070</v>
+      </c>
+    </row>
+    <row r="1174" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1174" s="1">
+        <v>46318</v>
+      </c>
+      <c r="B1174">
+        <v>101</v>
+      </c>
+      <c r="C1174" t="s">
+        <v>39</v>
+      </c>
+      <c r="D1174">
+        <v>70478</v>
+      </c>
+      <c r="E1174">
+        <v>180034</v>
+      </c>
+    </row>
+    <row r="1175" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1175" s="1">
+        <v>46318</v>
+      </c>
+      <c r="B1175">
+        <v>101</v>
+      </c>
+      <c r="C1175" t="s">
+        <v>15</v>
+      </c>
+      <c r="D1175">
+        <v>70449</v>
+      </c>
+      <c r="E1175">
+        <v>180035</v>
+      </c>
+    </row>
+    <row r="1176" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1176" s="1">
+        <v>46318</v>
+      </c>
+      <c r="B1176">
+        <v>101</v>
+      </c>
+      <c r="C1176" t="s">
+        <v>163</v>
+      </c>
+      <c r="D1176">
+        <v>70528</v>
+      </c>
+      <c r="E1176">
+        <v>180062</v>
+      </c>
+    </row>
+    <row r="1177" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1177" s="1">
+        <v>46318</v>
+      </c>
+      <c r="B1177">
+        <v>101</v>
+      </c>
+      <c r="C1177" t="s">
+        <v>32</v>
+      </c>
+      <c r="D1177">
+        <v>70312</v>
+      </c>
+      <c r="E1177">
+        <v>180003</v>
+      </c>
+    </row>
+    <row r="1178" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1178" s="1">
+        <v>46318</v>
+      </c>
+      <c r="B1178">
+        <v>101</v>
+      </c>
+      <c r="C1178" t="s">
+        <v>231</v>
+      </c>
+      <c r="D1178">
+        <v>69815</v>
+      </c>
+      <c r="E1178">
+        <v>180095</v>
+      </c>
+    </row>
+    <row r="1179" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1179" s="1">
+        <v>46318</v>
+      </c>
+      <c r="B1179">
+        <v>101</v>
+      </c>
+      <c r="C1179" t="s">
+        <v>0</v>
+      </c>
+      <c r="D1179">
+        <v>69897</v>
+      </c>
+      <c r="E1179">
+        <v>180024</v>
+      </c>
+    </row>
+    <row r="1180" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1180" s="1">
+        <v>46318</v>
+      </c>
+      <c r="B1180">
+        <v>101</v>
+      </c>
+      <c r="C1180" t="s">
+        <v>0</v>
+      </c>
+      <c r="E1180">
+        <v>180058</v>
+      </c>
+    </row>
+    <row r="1181" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1181" s="1">
+        <v>46318</v>
+      </c>
+      <c r="B1181">
+        <v>101</v>
+      </c>
+      <c r="C1181" t="s">
+        <v>0</v>
+      </c>
+      <c r="D1181">
+        <v>70167</v>
+      </c>
+      <c r="E1181">
+        <v>180075</v>
+      </c>
+    </row>
+    <row r="1182" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1182" s="1">
+        <v>46318</v>
+      </c>
+      <c r="B1182">
+        <v>101</v>
+      </c>
+      <c r="C1182" t="s">
+        <v>0</v>
+      </c>
+      <c r="D1182">
+        <v>69404</v>
+      </c>
+      <c r="E1182">
+        <v>179115</v>
+      </c>
+    </row>
+    <row r="1183" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1183" s="1">
+        <v>46318</v>
+      </c>
+      <c r="B1183">
+        <v>101</v>
+      </c>
+      <c r="C1183" t="s">
+        <v>0</v>
+      </c>
+      <c r="D1183">
+        <v>66212</v>
+      </c>
+      <c r="E1183">
+        <v>179111</v>
+      </c>
+    </row>
+    <row r="1184" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1184" s="1">
+        <v>46318</v>
+      </c>
+      <c r="B1184">
+        <v>101</v>
+      </c>
+      <c r="C1184" t="s">
+        <v>0</v>
+      </c>
+      <c r="D1184">
+        <v>69048</v>
+      </c>
+      <c r="E1184">
+        <v>179550</v>
+      </c>
+    </row>
+    <row r="1185" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1185" s="1">
+        <v>46318</v>
+      </c>
+      <c r="B1185">
+        <v>101</v>
+      </c>
+      <c r="C1185" t="s">
+        <v>0</v>
+      </c>
+      <c r="D1185">
+        <v>69453</v>
+      </c>
+      <c r="E1185">
+        <v>179319</v>
+      </c>
+    </row>
+    <row r="1186" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1186" s="1">
+        <v>46318</v>
+      </c>
+      <c r="B1186">
+        <v>101</v>
+      </c>
+      <c r="C1186" t="s">
+        <v>0</v>
+      </c>
+      <c r="E1186">
+        <v>179907</v>
+      </c>
+    </row>
+    <row r="1187" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1187" s="1">
+        <v>46318</v>
+      </c>
+      <c r="B1187">
+        <v>101</v>
+      </c>
+      <c r="C1187" t="s">
+        <v>0</v>
+      </c>
+      <c r="D1187">
+        <v>68735</v>
+      </c>
+      <c r="E1187">
+        <v>179107</v>
+      </c>
+    </row>
+    <row r="1188" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1188" s="1">
+        <v>46318</v>
+      </c>
+      <c r="B1188">
+        <v>101</v>
+      </c>
+      <c r="C1188" t="s">
+        <v>0</v>
+      </c>
+      <c r="D1188">
+        <v>69698</v>
+      </c>
+      <c r="E1188">
+        <v>179993</v>
+      </c>
+    </row>
+    <row r="1189" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1189" s="1">
+        <v>46318</v>
+      </c>
+      <c r="B1189">
+        <v>101</v>
+      </c>
+      <c r="C1189" t="s">
+        <v>0</v>
+      </c>
+      <c r="D1189">
+        <v>69902</v>
+      </c>
+      <c r="E1189">
+        <v>179366</v>
+      </c>
+    </row>
+    <row r="1190" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1190" s="1">
+        <v>46318</v>
+      </c>
+      <c r="B1190">
+        <v>101</v>
+      </c>
+      <c r="C1190" t="s">
+        <v>0</v>
+      </c>
+      <c r="E1190">
+        <v>179992</v>
+      </c>
+    </row>
+    <row r="1191" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1191" s="1">
+        <v>46318</v>
+      </c>
+      <c r="B1191">
+        <v>101</v>
+      </c>
+      <c r="C1191" t="s">
+        <v>0</v>
+      </c>
+      <c r="D1191">
+        <v>68748</v>
+      </c>
+      <c r="E1191">
+        <v>179066</v>
+      </c>
+    </row>
+    <row r="1192" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1192" s="1">
+        <v>46318</v>
+      </c>
+      <c r="B1192">
+        <v>101</v>
+      </c>
+      <c r="C1192" t="s">
+        <v>0</v>
+      </c>
+      <c r="E1192">
+        <v>180068</v>
+      </c>
+    </row>
+    <row r="1193" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1193" s="1">
+        <v>46318</v>
+      </c>
+      <c r="B1193">
+        <v>101</v>
+      </c>
+      <c r="C1193" t="s">
+        <v>0</v>
+      </c>
+      <c r="D1193">
+        <v>70495</v>
+      </c>
+      <c r="E1193">
+        <v>179994</v>
+      </c>
+    </row>
+    <row r="1194" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1194" s="1">
+        <v>46318</v>
+      </c>
+      <c r="B1194">
+        <v>101</v>
+      </c>
+      <c r="C1194" t="s">
+        <v>0</v>
+      </c>
+      <c r="D1194">
+        <v>63892</v>
+      </c>
+      <c r="E1194">
+        <v>180051</v>
+      </c>
+    </row>
+    <row r="1195" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1195" s="1">
+        <v>46318</v>
+      </c>
+      <c r="B1195">
+        <v>101</v>
+      </c>
+      <c r="C1195" t="s">
+        <v>0</v>
+      </c>
+      <c r="D1195">
+        <v>69398</v>
+      </c>
+      <c r="E1195">
+        <v>179106</v>
+      </c>
+    </row>
+    <row r="1196" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1196" s="1">
+        <v>46318</v>
+      </c>
+      <c r="B1196">
+        <v>101</v>
+      </c>
+      <c r="C1196" t="s">
+        <v>0</v>
+      </c>
+      <c r="D1196">
+        <v>69043</v>
+      </c>
+      <c r="E1196">
+        <v>180011</v>
+      </c>
+    </row>
+    <row r="1197" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1197" s="1">
+        <v>46318</v>
+      </c>
+      <c r="B1197">
+        <v>101</v>
+      </c>
+      <c r="C1197" t="s">
+        <v>0</v>
+      </c>
+      <c r="D1197">
+        <v>70124</v>
+      </c>
+      <c r="E1197">
+        <v>179812</v>
+      </c>
+    </row>
+    <row r="1198" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1198" s="1">
+        <v>46318</v>
+      </c>
+      <c r="B1198">
+        <v>101</v>
+      </c>
+      <c r="C1198" t="s">
+        <v>0</v>
+      </c>
+      <c r="D1198">
+        <v>69147</v>
+      </c>
+      <c r="E1198">
+        <v>180100</v>
+      </c>
+    </row>
+    <row r="1199" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1199" s="1">
+        <v>46318</v>
+      </c>
+      <c r="B1199">
+        <v>101</v>
+      </c>
+      <c r="C1199" t="s">
+        <v>0</v>
+      </c>
+      <c r="E1199">
+        <v>179914</v>
+      </c>
+    </row>
+    <row r="1200" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1200" s="1">
+        <v>46318</v>
+      </c>
+      <c r="B1200">
+        <v>101</v>
+      </c>
+      <c r="C1200" t="s">
+        <v>0</v>
+      </c>
+      <c r="D1200">
+        <v>69443</v>
+      </c>
+      <c r="E1200">
+        <v>180093</v>
+      </c>
+    </row>
+    <row r="1201" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1201" s="1">
+        <v>46318</v>
+      </c>
+      <c r="B1201">
+        <v>101</v>
+      </c>
+      <c r="C1201" t="s">
+        <v>0</v>
+      </c>
+      <c r="E1201">
+        <v>180016</v>
+      </c>
+    </row>
+    <row r="1202" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1202" s="1">
+        <v>46318</v>
+      </c>
+      <c r="B1202">
+        <v>101</v>
+      </c>
+      <c r="C1202" t="s">
+        <v>0</v>
+      </c>
+      <c r="D1202">
+        <v>69849</v>
+      </c>
+      <c r="E1202">
+        <v>180010</v>
+      </c>
+    </row>
+    <row r="1203" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1203" s="1">
+        <v>46318</v>
+      </c>
+      <c r="B1203">
+        <v>101</v>
+      </c>
+      <c r="C1203" t="s">
+        <v>0</v>
+      </c>
+      <c r="D1203">
+        <v>70304</v>
+      </c>
+      <c r="E1203">
+        <v>180067</v>
+      </c>
+    </row>
+    <row r="1204" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1204" s="1">
+        <v>46318</v>
+      </c>
+      <c r="B1204">
+        <v>101</v>
+      </c>
+      <c r="C1204" t="s">
+        <v>80</v>
+      </c>
+      <c r="D1204">
+        <v>70466</v>
+      </c>
+      <c r="E1204">
+        <v>179957</v>
+      </c>
+    </row>
+    <row r="1205" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1205" s="1">
+        <v>46318</v>
+      </c>
+      <c r="B1205">
+        <v>101</v>
+      </c>
+      <c r="C1205" t="s">
+        <v>50</v>
+      </c>
+      <c r="D1205">
+        <v>70475</v>
+      </c>
+      <c r="E1205">
+        <v>180049</v>
+      </c>
+    </row>
+    <row r="1206" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1206" s="1">
+        <v>46318</v>
+      </c>
+      <c r="B1206">
+        <v>101</v>
+      </c>
+      <c r="C1206" t="s">
+        <v>80</v>
+      </c>
+      <c r="E1206">
+        <v>180060</v>
+      </c>
+    </row>
+    <row r="1207" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1207" s="1">
+        <v>46318</v>
+      </c>
+      <c r="B1207">
+        <v>101</v>
+      </c>
+      <c r="C1207" t="s">
+        <v>51</v>
+      </c>
+      <c r="D1207">
+        <v>70477</v>
+      </c>
+      <c r="E1207">
+        <v>180055</v>
+      </c>
+    </row>
+    <row r="1208" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1208" s="1">
+        <v>46318</v>
+      </c>
+      <c r="B1208">
+        <v>101</v>
+      </c>
+      <c r="C1208" t="s">
+        <v>52</v>
+      </c>
+      <c r="D1208">
+        <v>70483</v>
+      </c>
+      <c r="E1208">
+        <v>180056</v>
+      </c>
+    </row>
+    <row r="1209" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1209" s="1">
+        <v>46318</v>
+      </c>
+      <c r="B1209">
+        <v>101</v>
+      </c>
+      <c r="C1209" t="s">
+        <v>54</v>
+      </c>
+      <c r="D1209">
+        <v>70486</v>
+      </c>
+      <c r="E1209">
+        <v>180045</v>
+      </c>
+    </row>
+    <row r="1210" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1210" s="1">
+        <v>46318</v>
+      </c>
+      <c r="B1210">
+        <v>101</v>
+      </c>
+      <c r="C1210" t="s">
+        <v>53</v>
+      </c>
+      <c r="D1210">
+        <v>70485</v>
+      </c>
+      <c r="E1210">
+        <v>180054</v>
+      </c>
+    </row>
+    <row r="1211" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1211" s="1">
+        <v>46318</v>
+      </c>
+      <c r="B1211">
+        <v>101</v>
+      </c>
+      <c r="C1211" t="s">
+        <v>232</v>
+      </c>
+      <c r="D1211">
+        <v>70489</v>
+      </c>
+      <c r="E1211">
+        <v>180044</v>
+      </c>
+    </row>
+    <row r="1212" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1212" s="1">
+        <v>46318</v>
+      </c>
+      <c r="B1212">
+        <v>101</v>
+      </c>
+      <c r="C1212" t="s">
+        <v>23</v>
+      </c>
+      <c r="E1212">
+        <v>179596</v>
+      </c>
+    </row>
+    <row r="1213" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1213" s="1">
+        <v>46318</v>
+      </c>
+      <c r="B1213">
+        <v>101</v>
+      </c>
+      <c r="C1213" t="s">
+        <v>23</v>
+      </c>
+      <c r="D1213">
+        <v>70518</v>
+      </c>
+      <c r="E1213">
+        <v>180048</v>
+      </c>
+    </row>
+    <row r="1214" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1214" s="1">
+        <v>46318</v>
+      </c>
+      <c r="B1214">
+        <v>101</v>
+      </c>
+      <c r="C1214" t="s">
+        <v>69</v>
+      </c>
+      <c r="D1214">
+        <v>68142</v>
+      </c>
+      <c r="E1214">
+        <v>180028</v>
+      </c>
+    </row>
+    <row r="1215" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1215" s="1">
+        <v>46318</v>
+      </c>
+      <c r="B1215">
+        <v>101</v>
+      </c>
+      <c r="C1215" t="s">
+        <v>23</v>
+      </c>
+      <c r="D1215">
+        <v>70388</v>
+      </c>
+      <c r="E1215">
+        <v>179924</v>
+      </c>
+    </row>
+    <row r="1216" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1216" s="1">
+        <v>46318</v>
+      </c>
+      <c r="B1216">
+        <v>101</v>
+      </c>
+      <c r="C1216" t="s">
+        <v>84</v>
+      </c>
+      <c r="D1216">
+        <v>70526</v>
+      </c>
+      <c r="E1216">
+        <v>180061</v>
+      </c>
+    </row>
+    <row r="1217" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1217" s="1">
+        <v>46318</v>
+      </c>
+      <c r="B1217">
+        <v>101</v>
+      </c>
+      <c r="C1217" t="s">
+        <v>0</v>
+      </c>
+      <c r="D1217">
+        <v>70140</v>
+      </c>
+      <c r="E1217">
+        <v>180074</v>
+      </c>
+    </row>
+    <row r="1218" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1218" s="1">
+        <v>46318</v>
+      </c>
+      <c r="B1218">
+        <v>101</v>
+      </c>
+      <c r="C1218" t="s">
+        <v>0</v>
+      </c>
+      <c r="D1218">
+        <v>69450</v>
+      </c>
+      <c r="E1218">
+        <v>179322</v>
+      </c>
+    </row>
+    <row r="1219" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1219" s="1">
+        <v>46318</v>
+      </c>
+      <c r="B1219">
+        <v>101</v>
+      </c>
+      <c r="C1219" t="s">
+        <v>89</v>
+      </c>
+      <c r="D1219">
+        <v>70530</v>
+      </c>
+      <c r="E1219">
+        <v>180027</v>
+      </c>
+    </row>
+    <row r="1220" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1220" s="1">
+        <v>46318</v>
+      </c>
+      <c r="B1220">
+        <v>101</v>
+      </c>
+      <c r="C1220" t="s">
+        <v>55</v>
+      </c>
+      <c r="D1220">
+        <v>70529</v>
+      </c>
+      <c r="E1220">
+        <v>180046</v>
+      </c>
+    </row>
+    <row r="1221" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1221" s="1">
+        <v>46318</v>
+      </c>
+      <c r="B1221">
+        <v>101</v>
+      </c>
+      <c r="C1221" t="s">
+        <v>0</v>
+      </c>
+      <c r="E1221">
+        <v>180057</v>
+      </c>
+    </row>
+    <row r="1222" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1222" s="1">
+        <v>46318</v>
+      </c>
+      <c r="B1222">
+        <v>101</v>
+      </c>
+      <c r="C1222" t="s">
+        <v>0</v>
+      </c>
+      <c r="D1222">
+        <v>69492</v>
+      </c>
+      <c r="E1222">
+        <v>180050</v>
+      </c>
+    </row>
+    <row r="1223" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1223" s="1">
+        <v>46318</v>
+      </c>
+      <c r="B1223">
+        <v>101</v>
+      </c>
+      <c r="C1223" t="s">
+        <v>60</v>
+      </c>
+      <c r="D1223">
+        <v>70504</v>
+      </c>
+      <c r="E1223">
+        <v>180066</v>
+      </c>
+    </row>
+    <row r="1224" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1224" s="1">
+        <v>46318</v>
+      </c>
+      <c r="B1224">
+        <v>101</v>
+      </c>
+      <c r="C1224" t="s">
+        <v>0</v>
+      </c>
+      <c r="D1224">
+        <v>69863</v>
+      </c>
+      <c r="E1224">
+        <v>180084</v>
+      </c>
+    </row>
+    <row r="1225" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1225" s="1">
+        <v>46318</v>
+      </c>
+      <c r="B1225">
+        <v>101</v>
+      </c>
+      <c r="C1225" t="s">
+        <v>58</v>
+      </c>
+      <c r="D1225">
+        <v>70254</v>
+      </c>
+      <c r="E1225">
+        <v>180082</v>
+      </c>
+    </row>
+    <row r="1226" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1226" s="1">
+        <v>46318</v>
+      </c>
+      <c r="B1226">
+        <v>101</v>
+      </c>
+      <c r="C1226" t="s">
+        <v>0</v>
+      </c>
+      <c r="D1226">
+        <v>70218</v>
+      </c>
+      <c r="E1226">
+        <v>180072</v>
+      </c>
+    </row>
+    <row r="1227" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1227" s="1">
+        <v>46318</v>
+      </c>
+      <c r="B1227">
+        <v>101</v>
+      </c>
+      <c r="C1227" t="s">
+        <v>60</v>
+      </c>
+      <c r="D1227">
+        <v>70056</v>
+      </c>
+      <c r="E1227">
+        <v>180059</v>
+      </c>
+    </row>
   </sheetData>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:E719">
     <sortCondition ref="A703:A719"/>
@@ -18492,7 +21618,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5180BF9C-1943-4030-8A1B-6F86FE205C17}">
-  <dimension ref="A1:C16"/>
+  <dimension ref="A1:C18"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="12.85546875" style="1" bestFit="1" customWidth="1"/>
@@ -18501,7 +21627,7 @@
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="str" cm="1">
-        <f t="array" ref="A1:A16">_xlfn.UNIQUE(Romaneios!A1:A1041)</f>
+        <f t="array" ref="A1:A18">_xlfn.UNIQUE(Romaneios!A1:A1227)</f>
         <v>Dt. Romaneio</v>
       </c>
       <c r="B1" t="s">
@@ -18642,6 +21768,24 @@
       <c r="B16">
         <f>COUNTIF(Romaneios!A:A,DadosRomaneios!A16)</f>
         <v>123</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A17" s="1">
+        <v>46317</v>
+      </c>
+      <c r="B17">
+        <f>COUNTIF(Romaneios!A:A,DadosRomaneios!A17)</f>
+        <v>110</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A18" s="1">
+        <v>46318</v>
+      </c>
+      <c r="B18">
+        <f>COUNTIF(Romaneios!A:A,DadosRomaneios!A18)</f>
+        <v>76</v>
       </c>
     </row>
   </sheetData>

--- a/DadosRomaneios.xlsx
+++ b/DadosRomaneios.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="U:\AcompanhamentoProducao\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1320ED70-5104-45CE-8E00-A8C7073D0C1F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7324FDFC-D845-40F9-A46A-88EADD39320A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" activeTab="1" xr2:uid="{B6976704-8E51-4052-B60A-5847F95A5AE5}"/>
   </bookViews>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
-<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xlrd="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
+<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
   <metadataTypes count="1">
     <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
   </metadataTypes>
@@ -62,7 +62,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1232" uniqueCount="233">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1240" uniqueCount="233">
   <si>
     <t>ALBERT EINSTEIN</t>
   </si>
@@ -1140,7 +1140,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BF29A37F-A1D1-4315-91AB-A952895E1E73}">
-  <dimension ref="A1:E1227"/>
+  <dimension ref="A1:E1235"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="12.85546875" bestFit="1" customWidth="1"/>
@@ -21605,6 +21605,139 @@
       </c>
       <c r="E1227">
         <v>180059</v>
+      </c>
+    </row>
+    <row r="1228" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1228" s="1">
+        <v>46318</v>
+      </c>
+      <c r="B1228">
+        <v>106</v>
+      </c>
+      <c r="C1228" t="s">
+        <v>40</v>
+      </c>
+      <c r="D1228">
+        <v>574</v>
+      </c>
+      <c r="E1228">
+        <v>558</v>
+      </c>
+    </row>
+    <row r="1229" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1229" s="1">
+        <v>46318</v>
+      </c>
+      <c r="B1229">
+        <v>106</v>
+      </c>
+      <c r="C1229" t="s">
+        <v>40</v>
+      </c>
+      <c r="D1229">
+        <v>575</v>
+      </c>
+      <c r="E1229">
+        <v>559</v>
+      </c>
+    </row>
+    <row r="1230" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1230" s="1">
+        <v>46318</v>
+      </c>
+      <c r="B1230">
+        <v>101</v>
+      </c>
+      <c r="C1230" t="s">
+        <v>7</v>
+      </c>
+      <c r="D1230">
+        <v>70452</v>
+      </c>
+      <c r="E1230">
+        <v>180125</v>
+      </c>
+    </row>
+    <row r="1231" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1231" s="1">
+        <v>46318</v>
+      </c>
+      <c r="B1231">
+        <v>106</v>
+      </c>
+      <c r="C1231" t="s">
+        <v>24</v>
+      </c>
+      <c r="D1231">
+        <v>580</v>
+      </c>
+      <c r="E1231">
+        <v>564</v>
+      </c>
+    </row>
+    <row r="1232" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1232" s="1">
+        <v>46318</v>
+      </c>
+      <c r="B1232">
+        <v>106</v>
+      </c>
+      <c r="C1232" t="s">
+        <v>24</v>
+      </c>
+      <c r="D1232">
+        <v>579</v>
+      </c>
+      <c r="E1232">
+        <v>563</v>
+      </c>
+    </row>
+    <row r="1233" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1233" s="1">
+        <v>46318</v>
+      </c>
+      <c r="B1233">
+        <v>101</v>
+      </c>
+      <c r="C1233" t="s">
+        <v>15</v>
+      </c>
+      <c r="D1233">
+        <v>70200</v>
+      </c>
+      <c r="E1233">
+        <v>180126</v>
+      </c>
+    </row>
+    <row r="1234" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1234" s="1">
+        <v>46318</v>
+      </c>
+      <c r="B1234">
+        <v>101</v>
+      </c>
+      <c r="C1234" t="s">
+        <v>15</v>
+      </c>
+      <c r="E1234">
+        <v>179651</v>
+      </c>
+    </row>
+    <row r="1235" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1235" s="1">
+        <v>46318</v>
+      </c>
+      <c r="B1235">
+        <v>101</v>
+      </c>
+      <c r="C1235" t="s">
+        <v>19</v>
+      </c>
+      <c r="D1235">
+        <v>70781</v>
+      </c>
+      <c r="E1235">
+        <v>180167</v>
       </c>
     </row>
   </sheetData>
@@ -21785,7 +21918,7 @@
       </c>
       <c r="B18">
         <f>COUNTIF(Romaneios!A:A,DadosRomaneios!A18)</f>
-        <v>76</v>
+        <v>84</v>
       </c>
     </row>
   </sheetData>

--- a/DadosRomaneios.xlsx
+++ b/DadosRomaneios.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30527"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="U:\AcompanhamentoProducao\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7324FDFC-D845-40F9-A46A-88EADD39320A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{018B7132-3AFE-486A-80D5-7C9526D7904D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" activeTab="1" xr2:uid="{B6976704-8E51-4052-B60A-5847F95A5AE5}"/>
   </bookViews>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
-<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
+<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xlrd="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
   <metadataTypes count="1">
     <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
   </metadataTypes>
@@ -62,7 +62,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1240" uniqueCount="233">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1303" uniqueCount="247">
   <si>
     <t>ALBERT EINSTEIN</t>
   </si>
@@ -761,6 +761,48 @@
   </si>
   <si>
     <t>TEC LAB 51.131.969/0</t>
+  </si>
+  <si>
+    <t>CLINICA GUARIBA</t>
+  </si>
+  <si>
+    <t>AMPARO MATERNAL SPDM</t>
+  </si>
+  <si>
+    <t>CLEANING SOLUTIONS C</t>
+  </si>
+  <si>
+    <t>SECONCI CENTRO</t>
+  </si>
+  <si>
+    <t>CLINICA JD PRIMAVERA</t>
+  </si>
+  <si>
+    <t>DIAGNOSTICO GUAIRA</t>
+  </si>
+  <si>
+    <t>PRUDENTE DE MORAES</t>
+  </si>
+  <si>
+    <t>SAMHO-INTERMEDICA</t>
+  </si>
+  <si>
+    <t>ESPACO SAUDE II</t>
+  </si>
+  <si>
+    <t>CLIN NOVO HORIZONTE</t>
+  </si>
+  <si>
+    <t>CLINICA PRADOPOLIS</t>
+  </si>
+  <si>
+    <t>CLINICA LUIS ANTONIO</t>
+  </si>
+  <si>
+    <t>POSTO COL LIMEIRA</t>
+  </si>
+  <si>
+    <t>TRE TRIBUNAL</t>
   </si>
 </sst>
 </file>
@@ -1140,7 +1182,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BF29A37F-A1D1-4315-91AB-A952895E1E73}">
-  <dimension ref="A1:E1235"/>
+  <dimension ref="A1:E1298"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="12.85546875" bestFit="1" customWidth="1"/>
@@ -21740,6 +21782,1065 @@
         <v>180167</v>
       </c>
     </row>
+    <row r="1236" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1236" s="1">
+        <v>46318</v>
+      </c>
+      <c r="B1236">
+        <v>101</v>
+      </c>
+      <c r="C1236" t="s">
+        <v>5</v>
+      </c>
+      <c r="D1236">
+        <v>70147</v>
+      </c>
+      <c r="E1236">
+        <v>179964</v>
+      </c>
+    </row>
+    <row r="1237" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1237" s="1">
+        <v>46318</v>
+      </c>
+      <c r="B1237">
+        <v>101</v>
+      </c>
+      <c r="C1237" t="s">
+        <v>141</v>
+      </c>
+      <c r="D1237">
+        <v>70465</v>
+      </c>
+      <c r="E1237">
+        <v>180014</v>
+      </c>
+    </row>
+    <row r="1238" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1238" s="1">
+        <v>46318</v>
+      </c>
+      <c r="B1238">
+        <v>101</v>
+      </c>
+      <c r="C1238" t="s">
+        <v>89</v>
+      </c>
+      <c r="D1238">
+        <v>70562</v>
+      </c>
+      <c r="E1238">
+        <v>180092</v>
+      </c>
+    </row>
+    <row r="1239" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1239" s="1">
+        <v>46318</v>
+      </c>
+      <c r="B1239">
+        <v>101</v>
+      </c>
+      <c r="C1239" t="s">
+        <v>7</v>
+      </c>
+      <c r="D1239">
+        <v>70412</v>
+      </c>
+      <c r="E1239">
+        <v>179832</v>
+      </c>
+    </row>
+    <row r="1240" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1240" s="1">
+        <v>46318</v>
+      </c>
+      <c r="B1240">
+        <v>101</v>
+      </c>
+      <c r="C1240" t="s">
+        <v>119</v>
+      </c>
+      <c r="D1240">
+        <v>70702</v>
+      </c>
+      <c r="E1240">
+        <v>180164</v>
+      </c>
+    </row>
+    <row r="1241" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1241" s="1">
+        <v>46318</v>
+      </c>
+      <c r="B1241">
+        <v>101</v>
+      </c>
+      <c r="C1241" t="s">
+        <v>119</v>
+      </c>
+      <c r="D1241">
+        <v>70712</v>
+      </c>
+      <c r="E1241">
+        <v>180174</v>
+      </c>
+    </row>
+    <row r="1242" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1242" s="1">
+        <v>46318</v>
+      </c>
+      <c r="B1242">
+        <v>101</v>
+      </c>
+      <c r="C1242" t="s">
+        <v>119</v>
+      </c>
+      <c r="D1242">
+        <v>70707</v>
+      </c>
+      <c r="E1242">
+        <v>180168</v>
+      </c>
+    </row>
+    <row r="1243" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1243" s="1">
+        <v>46318</v>
+      </c>
+      <c r="B1243">
+        <v>101</v>
+      </c>
+      <c r="C1243" t="s">
+        <v>119</v>
+      </c>
+      <c r="D1243">
+        <v>70703</v>
+      </c>
+      <c r="E1243">
+        <v>180165</v>
+      </c>
+    </row>
+    <row r="1244" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1244" s="1">
+        <v>46318</v>
+      </c>
+      <c r="B1244">
+        <v>101</v>
+      </c>
+      <c r="C1244" t="s">
+        <v>119</v>
+      </c>
+      <c r="D1244">
+        <v>70708</v>
+      </c>
+      <c r="E1244">
+        <v>180169</v>
+      </c>
+    </row>
+    <row r="1245" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1245" s="1">
+        <v>46318</v>
+      </c>
+      <c r="B1245">
+        <v>101</v>
+      </c>
+      <c r="C1245" t="s">
+        <v>119</v>
+      </c>
+      <c r="D1245">
+        <v>70706</v>
+      </c>
+      <c r="E1245">
+        <v>180166</v>
+      </c>
+    </row>
+    <row r="1246" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1246" s="1">
+        <v>46318</v>
+      </c>
+      <c r="B1246">
+        <v>101</v>
+      </c>
+      <c r="C1246" t="s">
+        <v>119</v>
+      </c>
+      <c r="D1246">
+        <v>70709</v>
+      </c>
+      <c r="E1246">
+        <v>180172</v>
+      </c>
+    </row>
+    <row r="1247" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1247" s="1">
+        <v>46318</v>
+      </c>
+      <c r="B1247">
+        <v>101</v>
+      </c>
+      <c r="C1247" t="s">
+        <v>119</v>
+      </c>
+      <c r="D1247">
+        <v>70711</v>
+      </c>
+      <c r="E1247">
+        <v>180173</v>
+      </c>
+    </row>
+    <row r="1248" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1248" s="1">
+        <v>46319</v>
+      </c>
+      <c r="B1248">
+        <v>101</v>
+      </c>
+      <c r="C1248" t="s">
+        <v>89</v>
+      </c>
+      <c r="D1248">
+        <v>70455</v>
+      </c>
+      <c r="E1248">
+        <v>180142</v>
+      </c>
+    </row>
+    <row r="1249" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1249" s="1">
+        <v>46319</v>
+      </c>
+      <c r="B1249">
+        <v>101</v>
+      </c>
+      <c r="C1249" t="s">
+        <v>233</v>
+      </c>
+      <c r="D1249">
+        <v>69915</v>
+      </c>
+      <c r="E1249">
+        <v>179448</v>
+      </c>
+    </row>
+    <row r="1250" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1250" s="1">
+        <v>46319</v>
+      </c>
+      <c r="B1250">
+        <v>101</v>
+      </c>
+      <c r="C1250" t="s">
+        <v>233</v>
+      </c>
+      <c r="D1250">
+        <v>69913</v>
+      </c>
+      <c r="E1250">
+        <v>179252</v>
+      </c>
+    </row>
+    <row r="1251" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1251" s="1">
+        <v>46321</v>
+      </c>
+      <c r="B1251">
+        <v>101</v>
+      </c>
+      <c r="C1251" t="s">
+        <v>94</v>
+      </c>
+      <c r="D1251">
+        <v>70561</v>
+      </c>
+      <c r="E1251">
+        <v>180148</v>
+      </c>
+    </row>
+    <row r="1252" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1252" s="1">
+        <v>46321</v>
+      </c>
+      <c r="B1252">
+        <v>101</v>
+      </c>
+      <c r="C1252" t="s">
+        <v>234</v>
+      </c>
+      <c r="D1252">
+        <v>70591</v>
+      </c>
+      <c r="E1252">
+        <v>180114</v>
+      </c>
+    </row>
+    <row r="1253" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1253" s="1">
+        <v>46321</v>
+      </c>
+      <c r="B1253">
+        <v>101</v>
+      </c>
+      <c r="C1253" t="s">
+        <v>234</v>
+      </c>
+      <c r="D1253">
+        <v>69944</v>
+      </c>
+      <c r="E1253">
+        <v>180099</v>
+      </c>
+    </row>
+    <row r="1254" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1254" s="1">
+        <v>46321</v>
+      </c>
+      <c r="B1254">
+        <v>101</v>
+      </c>
+      <c r="C1254" t="s">
+        <v>94</v>
+      </c>
+      <c r="D1254">
+        <v>70535</v>
+      </c>
+      <c r="E1254">
+        <v>180131</v>
+      </c>
+    </row>
+    <row r="1255" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1255" s="1">
+        <v>46321</v>
+      </c>
+      <c r="B1255">
+        <v>101</v>
+      </c>
+      <c r="C1255" t="s">
+        <v>94</v>
+      </c>
+      <c r="D1255">
+        <v>70536</v>
+      </c>
+      <c r="E1255">
+        <v>180158</v>
+      </c>
+    </row>
+    <row r="1256" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1256" s="1">
+        <v>46321</v>
+      </c>
+      <c r="B1256">
+        <v>101</v>
+      </c>
+      <c r="C1256" t="s">
+        <v>235</v>
+      </c>
+      <c r="D1256">
+        <v>70550</v>
+      </c>
+      <c r="E1256">
+        <v>180149</v>
+      </c>
+    </row>
+    <row r="1257" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1257" s="1">
+        <v>46321</v>
+      </c>
+      <c r="B1257">
+        <v>101</v>
+      </c>
+      <c r="C1257" t="s">
+        <v>98</v>
+      </c>
+      <c r="D1257">
+        <v>70610</v>
+      </c>
+      <c r="E1257">
+        <v>180130</v>
+      </c>
+    </row>
+    <row r="1258" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1258" s="1">
+        <v>46321</v>
+      </c>
+      <c r="B1258">
+        <v>101</v>
+      </c>
+      <c r="C1258" t="s">
+        <v>37</v>
+      </c>
+      <c r="D1258">
+        <v>69632</v>
+      </c>
+      <c r="E1258">
+        <v>180155</v>
+      </c>
+    </row>
+    <row r="1259" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1259" s="1">
+        <v>46321</v>
+      </c>
+      <c r="B1259">
+        <v>101</v>
+      </c>
+      <c r="C1259" t="s">
+        <v>166</v>
+      </c>
+      <c r="D1259">
+        <v>69542</v>
+      </c>
+      <c r="E1259">
+        <v>180145</v>
+      </c>
+    </row>
+    <row r="1260" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1260" s="1">
+        <v>46321</v>
+      </c>
+      <c r="B1260">
+        <v>101</v>
+      </c>
+      <c r="C1260" t="s">
+        <v>26</v>
+      </c>
+      <c r="D1260">
+        <v>69579</v>
+      </c>
+      <c r="E1260">
+        <v>180143</v>
+      </c>
+    </row>
+    <row r="1261" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1261" s="1">
+        <v>46321</v>
+      </c>
+      <c r="B1261">
+        <v>101</v>
+      </c>
+      <c r="C1261" t="s">
+        <v>25</v>
+      </c>
+      <c r="D1261">
+        <v>68463</v>
+      </c>
+      <c r="E1261">
+        <v>180184</v>
+      </c>
+    </row>
+    <row r="1262" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1262" s="1">
+        <v>46321</v>
+      </c>
+      <c r="B1262">
+        <v>101</v>
+      </c>
+      <c r="C1262" t="s">
+        <v>25</v>
+      </c>
+      <c r="E1262">
+        <v>180094</v>
+      </c>
+    </row>
+    <row r="1263" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1263" s="1">
+        <v>46321</v>
+      </c>
+      <c r="B1263">
+        <v>101</v>
+      </c>
+      <c r="C1263" t="s">
+        <v>25</v>
+      </c>
+      <c r="D1263">
+        <v>67323</v>
+      </c>
+      <c r="E1263">
+        <v>180087</v>
+      </c>
+    </row>
+    <row r="1264" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1264" s="1">
+        <v>46321</v>
+      </c>
+      <c r="B1264">
+        <v>101</v>
+      </c>
+      <c r="C1264" t="s">
+        <v>24</v>
+      </c>
+      <c r="D1264">
+        <v>70524</v>
+      </c>
+      <c r="E1264">
+        <v>180113</v>
+      </c>
+    </row>
+    <row r="1265" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1265" s="1">
+        <v>46321</v>
+      </c>
+      <c r="B1265">
+        <v>101</v>
+      </c>
+      <c r="C1265" t="s">
+        <v>39</v>
+      </c>
+      <c r="D1265">
+        <v>69960</v>
+      </c>
+      <c r="E1265">
+        <v>180115</v>
+      </c>
+    </row>
+    <row r="1266" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1266" s="1">
+        <v>46321</v>
+      </c>
+      <c r="B1266">
+        <v>101</v>
+      </c>
+      <c r="C1266" t="s">
+        <v>23</v>
+      </c>
+      <c r="D1266">
+        <v>70389</v>
+      </c>
+      <c r="E1266">
+        <v>180183</v>
+      </c>
+    </row>
+    <row r="1267" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1267" s="1">
+        <v>46321</v>
+      </c>
+      <c r="B1267">
+        <v>101</v>
+      </c>
+      <c r="C1267" t="s">
+        <v>0</v>
+      </c>
+      <c r="E1267">
+        <v>180147</v>
+      </c>
+    </row>
+    <row r="1268" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1268" s="1">
+        <v>46321</v>
+      </c>
+      <c r="B1268">
+        <v>101</v>
+      </c>
+      <c r="C1268" t="s">
+        <v>0</v>
+      </c>
+      <c r="E1268">
+        <v>179955</v>
+      </c>
+    </row>
+    <row r="1269" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1269" s="1">
+        <v>46321</v>
+      </c>
+      <c r="B1269">
+        <v>101</v>
+      </c>
+      <c r="C1269" t="s">
+        <v>41</v>
+      </c>
+      <c r="D1269">
+        <v>70602</v>
+      </c>
+      <c r="E1269">
+        <v>180137</v>
+      </c>
+    </row>
+    <row r="1270" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1270" s="1">
+        <v>46321</v>
+      </c>
+      <c r="B1270">
+        <v>101</v>
+      </c>
+      <c r="C1270" t="s">
+        <v>0</v>
+      </c>
+      <c r="D1270">
+        <v>69727</v>
+      </c>
+      <c r="E1270">
+        <v>180088</v>
+      </c>
+    </row>
+    <row r="1271" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1271" s="1">
+        <v>46321</v>
+      </c>
+      <c r="B1271">
+        <v>101</v>
+      </c>
+      <c r="C1271" t="s">
+        <v>89</v>
+      </c>
+      <c r="D1271">
+        <v>70194</v>
+      </c>
+      <c r="E1271">
+        <v>180116</v>
+      </c>
+    </row>
+    <row r="1272" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1272" s="1">
+        <v>46321</v>
+      </c>
+      <c r="B1272">
+        <v>101</v>
+      </c>
+      <c r="C1272" t="s">
+        <v>57</v>
+      </c>
+      <c r="D1272">
+        <v>70603</v>
+      </c>
+      <c r="E1272">
+        <v>180122</v>
+      </c>
+    </row>
+    <row r="1273" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1273" s="1">
+        <v>46321</v>
+      </c>
+      <c r="B1273">
+        <v>101</v>
+      </c>
+      <c r="C1273" t="s">
+        <v>0</v>
+      </c>
+      <c r="E1273">
+        <v>180133</v>
+      </c>
+    </row>
+    <row r="1274" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1274" s="1">
+        <v>46321</v>
+      </c>
+      <c r="B1274">
+        <v>101</v>
+      </c>
+      <c r="C1274" t="s">
+        <v>15</v>
+      </c>
+      <c r="D1274">
+        <v>70514</v>
+      </c>
+      <c r="E1274">
+        <v>180157</v>
+      </c>
+    </row>
+    <row r="1275" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1275" s="1">
+        <v>46321</v>
+      </c>
+      <c r="B1275">
+        <v>101</v>
+      </c>
+      <c r="C1275" t="s">
+        <v>89</v>
+      </c>
+      <c r="D1275">
+        <v>70612</v>
+      </c>
+      <c r="E1275">
+        <v>180140</v>
+      </c>
+    </row>
+    <row r="1276" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1276" s="1">
+        <v>46321</v>
+      </c>
+      <c r="B1276">
+        <v>101</v>
+      </c>
+      <c r="C1276" t="s">
+        <v>57</v>
+      </c>
+      <c r="D1276">
+        <v>70606</v>
+      </c>
+      <c r="E1276">
+        <v>180123</v>
+      </c>
+    </row>
+    <row r="1277" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1277" s="1">
+        <v>46321</v>
+      </c>
+      <c r="B1277">
+        <v>101</v>
+      </c>
+      <c r="C1277" t="s">
+        <v>58</v>
+      </c>
+      <c r="D1277">
+        <v>69951</v>
+      </c>
+      <c r="E1277">
+        <v>179944</v>
+      </c>
+    </row>
+    <row r="1278" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1278" s="1">
+        <v>46321</v>
+      </c>
+      <c r="B1278">
+        <v>101</v>
+      </c>
+      <c r="C1278" t="s">
+        <v>60</v>
+      </c>
+      <c r="D1278">
+        <v>70110</v>
+      </c>
+      <c r="E1278">
+        <v>180129</v>
+      </c>
+    </row>
+    <row r="1279" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1279" s="1">
+        <v>46321</v>
+      </c>
+      <c r="B1279">
+        <v>101</v>
+      </c>
+      <c r="C1279" t="s">
+        <v>60</v>
+      </c>
+      <c r="D1279">
+        <v>70115</v>
+      </c>
+      <c r="E1279">
+        <v>180098</v>
+      </c>
+    </row>
+    <row r="1280" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1280" s="1">
+        <v>46321</v>
+      </c>
+      <c r="B1280">
+        <v>101</v>
+      </c>
+      <c r="C1280" t="s">
+        <v>39</v>
+      </c>
+      <c r="D1280">
+        <v>70151</v>
+      </c>
+      <c r="E1280">
+        <v>180152</v>
+      </c>
+    </row>
+    <row r="1281" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1281" s="1">
+        <v>46321</v>
+      </c>
+      <c r="B1281">
+        <v>101</v>
+      </c>
+      <c r="C1281" t="s">
+        <v>236</v>
+      </c>
+      <c r="D1281">
+        <v>69947</v>
+      </c>
+      <c r="E1281">
+        <v>180112</v>
+      </c>
+    </row>
+    <row r="1282" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1282" s="1">
+        <v>46321</v>
+      </c>
+      <c r="B1282">
+        <v>101</v>
+      </c>
+      <c r="C1282" t="s">
+        <v>60</v>
+      </c>
+      <c r="D1282">
+        <v>70587</v>
+      </c>
+      <c r="E1282">
+        <v>180135</v>
+      </c>
+    </row>
+    <row r="1283" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1283" s="1">
+        <v>46321</v>
+      </c>
+      <c r="B1283">
+        <v>101</v>
+      </c>
+      <c r="C1283" t="s">
+        <v>93</v>
+      </c>
+      <c r="D1283">
+        <v>70555</v>
+      </c>
+      <c r="E1283">
+        <v>180110</v>
+      </c>
+    </row>
+    <row r="1284" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1284" s="1">
+        <v>46321</v>
+      </c>
+      <c r="B1284">
+        <v>101</v>
+      </c>
+      <c r="C1284" t="s">
+        <v>237</v>
+      </c>
+      <c r="D1284">
+        <v>69271</v>
+      </c>
+      <c r="E1284">
+        <v>178345</v>
+      </c>
+    </row>
+    <row r="1285" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1285" s="1">
+        <v>46321</v>
+      </c>
+      <c r="B1285">
+        <v>101</v>
+      </c>
+      <c r="C1285" t="s">
+        <v>238</v>
+      </c>
+      <c r="D1285">
+        <v>69734</v>
+      </c>
+      <c r="E1285">
+        <v>178794</v>
+      </c>
+    </row>
+    <row r="1286" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1286" s="1">
+        <v>46321</v>
+      </c>
+      <c r="B1286">
+        <v>101</v>
+      </c>
+      <c r="C1286" t="s">
+        <v>239</v>
+      </c>
+      <c r="D1286">
+        <v>69270</v>
+      </c>
+      <c r="E1286">
+        <v>178344</v>
+      </c>
+    </row>
+    <row r="1287" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1287" s="1">
+        <v>46321</v>
+      </c>
+      <c r="B1287">
+        <v>101</v>
+      </c>
+      <c r="C1287" t="s">
+        <v>240</v>
+      </c>
+      <c r="D1287">
+        <v>69109</v>
+      </c>
+      <c r="E1287">
+        <v>178217</v>
+      </c>
+    </row>
+    <row r="1288" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1288" s="1">
+        <v>46321</v>
+      </c>
+      <c r="B1288">
+        <v>101</v>
+      </c>
+      <c r="C1288" t="s">
+        <v>241</v>
+      </c>
+      <c r="D1288">
+        <v>69196</v>
+      </c>
+      <c r="E1288">
+        <v>178258</v>
+      </c>
+    </row>
+    <row r="1289" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1289" s="1">
+        <v>46321</v>
+      </c>
+      <c r="B1289">
+        <v>101</v>
+      </c>
+      <c r="C1289" t="s">
+        <v>242</v>
+      </c>
+      <c r="D1289">
+        <v>70134</v>
+      </c>
+      <c r="E1289">
+        <v>179445</v>
+      </c>
+    </row>
+    <row r="1290" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1290" s="1">
+        <v>46321</v>
+      </c>
+      <c r="B1290">
+        <v>101</v>
+      </c>
+      <c r="C1290" t="s">
+        <v>19</v>
+      </c>
+      <c r="D1290">
+        <v>69677</v>
+      </c>
+      <c r="E1290">
+        <v>178766</v>
+      </c>
+    </row>
+    <row r="1291" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1291" s="1">
+        <v>46321</v>
+      </c>
+      <c r="B1291">
+        <v>101</v>
+      </c>
+      <c r="C1291" t="s">
+        <v>240</v>
+      </c>
+      <c r="D1291">
+        <v>69134</v>
+      </c>
+      <c r="E1291">
+        <v>178218</v>
+      </c>
+    </row>
+    <row r="1292" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1292" s="1">
+        <v>46321</v>
+      </c>
+      <c r="B1292">
+        <v>101</v>
+      </c>
+      <c r="C1292" t="s">
+        <v>19</v>
+      </c>
+      <c r="D1292">
+        <v>69733</v>
+      </c>
+      <c r="E1292">
+        <v>178793</v>
+      </c>
+    </row>
+    <row r="1293" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1293" s="1">
+        <v>46321</v>
+      </c>
+      <c r="B1293">
+        <v>101</v>
+      </c>
+      <c r="C1293" t="s">
+        <v>243</v>
+      </c>
+      <c r="D1293">
+        <v>70135</v>
+      </c>
+      <c r="E1293">
+        <v>179446</v>
+      </c>
+    </row>
+    <row r="1294" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1294" s="1">
+        <v>46321</v>
+      </c>
+      <c r="B1294">
+        <v>101</v>
+      </c>
+      <c r="C1294" t="s">
+        <v>244</v>
+      </c>
+      <c r="D1294">
+        <v>69920</v>
+      </c>
+      <c r="E1294">
+        <v>179452</v>
+      </c>
+    </row>
+    <row r="1295" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1295" s="1">
+        <v>46321</v>
+      </c>
+      <c r="B1295">
+        <v>101</v>
+      </c>
+      <c r="C1295" t="s">
+        <v>244</v>
+      </c>
+      <c r="D1295">
+        <v>69921</v>
+      </c>
+      <c r="E1295">
+        <v>179453</v>
+      </c>
+    </row>
+    <row r="1296" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1296" s="1">
+        <v>46321</v>
+      </c>
+      <c r="B1296">
+        <v>101</v>
+      </c>
+      <c r="C1296" t="s">
+        <v>245</v>
+      </c>
+      <c r="D1296">
+        <v>68101</v>
+      </c>
+      <c r="E1296">
+        <v>179552</v>
+      </c>
+    </row>
+    <row r="1297" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1297" s="1">
+        <v>46321</v>
+      </c>
+      <c r="B1297">
+        <v>101</v>
+      </c>
+      <c r="C1297" t="s">
+        <v>246</v>
+      </c>
+      <c r="D1297">
+        <v>70583</v>
+      </c>
+      <c r="E1297">
+        <v>180196</v>
+      </c>
+    </row>
+    <row r="1298" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1298" s="1">
+        <v>46321</v>
+      </c>
+      <c r="B1298">
+        <v>101</v>
+      </c>
+      <c r="C1298" t="s">
+        <v>246</v>
+      </c>
+      <c r="D1298">
+        <v>70585</v>
+      </c>
+      <c r="E1298">
+        <v>180195</v>
+      </c>
+    </row>
   </sheetData>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:E719">
     <sortCondition ref="A703:A719"/>
@@ -21751,7 +22852,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5180BF9C-1943-4030-8A1B-6F86FE205C17}">
-  <dimension ref="A1:C18"/>
+  <dimension ref="A1:C20"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="12.85546875" style="1" bestFit="1" customWidth="1"/>
@@ -21760,7 +22861,7 @@
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="str" cm="1">
-        <f t="array" ref="A1:A18">_xlfn.UNIQUE(Romaneios!A1:A1227)</f>
+        <f t="array" ref="A1:A20">_xlfn.UNIQUE(Romaneios!A1:A1298)</f>
         <v>Dt. Romaneio</v>
       </c>
       <c r="B1" t="s">
@@ -21918,7 +23019,25 @@
       </c>
       <c r="B18">
         <f>COUNTIF(Romaneios!A:A,DadosRomaneios!A18)</f>
-        <v>84</v>
+        <v>96</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A19" s="1">
+        <v>46319</v>
+      </c>
+      <c r="B19">
+        <f>COUNTIF(Romaneios!A:A,DadosRomaneios!A19)</f>
+        <v>3</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A20" s="1">
+        <v>46321</v>
+      </c>
+      <c r="B20">
+        <f>COUNTIF(Romaneios!A:A,DadosRomaneios!A20)</f>
+        <v>48</v>
       </c>
     </row>
   </sheetData>

--- a/DadosRomaneios.xlsx
+++ b/DadosRomaneios.xlsx
@@ -8,13 +8,14 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="U:\AcompanhamentoProducao\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{018B7132-3AFE-486A-80D5-7C9526D7904D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{31618FE5-6DD6-4CE7-95AF-CD9F14D1B7BF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" activeTab="1" xr2:uid="{B6976704-8E51-4052-B60A-5847F95A5AE5}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" activeTab="2" xr2:uid="{B6976704-8E51-4052-B60A-5847F95A5AE5}"/>
   </bookViews>
   <sheets>
     <sheet name="Romaneios" sheetId="2" r:id="rId1"/>
-    <sheet name="DadosRomaneios" sheetId="3" r:id="rId2"/>
+    <sheet name="Planilha1" sheetId="4" r:id="rId2"/>
+    <sheet name="DadosRomaneios" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -40,7 +41,7 @@
 </file>
 
 <file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
-<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xlrd="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
+<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
   <metadataTypes count="1">
     <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
   </metadataTypes>
@@ -62,7 +63,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1303" uniqueCount="247">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1336" uniqueCount="259">
   <si>
     <t>ALBERT EINSTEIN</t>
   </si>
@@ -803,6 +804,42 @@
   </si>
   <si>
     <t>TRE TRIBUNAL</t>
+  </si>
+  <si>
+    <t>000011 - 001</t>
+  </si>
+  <si>
+    <t>000020 - 010</t>
+  </si>
+  <si>
+    <t>000020 - 106</t>
+  </si>
+  <si>
+    <t>DASA UNIDADE CENTRAL</t>
+  </si>
+  <si>
+    <t>000020 - 504</t>
+  </si>
+  <si>
+    <t>DASA LAB NOBEL S.</t>
+  </si>
+  <si>
+    <t>000020 - 625</t>
+  </si>
+  <si>
+    <t>000020 - 009</t>
+  </si>
+  <si>
+    <t>003558 - 001</t>
+  </si>
+  <si>
+    <t>000020 - 008</t>
+  </si>
+  <si>
+    <t>001240 - 008</t>
+  </si>
+  <si>
+    <t>003098 - 001</t>
   </si>
 </sst>
 </file>
@@ -1182,7 +1219,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BF29A37F-A1D1-4315-91AB-A952895E1E73}">
-  <dimension ref="A1:E1298"/>
+  <dimension ref="A1:E1309"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="12.85546875" bestFit="1" customWidth="1"/>
@@ -22841,6 +22878,181 @@
         <v>180195</v>
       </c>
     </row>
+    <row r="1299" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1299" s="1">
+        <v>46321</v>
+      </c>
+      <c r="B1299">
+        <v>101</v>
+      </c>
+      <c r="C1299" t="s">
+        <v>6</v>
+      </c>
+      <c r="D1299">
+        <v>68158</v>
+      </c>
+      <c r="E1299">
+        <v>180146</v>
+      </c>
+    </row>
+    <row r="1300" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1300" s="1">
+        <v>46321</v>
+      </c>
+      <c r="B1300">
+        <v>101</v>
+      </c>
+      <c r="C1300" t="s">
+        <v>6</v>
+      </c>
+      <c r="E1300">
+        <v>180198</v>
+      </c>
+    </row>
+    <row r="1301" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1301" s="1">
+        <v>46321</v>
+      </c>
+      <c r="B1301">
+        <v>101</v>
+      </c>
+      <c r="C1301" t="s">
+        <v>61</v>
+      </c>
+      <c r="E1301">
+        <v>180180</v>
+      </c>
+    </row>
+    <row r="1302" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1302" s="1">
+        <v>46321</v>
+      </c>
+      <c r="B1302">
+        <v>101</v>
+      </c>
+      <c r="C1302" t="s">
+        <v>250</v>
+      </c>
+      <c r="D1302">
+        <v>70595</v>
+      </c>
+      <c r="E1302">
+        <v>180179</v>
+      </c>
+    </row>
+    <row r="1303" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1303" s="1">
+        <v>46321</v>
+      </c>
+      <c r="B1303">
+        <v>101</v>
+      </c>
+      <c r="C1303" t="s">
+        <v>252</v>
+      </c>
+      <c r="E1303">
+        <v>180127</v>
+      </c>
+    </row>
+    <row r="1304" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1304" s="1">
+        <v>46321</v>
+      </c>
+      <c r="B1304">
+        <v>101</v>
+      </c>
+      <c r="C1304" t="s">
+        <v>45</v>
+      </c>
+      <c r="D1304">
+        <v>69877</v>
+      </c>
+      <c r="E1304">
+        <v>179609</v>
+      </c>
+    </row>
+    <row r="1305" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1305" s="1">
+        <v>46321</v>
+      </c>
+      <c r="B1305">
+        <v>101</v>
+      </c>
+      <c r="C1305" t="s">
+        <v>65</v>
+      </c>
+      <c r="D1305">
+        <v>70567</v>
+      </c>
+      <c r="E1305">
+        <v>180128</v>
+      </c>
+    </row>
+    <row r="1306" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1306" s="1">
+        <v>46321</v>
+      </c>
+      <c r="B1306">
+        <v>101</v>
+      </c>
+      <c r="C1306" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1306">
+        <v>70650</v>
+      </c>
+      <c r="E1306">
+        <v>180144</v>
+      </c>
+    </row>
+    <row r="1307" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1307" s="1">
+        <v>46321</v>
+      </c>
+      <c r="B1307">
+        <v>101</v>
+      </c>
+      <c r="C1307" t="s">
+        <v>64</v>
+      </c>
+      <c r="E1307">
+        <v>180153</v>
+      </c>
+    </row>
+    <row r="1308" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1308" s="1">
+        <v>46321</v>
+      </c>
+      <c r="B1308">
+        <v>101</v>
+      </c>
+      <c r="C1308" t="s">
+        <v>159</v>
+      </c>
+      <c r="D1308">
+        <v>70688</v>
+      </c>
+      <c r="E1308">
+        <v>180124</v>
+      </c>
+    </row>
+    <row r="1309" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1309" s="1">
+        <v>46321</v>
+      </c>
+      <c r="B1309">
+        <v>101</v>
+      </c>
+      <c r="C1309" t="s">
+        <v>246</v>
+      </c>
+      <c r="D1309">
+        <v>70605</v>
+      </c>
+      <c r="E1309">
+        <v>180269</v>
+      </c>
+    </row>
   </sheetData>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:E719">
     <sortCondition ref="A703:A719"/>
@@ -22851,6 +23063,191 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{436A81F1-C523-4C8F-89BB-A715EFC34A51}">
+  <dimension ref="A1:E11"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetData>
+    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1">
+        <v>101</v>
+      </c>
+      <c r="B1" t="s">
+        <v>247</v>
+      </c>
+      <c r="C1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D1">
+        <v>68158</v>
+      </c>
+      <c r="E1">
+        <v>180146</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A2">
+        <v>101</v>
+      </c>
+      <c r="B2" t="s">
+        <v>247</v>
+      </c>
+      <c r="C2" t="s">
+        <v>6</v>
+      </c>
+      <c r="E2">
+        <v>180198</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A3">
+        <v>101</v>
+      </c>
+      <c r="B3" t="s">
+        <v>248</v>
+      </c>
+      <c r="C3" t="s">
+        <v>61</v>
+      </c>
+      <c r="E3">
+        <v>180180</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4">
+        <v>101</v>
+      </c>
+      <c r="B4" t="s">
+        <v>249</v>
+      </c>
+      <c r="C4" t="s">
+        <v>250</v>
+      </c>
+      <c r="D4">
+        <v>70595</v>
+      </c>
+      <c r="E4">
+        <v>180179</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A5">
+        <v>101</v>
+      </c>
+      <c r="B5" t="s">
+        <v>251</v>
+      </c>
+      <c r="C5" t="s">
+        <v>252</v>
+      </c>
+      <c r="E5">
+        <v>180127</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A6">
+        <v>101</v>
+      </c>
+      <c r="B6" t="s">
+        <v>253</v>
+      </c>
+      <c r="C6" t="s">
+        <v>45</v>
+      </c>
+      <c r="D6">
+        <v>69877</v>
+      </c>
+      <c r="E6">
+        <v>179609</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A7">
+        <v>101</v>
+      </c>
+      <c r="B7" t="s">
+        <v>254</v>
+      </c>
+      <c r="C7" t="s">
+        <v>65</v>
+      </c>
+      <c r="D7">
+        <v>70567</v>
+      </c>
+      <c r="E7">
+        <v>180128</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A8">
+        <v>101</v>
+      </c>
+      <c r="B8" t="s">
+        <v>255</v>
+      </c>
+      <c r="C8" t="s">
+        <v>4</v>
+      </c>
+      <c r="D8">
+        <v>70650</v>
+      </c>
+      <c r="E8">
+        <v>180144</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A9">
+        <v>101</v>
+      </c>
+      <c r="B9" t="s">
+        <v>256</v>
+      </c>
+      <c r="C9" t="s">
+        <v>64</v>
+      </c>
+      <c r="E9">
+        <v>180153</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A10">
+        <v>101</v>
+      </c>
+      <c r="B10" t="s">
+        <v>257</v>
+      </c>
+      <c r="C10" t="s">
+        <v>159</v>
+      </c>
+      <c r="D10">
+        <v>70688</v>
+      </c>
+      <c r="E10">
+        <v>180124</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A11">
+        <v>101</v>
+      </c>
+      <c r="B11" t="s">
+        <v>258</v>
+      </c>
+      <c r="C11" t="s">
+        <v>246</v>
+      </c>
+      <c r="D11">
+        <v>70605</v>
+      </c>
+      <c r="E11">
+        <v>180269</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5180BF9C-1943-4030-8A1B-6F86FE205C17}">
   <dimension ref="A1:C20"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -23037,7 +23434,7 @@
       </c>
       <c r="B20">
         <f>COUNTIF(Romaneios!A:A,DadosRomaneios!A20)</f>
-        <v>48</v>
+        <v>59</v>
       </c>
     </row>
   </sheetData>

--- a/DadosRomaneios.xlsx
+++ b/DadosRomaneios.xlsx
@@ -8,14 +8,13 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="U:\AcompanhamentoProducao\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{31618FE5-6DD6-4CE7-95AF-CD9F14D1B7BF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6CDB642E-E946-46AC-854D-9A91E4011754}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" activeTab="2" xr2:uid="{B6976704-8E51-4052-B60A-5847F95A5AE5}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" activeTab="1" xr2:uid="{B6976704-8E51-4052-B60A-5847F95A5AE5}"/>
   </bookViews>
   <sheets>
     <sheet name="Romaneios" sheetId="2" r:id="rId1"/>
-    <sheet name="Planilha1" sheetId="4" r:id="rId2"/>
-    <sheet name="DadosRomaneios" sheetId="3" r:id="rId3"/>
+    <sheet name="DadosRomaneios" sheetId="3" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -41,7 +40,7 @@
 </file>
 
 <file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
-<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
+<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xlrd="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
   <metadataTypes count="1">
     <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
   </metadataTypes>
@@ -63,7 +62,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1336" uniqueCount="259">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1434" uniqueCount="254">
   <si>
     <t>ALBERT EINSTEIN</t>
   </si>
@@ -806,40 +805,25 @@
     <t>TRE TRIBUNAL</t>
   </si>
   <si>
-    <t>000011 - 001</t>
-  </si>
-  <si>
-    <t>000020 - 010</t>
-  </si>
-  <si>
-    <t>000020 - 106</t>
-  </si>
-  <si>
     <t>DASA UNIDADE CENTRAL</t>
   </si>
   <si>
-    <t>000020 - 504</t>
-  </si>
-  <si>
     <t>DASA LAB NOBEL S.</t>
   </si>
   <si>
-    <t>000020 - 625</t>
-  </si>
-  <si>
-    <t>000020 - 009</t>
-  </si>
-  <si>
-    <t>003558 - 001</t>
-  </si>
-  <si>
-    <t>000020 - 008</t>
-  </si>
-  <si>
-    <t>001240 - 008</t>
-  </si>
-  <si>
-    <t>003098 - 001</t>
+    <t>HOSPITAL SAO JOSE</t>
+  </si>
+  <si>
+    <t>MATRIZ</t>
+  </si>
+  <si>
+    <t>ALTHAIA</t>
+  </si>
+  <si>
+    <t>DASA 61.486.650/0686</t>
+  </si>
+  <si>
+    <t>JPM SERVICOS</t>
   </si>
 </sst>
 </file>
@@ -1219,7 +1203,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BF29A37F-A1D1-4315-91AB-A952895E1E73}">
-  <dimension ref="A1:E1309"/>
+  <dimension ref="A1:E1429"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="12.85546875" bestFit="1" customWidth="1"/>
@@ -1857,7 +1841,7 @@
         <v>46303</v>
       </c>
       <c r="B38">
-        <v>101</v>
+        <v>0</v>
       </c>
       <c r="C38" t="s">
         <v>13</v>
@@ -22931,7 +22915,7 @@
         <v>101</v>
       </c>
       <c r="C1302" t="s">
-        <v>250</v>
+        <v>247</v>
       </c>
       <c r="D1302">
         <v>70595</v>
@@ -22948,7 +22932,7 @@
         <v>101</v>
       </c>
       <c r="C1303" t="s">
-        <v>252</v>
+        <v>248</v>
       </c>
       <c r="E1303">
         <v>180127</v>
@@ -23051,6 +23035,1998 @@
       </c>
       <c r="E1309">
         <v>180269</v>
+      </c>
+    </row>
+    <row r="1310" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1310" s="1">
+        <v>46321</v>
+      </c>
+      <c r="B1310">
+        <v>101</v>
+      </c>
+      <c r="C1310" t="s">
+        <v>89</v>
+      </c>
+      <c r="D1310">
+        <v>70584</v>
+      </c>
+      <c r="E1310">
+        <v>180182</v>
+      </c>
+    </row>
+    <row r="1311" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1311" s="1">
+        <v>46321</v>
+      </c>
+      <c r="B1311">
+        <v>101</v>
+      </c>
+      <c r="C1311" t="s">
+        <v>70</v>
+      </c>
+      <c r="E1311">
+        <v>180132</v>
+      </c>
+    </row>
+    <row r="1312" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1312" s="1">
+        <v>46321</v>
+      </c>
+      <c r="B1312">
+        <v>101</v>
+      </c>
+      <c r="C1312" t="s">
+        <v>141</v>
+      </c>
+      <c r="D1312">
+        <v>70559</v>
+      </c>
+      <c r="E1312">
+        <v>180151</v>
+      </c>
+    </row>
+    <row r="1313" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1313" s="1">
+        <v>46321</v>
+      </c>
+      <c r="B1313">
+        <v>101</v>
+      </c>
+      <c r="C1313" t="s">
+        <v>121</v>
+      </c>
+      <c r="D1313">
+        <v>70451</v>
+      </c>
+      <c r="E1313">
+        <v>180134</v>
+      </c>
+    </row>
+    <row r="1314" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1314" s="1">
+        <v>46321</v>
+      </c>
+      <c r="B1314">
+        <v>101</v>
+      </c>
+      <c r="C1314" t="s">
+        <v>159</v>
+      </c>
+      <c r="D1314">
+        <v>69925</v>
+      </c>
+      <c r="E1314">
+        <v>180119</v>
+      </c>
+    </row>
+    <row r="1315" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1315" s="1">
+        <v>46321</v>
+      </c>
+      <c r="B1315">
+        <v>101</v>
+      </c>
+      <c r="C1315" t="s">
+        <v>133</v>
+      </c>
+      <c r="E1315">
+        <v>180080</v>
+      </c>
+    </row>
+    <row r="1316" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1316" s="1">
+        <v>46321</v>
+      </c>
+      <c r="B1316">
+        <v>101</v>
+      </c>
+      <c r="C1316" t="s">
+        <v>249</v>
+      </c>
+      <c r="D1316">
+        <v>70231</v>
+      </c>
+      <c r="E1316">
+        <v>180077</v>
+      </c>
+    </row>
+    <row r="1317" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1317" s="1">
+        <v>46321</v>
+      </c>
+      <c r="B1317">
+        <v>101</v>
+      </c>
+      <c r="C1317" t="s">
+        <v>224</v>
+      </c>
+      <c r="D1317">
+        <v>70281</v>
+      </c>
+      <c r="E1317">
+        <v>180101</v>
+      </c>
+    </row>
+    <row r="1318" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1318" s="1">
+        <v>46321</v>
+      </c>
+      <c r="B1318">
+        <v>101</v>
+      </c>
+      <c r="C1318" t="s">
+        <v>250</v>
+      </c>
+      <c r="D1318">
+        <v>70253</v>
+      </c>
+      <c r="E1318">
+        <v>180071</v>
+      </c>
+    </row>
+    <row r="1319" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1319" s="1">
+        <v>46321</v>
+      </c>
+      <c r="B1319">
+        <v>101</v>
+      </c>
+      <c r="C1319" t="s">
+        <v>10</v>
+      </c>
+      <c r="D1319">
+        <v>70678</v>
+      </c>
+      <c r="E1319">
+        <v>180154</v>
+      </c>
+    </row>
+    <row r="1320" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1320" s="1">
+        <v>46321</v>
+      </c>
+      <c r="B1320">
+        <v>101</v>
+      </c>
+      <c r="C1320" t="s">
+        <v>250</v>
+      </c>
+      <c r="D1320">
+        <v>70308</v>
+      </c>
+      <c r="E1320">
+        <v>180078</v>
+      </c>
+    </row>
+    <row r="1321" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1321" s="1">
+        <v>46321</v>
+      </c>
+      <c r="B1321">
+        <v>101</v>
+      </c>
+      <c r="C1321" t="s">
+        <v>251</v>
+      </c>
+      <c r="D1321">
+        <v>70448</v>
+      </c>
+      <c r="E1321">
+        <v>180089</v>
+      </c>
+    </row>
+    <row r="1322" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1322" s="1">
+        <v>46321</v>
+      </c>
+      <c r="B1322">
+        <v>101</v>
+      </c>
+      <c r="C1322" t="s">
+        <v>12</v>
+      </c>
+      <c r="D1322">
+        <v>70198</v>
+      </c>
+      <c r="E1322">
+        <v>180139</v>
+      </c>
+    </row>
+    <row r="1323" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1323" s="1">
+        <v>46321</v>
+      </c>
+      <c r="B1323">
+        <v>101</v>
+      </c>
+      <c r="C1323" t="s">
+        <v>19</v>
+      </c>
+      <c r="D1323">
+        <v>70715</v>
+      </c>
+      <c r="E1323">
+        <v>180181</v>
+      </c>
+    </row>
+    <row r="1324" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1324" s="1">
+        <v>46321</v>
+      </c>
+      <c r="B1324">
+        <v>101</v>
+      </c>
+      <c r="C1324" t="s">
+        <v>156</v>
+      </c>
+      <c r="D1324">
+        <v>70545</v>
+      </c>
+      <c r="E1324">
+        <v>180118</v>
+      </c>
+    </row>
+    <row r="1325" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1325" s="1">
+        <v>46321</v>
+      </c>
+      <c r="B1325">
+        <v>101</v>
+      </c>
+      <c r="C1325" t="s">
+        <v>10</v>
+      </c>
+      <c r="D1325">
+        <v>70507</v>
+      </c>
+      <c r="E1325">
+        <v>180109</v>
+      </c>
+    </row>
+    <row r="1326" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1326" s="1">
+        <v>46321</v>
+      </c>
+      <c r="B1326">
+        <v>101</v>
+      </c>
+      <c r="C1326" t="s">
+        <v>5</v>
+      </c>
+      <c r="E1326">
+        <v>180176</v>
+      </c>
+    </row>
+    <row r="1327" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1327" s="1">
+        <v>46321</v>
+      </c>
+      <c r="B1327">
+        <v>101</v>
+      </c>
+      <c r="C1327" t="s">
+        <v>125</v>
+      </c>
+      <c r="E1327">
+        <v>180120</v>
+      </c>
+    </row>
+    <row r="1328" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1328" s="1">
+        <v>46321</v>
+      </c>
+      <c r="B1328">
+        <v>101</v>
+      </c>
+      <c r="C1328" t="s">
+        <v>213</v>
+      </c>
+      <c r="D1328">
+        <v>70385</v>
+      </c>
+      <c r="E1328">
+        <v>180111</v>
+      </c>
+    </row>
+    <row r="1329" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1329" s="1">
+        <v>46321</v>
+      </c>
+      <c r="B1329">
+        <v>101</v>
+      </c>
+      <c r="C1329" t="s">
+        <v>0</v>
+      </c>
+      <c r="D1329">
+        <v>70511</v>
+      </c>
+      <c r="E1329">
+        <v>180073</v>
+      </c>
+    </row>
+    <row r="1330" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1330" s="1">
+        <v>46321</v>
+      </c>
+      <c r="B1330">
+        <v>101</v>
+      </c>
+      <c r="C1330" t="s">
+        <v>45</v>
+      </c>
+      <c r="D1330">
+        <v>70148</v>
+      </c>
+      <c r="E1330">
+        <v>180138</v>
+      </c>
+    </row>
+    <row r="1331" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1331" s="1">
+        <v>46321</v>
+      </c>
+      <c r="B1331">
+        <v>101</v>
+      </c>
+      <c r="C1331" t="s">
+        <v>124</v>
+      </c>
+      <c r="D1331">
+        <v>70189</v>
+      </c>
+      <c r="E1331">
+        <v>180233</v>
+      </c>
+    </row>
+    <row r="1332" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1332" s="1">
+        <v>46321</v>
+      </c>
+      <c r="B1332">
+        <v>101</v>
+      </c>
+      <c r="C1332" t="s">
+        <v>125</v>
+      </c>
+      <c r="D1332">
+        <v>70599</v>
+      </c>
+      <c r="E1332">
+        <v>180193</v>
+      </c>
+    </row>
+    <row r="1333" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1333" s="1">
+        <v>46321</v>
+      </c>
+      <c r="B1333">
+        <v>101</v>
+      </c>
+      <c r="C1333" t="s">
+        <v>9</v>
+      </c>
+      <c r="D1333">
+        <v>70410</v>
+      </c>
+      <c r="E1333">
+        <v>179829</v>
+      </c>
+    </row>
+    <row r="1334" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1334" s="1">
+        <v>46321</v>
+      </c>
+      <c r="B1334">
+        <v>101</v>
+      </c>
+      <c r="C1334" t="s">
+        <v>152</v>
+      </c>
+      <c r="D1334">
+        <v>70434</v>
+      </c>
+      <c r="E1334">
+        <v>179872</v>
+      </c>
+    </row>
+    <row r="1335" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1335" s="1">
+        <v>46321</v>
+      </c>
+      <c r="B1335">
+        <v>101</v>
+      </c>
+      <c r="C1335" t="s">
+        <v>8</v>
+      </c>
+      <c r="D1335">
+        <v>70393</v>
+      </c>
+      <c r="E1335">
+        <v>179777</v>
+      </c>
+    </row>
+    <row r="1336" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1336" s="1">
+        <v>46321</v>
+      </c>
+      <c r="B1336">
+        <v>101</v>
+      </c>
+      <c r="C1336" t="s">
+        <v>7</v>
+      </c>
+      <c r="D1336">
+        <v>70435</v>
+      </c>
+      <c r="E1336">
+        <v>179873</v>
+      </c>
+    </row>
+    <row r="1337" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1337" s="1">
+        <v>46321</v>
+      </c>
+      <c r="B1337">
+        <v>101</v>
+      </c>
+      <c r="C1337" t="s">
+        <v>9</v>
+      </c>
+      <c r="D1337">
+        <v>70740</v>
+      </c>
+      <c r="E1337">
+        <v>180290</v>
+      </c>
+    </row>
+    <row r="1338" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1338" s="1">
+        <v>46321</v>
+      </c>
+      <c r="B1338">
+        <v>101</v>
+      </c>
+      <c r="C1338" t="s">
+        <v>8</v>
+      </c>
+      <c r="D1338">
+        <v>70342</v>
+      </c>
+      <c r="E1338">
+        <v>179768</v>
+      </c>
+    </row>
+    <row r="1339" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1339" s="1">
+        <v>46321</v>
+      </c>
+      <c r="B1339">
+        <v>101</v>
+      </c>
+      <c r="C1339" t="s">
+        <v>11</v>
+      </c>
+      <c r="D1339">
+        <v>70420</v>
+      </c>
+      <c r="E1339">
+        <v>179842</v>
+      </c>
+    </row>
+    <row r="1340" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1340" s="1">
+        <v>46321</v>
+      </c>
+      <c r="B1340">
+        <v>101</v>
+      </c>
+      <c r="C1340" t="s">
+        <v>152</v>
+      </c>
+      <c r="D1340">
+        <v>70433</v>
+      </c>
+      <c r="E1340">
+        <v>179870</v>
+      </c>
+    </row>
+    <row r="1341" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1341" s="1">
+        <v>46321</v>
+      </c>
+      <c r="B1341">
+        <v>101</v>
+      </c>
+      <c r="C1341" t="s">
+        <v>9</v>
+      </c>
+      <c r="D1341">
+        <v>70739</v>
+      </c>
+      <c r="E1341">
+        <v>180291</v>
+      </c>
+    </row>
+    <row r="1342" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1342" s="1">
+        <v>46321</v>
+      </c>
+      <c r="B1342">
+        <v>101</v>
+      </c>
+      <c r="C1342" t="s">
+        <v>8</v>
+      </c>
+      <c r="D1342">
+        <v>70359</v>
+      </c>
+      <c r="E1342">
+        <v>179775</v>
+      </c>
+    </row>
+    <row r="1343" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1343" s="1">
+        <v>46321</v>
+      </c>
+      <c r="B1343">
+        <v>101</v>
+      </c>
+      <c r="C1343" t="s">
+        <v>8</v>
+      </c>
+      <c r="D1343">
+        <v>70737</v>
+      </c>
+      <c r="E1343">
+        <v>180293</v>
+      </c>
+    </row>
+    <row r="1344" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1344" s="1">
+        <v>46321</v>
+      </c>
+      <c r="B1344">
+        <v>101</v>
+      </c>
+      <c r="C1344" t="s">
+        <v>8</v>
+      </c>
+      <c r="D1344">
+        <v>70762</v>
+      </c>
+      <c r="E1344">
+        <v>180270</v>
+      </c>
+    </row>
+    <row r="1345" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1345" s="1">
+        <v>46321</v>
+      </c>
+      <c r="B1345">
+        <v>101</v>
+      </c>
+      <c r="C1345" t="s">
+        <v>119</v>
+      </c>
+      <c r="D1345">
+        <v>70590</v>
+      </c>
+      <c r="E1345">
+        <v>180274</v>
+      </c>
+    </row>
+    <row r="1346" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1346" s="1">
+        <v>46321</v>
+      </c>
+      <c r="B1346">
+        <v>101</v>
+      </c>
+      <c r="C1346" t="s">
+        <v>11</v>
+      </c>
+      <c r="D1346">
+        <v>70736</v>
+      </c>
+      <c r="E1346">
+        <v>180294</v>
+      </c>
+    </row>
+    <row r="1347" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1347" s="1">
+        <v>46321</v>
+      </c>
+      <c r="B1347">
+        <v>101</v>
+      </c>
+      <c r="C1347" t="s">
+        <v>11</v>
+      </c>
+      <c r="D1347">
+        <v>70728</v>
+      </c>
+      <c r="E1347">
+        <v>180300</v>
+      </c>
+    </row>
+    <row r="1348" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1348" s="1">
+        <v>46321</v>
+      </c>
+      <c r="B1348">
+        <v>101</v>
+      </c>
+      <c r="C1348" t="s">
+        <v>19</v>
+      </c>
+      <c r="D1348">
+        <v>70577</v>
+      </c>
+      <c r="E1348">
+        <v>180150</v>
+      </c>
+    </row>
+    <row r="1349" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1349" s="1">
+        <v>46321</v>
+      </c>
+      <c r="B1349">
+        <v>101</v>
+      </c>
+      <c r="C1349" t="s">
+        <v>19</v>
+      </c>
+      <c r="D1349">
+        <v>67924</v>
+      </c>
+      <c r="E1349">
+        <v>180234</v>
+      </c>
+    </row>
+    <row r="1350" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1350" s="1">
+        <v>46321</v>
+      </c>
+      <c r="B1350">
+        <v>101</v>
+      </c>
+      <c r="C1350" t="s">
+        <v>19</v>
+      </c>
+      <c r="E1350">
+        <v>180295</v>
+      </c>
+    </row>
+    <row r="1351" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1351" s="1">
+        <v>46321</v>
+      </c>
+      <c r="B1351">
+        <v>101</v>
+      </c>
+      <c r="C1351" t="s">
+        <v>19</v>
+      </c>
+      <c r="D1351">
+        <v>70581</v>
+      </c>
+      <c r="E1351">
+        <v>180278</v>
+      </c>
+    </row>
+    <row r="1352" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1352" s="1">
+        <v>46321</v>
+      </c>
+      <c r="B1352">
+        <v>101</v>
+      </c>
+      <c r="C1352" t="s">
+        <v>19</v>
+      </c>
+      <c r="D1352">
+        <v>70629</v>
+      </c>
+      <c r="E1352">
+        <v>180136</v>
+      </c>
+    </row>
+    <row r="1353" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1353" s="1">
+        <v>46321</v>
+      </c>
+      <c r="B1353">
+        <v>101</v>
+      </c>
+      <c r="C1353" t="s">
+        <v>19</v>
+      </c>
+      <c r="D1353">
+        <v>70630</v>
+      </c>
+      <c r="E1353">
+        <v>180247</v>
+      </c>
+    </row>
+    <row r="1354" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1354" s="1">
+        <v>46322</v>
+      </c>
+      <c r="B1354">
+        <v>101</v>
+      </c>
+      <c r="C1354" t="s">
+        <v>0</v>
+      </c>
+      <c r="D1354">
+        <v>66212</v>
+      </c>
+      <c r="E1354">
+        <v>179111</v>
+      </c>
+    </row>
+    <row r="1355" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1355" s="1">
+        <v>46322</v>
+      </c>
+      <c r="B1355">
+        <v>101</v>
+      </c>
+      <c r="C1355" t="s">
+        <v>0</v>
+      </c>
+      <c r="D1355">
+        <v>69406</v>
+      </c>
+      <c r="E1355">
+        <v>179318</v>
+      </c>
+    </row>
+    <row r="1356" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1356" s="1">
+        <v>46322</v>
+      </c>
+      <c r="B1356">
+        <v>101</v>
+      </c>
+      <c r="C1356" t="s">
+        <v>0</v>
+      </c>
+      <c r="E1356">
+        <v>180068</v>
+      </c>
+    </row>
+    <row r="1357" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1357" s="1">
+        <v>46322</v>
+      </c>
+      <c r="B1357">
+        <v>101</v>
+      </c>
+      <c r="C1357" t="s">
+        <v>0</v>
+      </c>
+      <c r="D1357">
+        <v>70282</v>
+      </c>
+      <c r="E1357">
+        <v>179882</v>
+      </c>
+    </row>
+    <row r="1358" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1358" s="1">
+        <v>46322</v>
+      </c>
+      <c r="B1358">
+        <v>101</v>
+      </c>
+      <c r="C1358" t="s">
+        <v>0</v>
+      </c>
+      <c r="D1358">
+        <v>69870</v>
+      </c>
+      <c r="E1358">
+        <v>180239</v>
+      </c>
+    </row>
+    <row r="1359" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1359" s="1">
+        <v>46322</v>
+      </c>
+      <c r="B1359">
+        <v>101</v>
+      </c>
+      <c r="C1359" t="s">
+        <v>0</v>
+      </c>
+      <c r="D1359">
+        <v>70108</v>
+      </c>
+      <c r="E1359">
+        <v>179880</v>
+      </c>
+    </row>
+    <row r="1360" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1360" s="1">
+        <v>46322</v>
+      </c>
+      <c r="B1360">
+        <v>101</v>
+      </c>
+      <c r="C1360" t="s">
+        <v>0</v>
+      </c>
+      <c r="D1360">
+        <v>69147</v>
+      </c>
+      <c r="E1360">
+        <v>180100</v>
+      </c>
+    </row>
+    <row r="1361" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1361" s="1">
+        <v>46322</v>
+      </c>
+      <c r="B1361">
+        <v>101</v>
+      </c>
+      <c r="C1361" t="s">
+        <v>0</v>
+      </c>
+      <c r="D1361">
+        <v>69702</v>
+      </c>
+      <c r="E1361">
+        <v>180259</v>
+      </c>
+    </row>
+    <row r="1362" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1362" s="1">
+        <v>46322</v>
+      </c>
+      <c r="B1362">
+        <v>101</v>
+      </c>
+      <c r="C1362" t="s">
+        <v>0</v>
+      </c>
+      <c r="D1362">
+        <v>70033</v>
+      </c>
+      <c r="E1362">
+        <v>180258</v>
+      </c>
+    </row>
+    <row r="1363" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1363" s="1">
+        <v>46322</v>
+      </c>
+      <c r="B1363">
+        <v>101</v>
+      </c>
+      <c r="C1363" t="s">
+        <v>0</v>
+      </c>
+      <c r="D1363">
+        <v>69697</v>
+      </c>
+      <c r="E1363">
+        <v>180262</v>
+      </c>
+    </row>
+    <row r="1364" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1364" s="1">
+        <v>46322</v>
+      </c>
+      <c r="B1364">
+        <v>101</v>
+      </c>
+      <c r="C1364" t="s">
+        <v>0</v>
+      </c>
+      <c r="D1364">
+        <v>70304</v>
+      </c>
+      <c r="E1364">
+        <v>180067</v>
+      </c>
+    </row>
+    <row r="1365" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1365" s="1">
+        <v>46322</v>
+      </c>
+      <c r="B1365">
+        <v>101</v>
+      </c>
+      <c r="C1365" t="s">
+        <v>0</v>
+      </c>
+      <c r="D1365">
+        <v>69729</v>
+      </c>
+      <c r="E1365">
+        <v>180240</v>
+      </c>
+    </row>
+    <row r="1366" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1366" s="1">
+        <v>46322</v>
+      </c>
+      <c r="B1366">
+        <v>101</v>
+      </c>
+      <c r="C1366" t="s">
+        <v>0</v>
+      </c>
+      <c r="D1366">
+        <v>70081</v>
+      </c>
+      <c r="E1366">
+        <v>180249</v>
+      </c>
+    </row>
+    <row r="1367" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1367" s="1">
+        <v>46322</v>
+      </c>
+      <c r="B1367">
+        <v>101</v>
+      </c>
+      <c r="C1367" t="s">
+        <v>0</v>
+      </c>
+      <c r="D1367">
+        <v>69889</v>
+      </c>
+      <c r="E1367">
+        <v>180260</v>
+      </c>
+    </row>
+    <row r="1368" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1368" s="1">
+        <v>46322</v>
+      </c>
+      <c r="B1368">
+        <v>101</v>
+      </c>
+      <c r="C1368" t="s">
+        <v>0</v>
+      </c>
+      <c r="E1368">
+        <v>180299</v>
+      </c>
+    </row>
+    <row r="1369" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1369" s="1">
+        <v>46322</v>
+      </c>
+      <c r="B1369">
+        <v>101</v>
+      </c>
+      <c r="C1369" t="s">
+        <v>0</v>
+      </c>
+      <c r="D1369">
+        <v>69865</v>
+      </c>
+      <c r="E1369">
+        <v>180244</v>
+      </c>
+    </row>
+    <row r="1370" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1370" s="1">
+        <v>46322</v>
+      </c>
+      <c r="B1370">
+        <v>101</v>
+      </c>
+      <c r="C1370" t="s">
+        <v>0</v>
+      </c>
+      <c r="D1370">
+        <v>70086</v>
+      </c>
+      <c r="E1370">
+        <v>180243</v>
+      </c>
+    </row>
+    <row r="1371" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1371" s="1">
+        <v>46322</v>
+      </c>
+      <c r="B1371">
+        <v>101</v>
+      </c>
+      <c r="C1371" t="s">
+        <v>0</v>
+      </c>
+      <c r="D1371">
+        <v>70085</v>
+      </c>
+      <c r="E1371">
+        <v>180246</v>
+      </c>
+    </row>
+    <row r="1372" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1372" s="1">
+        <v>46322</v>
+      </c>
+      <c r="B1372">
+        <v>101</v>
+      </c>
+      <c r="C1372" t="s">
+        <v>0</v>
+      </c>
+      <c r="D1372">
+        <v>69896</v>
+      </c>
+      <c r="E1372">
+        <v>180237</v>
+      </c>
+    </row>
+    <row r="1373" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1373" s="1">
+        <v>46322</v>
+      </c>
+      <c r="B1373">
+        <v>101</v>
+      </c>
+      <c r="C1373" t="s">
+        <v>0</v>
+      </c>
+      <c r="D1373">
+        <v>70028</v>
+      </c>
+      <c r="E1373">
+        <v>180191</v>
+      </c>
+    </row>
+    <row r="1374" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1374" s="1">
+        <v>46322</v>
+      </c>
+      <c r="B1374">
+        <v>101</v>
+      </c>
+      <c r="C1374" t="s">
+        <v>0</v>
+      </c>
+      <c r="D1374">
+        <v>70127</v>
+      </c>
+      <c r="E1374">
+        <v>180248</v>
+      </c>
+    </row>
+    <row r="1375" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1375" s="1">
+        <v>46322</v>
+      </c>
+      <c r="B1375">
+        <v>101</v>
+      </c>
+      <c r="C1375" t="s">
+        <v>0</v>
+      </c>
+      <c r="D1375">
+        <v>70130</v>
+      </c>
+      <c r="E1375">
+        <v>180236</v>
+      </c>
+    </row>
+    <row r="1376" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1376" s="1">
+        <v>46322</v>
+      </c>
+      <c r="B1376">
+        <v>101</v>
+      </c>
+      <c r="C1376" t="s">
+        <v>0</v>
+      </c>
+      <c r="D1376">
+        <v>70107</v>
+      </c>
+      <c r="E1376">
+        <v>180251</v>
+      </c>
+    </row>
+    <row r="1377" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1377" s="1">
+        <v>46322</v>
+      </c>
+      <c r="B1377">
+        <v>101</v>
+      </c>
+      <c r="C1377" t="s">
+        <v>0</v>
+      </c>
+      <c r="D1377">
+        <v>70083</v>
+      </c>
+      <c r="E1377">
+        <v>180245</v>
+      </c>
+    </row>
+    <row r="1378" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1378" s="1">
+        <v>46322</v>
+      </c>
+      <c r="B1378">
+        <v>101</v>
+      </c>
+      <c r="C1378" t="s">
+        <v>0</v>
+      </c>
+      <c r="D1378">
+        <v>70125</v>
+      </c>
+      <c r="E1378">
+        <v>180235</v>
+      </c>
+    </row>
+    <row r="1379" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1379" s="1">
+        <v>46322</v>
+      </c>
+      <c r="B1379">
+        <v>101</v>
+      </c>
+      <c r="C1379" t="s">
+        <v>0</v>
+      </c>
+      <c r="D1379">
+        <v>70141</v>
+      </c>
+      <c r="E1379">
+        <v>180250</v>
+      </c>
+    </row>
+    <row r="1380" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1380" s="1">
+        <v>46322</v>
+      </c>
+      <c r="B1380">
+        <v>101</v>
+      </c>
+      <c r="C1380" t="s">
+        <v>0</v>
+      </c>
+      <c r="D1380">
+        <v>70668</v>
+      </c>
+      <c r="E1380">
+        <v>180268</v>
+      </c>
+    </row>
+    <row r="1381" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1381" s="1">
+        <v>46322</v>
+      </c>
+      <c r="B1381">
+        <v>101</v>
+      </c>
+      <c r="C1381" t="s">
+        <v>0</v>
+      </c>
+      <c r="D1381">
+        <v>70109</v>
+      </c>
+      <c r="E1381">
+        <v>180261</v>
+      </c>
+    </row>
+    <row r="1382" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1382" s="1">
+        <v>46322</v>
+      </c>
+      <c r="B1382">
+        <v>101</v>
+      </c>
+      <c r="C1382" t="s">
+        <v>0</v>
+      </c>
+      <c r="D1382">
+        <v>70286</v>
+      </c>
+      <c r="E1382">
+        <v>180242</v>
+      </c>
+    </row>
+    <row r="1383" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1383" s="1">
+        <v>46322</v>
+      </c>
+      <c r="B1383">
+        <v>101</v>
+      </c>
+      <c r="C1383" t="s">
+        <v>0</v>
+      </c>
+      <c r="D1383">
+        <v>70123</v>
+      </c>
+      <c r="E1383">
+        <v>180252</v>
+      </c>
+    </row>
+    <row r="1384" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1384" s="1">
+        <v>46322</v>
+      </c>
+      <c r="B1384">
+        <v>101</v>
+      </c>
+      <c r="C1384" t="s">
+        <v>0</v>
+      </c>
+      <c r="D1384">
+        <v>70300</v>
+      </c>
+      <c r="E1384">
+        <v>180241</v>
+      </c>
+    </row>
+    <row r="1385" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1385" s="1">
+        <v>46322</v>
+      </c>
+      <c r="B1385">
+        <v>101</v>
+      </c>
+      <c r="C1385" t="s">
+        <v>0</v>
+      </c>
+      <c r="D1385">
+        <v>70223</v>
+      </c>
+      <c r="E1385">
+        <v>180238</v>
+      </c>
+    </row>
+    <row r="1386" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1386" s="1">
+        <v>46322</v>
+      </c>
+      <c r="B1386">
+        <v>101</v>
+      </c>
+      <c r="C1386" t="s">
+        <v>0</v>
+      </c>
+      <c r="D1386">
+        <v>70671</v>
+      </c>
+      <c r="E1386">
+        <v>180255</v>
+      </c>
+    </row>
+    <row r="1387" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1387" s="1">
+        <v>46322</v>
+      </c>
+      <c r="B1387">
+        <v>101</v>
+      </c>
+      <c r="C1387" t="s">
+        <v>0</v>
+      </c>
+      <c r="D1387">
+        <v>70669</v>
+      </c>
+      <c r="E1387">
+        <v>180267</v>
+      </c>
+    </row>
+    <row r="1388" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1388" s="1">
+        <v>46322</v>
+      </c>
+      <c r="B1388">
+        <v>101</v>
+      </c>
+      <c r="C1388" t="s">
+        <v>58</v>
+      </c>
+      <c r="D1388">
+        <v>70499</v>
+      </c>
+      <c r="E1388">
+        <v>180277</v>
+      </c>
+    </row>
+    <row r="1389" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1389" s="1">
+        <v>46322</v>
+      </c>
+      <c r="B1389">
+        <v>101</v>
+      </c>
+      <c r="C1389" t="s">
+        <v>60</v>
+      </c>
+      <c r="E1389">
+        <v>180210</v>
+      </c>
+    </row>
+    <row r="1390" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1390" s="1">
+        <v>46322</v>
+      </c>
+      <c r="B1390">
+        <v>101</v>
+      </c>
+      <c r="C1390" t="s">
+        <v>58</v>
+      </c>
+      <c r="D1390">
+        <v>70716</v>
+      </c>
+      <c r="E1390">
+        <v>180212</v>
+      </c>
+    </row>
+    <row r="1391" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1391" s="1">
+        <v>46322</v>
+      </c>
+      <c r="B1391">
+        <v>101</v>
+      </c>
+      <c r="C1391" t="s">
+        <v>90</v>
+      </c>
+      <c r="D1391">
+        <v>70510</v>
+      </c>
+      <c r="E1391">
+        <v>180211</v>
+      </c>
+    </row>
+    <row r="1392" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1392" s="1">
+        <v>46322</v>
+      </c>
+      <c r="B1392">
+        <v>101</v>
+      </c>
+      <c r="C1392" t="s">
+        <v>6</v>
+      </c>
+      <c r="D1392">
+        <v>69526</v>
+      </c>
+      <c r="E1392">
+        <v>180265</v>
+      </c>
+    </row>
+    <row r="1393" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1393" s="1">
+        <v>46322</v>
+      </c>
+      <c r="B1393">
+        <v>101</v>
+      </c>
+      <c r="C1393" t="s">
+        <v>39</v>
+      </c>
+      <c r="D1393">
+        <v>70601</v>
+      </c>
+      <c r="E1393">
+        <v>180230</v>
+      </c>
+    </row>
+    <row r="1394" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1394" s="1">
+        <v>46322</v>
+      </c>
+      <c r="B1394">
+        <v>101</v>
+      </c>
+      <c r="C1394" t="s">
+        <v>15</v>
+      </c>
+      <c r="D1394">
+        <v>70274</v>
+      </c>
+      <c r="E1394">
+        <v>180276</v>
+      </c>
+    </row>
+    <row r="1395" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1395" s="1">
+        <v>46322</v>
+      </c>
+      <c r="B1395">
+        <v>101</v>
+      </c>
+      <c r="C1395" t="s">
+        <v>20</v>
+      </c>
+      <c r="D1395">
+        <v>69564</v>
+      </c>
+      <c r="E1395">
+        <v>180213</v>
+      </c>
+    </row>
+    <row r="1396" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1396" s="1">
+        <v>46322</v>
+      </c>
+      <c r="B1396">
+        <v>101</v>
+      </c>
+      <c r="C1396" t="s">
+        <v>20</v>
+      </c>
+      <c r="E1396">
+        <v>180200</v>
+      </c>
+    </row>
+    <row r="1397" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1397" s="1">
+        <v>46322</v>
+      </c>
+      <c r="B1397">
+        <v>101</v>
+      </c>
+      <c r="C1397" t="s">
+        <v>20</v>
+      </c>
+      <c r="D1397">
+        <v>69062</v>
+      </c>
+      <c r="E1397">
+        <v>180289</v>
+      </c>
+    </row>
+    <row r="1398" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1398" s="1">
+        <v>46322</v>
+      </c>
+      <c r="B1398">
+        <v>101</v>
+      </c>
+      <c r="C1398" t="s">
+        <v>86</v>
+      </c>
+      <c r="D1398">
+        <v>70690</v>
+      </c>
+      <c r="E1398">
+        <v>180217</v>
+      </c>
+    </row>
+    <row r="1399" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1399" s="1">
+        <v>46322</v>
+      </c>
+      <c r="B1399">
+        <v>101</v>
+      </c>
+      <c r="C1399" t="s">
+        <v>15</v>
+      </c>
+      <c r="D1399">
+        <v>70273</v>
+      </c>
+      <c r="E1399">
+        <v>180279</v>
+      </c>
+    </row>
+    <row r="1400" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1400" s="1">
+        <v>46322</v>
+      </c>
+      <c r="B1400">
+        <v>101</v>
+      </c>
+      <c r="C1400" t="s">
+        <v>252</v>
+      </c>
+      <c r="D1400">
+        <v>70696</v>
+      </c>
+      <c r="E1400">
+        <v>180225</v>
+      </c>
+    </row>
+    <row r="1401" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1401" s="1">
+        <v>46322</v>
+      </c>
+      <c r="B1401">
+        <v>101</v>
+      </c>
+      <c r="C1401" t="s">
+        <v>39</v>
+      </c>
+      <c r="D1401">
+        <v>70694</v>
+      </c>
+      <c r="E1401">
+        <v>180283</v>
+      </c>
+    </row>
+    <row r="1402" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1402" s="1">
+        <v>46322</v>
+      </c>
+      <c r="B1402">
+        <v>101</v>
+      </c>
+      <c r="C1402" t="s">
+        <v>0</v>
+      </c>
+      <c r="D1402">
+        <v>70221</v>
+      </c>
+      <c r="E1402">
+        <v>180221</v>
+      </c>
+    </row>
+    <row r="1403" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1403" s="1">
+        <v>46322</v>
+      </c>
+      <c r="B1403">
+        <v>101</v>
+      </c>
+      <c r="C1403" t="s">
+        <v>0</v>
+      </c>
+      <c r="E1403">
+        <v>180226</v>
+      </c>
+    </row>
+    <row r="1404" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1404" s="1">
+        <v>46322</v>
+      </c>
+      <c r="B1404">
+        <v>101</v>
+      </c>
+      <c r="C1404" t="s">
+        <v>89</v>
+      </c>
+      <c r="D1404">
+        <v>70454</v>
+      </c>
+      <c r="E1404">
+        <v>180253</v>
+      </c>
+    </row>
+    <row r="1405" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1405" s="1">
+        <v>46322</v>
+      </c>
+      <c r="B1405">
+        <v>101</v>
+      </c>
+      <c r="C1405" t="s">
+        <v>151</v>
+      </c>
+      <c r="D1405">
+        <v>70556</v>
+      </c>
+      <c r="E1405">
+        <v>180284</v>
+      </c>
+    </row>
+    <row r="1406" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1406" s="1">
+        <v>46322</v>
+      </c>
+      <c r="B1406">
+        <v>101</v>
+      </c>
+      <c r="C1406" t="s">
+        <v>0</v>
+      </c>
+      <c r="E1406">
+        <v>180190</v>
+      </c>
+    </row>
+    <row r="1407" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1407" s="1">
+        <v>46322</v>
+      </c>
+      <c r="B1407">
+        <v>101</v>
+      </c>
+      <c r="C1407" t="s">
+        <v>40</v>
+      </c>
+      <c r="D1407">
+        <v>70541</v>
+      </c>
+      <c r="E1407">
+        <v>180192</v>
+      </c>
+    </row>
+    <row r="1408" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1408" s="1">
+        <v>46322</v>
+      </c>
+      <c r="B1408">
+        <v>101</v>
+      </c>
+      <c r="C1408" t="s">
+        <v>15</v>
+      </c>
+      <c r="D1408">
+        <v>69957</v>
+      </c>
+      <c r="E1408">
+        <v>180076</v>
+      </c>
+    </row>
+    <row r="1409" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1409" s="1">
+        <v>46322</v>
+      </c>
+      <c r="B1409">
+        <v>101</v>
+      </c>
+      <c r="C1409" t="s">
+        <v>194</v>
+      </c>
+      <c r="D1409">
+        <v>70852</v>
+      </c>
+      <c r="E1409">
+        <v>180215</v>
+      </c>
+    </row>
+    <row r="1410" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1410" s="1">
+        <v>46322</v>
+      </c>
+      <c r="B1410">
+        <v>101</v>
+      </c>
+      <c r="C1410" t="s">
+        <v>0</v>
+      </c>
+      <c r="D1410">
+        <v>67089</v>
+      </c>
+      <c r="E1410">
+        <v>180292</v>
+      </c>
+    </row>
+    <row r="1411" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1411" s="1">
+        <v>46322</v>
+      </c>
+      <c r="B1411">
+        <v>101</v>
+      </c>
+      <c r="C1411" t="s">
+        <v>253</v>
+      </c>
+      <c r="D1411">
+        <v>70660</v>
+      </c>
+      <c r="E1411">
+        <v>180096</v>
+      </c>
+    </row>
+    <row r="1412" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1412" s="1">
+        <v>46322</v>
+      </c>
+      <c r="B1412">
+        <v>101</v>
+      </c>
+      <c r="C1412" t="s">
+        <v>44</v>
+      </c>
+      <c r="D1412">
+        <v>70271</v>
+      </c>
+      <c r="E1412">
+        <v>180275</v>
+      </c>
+    </row>
+    <row r="1413" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1413" s="1">
+        <v>46322</v>
+      </c>
+      <c r="B1413">
+        <v>101</v>
+      </c>
+      <c r="C1413" t="s">
+        <v>29</v>
+      </c>
+      <c r="D1413">
+        <v>70613</v>
+      </c>
+      <c r="E1413">
+        <v>180345</v>
+      </c>
+    </row>
+    <row r="1414" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1414" s="1">
+        <v>46322</v>
+      </c>
+      <c r="B1414">
+        <v>101</v>
+      </c>
+      <c r="C1414" t="s">
+        <v>29</v>
+      </c>
+      <c r="D1414">
+        <v>70174</v>
+      </c>
+      <c r="E1414">
+        <v>180202</v>
+      </c>
+    </row>
+    <row r="1415" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1415" s="1">
+        <v>46322</v>
+      </c>
+      <c r="B1415">
+        <v>101</v>
+      </c>
+      <c r="C1415" t="s">
+        <v>29</v>
+      </c>
+      <c r="D1415">
+        <v>69811</v>
+      </c>
+      <c r="E1415">
+        <v>180220</v>
+      </c>
+    </row>
+    <row r="1416" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1416" s="1">
+        <v>46322</v>
+      </c>
+      <c r="B1416">
+        <v>101</v>
+      </c>
+      <c r="C1416" t="s">
+        <v>187</v>
+      </c>
+      <c r="D1416">
+        <v>62105</v>
+      </c>
+      <c r="E1416">
+        <v>173851</v>
+      </c>
+    </row>
+    <row r="1417" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1417" s="1">
+        <v>46322</v>
+      </c>
+      <c r="B1417">
+        <v>101</v>
+      </c>
+      <c r="C1417" t="s">
+        <v>29</v>
+      </c>
+      <c r="D1417">
+        <v>70614</v>
+      </c>
+      <c r="E1417">
+        <v>180216</v>
+      </c>
+    </row>
+    <row r="1418" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1418" s="1">
+        <v>46322</v>
+      </c>
+      <c r="B1418">
+        <v>101</v>
+      </c>
+      <c r="C1418" t="s">
+        <v>118</v>
+      </c>
+      <c r="D1418">
+        <v>69761</v>
+      </c>
+      <c r="E1418">
+        <v>180354</v>
+      </c>
+    </row>
+    <row r="1419" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1419" s="1">
+        <v>46322</v>
+      </c>
+      <c r="B1419">
+        <v>101</v>
+      </c>
+      <c r="C1419" t="s">
+        <v>29</v>
+      </c>
+      <c r="D1419">
+        <v>70176</v>
+      </c>
+      <c r="E1419">
+        <v>180203</v>
+      </c>
+    </row>
+    <row r="1420" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1420" s="1">
+        <v>46322</v>
+      </c>
+      <c r="B1420">
+        <v>101</v>
+      </c>
+      <c r="C1420" t="s">
+        <v>29</v>
+      </c>
+      <c r="E1420">
+        <v>180199</v>
+      </c>
+    </row>
+    <row r="1421" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1421" s="1">
+        <v>46322</v>
+      </c>
+      <c r="B1421">
+        <v>101</v>
+      </c>
+      <c r="C1421" t="s">
+        <v>117</v>
+      </c>
+      <c r="D1421">
+        <v>70162</v>
+      </c>
+      <c r="E1421">
+        <v>180205</v>
+      </c>
+    </row>
+    <row r="1422" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1422" s="1">
+        <v>46322</v>
+      </c>
+      <c r="B1422">
+        <v>101</v>
+      </c>
+      <c r="C1422" t="s">
+        <v>118</v>
+      </c>
+      <c r="D1422">
+        <v>70196</v>
+      </c>
+      <c r="E1422">
+        <v>180204</v>
+      </c>
+    </row>
+    <row r="1423" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1423" s="1">
+        <v>46322</v>
+      </c>
+      <c r="B1423">
+        <v>101</v>
+      </c>
+      <c r="C1423" t="s">
+        <v>118</v>
+      </c>
+      <c r="D1423">
+        <v>70169</v>
+      </c>
+      <c r="E1423">
+        <v>180344</v>
+      </c>
+    </row>
+    <row r="1424" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1424" s="1">
+        <v>46322</v>
+      </c>
+      <c r="B1424">
+        <v>101</v>
+      </c>
+      <c r="C1424" t="s">
+        <v>29</v>
+      </c>
+      <c r="E1424">
+        <v>180222</v>
+      </c>
+    </row>
+    <row r="1425" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1425" s="1">
+        <v>46322</v>
+      </c>
+      <c r="B1425">
+        <v>101</v>
+      </c>
+      <c r="C1425" t="s">
+        <v>86</v>
+      </c>
+      <c r="E1425">
+        <v>180229</v>
+      </c>
+    </row>
+    <row r="1426" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1426" s="1">
+        <v>46322</v>
+      </c>
+      <c r="B1426">
+        <v>101</v>
+      </c>
+      <c r="C1426" t="s">
+        <v>86</v>
+      </c>
+      <c r="E1426">
+        <v>180207</v>
+      </c>
+    </row>
+    <row r="1427" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1427" s="1">
+        <v>46322</v>
+      </c>
+      <c r="B1427">
+        <v>101</v>
+      </c>
+      <c r="C1427" t="s">
+        <v>86</v>
+      </c>
+      <c r="D1427">
+        <v>70624</v>
+      </c>
+      <c r="E1427">
+        <v>180266</v>
+      </c>
+    </row>
+    <row r="1428" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1428" s="1">
+        <v>46322</v>
+      </c>
+      <c r="B1428">
+        <v>101</v>
+      </c>
+      <c r="C1428" t="s">
+        <v>0</v>
+      </c>
+      <c r="D1428">
+        <v>70662</v>
+      </c>
+      <c r="E1428">
+        <v>180347</v>
+      </c>
+    </row>
+    <row r="1429" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1429" s="1">
+        <v>46322</v>
+      </c>
+      <c r="B1429">
+        <v>101</v>
+      </c>
+      <c r="C1429" t="s">
+        <v>23</v>
+      </c>
+      <c r="E1429">
+        <v>179818</v>
       </c>
     </row>
   </sheetData>
@@ -23063,193 +25039,8 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{436A81F1-C523-4C8F-89BB-A715EFC34A51}">
-  <dimension ref="A1:E11"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A1">
-        <v>101</v>
-      </c>
-      <c r="B1" t="s">
-        <v>247</v>
-      </c>
-      <c r="C1" t="s">
-        <v>6</v>
-      </c>
-      <c r="D1">
-        <v>68158</v>
-      </c>
-      <c r="E1">
-        <v>180146</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A2">
-        <v>101</v>
-      </c>
-      <c r="B2" t="s">
-        <v>247</v>
-      </c>
-      <c r="C2" t="s">
-        <v>6</v>
-      </c>
-      <c r="E2">
-        <v>180198</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A3">
-        <v>101</v>
-      </c>
-      <c r="B3" t="s">
-        <v>248</v>
-      </c>
-      <c r="C3" t="s">
-        <v>61</v>
-      </c>
-      <c r="E3">
-        <v>180180</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A4">
-        <v>101</v>
-      </c>
-      <c r="B4" t="s">
-        <v>249</v>
-      </c>
-      <c r="C4" t="s">
-        <v>250</v>
-      </c>
-      <c r="D4">
-        <v>70595</v>
-      </c>
-      <c r="E4">
-        <v>180179</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A5">
-        <v>101</v>
-      </c>
-      <c r="B5" t="s">
-        <v>251</v>
-      </c>
-      <c r="C5" t="s">
-        <v>252</v>
-      </c>
-      <c r="E5">
-        <v>180127</v>
-      </c>
-    </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A6">
-        <v>101</v>
-      </c>
-      <c r="B6" t="s">
-        <v>253</v>
-      </c>
-      <c r="C6" t="s">
-        <v>45</v>
-      </c>
-      <c r="D6">
-        <v>69877</v>
-      </c>
-      <c r="E6">
-        <v>179609</v>
-      </c>
-    </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A7">
-        <v>101</v>
-      </c>
-      <c r="B7" t="s">
-        <v>254</v>
-      </c>
-      <c r="C7" t="s">
-        <v>65</v>
-      </c>
-      <c r="D7">
-        <v>70567</v>
-      </c>
-      <c r="E7">
-        <v>180128</v>
-      </c>
-    </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A8">
-        <v>101</v>
-      </c>
-      <c r="B8" t="s">
-        <v>255</v>
-      </c>
-      <c r="C8" t="s">
-        <v>4</v>
-      </c>
-      <c r="D8">
-        <v>70650</v>
-      </c>
-      <c r="E8">
-        <v>180144</v>
-      </c>
-    </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A9">
-        <v>101</v>
-      </c>
-      <c r="B9" t="s">
-        <v>256</v>
-      </c>
-      <c r="C9" t="s">
-        <v>64</v>
-      </c>
-      <c r="E9">
-        <v>180153</v>
-      </c>
-    </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A10">
-        <v>101</v>
-      </c>
-      <c r="B10" t="s">
-        <v>257</v>
-      </c>
-      <c r="C10" t="s">
-        <v>159</v>
-      </c>
-      <c r="D10">
-        <v>70688</v>
-      </c>
-      <c r="E10">
-        <v>180124</v>
-      </c>
-    </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A11">
-        <v>101</v>
-      </c>
-      <c r="B11" t="s">
-        <v>258</v>
-      </c>
-      <c r="C11" t="s">
-        <v>246</v>
-      </c>
-      <c r="D11">
-        <v>70605</v>
-      </c>
-      <c r="E11">
-        <v>180269</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5180BF9C-1943-4030-8A1B-6F86FE205C17}">
-  <dimension ref="A1:C20"/>
+  <dimension ref="A1:C21"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="12.85546875" style="1" bestFit="1" customWidth="1"/>
@@ -23258,7 +25049,7 @@
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="str" cm="1">
-        <f t="array" ref="A1:A20">_xlfn.UNIQUE(Romaneios!A1:A1298)</f>
+        <f t="array" ref="A1:A21">_xlfn.UNIQUE(Romaneios!A1:A1429)</f>
         <v>Dt. Romaneio</v>
       </c>
       <c r="B1" t="s">
@@ -23434,7 +25225,16 @@
       </c>
       <c r="B20">
         <f>COUNTIF(Romaneios!A:A,DadosRomaneios!A20)</f>
-        <v>59</v>
+        <v>103</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A21" s="1">
+        <v>46322</v>
+      </c>
+      <c r="B21">
+        <f>COUNTIF(Romaneios!A:A,DadosRomaneios!A21)</f>
+        <v>76</v>
       </c>
     </row>
   </sheetData>

--- a/DadosRomaneios.xlsx
+++ b/DadosRomaneios.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="U:\AcompanhamentoProducao\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6CDB642E-E946-46AC-854D-9A91E4011754}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{04F4BE95-D83D-463D-94A9-85602DD66D55}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" activeTab="1" xr2:uid="{B6976704-8E51-4052-B60A-5847F95A5AE5}"/>
   </bookViews>
@@ -62,7 +62,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1434" uniqueCount="254">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1539" uniqueCount="259">
   <si>
     <t>ALBERT EINSTEIN</t>
   </si>
@@ -825,6 +825,21 @@
   <si>
     <t>JPM SERVICOS</t>
   </si>
+  <si>
+    <t>QUANTITY</t>
+  </si>
+  <si>
+    <t>WCA DO BRASIL</t>
+  </si>
+  <si>
+    <t>INSTITUTO HOC</t>
+  </si>
+  <si>
+    <t>GENERA SERVICOS LABO</t>
+  </si>
+  <si>
+    <t>CRAL</t>
+  </si>
 </sst>
 </file>
 
@@ -1203,7 +1218,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BF29A37F-A1D1-4315-91AB-A952895E1E73}">
-  <dimension ref="A1:E1429"/>
+  <dimension ref="A1:E1534"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="12.85546875" bestFit="1" customWidth="1"/>
@@ -25029,6 +25044,1761 @@
         <v>179818</v>
       </c>
     </row>
+    <row r="1430" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1430" s="1">
+        <v>46322</v>
+      </c>
+      <c r="B1430">
+        <v>101</v>
+      </c>
+      <c r="C1430" t="s">
+        <v>62</v>
+      </c>
+      <c r="E1430">
+        <v>180231</v>
+      </c>
+    </row>
+    <row r="1431" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1431" s="1">
+        <v>46322</v>
+      </c>
+      <c r="B1431">
+        <v>101</v>
+      </c>
+      <c r="C1431" t="s">
+        <v>246</v>
+      </c>
+      <c r="D1431">
+        <v>70607</v>
+      </c>
+      <c r="E1431">
+        <v>180379</v>
+      </c>
+    </row>
+    <row r="1432" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1432" s="1">
+        <v>46322</v>
+      </c>
+      <c r="B1432">
+        <v>101</v>
+      </c>
+      <c r="C1432" t="s">
+        <v>34</v>
+      </c>
+      <c r="D1432">
+        <v>70806</v>
+      </c>
+      <c r="E1432">
+        <v>180322</v>
+      </c>
+    </row>
+    <row r="1433" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1433" s="1">
+        <v>46322</v>
+      </c>
+      <c r="B1433">
+        <v>101</v>
+      </c>
+      <c r="C1433" t="s">
+        <v>34</v>
+      </c>
+      <c r="D1433">
+        <v>70413</v>
+      </c>
+      <c r="E1433">
+        <v>179833</v>
+      </c>
+    </row>
+    <row r="1434" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1434" s="1">
+        <v>46322</v>
+      </c>
+      <c r="B1434">
+        <v>101</v>
+      </c>
+      <c r="C1434" t="s">
+        <v>9</v>
+      </c>
+      <c r="D1434">
+        <v>70392</v>
+      </c>
+      <c r="E1434">
+        <v>179776</v>
+      </c>
+    </row>
+    <row r="1435" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1435" s="1">
+        <v>46322</v>
+      </c>
+      <c r="B1435">
+        <v>101</v>
+      </c>
+      <c r="C1435" t="s">
+        <v>34</v>
+      </c>
+      <c r="D1435">
+        <v>70777</v>
+      </c>
+      <c r="E1435">
+        <v>180271</v>
+      </c>
+    </row>
+    <row r="1436" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1436" s="1">
+        <v>46322</v>
+      </c>
+      <c r="B1436">
+        <v>101</v>
+      </c>
+      <c r="C1436" t="s">
+        <v>34</v>
+      </c>
+      <c r="D1436">
+        <v>70904</v>
+      </c>
+      <c r="E1436">
+        <v>180371</v>
+      </c>
+    </row>
+    <row r="1437" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1437" s="1">
+        <v>46322</v>
+      </c>
+      <c r="B1437">
+        <v>101</v>
+      </c>
+      <c r="C1437" t="s">
+        <v>152</v>
+      </c>
+      <c r="D1437">
+        <v>70810</v>
+      </c>
+      <c r="E1437">
+        <v>180329</v>
+      </c>
+    </row>
+    <row r="1438" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1438" s="1">
+        <v>46322</v>
+      </c>
+      <c r="B1438">
+        <v>101</v>
+      </c>
+      <c r="C1438" t="s">
+        <v>9</v>
+      </c>
+      <c r="D1438">
+        <v>70744</v>
+      </c>
+      <c r="E1438">
+        <v>180287</v>
+      </c>
+    </row>
+    <row r="1439" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1439" s="1">
+        <v>46322</v>
+      </c>
+      <c r="B1439">
+        <v>101</v>
+      </c>
+      <c r="C1439" t="s">
+        <v>34</v>
+      </c>
+      <c r="D1439">
+        <v>70905</v>
+      </c>
+      <c r="E1439">
+        <v>180372</v>
+      </c>
+    </row>
+    <row r="1440" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1440" s="1">
+        <v>46322</v>
+      </c>
+      <c r="B1440">
+        <v>101</v>
+      </c>
+      <c r="C1440" t="s">
+        <v>152</v>
+      </c>
+      <c r="D1440">
+        <v>70906</v>
+      </c>
+      <c r="E1440">
+        <v>180373</v>
+      </c>
+    </row>
+    <row r="1441" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1441" s="1">
+        <v>46322</v>
+      </c>
+      <c r="B1441">
+        <v>101</v>
+      </c>
+      <c r="C1441" t="s">
+        <v>8</v>
+      </c>
+      <c r="D1441">
+        <v>70816</v>
+      </c>
+      <c r="E1441">
+        <v>180334</v>
+      </c>
+    </row>
+    <row r="1442" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1442" s="1">
+        <v>46322</v>
+      </c>
+      <c r="B1442">
+        <v>101</v>
+      </c>
+      <c r="C1442" t="s">
+        <v>8</v>
+      </c>
+      <c r="D1442">
+        <v>70786</v>
+      </c>
+      <c r="E1442">
+        <v>180330</v>
+      </c>
+    </row>
+    <row r="1443" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1443" s="1">
+        <v>46322</v>
+      </c>
+      <c r="B1443">
+        <v>101</v>
+      </c>
+      <c r="C1443" t="s">
+        <v>152</v>
+      </c>
+      <c r="D1443">
+        <v>70811</v>
+      </c>
+      <c r="E1443">
+        <v>180328</v>
+      </c>
+    </row>
+    <row r="1444" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1444" s="1">
+        <v>46322</v>
+      </c>
+      <c r="B1444">
+        <v>101</v>
+      </c>
+      <c r="C1444" t="s">
+        <v>11</v>
+      </c>
+      <c r="D1444">
+        <v>70793</v>
+      </c>
+      <c r="E1444">
+        <v>180365</v>
+      </c>
+    </row>
+    <row r="1445" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1445" s="1">
+        <v>46322</v>
+      </c>
+      <c r="B1445">
+        <v>101</v>
+      </c>
+      <c r="C1445" t="s">
+        <v>9</v>
+      </c>
+      <c r="D1445">
+        <v>70926</v>
+      </c>
+      <c r="E1445">
+        <v>180454</v>
+      </c>
+    </row>
+    <row r="1446" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1446" s="1">
+        <v>46322</v>
+      </c>
+      <c r="B1446">
+        <v>101</v>
+      </c>
+      <c r="C1446" t="s">
+        <v>119</v>
+      </c>
+      <c r="D1446">
+        <v>70782</v>
+      </c>
+      <c r="E1446">
+        <v>180325</v>
+      </c>
+    </row>
+    <row r="1447" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1447" s="1">
+        <v>46322</v>
+      </c>
+      <c r="B1447">
+        <v>101</v>
+      </c>
+      <c r="C1447" t="s">
+        <v>119</v>
+      </c>
+      <c r="D1447">
+        <v>70783</v>
+      </c>
+      <c r="E1447">
+        <v>180326</v>
+      </c>
+    </row>
+    <row r="1448" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1448" s="1">
+        <v>46322</v>
+      </c>
+      <c r="B1448">
+        <v>101</v>
+      </c>
+      <c r="C1448" t="s">
+        <v>152</v>
+      </c>
+      <c r="D1448">
+        <v>70748</v>
+      </c>
+      <c r="E1448">
+        <v>180420</v>
+      </c>
+    </row>
+    <row r="1449" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1449" s="1">
+        <v>46322</v>
+      </c>
+      <c r="B1449">
+        <v>101</v>
+      </c>
+      <c r="C1449" t="s">
+        <v>119</v>
+      </c>
+      <c r="D1449">
+        <v>70779</v>
+      </c>
+      <c r="E1449">
+        <v>180413</v>
+      </c>
+    </row>
+    <row r="1450" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1450" s="1">
+        <v>46322</v>
+      </c>
+      <c r="B1450">
+        <v>101</v>
+      </c>
+      <c r="C1450" t="s">
+        <v>119</v>
+      </c>
+      <c r="D1450">
+        <v>70900</v>
+      </c>
+      <c r="E1450">
+        <v>180367</v>
+      </c>
+    </row>
+    <row r="1451" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1451" s="1">
+        <v>46322</v>
+      </c>
+      <c r="B1451">
+        <v>101</v>
+      </c>
+      <c r="C1451" t="s">
+        <v>7</v>
+      </c>
+      <c r="D1451">
+        <v>70759</v>
+      </c>
+      <c r="E1451">
+        <v>180399</v>
+      </c>
+    </row>
+    <row r="1452" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1452" s="1">
+        <v>46322</v>
+      </c>
+      <c r="B1452">
+        <v>101</v>
+      </c>
+      <c r="C1452" t="s">
+        <v>9</v>
+      </c>
+      <c r="D1452">
+        <v>70761</v>
+      </c>
+      <c r="E1452">
+        <v>180424</v>
+      </c>
+    </row>
+    <row r="1453" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1453" s="1">
+        <v>46322</v>
+      </c>
+      <c r="B1453">
+        <v>101</v>
+      </c>
+      <c r="C1453" t="s">
+        <v>9</v>
+      </c>
+      <c r="D1453">
+        <v>70750</v>
+      </c>
+      <c r="E1453">
+        <v>180405</v>
+      </c>
+    </row>
+    <row r="1454" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1454" s="1">
+        <v>46322</v>
+      </c>
+      <c r="B1454">
+        <v>101</v>
+      </c>
+      <c r="C1454" t="s">
+        <v>152</v>
+      </c>
+      <c r="D1454">
+        <v>70747</v>
+      </c>
+      <c r="E1454">
+        <v>180419</v>
+      </c>
+    </row>
+    <row r="1455" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1455" s="1">
+        <v>46322</v>
+      </c>
+      <c r="B1455">
+        <v>101</v>
+      </c>
+      <c r="C1455" t="s">
+        <v>9</v>
+      </c>
+      <c r="D1455">
+        <v>70764</v>
+      </c>
+      <c r="E1455">
+        <v>180410</v>
+      </c>
+    </row>
+    <row r="1456" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1456" s="1">
+        <v>46322</v>
+      </c>
+      <c r="B1456">
+        <v>101</v>
+      </c>
+      <c r="C1456" t="s">
+        <v>9</v>
+      </c>
+      <c r="D1456">
+        <v>70763</v>
+      </c>
+      <c r="E1456">
+        <v>180411</v>
+      </c>
+    </row>
+    <row r="1457" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1457" s="1">
+        <v>46322</v>
+      </c>
+      <c r="B1457">
+        <v>101</v>
+      </c>
+      <c r="C1457" t="s">
+        <v>8</v>
+      </c>
+      <c r="D1457">
+        <v>70756</v>
+      </c>
+      <c r="E1457">
+        <v>180423</v>
+      </c>
+    </row>
+    <row r="1458" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1458" s="1">
+        <v>46322</v>
+      </c>
+      <c r="B1458">
+        <v>101</v>
+      </c>
+      <c r="C1458" t="s">
+        <v>9</v>
+      </c>
+      <c r="D1458">
+        <v>70760</v>
+      </c>
+      <c r="E1458">
+        <v>180425</v>
+      </c>
+    </row>
+    <row r="1459" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1459" s="1">
+        <v>46322</v>
+      </c>
+      <c r="B1459">
+        <v>101</v>
+      </c>
+      <c r="C1459" t="s">
+        <v>119</v>
+      </c>
+      <c r="D1459">
+        <v>70751</v>
+      </c>
+      <c r="E1459">
+        <v>180418</v>
+      </c>
+    </row>
+    <row r="1460" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1460" s="1">
+        <v>46322</v>
+      </c>
+      <c r="B1460">
+        <v>101</v>
+      </c>
+      <c r="C1460" t="s">
+        <v>9</v>
+      </c>
+      <c r="D1460">
+        <v>70776</v>
+      </c>
+      <c r="E1460">
+        <v>180391</v>
+      </c>
+    </row>
+    <row r="1461" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1461" s="1">
+        <v>46322</v>
+      </c>
+      <c r="B1461">
+        <v>101</v>
+      </c>
+      <c r="C1461" t="s">
+        <v>9</v>
+      </c>
+      <c r="D1461">
+        <v>70775</v>
+      </c>
+      <c r="E1461">
+        <v>180398</v>
+      </c>
+    </row>
+    <row r="1462" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1462" s="1">
+        <v>46322</v>
+      </c>
+      <c r="B1462">
+        <v>101</v>
+      </c>
+      <c r="C1462" t="s">
+        <v>119</v>
+      </c>
+      <c r="D1462">
+        <v>70778</v>
+      </c>
+      <c r="E1462">
+        <v>180415</v>
+      </c>
+    </row>
+    <row r="1463" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1463" s="1">
+        <v>46322</v>
+      </c>
+      <c r="B1463">
+        <v>101</v>
+      </c>
+      <c r="C1463" t="s">
+        <v>9</v>
+      </c>
+      <c r="D1463">
+        <v>70925</v>
+      </c>
+      <c r="E1463">
+        <v>180452</v>
+      </c>
+    </row>
+    <row r="1464" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1464" s="1">
+        <v>46322</v>
+      </c>
+      <c r="B1464">
+        <v>101</v>
+      </c>
+      <c r="C1464" t="s">
+        <v>11</v>
+      </c>
+      <c r="D1464">
+        <v>70767</v>
+      </c>
+      <c r="E1464">
+        <v>180422</v>
+      </c>
+    </row>
+    <row r="1465" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1465" s="1">
+        <v>46322</v>
+      </c>
+      <c r="B1465">
+        <v>101</v>
+      </c>
+      <c r="C1465" t="s">
+        <v>119</v>
+      </c>
+      <c r="D1465">
+        <v>70752</v>
+      </c>
+      <c r="E1465">
+        <v>180417</v>
+      </c>
+    </row>
+    <row r="1466" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1466" s="1">
+        <v>46322</v>
+      </c>
+      <c r="B1466">
+        <v>101</v>
+      </c>
+      <c r="C1466" t="s">
+        <v>64</v>
+      </c>
+      <c r="E1466">
+        <v>180479</v>
+      </c>
+    </row>
+    <row r="1467" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1467" s="1">
+        <v>46322</v>
+      </c>
+      <c r="B1467">
+        <v>101</v>
+      </c>
+      <c r="C1467" t="s">
+        <v>64</v>
+      </c>
+      <c r="D1467">
+        <v>69773</v>
+      </c>
+      <c r="E1467">
+        <v>180478</v>
+      </c>
+    </row>
+    <row r="1468" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1468" s="1">
+        <v>46322</v>
+      </c>
+      <c r="B1468">
+        <v>101</v>
+      </c>
+      <c r="C1468" t="s">
+        <v>66</v>
+      </c>
+      <c r="D1468">
+        <v>69765</v>
+      </c>
+      <c r="E1468">
+        <v>180441</v>
+      </c>
+    </row>
+    <row r="1469" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1469" s="1">
+        <v>46322</v>
+      </c>
+      <c r="B1469">
+        <v>101</v>
+      </c>
+      <c r="C1469" t="s">
+        <v>66</v>
+      </c>
+      <c r="D1469">
+        <v>69326</v>
+      </c>
+      <c r="E1469">
+        <v>180440</v>
+      </c>
+    </row>
+    <row r="1470" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1470" s="1">
+        <v>46322</v>
+      </c>
+      <c r="B1470">
+        <v>101</v>
+      </c>
+      <c r="C1470" t="s">
+        <v>159</v>
+      </c>
+      <c r="E1470">
+        <v>180257</v>
+      </c>
+    </row>
+    <row r="1471" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1471" s="1">
+        <v>46322</v>
+      </c>
+      <c r="B1471">
+        <v>101</v>
+      </c>
+      <c r="C1471" t="s">
+        <v>159</v>
+      </c>
+      <c r="D1471">
+        <v>70820</v>
+      </c>
+      <c r="E1471">
+        <v>180187</v>
+      </c>
+    </row>
+    <row r="1472" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1472" s="1">
+        <v>46322</v>
+      </c>
+      <c r="B1472">
+        <v>101</v>
+      </c>
+      <c r="C1472" t="s">
+        <v>89</v>
+      </c>
+      <c r="D1472">
+        <v>70070</v>
+      </c>
+      <c r="E1472">
+        <v>180436</v>
+      </c>
+    </row>
+    <row r="1473" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1473" s="1">
+        <v>46322</v>
+      </c>
+      <c r="B1473">
+        <v>101</v>
+      </c>
+      <c r="C1473" t="s">
+        <v>141</v>
+      </c>
+      <c r="D1473">
+        <v>69662</v>
+      </c>
+      <c r="E1473">
+        <v>180263</v>
+      </c>
+    </row>
+    <row r="1474" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1474" s="1">
+        <v>46322</v>
+      </c>
+      <c r="B1474">
+        <v>101</v>
+      </c>
+      <c r="C1474" t="s">
+        <v>89</v>
+      </c>
+      <c r="D1474">
+        <v>69678</v>
+      </c>
+      <c r="E1474">
+        <v>180264</v>
+      </c>
+    </row>
+    <row r="1475" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1475" s="1">
+        <v>46322</v>
+      </c>
+      <c r="B1475">
+        <v>101</v>
+      </c>
+      <c r="C1475" t="s">
+        <v>120</v>
+      </c>
+      <c r="D1475">
+        <v>70575</v>
+      </c>
+      <c r="E1475">
+        <v>180254</v>
+      </c>
+    </row>
+    <row r="1476" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1476" s="1">
+        <v>46322</v>
+      </c>
+      <c r="B1476">
+        <v>101</v>
+      </c>
+      <c r="C1476" t="s">
+        <v>254</v>
+      </c>
+      <c r="D1476">
+        <v>70665</v>
+      </c>
+      <c r="E1476">
+        <v>180194</v>
+      </c>
+    </row>
+    <row r="1477" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1477" s="1">
+        <v>46322</v>
+      </c>
+      <c r="B1477">
+        <v>101</v>
+      </c>
+      <c r="C1477" t="s">
+        <v>5</v>
+      </c>
+      <c r="D1477">
+        <v>68859</v>
+      </c>
+      <c r="E1477">
+        <v>180228</v>
+      </c>
+    </row>
+    <row r="1478" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1478" s="1">
+        <v>46322</v>
+      </c>
+      <c r="B1478">
+        <v>101</v>
+      </c>
+      <c r="C1478" t="s">
+        <v>5</v>
+      </c>
+      <c r="D1478">
+        <v>69804</v>
+      </c>
+      <c r="E1478">
+        <v>180476</v>
+      </c>
+    </row>
+    <row r="1479" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1479" s="1">
+        <v>46322</v>
+      </c>
+      <c r="B1479">
+        <v>101</v>
+      </c>
+      <c r="C1479" t="s">
+        <v>5</v>
+      </c>
+      <c r="D1479">
+        <v>70892</v>
+      </c>
+      <c r="E1479">
+        <v>180511</v>
+      </c>
+    </row>
+    <row r="1480" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1480" s="1">
+        <v>46323</v>
+      </c>
+      <c r="B1480">
+        <v>101</v>
+      </c>
+      <c r="C1480" t="s">
+        <v>0</v>
+      </c>
+      <c r="E1480">
+        <v>180090</v>
+      </c>
+    </row>
+    <row r="1481" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1481" s="1">
+        <v>46323</v>
+      </c>
+      <c r="B1481">
+        <v>101</v>
+      </c>
+      <c r="C1481" t="s">
+        <v>0</v>
+      </c>
+      <c r="D1481">
+        <v>70168</v>
+      </c>
+      <c r="E1481">
+        <v>180473</v>
+      </c>
+    </row>
+    <row r="1482" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1482" s="1">
+        <v>46323</v>
+      </c>
+      <c r="B1482">
+        <v>101</v>
+      </c>
+      <c r="C1482" t="s">
+        <v>28</v>
+      </c>
+      <c r="D1482">
+        <v>70868</v>
+      </c>
+      <c r="E1482">
+        <v>180449</v>
+      </c>
+    </row>
+    <row r="1483" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1483" s="1">
+        <v>46323</v>
+      </c>
+      <c r="B1483">
+        <v>101</v>
+      </c>
+      <c r="C1483" t="s">
+        <v>28</v>
+      </c>
+      <c r="D1483">
+        <v>64514</v>
+      </c>
+      <c r="E1483">
+        <v>180086</v>
+      </c>
+    </row>
+    <row r="1484" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1484" s="1">
+        <v>46323</v>
+      </c>
+      <c r="B1484">
+        <v>101</v>
+      </c>
+      <c r="C1484" t="s">
+        <v>28</v>
+      </c>
+      <c r="D1484">
+        <v>70867</v>
+      </c>
+      <c r="E1484">
+        <v>180390</v>
+      </c>
+    </row>
+    <row r="1485" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1485" s="1">
+        <v>46323</v>
+      </c>
+      <c r="B1485">
+        <v>101</v>
+      </c>
+      <c r="C1485" t="s">
+        <v>28</v>
+      </c>
+      <c r="D1485">
+        <v>70871</v>
+      </c>
+      <c r="E1485">
+        <v>180463</v>
+      </c>
+    </row>
+    <row r="1486" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1486" s="1">
+        <v>46323</v>
+      </c>
+      <c r="B1486">
+        <v>101</v>
+      </c>
+      <c r="C1486" t="s">
+        <v>28</v>
+      </c>
+      <c r="D1486">
+        <v>70869</v>
+      </c>
+      <c r="E1486">
+        <v>180451</v>
+      </c>
+    </row>
+    <row r="1487" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1487" s="1">
+        <v>46323</v>
+      </c>
+      <c r="B1487">
+        <v>101</v>
+      </c>
+      <c r="C1487" t="s">
+        <v>28</v>
+      </c>
+      <c r="D1487">
+        <v>70870</v>
+      </c>
+      <c r="E1487">
+        <v>180467</v>
+      </c>
+    </row>
+    <row r="1488" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1488" s="1">
+        <v>46323</v>
+      </c>
+      <c r="B1488">
+        <v>101</v>
+      </c>
+      <c r="C1488" t="s">
+        <v>28</v>
+      </c>
+      <c r="D1488">
+        <v>70872</v>
+      </c>
+      <c r="E1488">
+        <v>180464</v>
+      </c>
+    </row>
+    <row r="1489" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1489" s="1">
+        <v>46323</v>
+      </c>
+      <c r="B1489">
+        <v>101</v>
+      </c>
+      <c r="C1489" t="s">
+        <v>28</v>
+      </c>
+      <c r="D1489">
+        <v>70873</v>
+      </c>
+      <c r="E1489">
+        <v>180462</v>
+      </c>
+    </row>
+    <row r="1490" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1490" s="1">
+        <v>46323</v>
+      </c>
+      <c r="B1490">
+        <v>101</v>
+      </c>
+      <c r="C1490" t="s">
+        <v>28</v>
+      </c>
+      <c r="D1490">
+        <v>70876</v>
+      </c>
+      <c r="E1490">
+        <v>180471</v>
+      </c>
+    </row>
+    <row r="1491" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1491" s="1">
+        <v>46323</v>
+      </c>
+      <c r="B1491">
+        <v>101</v>
+      </c>
+      <c r="C1491" t="s">
+        <v>28</v>
+      </c>
+      <c r="D1491">
+        <v>70874</v>
+      </c>
+      <c r="E1491">
+        <v>180466</v>
+      </c>
+    </row>
+    <row r="1492" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1492" s="1">
+        <v>46323</v>
+      </c>
+      <c r="B1492">
+        <v>101</v>
+      </c>
+      <c r="C1492" t="s">
+        <v>15</v>
+      </c>
+      <c r="D1492">
+        <v>70854</v>
+      </c>
+      <c r="E1492">
+        <v>180465</v>
+      </c>
+    </row>
+    <row r="1493" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1493" s="1">
+        <v>46323</v>
+      </c>
+      <c r="B1493">
+        <v>101</v>
+      </c>
+      <c r="C1493" t="s">
+        <v>255</v>
+      </c>
+      <c r="D1493">
+        <v>70542</v>
+      </c>
+      <c r="E1493">
+        <v>180352</v>
+      </c>
+    </row>
+    <row r="1494" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1494" s="1">
+        <v>46323</v>
+      </c>
+      <c r="B1494">
+        <v>101</v>
+      </c>
+      <c r="C1494" t="s">
+        <v>40</v>
+      </c>
+      <c r="D1494">
+        <v>70720</v>
+      </c>
+      <c r="E1494">
+        <v>180338</v>
+      </c>
+    </row>
+    <row r="1495" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1495" s="1">
+        <v>46323</v>
+      </c>
+      <c r="B1495">
+        <v>101</v>
+      </c>
+      <c r="C1495" t="s">
+        <v>15</v>
+      </c>
+      <c r="D1495">
+        <v>69716</v>
+      </c>
+      <c r="E1495">
+        <v>180509</v>
+      </c>
+    </row>
+    <row r="1496" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1496" s="1">
+        <v>46323</v>
+      </c>
+      <c r="B1496">
+        <v>101</v>
+      </c>
+      <c r="C1496" t="s">
+        <v>15</v>
+      </c>
+      <c r="D1496">
+        <v>70857</v>
+      </c>
+      <c r="E1496">
+        <v>180414</v>
+      </c>
+    </row>
+    <row r="1497" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1497" s="1">
+        <v>46323</v>
+      </c>
+      <c r="B1497">
+        <v>101</v>
+      </c>
+      <c r="C1497" t="s">
+        <v>60</v>
+      </c>
+      <c r="E1497">
+        <v>180447</v>
+      </c>
+    </row>
+    <row r="1498" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1498" s="1">
+        <v>46323</v>
+      </c>
+      <c r="B1498">
+        <v>101</v>
+      </c>
+      <c r="C1498" t="s">
+        <v>60</v>
+      </c>
+      <c r="D1498">
+        <v>70115</v>
+      </c>
+      <c r="E1498">
+        <v>180098</v>
+      </c>
+    </row>
+    <row r="1499" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1499" s="1">
+        <v>46323</v>
+      </c>
+      <c r="B1499">
+        <v>101</v>
+      </c>
+      <c r="C1499" t="s">
+        <v>60</v>
+      </c>
+      <c r="D1499">
+        <v>70887</v>
+      </c>
+      <c r="E1499">
+        <v>180394</v>
+      </c>
+    </row>
+    <row r="1500" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1500" s="1">
+        <v>46323</v>
+      </c>
+      <c r="B1500">
+        <v>101</v>
+      </c>
+      <c r="C1500" t="s">
+        <v>27</v>
+      </c>
+      <c r="E1500">
+        <v>180472</v>
+      </c>
+    </row>
+    <row r="1501" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1501" s="1">
+        <v>46323</v>
+      </c>
+      <c r="B1501">
+        <v>101</v>
+      </c>
+      <c r="C1501" t="s">
+        <v>27</v>
+      </c>
+      <c r="D1501">
+        <v>70260</v>
+      </c>
+      <c r="E1501">
+        <v>180475</v>
+      </c>
+    </row>
+    <row r="1502" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1502" s="1">
+        <v>46323</v>
+      </c>
+      <c r="B1502">
+        <v>101</v>
+      </c>
+      <c r="C1502" t="s">
+        <v>24</v>
+      </c>
+      <c r="D1502">
+        <v>70525</v>
+      </c>
+      <c r="E1502">
+        <v>180486</v>
+      </c>
+    </row>
+    <row r="1503" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1503" s="1">
+        <v>46323</v>
+      </c>
+      <c r="B1503">
+        <v>101</v>
+      </c>
+      <c r="C1503" t="s">
+        <v>228</v>
+      </c>
+      <c r="D1503">
+        <v>70859</v>
+      </c>
+      <c r="E1503">
+        <v>180393</v>
+      </c>
+    </row>
+    <row r="1504" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1504" s="1">
+        <v>46323</v>
+      </c>
+      <c r="B1504">
+        <v>101</v>
+      </c>
+      <c r="C1504" t="s">
+        <v>24</v>
+      </c>
+      <c r="D1504">
+        <v>70691</v>
+      </c>
+      <c r="E1504">
+        <v>180356</v>
+      </c>
+    </row>
+    <row r="1505" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1505" s="1">
+        <v>46323</v>
+      </c>
+      <c r="B1505">
+        <v>101</v>
+      </c>
+      <c r="C1505" t="s">
+        <v>95</v>
+      </c>
+      <c r="E1505">
+        <v>180459</v>
+      </c>
+    </row>
+    <row r="1506" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1506" s="1">
+        <v>46323</v>
+      </c>
+      <c r="B1506">
+        <v>101</v>
+      </c>
+      <c r="C1506" t="s">
+        <v>15</v>
+      </c>
+      <c r="D1506">
+        <v>70692</v>
+      </c>
+      <c r="E1506">
+        <v>180348</v>
+      </c>
+    </row>
+    <row r="1507" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1507" s="1">
+        <v>46323</v>
+      </c>
+      <c r="B1507">
+        <v>101</v>
+      </c>
+      <c r="C1507" t="s">
+        <v>15</v>
+      </c>
+      <c r="D1507">
+        <v>70866</v>
+      </c>
+      <c r="E1507">
+        <v>180412</v>
+      </c>
+    </row>
+    <row r="1508" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1508" s="1">
+        <v>46323</v>
+      </c>
+      <c r="B1508">
+        <v>101</v>
+      </c>
+      <c r="C1508" t="s">
+        <v>45</v>
+      </c>
+      <c r="D1508">
+        <v>70841</v>
+      </c>
+      <c r="E1508">
+        <v>180431</v>
+      </c>
+    </row>
+    <row r="1509" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1509" s="1">
+        <v>46323</v>
+      </c>
+      <c r="B1509">
+        <v>101</v>
+      </c>
+      <c r="C1509" t="s">
+        <v>0</v>
+      </c>
+      <c r="D1509">
+        <v>70825</v>
+      </c>
+      <c r="E1509">
+        <v>180480</v>
+      </c>
+    </row>
+    <row r="1510" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1510" s="1">
+        <v>46323</v>
+      </c>
+      <c r="B1510">
+        <v>101</v>
+      </c>
+      <c r="C1510" t="s">
+        <v>44</v>
+      </c>
+      <c r="D1510">
+        <v>70842</v>
+      </c>
+      <c r="E1510">
+        <v>180470</v>
+      </c>
+    </row>
+    <row r="1511" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1511" s="1">
+        <v>46323</v>
+      </c>
+      <c r="B1511">
+        <v>101</v>
+      </c>
+      <c r="C1511" t="s">
+        <v>0</v>
+      </c>
+      <c r="D1511">
+        <v>70829</v>
+      </c>
+      <c r="E1511">
+        <v>180516</v>
+      </c>
+    </row>
+    <row r="1512" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1512" s="1">
+        <v>46323</v>
+      </c>
+      <c r="B1512">
+        <v>101</v>
+      </c>
+      <c r="C1512" t="s">
+        <v>0</v>
+      </c>
+      <c r="E1512">
+        <v>180507</v>
+      </c>
+    </row>
+    <row r="1513" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1513" s="1">
+        <v>46323</v>
+      </c>
+      <c r="B1513">
+        <v>101</v>
+      </c>
+      <c r="C1513" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1513">
+        <v>68544</v>
+      </c>
+      <c r="E1513">
+        <v>177878</v>
+      </c>
+    </row>
+    <row r="1514" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1514" s="1">
+        <v>46323</v>
+      </c>
+      <c r="B1514">
+        <v>101</v>
+      </c>
+      <c r="C1514" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1514">
+        <v>69190</v>
+      </c>
+      <c r="E1514">
+        <v>179986</v>
+      </c>
+    </row>
+    <row r="1515" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1515" s="1">
+        <v>46323</v>
+      </c>
+      <c r="B1515">
+        <v>101</v>
+      </c>
+      <c r="C1515" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1515">
+        <v>180117</v>
+      </c>
+    </row>
+    <row r="1516" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1516" s="1">
+        <v>46323</v>
+      </c>
+      <c r="B1516">
+        <v>101</v>
+      </c>
+      <c r="C1516" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1516">
+        <v>69185</v>
+      </c>
+      <c r="E1516">
+        <v>180506</v>
+      </c>
+    </row>
+    <row r="1517" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1517" s="1">
+        <v>46323</v>
+      </c>
+      <c r="B1517">
+        <v>101</v>
+      </c>
+      <c r="C1517" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1517">
+        <v>180178</v>
+      </c>
+    </row>
+    <row r="1518" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1518" s="1">
+        <v>46323</v>
+      </c>
+      <c r="B1518">
+        <v>101</v>
+      </c>
+      <c r="C1518" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1518">
+        <v>70673</v>
+      </c>
+      <c r="E1518">
+        <v>180355</v>
+      </c>
+    </row>
+    <row r="1519" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1519" s="1">
+        <v>46323</v>
+      </c>
+      <c r="B1519">
+        <v>101</v>
+      </c>
+      <c r="C1519" t="s">
+        <v>103</v>
+      </c>
+      <c r="D1519">
+        <v>69355</v>
+      </c>
+      <c r="E1519">
+        <v>180227</v>
+      </c>
+    </row>
+    <row r="1520" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1520" s="1">
+        <v>46323</v>
+      </c>
+      <c r="B1520">
+        <v>101</v>
+      </c>
+      <c r="C1520" t="s">
+        <v>94</v>
+      </c>
+      <c r="D1520">
+        <v>69918</v>
+      </c>
+      <c r="E1520">
+        <v>180487</v>
+      </c>
+    </row>
+    <row r="1521" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1521" s="1">
+        <v>46323</v>
+      </c>
+      <c r="B1521">
+        <v>101</v>
+      </c>
+      <c r="C1521" t="s">
+        <v>0</v>
+      </c>
+      <c r="D1521">
+        <v>69881</v>
+      </c>
+      <c r="E1521">
+        <v>180442</v>
+      </c>
+    </row>
+    <row r="1522" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1522" s="1">
+        <v>46323</v>
+      </c>
+      <c r="B1522">
+        <v>101</v>
+      </c>
+      <c r="C1522" t="s">
+        <v>194</v>
+      </c>
+      <c r="D1522">
+        <v>70821</v>
+      </c>
+      <c r="E1522">
+        <v>180488</v>
+      </c>
+    </row>
+    <row r="1523" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1523" s="1">
+        <v>46323</v>
+      </c>
+      <c r="B1523">
+        <v>101</v>
+      </c>
+      <c r="C1523" t="s">
+        <v>39</v>
+      </c>
+      <c r="D1523">
+        <v>70151</v>
+      </c>
+      <c r="E1523">
+        <v>180152</v>
+      </c>
+    </row>
+    <row r="1524" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1524" s="1">
+        <v>46323</v>
+      </c>
+      <c r="B1524">
+        <v>101</v>
+      </c>
+      <c r="C1524" t="s">
+        <v>256</v>
+      </c>
+      <c r="D1524">
+        <v>70882</v>
+      </c>
+      <c r="E1524">
+        <v>180392</v>
+      </c>
+    </row>
+    <row r="1525" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1525" s="1">
+        <v>46323</v>
+      </c>
+      <c r="B1525">
+        <v>101</v>
+      </c>
+      <c r="C1525" t="s">
+        <v>180</v>
+      </c>
+      <c r="D1525">
+        <v>70017</v>
+      </c>
+      <c r="E1525">
+        <v>180489</v>
+      </c>
+    </row>
+    <row r="1526" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1526" s="1">
+        <v>46323</v>
+      </c>
+      <c r="B1526">
+        <v>101</v>
+      </c>
+      <c r="C1526" t="s">
+        <v>15</v>
+      </c>
+      <c r="D1526">
+        <v>70856</v>
+      </c>
+      <c r="E1526">
+        <v>180437</v>
+      </c>
+    </row>
+    <row r="1527" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1527" s="1">
+        <v>46323</v>
+      </c>
+      <c r="B1527">
+        <v>101</v>
+      </c>
+      <c r="C1527" t="s">
+        <v>257</v>
+      </c>
+      <c r="D1527">
+        <v>70150</v>
+      </c>
+      <c r="E1527">
+        <v>180555</v>
+      </c>
+    </row>
+    <row r="1528" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1528" s="1">
+        <v>46323</v>
+      </c>
+      <c r="B1528">
+        <v>101</v>
+      </c>
+      <c r="C1528" t="s">
+        <v>90</v>
+      </c>
+      <c r="D1528">
+        <v>70689</v>
+      </c>
+      <c r="E1528">
+        <v>180492</v>
+      </c>
+    </row>
+    <row r="1529" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1529" s="1">
+        <v>46323</v>
+      </c>
+      <c r="B1529">
+        <v>101</v>
+      </c>
+      <c r="C1529" t="s">
+        <v>258</v>
+      </c>
+      <c r="D1529">
+        <v>70746</v>
+      </c>
+      <c r="E1529">
+        <v>180460</v>
+      </c>
+    </row>
+    <row r="1530" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1530" s="1">
+        <v>46323</v>
+      </c>
+      <c r="B1530">
+        <v>101</v>
+      </c>
+      <c r="C1530" t="s">
+        <v>23</v>
+      </c>
+      <c r="D1530">
+        <v>69891</v>
+      </c>
+      <c r="E1530">
+        <v>180438</v>
+      </c>
+    </row>
+    <row r="1531" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1531" s="1">
+        <v>46323</v>
+      </c>
+      <c r="B1531">
+        <v>101</v>
+      </c>
+      <c r="C1531" t="s">
+        <v>15</v>
+      </c>
+      <c r="D1531">
+        <v>70697</v>
+      </c>
+      <c r="E1531">
+        <v>180389</v>
+      </c>
+    </row>
+    <row r="1532" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1532" s="1">
+        <v>46323</v>
+      </c>
+      <c r="B1532">
+        <v>101</v>
+      </c>
+      <c r="C1532" t="s">
+        <v>23</v>
+      </c>
+      <c r="D1532">
+        <v>70034</v>
+      </c>
+      <c r="E1532">
+        <v>180458</v>
+      </c>
+    </row>
+    <row r="1533" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1533" s="1">
+        <v>46323</v>
+      </c>
+      <c r="B1533">
+        <v>101</v>
+      </c>
+      <c r="C1533" t="s">
+        <v>33</v>
+      </c>
+      <c r="D1533">
+        <v>70843</v>
+      </c>
+      <c r="E1533">
+        <v>180444</v>
+      </c>
+    </row>
+    <row r="1534" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1534" s="1">
+        <v>46323</v>
+      </c>
+      <c r="B1534">
+        <v>101</v>
+      </c>
+      <c r="C1534" t="s">
+        <v>246</v>
+      </c>
+      <c r="D1534">
+        <v>70609</v>
+      </c>
+      <c r="E1534">
+        <v>180380</v>
+      </c>
+    </row>
   </sheetData>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:E719">
     <sortCondition ref="A703:A719"/>
@@ -25040,7 +26810,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5180BF9C-1943-4030-8A1B-6F86FE205C17}">
-  <dimension ref="A1:C21"/>
+  <dimension ref="A1:C22"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="12.85546875" style="1" bestFit="1" customWidth="1"/>
@@ -25049,7 +26819,7 @@
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="str" cm="1">
-        <f t="array" ref="A1:A21">_xlfn.UNIQUE(Romaneios!A1:A1429)</f>
+        <f t="array" ref="A1:A22">_xlfn.UNIQUE(Romaneios!A1:A1534)</f>
         <v>Dt. Romaneio</v>
       </c>
       <c r="B1" t="s">
@@ -25234,7 +27004,16 @@
       </c>
       <c r="B21">
         <f>COUNTIF(Romaneios!A:A,DadosRomaneios!A21)</f>
-        <v>76</v>
+        <v>126</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A22" s="1">
+        <v>46323</v>
+      </c>
+      <c r="B22">
+        <f>COUNTIF(Romaneios!A:A,DadosRomaneios!A22)</f>
+        <v>55</v>
       </c>
     </row>
   </sheetData>

--- a/DadosRomaneios.xlsx
+++ b/DadosRomaneios.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="U:\AcompanhamentoProducao\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{04F4BE95-D83D-463D-94A9-85602DD66D55}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E5FF9B14-423E-423E-9F47-92E5379E4840}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" activeTab="1" xr2:uid="{B6976704-8E51-4052-B60A-5847F95A5AE5}"/>
   </bookViews>
@@ -62,7 +62,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1539" uniqueCount="259">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1573" uniqueCount="260">
   <si>
     <t>ALBERT EINSTEIN</t>
   </si>
@@ -840,6 +840,9 @@
   <si>
     <t>CRAL</t>
   </si>
+  <si>
+    <t>SYNGENTA PROTECAO</t>
+  </si>
 </sst>
 </file>
 
@@ -1218,7 +1221,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BF29A37F-A1D1-4315-91AB-A952895E1E73}">
-  <dimension ref="A1:E1534"/>
+  <dimension ref="A1:E1568"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="12.85546875" bestFit="1" customWidth="1"/>
@@ -26797,6 +26800,578 @@
       </c>
       <c r="E1534">
         <v>180380</v>
+      </c>
+    </row>
+    <row r="1535" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1535" s="1">
+        <v>46323</v>
+      </c>
+      <c r="B1535">
+        <v>101</v>
+      </c>
+      <c r="C1535" t="s">
+        <v>246</v>
+      </c>
+      <c r="D1535">
+        <v>70576</v>
+      </c>
+      <c r="E1535">
+        <v>180576</v>
+      </c>
+    </row>
+    <row r="1536" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1536" s="1">
+        <v>46323</v>
+      </c>
+      <c r="B1536">
+        <v>101</v>
+      </c>
+      <c r="C1536" t="s">
+        <v>75</v>
+      </c>
+      <c r="D1536">
+        <v>69887</v>
+      </c>
+      <c r="E1536">
+        <v>180481</v>
+      </c>
+    </row>
+    <row r="1537" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1537" s="1">
+        <v>46323</v>
+      </c>
+      <c r="B1537">
+        <v>101</v>
+      </c>
+      <c r="C1537" t="s">
+        <v>259</v>
+      </c>
+      <c r="D1537">
+        <v>69305</v>
+      </c>
+      <c r="E1537">
+        <v>180256</v>
+      </c>
+    </row>
+    <row r="1538" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1538" s="1">
+        <v>46323</v>
+      </c>
+      <c r="B1538">
+        <v>101</v>
+      </c>
+      <c r="C1538" t="s">
+        <v>223</v>
+      </c>
+      <c r="D1538">
+        <v>70743</v>
+      </c>
+      <c r="E1538">
+        <v>180280</v>
+      </c>
+    </row>
+    <row r="1539" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1539" s="1">
+        <v>46323</v>
+      </c>
+      <c r="B1539">
+        <v>101</v>
+      </c>
+      <c r="C1539" t="s">
+        <v>205</v>
+      </c>
+      <c r="D1539">
+        <v>70652</v>
+      </c>
+      <c r="E1539">
+        <v>180206</v>
+      </c>
+    </row>
+    <row r="1540" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1540" s="1">
+        <v>46323</v>
+      </c>
+      <c r="B1540">
+        <v>101</v>
+      </c>
+      <c r="C1540" t="s">
+        <v>156</v>
+      </c>
+      <c r="D1540">
+        <v>67821</v>
+      </c>
+      <c r="E1540">
+        <v>180474</v>
+      </c>
+    </row>
+    <row r="1541" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1541" s="1">
+        <v>46323</v>
+      </c>
+      <c r="B1541">
+        <v>101</v>
+      </c>
+      <c r="C1541" t="s">
+        <v>212</v>
+      </c>
+      <c r="E1541">
+        <v>180209</v>
+      </c>
+    </row>
+    <row r="1542" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1542" s="1">
+        <v>46323</v>
+      </c>
+      <c r="B1542">
+        <v>101</v>
+      </c>
+      <c r="C1542" t="s">
+        <v>205</v>
+      </c>
+      <c r="D1542">
+        <v>69658</v>
+      </c>
+      <c r="E1542">
+        <v>180482</v>
+      </c>
+    </row>
+    <row r="1543" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1543" s="1">
+        <v>46323</v>
+      </c>
+      <c r="B1543">
+        <v>101</v>
+      </c>
+      <c r="C1543" t="s">
+        <v>7</v>
+      </c>
+      <c r="D1543">
+        <v>70439</v>
+      </c>
+      <c r="E1543">
+        <v>179877</v>
+      </c>
+    </row>
+    <row r="1544" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1544" s="1">
+        <v>46323</v>
+      </c>
+      <c r="B1544">
+        <v>101</v>
+      </c>
+      <c r="C1544" t="s">
+        <v>7</v>
+      </c>
+      <c r="D1544">
+        <v>70441</v>
+      </c>
+      <c r="E1544">
+        <v>179881</v>
+      </c>
+    </row>
+    <row r="1545" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1545" s="1">
+        <v>46323</v>
+      </c>
+      <c r="B1545">
+        <v>101</v>
+      </c>
+      <c r="C1545" t="s">
+        <v>246</v>
+      </c>
+      <c r="D1545">
+        <v>70611</v>
+      </c>
+      <c r="E1545">
+        <v>180579</v>
+      </c>
+    </row>
+    <row r="1546" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1546" s="1">
+        <v>46323</v>
+      </c>
+      <c r="B1546">
+        <v>101</v>
+      </c>
+      <c r="C1546" t="s">
+        <v>62</v>
+      </c>
+      <c r="E1546">
+        <v>180572</v>
+      </c>
+    </row>
+    <row r="1547" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1547" s="1">
+        <v>46323</v>
+      </c>
+      <c r="B1547">
+        <v>101</v>
+      </c>
+      <c r="C1547" t="s">
+        <v>61</v>
+      </c>
+      <c r="D1547">
+        <v>69775</v>
+      </c>
+      <c r="E1547">
+        <v>180483</v>
+      </c>
+    </row>
+    <row r="1548" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1548" s="1">
+        <v>46323</v>
+      </c>
+      <c r="B1548">
+        <v>101</v>
+      </c>
+      <c r="C1548" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1548">
+        <v>70679</v>
+      </c>
+      <c r="E1548">
+        <v>180594</v>
+      </c>
+    </row>
+    <row r="1549" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1549" s="1">
+        <v>46323</v>
+      </c>
+      <c r="B1549">
+        <v>101</v>
+      </c>
+      <c r="C1549" t="s">
+        <v>124</v>
+      </c>
+      <c r="D1549">
+        <v>70600</v>
+      </c>
+      <c r="E1549">
+        <v>180653</v>
+      </c>
+    </row>
+    <row r="1550" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1550" s="1">
+        <v>46323</v>
+      </c>
+      <c r="B1550">
+        <v>101</v>
+      </c>
+      <c r="C1550" t="s">
+        <v>0</v>
+      </c>
+      <c r="D1550">
+        <v>69453</v>
+      </c>
+      <c r="E1550">
+        <v>179319</v>
+      </c>
+    </row>
+    <row r="1551" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1551" s="1">
+        <v>46323</v>
+      </c>
+      <c r="B1551">
+        <v>101</v>
+      </c>
+      <c r="C1551" t="s">
+        <v>8</v>
+      </c>
+      <c r="D1551">
+        <v>70344</v>
+      </c>
+      <c r="E1551">
+        <v>179770</v>
+      </c>
+    </row>
+    <row r="1552" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1552" s="1">
+        <v>46323</v>
+      </c>
+      <c r="B1552">
+        <v>101</v>
+      </c>
+      <c r="C1552" t="s">
+        <v>7</v>
+      </c>
+      <c r="D1552">
+        <v>70335</v>
+      </c>
+      <c r="E1552">
+        <v>179757</v>
+      </c>
+    </row>
+    <row r="1553" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1553" s="1">
+        <v>46323</v>
+      </c>
+      <c r="B1553">
+        <v>101</v>
+      </c>
+      <c r="C1553" t="s">
+        <v>152</v>
+      </c>
+      <c r="D1553">
+        <v>70797</v>
+      </c>
+      <c r="E1553">
+        <v>180314</v>
+      </c>
+    </row>
+    <row r="1554" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1554" s="1">
+        <v>46323</v>
+      </c>
+      <c r="B1554">
+        <v>101</v>
+      </c>
+      <c r="C1554" t="s">
+        <v>152</v>
+      </c>
+      <c r="D1554">
+        <v>70402</v>
+      </c>
+      <c r="E1554">
+        <v>179822</v>
+      </c>
+    </row>
+    <row r="1555" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1555" s="1">
+        <v>46323</v>
+      </c>
+      <c r="B1555">
+        <v>101</v>
+      </c>
+      <c r="C1555" t="s">
+        <v>11</v>
+      </c>
+      <c r="D1555">
+        <v>70754</v>
+      </c>
+      <c r="E1555">
+        <v>180407</v>
+      </c>
+    </row>
+    <row r="1556" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1556" s="1">
+        <v>46323</v>
+      </c>
+      <c r="B1556">
+        <v>101</v>
+      </c>
+      <c r="C1556" t="s">
+        <v>8</v>
+      </c>
+      <c r="D1556">
+        <v>70347</v>
+      </c>
+      <c r="E1556">
+        <v>179773</v>
+      </c>
+    </row>
+    <row r="1557" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1557" s="1">
+        <v>46323</v>
+      </c>
+      <c r="B1557">
+        <v>101</v>
+      </c>
+      <c r="C1557" t="s">
+        <v>9</v>
+      </c>
+      <c r="D1557">
+        <v>70814</v>
+      </c>
+      <c r="E1557">
+        <v>180321</v>
+      </c>
+    </row>
+    <row r="1558" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1558" s="1">
+        <v>46323</v>
+      </c>
+      <c r="B1558">
+        <v>101</v>
+      </c>
+      <c r="C1558" t="s">
+        <v>119</v>
+      </c>
+      <c r="D1558">
+        <v>70902</v>
+      </c>
+      <c r="E1558">
+        <v>180369</v>
+      </c>
+    </row>
+    <row r="1559" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1559" s="1">
+        <v>46323</v>
+      </c>
+      <c r="B1559">
+        <v>101</v>
+      </c>
+      <c r="C1559" t="s">
+        <v>8</v>
+      </c>
+      <c r="D1559">
+        <v>70705</v>
+      </c>
+      <c r="E1559">
+        <v>180607</v>
+      </c>
+    </row>
+    <row r="1560" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1560" s="1">
+        <v>46323</v>
+      </c>
+      <c r="B1560">
+        <v>101</v>
+      </c>
+      <c r="C1560" t="s">
+        <v>152</v>
+      </c>
+      <c r="D1560">
+        <v>70796</v>
+      </c>
+      <c r="E1560">
+        <v>180315</v>
+      </c>
+    </row>
+    <row r="1561" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1561" s="1">
+        <v>46323</v>
+      </c>
+      <c r="B1561">
+        <v>101</v>
+      </c>
+      <c r="C1561" t="s">
+        <v>152</v>
+      </c>
+      <c r="D1561">
+        <v>70765</v>
+      </c>
+      <c r="E1561">
+        <v>180402</v>
+      </c>
+    </row>
+    <row r="1562" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1562" s="1">
+        <v>46323</v>
+      </c>
+      <c r="B1562">
+        <v>101</v>
+      </c>
+      <c r="C1562" t="s">
+        <v>152</v>
+      </c>
+      <c r="D1562">
+        <v>70770</v>
+      </c>
+      <c r="E1562">
+        <v>180427</v>
+      </c>
+    </row>
+    <row r="1563" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1563" s="1">
+        <v>46323</v>
+      </c>
+      <c r="B1563">
+        <v>101</v>
+      </c>
+      <c r="C1563" t="s">
+        <v>152</v>
+      </c>
+      <c r="D1563">
+        <v>70771</v>
+      </c>
+      <c r="E1563">
+        <v>180426</v>
+      </c>
+    </row>
+    <row r="1564" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1564" s="1">
+        <v>46323</v>
+      </c>
+      <c r="B1564">
+        <v>101</v>
+      </c>
+      <c r="C1564" t="s">
+        <v>9</v>
+      </c>
+      <c r="D1564">
+        <v>70815</v>
+      </c>
+      <c r="E1564">
+        <v>180320</v>
+      </c>
+    </row>
+    <row r="1565" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1565" s="1">
+        <v>46323</v>
+      </c>
+      <c r="B1565">
+        <v>101</v>
+      </c>
+      <c r="C1565" t="s">
+        <v>8</v>
+      </c>
+      <c r="D1565">
+        <v>70958</v>
+      </c>
+      <c r="E1565">
+        <v>180604</v>
+      </c>
+    </row>
+    <row r="1566" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1566" s="1">
+        <v>46323</v>
+      </c>
+      <c r="B1566">
+        <v>101</v>
+      </c>
+      <c r="C1566" t="s">
+        <v>119</v>
+      </c>
+      <c r="D1566">
+        <v>70901</v>
+      </c>
+      <c r="E1566">
+        <v>180368</v>
+      </c>
+    </row>
+    <row r="1567" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1567" s="1">
+        <v>46323</v>
+      </c>
+      <c r="B1567">
+        <v>101</v>
+      </c>
+      <c r="C1567" t="s">
+        <v>152</v>
+      </c>
+      <c r="D1567">
+        <v>70766</v>
+      </c>
+      <c r="E1567">
+        <v>180401</v>
+      </c>
+    </row>
+    <row r="1568" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1568" s="1">
+        <v>46323</v>
+      </c>
+      <c r="B1568">
+        <v>101</v>
+      </c>
+      <c r="C1568" t="s">
+        <v>8</v>
+      </c>
+      <c r="D1568">
+        <v>70753</v>
+      </c>
+      <c r="E1568">
+        <v>180400</v>
       </c>
     </row>
   </sheetData>
@@ -26819,7 +27394,7 @@
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="str" cm="1">
-        <f t="array" ref="A1:A22">_xlfn.UNIQUE(Romaneios!A1:A1534)</f>
+        <f t="array" ref="A1:A22">_xlfn.UNIQUE(Romaneios!A1:A1568)</f>
         <v>Dt. Romaneio</v>
       </c>
       <c r="B1" t="s">
@@ -27013,7 +27588,7 @@
       </c>
       <c r="B22">
         <f>COUNTIF(Romaneios!A:A,DadosRomaneios!A22)</f>
-        <v>55</v>
+        <v>89</v>
       </c>
     </row>
   </sheetData>

--- a/DadosRomaneios.xlsx
+++ b/DadosRomaneios.xlsx
@@ -8,13 +8,14 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="U:\AcompanhamentoProducao\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E5FF9B14-423E-423E-9F47-92E5379E4840}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0E0D5981-269A-4404-8894-3C77D6C672D7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" activeTab="1" xr2:uid="{B6976704-8E51-4052-B60A-5847F95A5AE5}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{B6976704-8E51-4052-B60A-5847F95A5AE5}"/>
   </bookViews>
   <sheets>
     <sheet name="Romaneios" sheetId="2" r:id="rId1"/>
-    <sheet name="DadosRomaneios" sheetId="3" r:id="rId2"/>
+    <sheet name="Planilha1" sheetId="4" r:id="rId2"/>
+    <sheet name="DadosRomaneios" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -40,7 +41,7 @@
 </file>
 
 <file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
-<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xlrd="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
+<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
   <metadataTypes count="1">
     <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
   </metadataTypes>
@@ -62,7 +63,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1573" uniqueCount="260">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1700" uniqueCount="274">
   <si>
     <t>ALBERT EINSTEIN</t>
   </si>
@@ -843,6 +844,48 @@
   <si>
     <t>SYNGENTA PROTECAO</t>
   </si>
+  <si>
+    <t>TEA RIBEIRAO PRETO</t>
+  </si>
+  <si>
+    <t>HOSP RIBEIRAO PRETO</t>
+  </si>
+  <si>
+    <t>DIAG ALTO BOA VISTA</t>
+  </si>
+  <si>
+    <t>CC RIBEIRAO PRETO</t>
+  </si>
+  <si>
+    <t>HAPCLINICA CAPIVARI</t>
+  </si>
+  <si>
+    <t>DIAG NACOES UNIDAS</t>
+  </si>
+  <si>
+    <t>CLINICA IRACEMAPOLIS</t>
+  </si>
+  <si>
+    <t>CLINICA SERRANA</t>
+  </si>
+  <si>
+    <t>CLINICA MORRO AGUDO</t>
+  </si>
+  <si>
+    <t>CLINICA PIRASSUNUNGA</t>
+  </si>
+  <si>
+    <t>CONGREGACAO</t>
+  </si>
+  <si>
+    <t>HOSPITAL BALBINO</t>
+  </si>
+  <si>
+    <t>CC JACAREPAGUA</t>
+  </si>
+  <si>
+    <t>CC MADUREIRA</t>
+  </si>
 </sst>
 </file>
 
@@ -1221,7 +1264,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BF29A37F-A1D1-4315-91AB-A952895E1E73}">
-  <dimension ref="A1:E1568"/>
+  <dimension ref="A1:E1695"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="12.85546875" bestFit="1" customWidth="1"/>
@@ -27374,6 +27417,2093 @@
         <v>180400</v>
       </c>
     </row>
+    <row r="1569" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1569" s="1">
+        <v>46323</v>
+      </c>
+      <c r="B1569">
+        <v>101</v>
+      </c>
+      <c r="C1569" t="s">
+        <v>191</v>
+      </c>
+      <c r="D1569">
+        <v>69169</v>
+      </c>
+      <c r="E1569">
+        <v>178863</v>
+      </c>
+    </row>
+    <row r="1570" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1570" s="1">
+        <v>46323</v>
+      </c>
+      <c r="B1570">
+        <v>101</v>
+      </c>
+      <c r="C1570" t="s">
+        <v>39</v>
+      </c>
+      <c r="D1570">
+        <v>68863</v>
+      </c>
+      <c r="E1570">
+        <v>178667</v>
+      </c>
+    </row>
+    <row r="1571" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1571" s="1">
+        <v>46323</v>
+      </c>
+      <c r="B1571">
+        <v>101</v>
+      </c>
+      <c r="C1571" t="s">
+        <v>0</v>
+      </c>
+      <c r="D1571">
+        <v>69160</v>
+      </c>
+      <c r="E1571">
+        <v>178631</v>
+      </c>
+    </row>
+    <row r="1572" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1572" s="1">
+        <v>46323</v>
+      </c>
+      <c r="B1572">
+        <v>101</v>
+      </c>
+      <c r="C1572" t="s">
+        <v>260</v>
+      </c>
+      <c r="D1572">
+        <v>69509</v>
+      </c>
+      <c r="E1572">
+        <v>178708</v>
+      </c>
+    </row>
+    <row r="1573" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1573" s="1">
+        <v>46323</v>
+      </c>
+      <c r="B1573">
+        <v>101</v>
+      </c>
+      <c r="C1573" t="s">
+        <v>33</v>
+      </c>
+      <c r="D1573">
+        <v>69911</v>
+      </c>
+      <c r="E1573">
+        <v>179002</v>
+      </c>
+    </row>
+    <row r="1574" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1574" s="1">
+        <v>46323</v>
+      </c>
+      <c r="B1574">
+        <v>101</v>
+      </c>
+      <c r="C1574" t="s">
+        <v>261</v>
+      </c>
+      <c r="D1574">
+        <v>69516</v>
+      </c>
+      <c r="E1574">
+        <v>178709</v>
+      </c>
+    </row>
+    <row r="1575" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1575" s="1">
+        <v>46323</v>
+      </c>
+      <c r="B1575">
+        <v>101</v>
+      </c>
+      <c r="C1575" t="s">
+        <v>262</v>
+      </c>
+      <c r="D1575">
+        <v>69506</v>
+      </c>
+      <c r="E1575">
+        <v>178706</v>
+      </c>
+    </row>
+    <row r="1576" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1576" s="1">
+        <v>46323</v>
+      </c>
+      <c r="B1576">
+        <v>101</v>
+      </c>
+      <c r="C1576" t="s">
+        <v>229</v>
+      </c>
+      <c r="D1576">
+        <v>69681</v>
+      </c>
+      <c r="E1576">
+        <v>178765</v>
+      </c>
+    </row>
+    <row r="1577" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1577" s="1">
+        <v>46323</v>
+      </c>
+      <c r="B1577">
+        <v>101</v>
+      </c>
+      <c r="C1577" t="s">
+        <v>0</v>
+      </c>
+      <c r="D1577">
+        <v>69494</v>
+      </c>
+      <c r="E1577">
+        <v>179063</v>
+      </c>
+    </row>
+    <row r="1578" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1578" s="1">
+        <v>46323</v>
+      </c>
+      <c r="B1578">
+        <v>101</v>
+      </c>
+      <c r="C1578" t="s">
+        <v>263</v>
+      </c>
+      <c r="D1578">
+        <v>69507</v>
+      </c>
+      <c r="E1578">
+        <v>178707</v>
+      </c>
+    </row>
+    <row r="1579" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1579" s="1">
+        <v>46323</v>
+      </c>
+      <c r="B1579">
+        <v>101</v>
+      </c>
+      <c r="C1579" t="s">
+        <v>264</v>
+      </c>
+      <c r="D1579">
+        <v>69523</v>
+      </c>
+      <c r="E1579">
+        <v>178710</v>
+      </c>
+    </row>
+    <row r="1580" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1580" s="1">
+        <v>46323</v>
+      </c>
+      <c r="B1580">
+        <v>101</v>
+      </c>
+      <c r="C1580" t="s">
+        <v>0</v>
+      </c>
+      <c r="D1580">
+        <v>69404</v>
+      </c>
+      <c r="E1580">
+        <v>179115</v>
+      </c>
+    </row>
+    <row r="1581" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1581" s="1">
+        <v>46323</v>
+      </c>
+      <c r="B1581">
+        <v>101</v>
+      </c>
+      <c r="C1581" t="s">
+        <v>0</v>
+      </c>
+      <c r="D1581">
+        <v>69453</v>
+      </c>
+      <c r="E1581">
+        <v>179319</v>
+      </c>
+    </row>
+    <row r="1582" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1582" s="1">
+        <v>46323</v>
+      </c>
+      <c r="B1582">
+        <v>101</v>
+      </c>
+      <c r="C1582" t="s">
+        <v>191</v>
+      </c>
+      <c r="D1582">
+        <v>68977</v>
+      </c>
+      <c r="E1582">
+        <v>178862</v>
+      </c>
+    </row>
+    <row r="1583" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1583" s="1">
+        <v>46323</v>
+      </c>
+      <c r="B1583">
+        <v>101</v>
+      </c>
+      <c r="C1583" t="s">
+        <v>265</v>
+      </c>
+      <c r="D1583">
+        <v>69525</v>
+      </c>
+      <c r="E1583">
+        <v>178705</v>
+      </c>
+    </row>
+    <row r="1584" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1584" s="1">
+        <v>46323</v>
+      </c>
+      <c r="B1584">
+        <v>101</v>
+      </c>
+      <c r="C1584" t="s">
+        <v>0</v>
+      </c>
+      <c r="D1584">
+        <v>69431</v>
+      </c>
+      <c r="E1584">
+        <v>179317</v>
+      </c>
+    </row>
+    <row r="1585" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1585" s="1">
+        <v>46323</v>
+      </c>
+      <c r="B1585">
+        <v>101</v>
+      </c>
+      <c r="C1585" t="s">
+        <v>0</v>
+      </c>
+      <c r="D1585">
+        <v>69532</v>
+      </c>
+      <c r="E1585">
+        <v>179325</v>
+      </c>
+    </row>
+    <row r="1586" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1586" s="1">
+        <v>46323</v>
+      </c>
+      <c r="B1586">
+        <v>101</v>
+      </c>
+      <c r="C1586" t="s">
+        <v>204</v>
+      </c>
+      <c r="D1586">
+        <v>69651</v>
+      </c>
+      <c r="E1586">
+        <v>179046</v>
+      </c>
+    </row>
+    <row r="1587" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1587" s="1">
+        <v>46323</v>
+      </c>
+      <c r="B1587">
+        <v>101</v>
+      </c>
+      <c r="C1587" t="s">
+        <v>158</v>
+      </c>
+      <c r="D1587">
+        <v>69613</v>
+      </c>
+      <c r="E1587">
+        <v>178877</v>
+      </c>
+    </row>
+    <row r="1588" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1588" s="1">
+        <v>46323</v>
+      </c>
+      <c r="B1588">
+        <v>101</v>
+      </c>
+      <c r="C1588" t="s">
+        <v>19</v>
+      </c>
+      <c r="D1588">
+        <v>69922</v>
+      </c>
+      <c r="E1588">
+        <v>179451</v>
+      </c>
+    </row>
+    <row r="1589" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1589" s="1">
+        <v>46323</v>
+      </c>
+      <c r="B1589">
+        <v>101</v>
+      </c>
+      <c r="C1589" t="s">
+        <v>0</v>
+      </c>
+      <c r="D1589">
+        <v>69864</v>
+      </c>
+      <c r="E1589">
+        <v>179302</v>
+      </c>
+    </row>
+    <row r="1590" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1590" s="1">
+        <v>46323</v>
+      </c>
+      <c r="B1590">
+        <v>101</v>
+      </c>
+      <c r="C1590" t="s">
+        <v>0</v>
+      </c>
+      <c r="D1590">
+        <v>69433</v>
+      </c>
+      <c r="E1590">
+        <v>179304</v>
+      </c>
+    </row>
+    <row r="1591" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1591" s="1">
+        <v>46323</v>
+      </c>
+      <c r="B1591">
+        <v>101</v>
+      </c>
+      <c r="C1591" t="s">
+        <v>0</v>
+      </c>
+      <c r="D1591">
+        <v>69419</v>
+      </c>
+      <c r="E1591">
+        <v>179064</v>
+      </c>
+    </row>
+    <row r="1592" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1592" s="1">
+        <v>46323</v>
+      </c>
+      <c r="B1592">
+        <v>101</v>
+      </c>
+      <c r="C1592" t="s">
+        <v>266</v>
+      </c>
+      <c r="D1592">
+        <v>69919</v>
+      </c>
+      <c r="E1592">
+        <v>179450</v>
+      </c>
+    </row>
+    <row r="1593" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1593" s="1">
+        <v>46323</v>
+      </c>
+      <c r="B1593">
+        <v>101</v>
+      </c>
+      <c r="C1593" t="s">
+        <v>0</v>
+      </c>
+      <c r="D1593">
+        <v>70032</v>
+      </c>
+      <c r="E1593">
+        <v>179341</v>
+      </c>
+    </row>
+    <row r="1594" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1594" s="1">
+        <v>46323</v>
+      </c>
+      <c r="B1594">
+        <v>101</v>
+      </c>
+      <c r="C1594" t="s">
+        <v>0</v>
+      </c>
+      <c r="D1594">
+        <v>69890</v>
+      </c>
+      <c r="E1594">
+        <v>179308</v>
+      </c>
+    </row>
+    <row r="1595" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1595" s="1">
+        <v>46323</v>
+      </c>
+      <c r="B1595">
+        <v>101</v>
+      </c>
+      <c r="C1595" t="s">
+        <v>0</v>
+      </c>
+      <c r="D1595">
+        <v>69728</v>
+      </c>
+      <c r="E1595">
+        <v>179299</v>
+      </c>
+    </row>
+    <row r="1596" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1596" s="1">
+        <v>46323</v>
+      </c>
+      <c r="B1596">
+        <v>101</v>
+      </c>
+      <c r="C1596" t="s">
+        <v>267</v>
+      </c>
+      <c r="D1596">
+        <v>70136</v>
+      </c>
+      <c r="E1596">
+        <v>179447</v>
+      </c>
+    </row>
+    <row r="1597" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1597" s="1">
+        <v>46323</v>
+      </c>
+      <c r="B1597">
+        <v>101</v>
+      </c>
+      <c r="C1597" t="s">
+        <v>268</v>
+      </c>
+      <c r="D1597">
+        <v>70145</v>
+      </c>
+      <c r="E1597">
+        <v>179454</v>
+      </c>
+    </row>
+    <row r="1598" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1598" s="1">
+        <v>46323</v>
+      </c>
+      <c r="B1598">
+        <v>101</v>
+      </c>
+      <c r="C1598" t="s">
+        <v>0</v>
+      </c>
+      <c r="D1598">
+        <v>69902</v>
+      </c>
+      <c r="E1598">
+        <v>179366</v>
+      </c>
+    </row>
+    <row r="1599" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1599" s="1">
+        <v>46323</v>
+      </c>
+      <c r="B1599">
+        <v>101</v>
+      </c>
+      <c r="C1599" t="s">
+        <v>19</v>
+      </c>
+      <c r="D1599">
+        <v>69916</v>
+      </c>
+      <c r="E1599">
+        <v>179449</v>
+      </c>
+    </row>
+    <row r="1600" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1600" s="1">
+        <v>46323</v>
+      </c>
+      <c r="B1600">
+        <v>101</v>
+      </c>
+      <c r="C1600" t="s">
+        <v>0</v>
+      </c>
+      <c r="E1600">
+        <v>179758</v>
+      </c>
+    </row>
+    <row r="1601" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1601" s="1">
+        <v>46323</v>
+      </c>
+      <c r="B1601">
+        <v>101</v>
+      </c>
+      <c r="C1601" t="s">
+        <v>7</v>
+      </c>
+      <c r="D1601">
+        <v>70091</v>
+      </c>
+      <c r="E1601">
+        <v>179487</v>
+      </c>
+    </row>
+    <row r="1602" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1602" s="1">
+        <v>46323</v>
+      </c>
+      <c r="B1602">
+        <v>101</v>
+      </c>
+      <c r="C1602" t="s">
+        <v>39</v>
+      </c>
+      <c r="E1602">
+        <v>179884</v>
+      </c>
+    </row>
+    <row r="1603" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1603" s="1">
+        <v>46323</v>
+      </c>
+      <c r="B1603">
+        <v>101</v>
+      </c>
+      <c r="C1603" t="s">
+        <v>0</v>
+      </c>
+      <c r="E1603">
+        <v>179559</v>
+      </c>
+    </row>
+    <row r="1604" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1604" s="1">
+        <v>46323</v>
+      </c>
+      <c r="B1604">
+        <v>101</v>
+      </c>
+      <c r="C1604" t="s">
+        <v>0</v>
+      </c>
+      <c r="E1604">
+        <v>179815</v>
+      </c>
+    </row>
+    <row r="1605" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1605" s="1">
+        <v>46323</v>
+      </c>
+      <c r="B1605">
+        <v>101</v>
+      </c>
+      <c r="C1605" t="s">
+        <v>183</v>
+      </c>
+      <c r="D1605">
+        <v>69361</v>
+      </c>
+      <c r="E1605">
+        <v>179595</v>
+      </c>
+    </row>
+    <row r="1606" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1606" s="1">
+        <v>46323</v>
+      </c>
+      <c r="B1606">
+        <v>101</v>
+      </c>
+      <c r="C1606" t="s">
+        <v>0</v>
+      </c>
+      <c r="E1606">
+        <v>179804</v>
+      </c>
+    </row>
+    <row r="1607" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1607" s="1">
+        <v>46323</v>
+      </c>
+      <c r="B1607">
+        <v>101</v>
+      </c>
+      <c r="C1607" t="s">
+        <v>269</v>
+      </c>
+      <c r="D1607">
+        <v>70318</v>
+      </c>
+      <c r="E1607">
+        <v>179633</v>
+      </c>
+    </row>
+    <row r="1608" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1608" s="1">
+        <v>46323</v>
+      </c>
+      <c r="B1608">
+        <v>101</v>
+      </c>
+      <c r="C1608" t="s">
+        <v>0</v>
+      </c>
+      <c r="D1608">
+        <v>70095</v>
+      </c>
+      <c r="E1608">
+        <v>179761</v>
+      </c>
+    </row>
+    <row r="1609" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1609" s="1">
+        <v>46323</v>
+      </c>
+      <c r="B1609">
+        <v>101</v>
+      </c>
+      <c r="C1609" t="s">
+        <v>0</v>
+      </c>
+      <c r="E1609">
+        <v>179814</v>
+      </c>
+    </row>
+    <row r="1610" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1610" s="1">
+        <v>46323</v>
+      </c>
+      <c r="B1610">
+        <v>101</v>
+      </c>
+      <c r="C1610" t="s">
+        <v>0</v>
+      </c>
+      <c r="D1610">
+        <v>69725</v>
+      </c>
+      <c r="E1610">
+        <v>179867</v>
+      </c>
+    </row>
+    <row r="1611" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1611" s="1">
+        <v>46323</v>
+      </c>
+      <c r="B1611">
+        <v>101</v>
+      </c>
+      <c r="C1611" t="s">
+        <v>183</v>
+      </c>
+      <c r="D1611">
+        <v>69362</v>
+      </c>
+      <c r="E1611">
+        <v>179598</v>
+      </c>
+    </row>
+    <row r="1612" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1612" s="1">
+        <v>46323</v>
+      </c>
+      <c r="B1612">
+        <v>101</v>
+      </c>
+      <c r="C1612" t="s">
+        <v>0</v>
+      </c>
+      <c r="D1612">
+        <v>70287</v>
+      </c>
+      <c r="E1612">
+        <v>179813</v>
+      </c>
+    </row>
+    <row r="1613" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1613" s="1">
+        <v>46323</v>
+      </c>
+      <c r="B1613">
+        <v>101</v>
+      </c>
+      <c r="C1613" t="s">
+        <v>0</v>
+      </c>
+      <c r="D1613">
+        <v>69845</v>
+      </c>
+      <c r="E1613">
+        <v>179868</v>
+      </c>
+    </row>
+    <row r="1614" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1614" s="1">
+        <v>46323</v>
+      </c>
+      <c r="B1614">
+        <v>101</v>
+      </c>
+      <c r="C1614" t="s">
+        <v>0</v>
+      </c>
+      <c r="D1614">
+        <v>69866</v>
+      </c>
+      <c r="E1614">
+        <v>179869</v>
+      </c>
+    </row>
+    <row r="1615" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1615" s="1">
+        <v>46323</v>
+      </c>
+      <c r="B1615">
+        <v>101</v>
+      </c>
+      <c r="C1615" t="s">
+        <v>20</v>
+      </c>
+      <c r="D1615">
+        <v>70458</v>
+      </c>
+      <c r="E1615">
+        <v>179729</v>
+      </c>
+    </row>
+    <row r="1616" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1616" s="1">
+        <v>46323</v>
+      </c>
+      <c r="B1616">
+        <v>101</v>
+      </c>
+      <c r="C1616" t="s">
+        <v>0</v>
+      </c>
+      <c r="D1616">
+        <v>70097</v>
+      </c>
+      <c r="E1616">
+        <v>179760</v>
+      </c>
+    </row>
+    <row r="1617" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1617" s="1">
+        <v>46323</v>
+      </c>
+      <c r="B1617">
+        <v>101</v>
+      </c>
+      <c r="C1617" t="s">
+        <v>0</v>
+      </c>
+      <c r="D1617">
+        <v>69882</v>
+      </c>
+      <c r="E1617">
+        <v>179866</v>
+      </c>
+    </row>
+    <row r="1618" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1618" s="1">
+        <v>46323</v>
+      </c>
+      <c r="B1618">
+        <v>101</v>
+      </c>
+      <c r="C1618" t="s">
+        <v>0</v>
+      </c>
+      <c r="D1618">
+        <v>70101</v>
+      </c>
+      <c r="E1618">
+        <v>179811</v>
+      </c>
+    </row>
+    <row r="1619" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1619" s="1">
+        <v>46323</v>
+      </c>
+      <c r="B1619">
+        <v>101</v>
+      </c>
+      <c r="C1619" t="s">
+        <v>0</v>
+      </c>
+      <c r="E1619">
+        <v>179764</v>
+      </c>
+    </row>
+    <row r="1620" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1620" s="1">
+        <v>46323</v>
+      </c>
+      <c r="B1620">
+        <v>101</v>
+      </c>
+      <c r="C1620" t="s">
+        <v>0</v>
+      </c>
+      <c r="D1620">
+        <v>70126</v>
+      </c>
+      <c r="E1620">
+        <v>179762</v>
+      </c>
+    </row>
+    <row r="1621" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1621" s="1">
+        <v>46323</v>
+      </c>
+      <c r="B1621">
+        <v>101</v>
+      </c>
+      <c r="C1621" t="s">
+        <v>0</v>
+      </c>
+      <c r="D1621">
+        <v>70098</v>
+      </c>
+      <c r="E1621">
+        <v>179759</v>
+      </c>
+    </row>
+    <row r="1622" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1622" s="1">
+        <v>46323</v>
+      </c>
+      <c r="B1622">
+        <v>101</v>
+      </c>
+      <c r="C1622" t="s">
+        <v>0</v>
+      </c>
+      <c r="D1622">
+        <v>70179</v>
+      </c>
+      <c r="E1622">
+        <v>179817</v>
+      </c>
+    </row>
+    <row r="1623" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1623" s="1">
+        <v>46323</v>
+      </c>
+      <c r="B1623">
+        <v>101</v>
+      </c>
+      <c r="C1623" t="s">
+        <v>0</v>
+      </c>
+      <c r="E1623">
+        <v>179816</v>
+      </c>
+    </row>
+    <row r="1624" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1624" s="1">
+        <v>46323</v>
+      </c>
+      <c r="B1624">
+        <v>101</v>
+      </c>
+      <c r="C1624" t="s">
+        <v>0</v>
+      </c>
+      <c r="D1624">
+        <v>70290</v>
+      </c>
+      <c r="E1624">
+        <v>179809</v>
+      </c>
+    </row>
+    <row r="1625" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1625" s="1">
+        <v>46323</v>
+      </c>
+      <c r="B1625">
+        <v>101</v>
+      </c>
+      <c r="C1625" t="s">
+        <v>0</v>
+      </c>
+      <c r="D1625">
+        <v>69443</v>
+      </c>
+      <c r="E1625">
+        <v>180093</v>
+      </c>
+    </row>
+    <row r="1626" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1626" s="1">
+        <v>46323</v>
+      </c>
+      <c r="B1626">
+        <v>101</v>
+      </c>
+      <c r="C1626" t="s">
+        <v>0</v>
+      </c>
+      <c r="D1626">
+        <v>69698</v>
+      </c>
+      <c r="E1626">
+        <v>179993</v>
+      </c>
+    </row>
+    <row r="1627" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1627" s="1">
+        <v>46323</v>
+      </c>
+      <c r="B1627">
+        <v>101</v>
+      </c>
+      <c r="C1627" t="s">
+        <v>0</v>
+      </c>
+      <c r="D1627">
+        <v>70100</v>
+      </c>
+      <c r="E1627">
+        <v>179763</v>
+      </c>
+    </row>
+    <row r="1628" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1628" s="1">
+        <v>46323</v>
+      </c>
+      <c r="B1628">
+        <v>101</v>
+      </c>
+      <c r="C1628" t="s">
+        <v>0</v>
+      </c>
+      <c r="D1628">
+        <v>70495</v>
+      </c>
+      <c r="E1628">
+        <v>179994</v>
+      </c>
+    </row>
+    <row r="1629" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1629" s="1">
+        <v>46323</v>
+      </c>
+      <c r="B1629">
+        <v>101</v>
+      </c>
+      <c r="C1629" t="s">
+        <v>0</v>
+      </c>
+      <c r="D1629">
+        <v>70124</v>
+      </c>
+      <c r="E1629">
+        <v>179812</v>
+      </c>
+    </row>
+    <row r="1630" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1630" s="1">
+        <v>46323</v>
+      </c>
+      <c r="B1630">
+        <v>101</v>
+      </c>
+      <c r="C1630" t="s">
+        <v>0</v>
+      </c>
+      <c r="D1630">
+        <v>70222</v>
+      </c>
+      <c r="E1630">
+        <v>179806</v>
+      </c>
+    </row>
+    <row r="1631" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1631" s="1">
+        <v>46323</v>
+      </c>
+      <c r="B1631">
+        <v>101</v>
+      </c>
+      <c r="C1631" t="s">
+        <v>0</v>
+      </c>
+      <c r="D1631">
+        <v>70224</v>
+      </c>
+      <c r="E1631">
+        <v>179805</v>
+      </c>
+    </row>
+    <row r="1632" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1632" s="1">
+        <v>46323</v>
+      </c>
+      <c r="B1632">
+        <v>101</v>
+      </c>
+      <c r="C1632" t="s">
+        <v>0</v>
+      </c>
+      <c r="D1632">
+        <v>69849</v>
+      </c>
+      <c r="E1632">
+        <v>180010</v>
+      </c>
+    </row>
+    <row r="1633" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1633" s="1">
+        <v>46324</v>
+      </c>
+      <c r="B1633">
+        <v>101</v>
+      </c>
+      <c r="C1633" t="s">
+        <v>29</v>
+      </c>
+      <c r="D1633">
+        <v>69980</v>
+      </c>
+      <c r="E1633">
+        <v>180433</v>
+      </c>
+    </row>
+    <row r="1634" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1634" s="1">
+        <v>46324</v>
+      </c>
+      <c r="B1634">
+        <v>101</v>
+      </c>
+      <c r="C1634" t="s">
+        <v>85</v>
+      </c>
+      <c r="D1634">
+        <v>70658</v>
+      </c>
+      <c r="E1634">
+        <v>180640</v>
+      </c>
+    </row>
+    <row r="1635" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1635" s="1">
+        <v>46324</v>
+      </c>
+      <c r="B1635">
+        <v>101</v>
+      </c>
+      <c r="C1635" t="s">
+        <v>0</v>
+      </c>
+      <c r="D1635">
+        <v>70889</v>
+      </c>
+      <c r="E1635">
+        <v>180662</v>
+      </c>
+    </row>
+    <row r="1636" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1636" s="1">
+        <v>46324</v>
+      </c>
+      <c r="B1636">
+        <v>101</v>
+      </c>
+      <c r="C1636" t="s">
+        <v>0</v>
+      </c>
+      <c r="D1636">
+        <v>70833</v>
+      </c>
+      <c r="E1636">
+        <v>180468</v>
+      </c>
+    </row>
+    <row r="1637" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1637" s="1">
+        <v>46324</v>
+      </c>
+      <c r="B1637">
+        <v>101</v>
+      </c>
+      <c r="C1637" t="s">
+        <v>0</v>
+      </c>
+      <c r="D1637">
+        <v>69398</v>
+      </c>
+      <c r="E1637">
+        <v>179106</v>
+      </c>
+    </row>
+    <row r="1638" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1638" s="1">
+        <v>46324</v>
+      </c>
+      <c r="B1638">
+        <v>101</v>
+      </c>
+      <c r="C1638" t="s">
+        <v>0</v>
+      </c>
+      <c r="D1638">
+        <v>70107</v>
+      </c>
+      <c r="E1638">
+        <v>180251</v>
+      </c>
+    </row>
+    <row r="1639" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1639" s="1">
+        <v>46324</v>
+      </c>
+      <c r="B1639">
+        <v>101</v>
+      </c>
+      <c r="C1639" t="s">
+        <v>0</v>
+      </c>
+      <c r="D1639">
+        <v>70669</v>
+      </c>
+      <c r="E1639">
+        <v>180267</v>
+      </c>
+    </row>
+    <row r="1640" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1640" s="1">
+        <v>46324</v>
+      </c>
+      <c r="B1640">
+        <v>101</v>
+      </c>
+      <c r="C1640" t="s">
+        <v>0</v>
+      </c>
+      <c r="E1640">
+        <v>180430</v>
+      </c>
+    </row>
+    <row r="1641" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1641" s="1">
+        <v>46324</v>
+      </c>
+      <c r="B1641">
+        <v>101</v>
+      </c>
+      <c r="C1641" t="s">
+        <v>0</v>
+      </c>
+      <c r="D1641">
+        <v>70834</v>
+      </c>
+      <c r="E1641">
+        <v>180395</v>
+      </c>
+    </row>
+    <row r="1642" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1642" s="1">
+        <v>46324</v>
+      </c>
+      <c r="B1642">
+        <v>101</v>
+      </c>
+      <c r="C1642" t="s">
+        <v>0</v>
+      </c>
+      <c r="D1642">
+        <v>69900</v>
+      </c>
+      <c r="E1642">
+        <v>180396</v>
+      </c>
+    </row>
+    <row r="1643" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1643" s="1">
+        <v>46324</v>
+      </c>
+      <c r="B1643">
+        <v>101</v>
+      </c>
+      <c r="C1643" t="s">
+        <v>0</v>
+      </c>
+      <c r="D1643">
+        <v>70822</v>
+      </c>
+      <c r="E1643">
+        <v>180432</v>
+      </c>
+    </row>
+    <row r="1644" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1644" s="1">
+        <v>46324</v>
+      </c>
+      <c r="B1644">
+        <v>101</v>
+      </c>
+      <c r="C1644" t="s">
+        <v>15</v>
+      </c>
+      <c r="D1644">
+        <v>70268</v>
+      </c>
+      <c r="E1644">
+        <v>180589</v>
+      </c>
+    </row>
+    <row r="1645" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1645" s="1">
+        <v>46324</v>
+      </c>
+      <c r="B1645">
+        <v>101</v>
+      </c>
+      <c r="C1645" t="s">
+        <v>0</v>
+      </c>
+      <c r="D1645">
+        <v>70106</v>
+      </c>
+      <c r="E1645">
+        <v>180660</v>
+      </c>
+    </row>
+    <row r="1646" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1646" s="1">
+        <v>46324</v>
+      </c>
+      <c r="B1646">
+        <v>101</v>
+      </c>
+      <c r="C1646" t="s">
+        <v>270</v>
+      </c>
+      <c r="D1646">
+        <v>71046</v>
+      </c>
+      <c r="E1646">
+        <v>180656</v>
+      </c>
+    </row>
+    <row r="1647" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1647" s="1">
+        <v>46324</v>
+      </c>
+      <c r="B1647">
+        <v>101</v>
+      </c>
+      <c r="C1647" t="s">
+        <v>20</v>
+      </c>
+      <c r="D1647">
+        <v>69037</v>
+      </c>
+      <c r="E1647">
+        <v>180477</v>
+      </c>
+    </row>
+    <row r="1648" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1648" s="1">
+        <v>46324</v>
+      </c>
+      <c r="B1648">
+        <v>101</v>
+      </c>
+      <c r="C1648" t="s">
+        <v>20</v>
+      </c>
+      <c r="E1648">
+        <v>180626</v>
+      </c>
+    </row>
+    <row r="1649" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1649" s="1">
+        <v>46324</v>
+      </c>
+      <c r="B1649">
+        <v>101</v>
+      </c>
+      <c r="C1649" t="s">
+        <v>20</v>
+      </c>
+      <c r="D1649">
+        <v>70249</v>
+      </c>
+      <c r="E1649">
+        <v>180597</v>
+      </c>
+    </row>
+    <row r="1650" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1650" s="1">
+        <v>46324</v>
+      </c>
+      <c r="B1650">
+        <v>101</v>
+      </c>
+      <c r="C1650" t="s">
+        <v>0</v>
+      </c>
+      <c r="D1650">
+        <v>70178</v>
+      </c>
+      <c r="E1650">
+        <v>180623</v>
+      </c>
+    </row>
+    <row r="1651" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1651" s="1">
+        <v>46324</v>
+      </c>
+      <c r="B1651">
+        <v>101</v>
+      </c>
+      <c r="C1651" t="s">
+        <v>45</v>
+      </c>
+      <c r="D1651">
+        <v>69746</v>
+      </c>
+      <c r="E1651">
+        <v>180637</v>
+      </c>
+    </row>
+    <row r="1652" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1652" s="1">
+        <v>46324</v>
+      </c>
+      <c r="B1652">
+        <v>101</v>
+      </c>
+      <c r="C1652" t="s">
+        <v>45</v>
+      </c>
+      <c r="D1652">
+        <v>69914</v>
+      </c>
+      <c r="E1652">
+        <v>180650</v>
+      </c>
+    </row>
+    <row r="1653" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1653" s="1">
+        <v>46324</v>
+      </c>
+      <c r="B1653">
+        <v>101</v>
+      </c>
+      <c r="C1653" t="s">
+        <v>0</v>
+      </c>
+      <c r="E1653">
+        <v>180570</v>
+      </c>
+    </row>
+    <row r="1654" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1654" s="1">
+        <v>46324</v>
+      </c>
+      <c r="B1654">
+        <v>101</v>
+      </c>
+      <c r="C1654" t="s">
+        <v>0</v>
+      </c>
+      <c r="D1654">
+        <v>70493</v>
+      </c>
+      <c r="E1654">
+        <v>180625</v>
+      </c>
+    </row>
+    <row r="1655" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1655" s="1">
+        <v>46324</v>
+      </c>
+      <c r="B1655">
+        <v>101</v>
+      </c>
+      <c r="C1655" t="s">
+        <v>0</v>
+      </c>
+      <c r="E1655">
+        <v>180571</v>
+      </c>
+    </row>
+    <row r="1656" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1656" s="1">
+        <v>46324</v>
+      </c>
+      <c r="B1656">
+        <v>101</v>
+      </c>
+      <c r="C1656" t="s">
+        <v>113</v>
+      </c>
+      <c r="D1656">
+        <v>69717</v>
+      </c>
+      <c r="E1656">
+        <v>180574</v>
+      </c>
+    </row>
+    <row r="1657" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1657" s="1">
+        <v>46324</v>
+      </c>
+      <c r="B1657">
+        <v>101</v>
+      </c>
+      <c r="C1657" t="s">
+        <v>180</v>
+      </c>
+      <c r="D1657">
+        <v>70492</v>
+      </c>
+      <c r="E1657">
+        <v>180631</v>
+      </c>
+    </row>
+    <row r="1658" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1658" s="1">
+        <v>46324</v>
+      </c>
+      <c r="B1658">
+        <v>101</v>
+      </c>
+      <c r="C1658" t="s">
+        <v>111</v>
+      </c>
+      <c r="D1658">
+        <v>69304</v>
+      </c>
+      <c r="E1658">
+        <v>180629</v>
+      </c>
+    </row>
+    <row r="1659" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1659" s="1">
+        <v>46324</v>
+      </c>
+      <c r="B1659">
+        <v>101</v>
+      </c>
+      <c r="C1659" t="s">
+        <v>58</v>
+      </c>
+      <c r="D1659">
+        <v>70933</v>
+      </c>
+      <c r="E1659">
+        <v>180635</v>
+      </c>
+    </row>
+    <row r="1660" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1660" s="1">
+        <v>46324</v>
+      </c>
+      <c r="B1660">
+        <v>101</v>
+      </c>
+      <c r="C1660" t="s">
+        <v>180</v>
+      </c>
+      <c r="D1660">
+        <v>70230</v>
+      </c>
+      <c r="E1660">
+        <v>180582</v>
+      </c>
+    </row>
+    <row r="1661" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1661" s="1">
+        <v>46324</v>
+      </c>
+      <c r="B1661">
+        <v>101</v>
+      </c>
+      <c r="C1661" t="s">
+        <v>45</v>
+      </c>
+      <c r="D1661">
+        <v>70382</v>
+      </c>
+      <c r="E1661">
+        <v>180652</v>
+      </c>
+    </row>
+    <row r="1662" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1662" s="1">
+        <v>46324</v>
+      </c>
+      <c r="B1662">
+        <v>101</v>
+      </c>
+      <c r="C1662" t="s">
+        <v>60</v>
+      </c>
+      <c r="E1662">
+        <v>180648</v>
+      </c>
+    </row>
+    <row r="1663" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1663" s="1">
+        <v>46324</v>
+      </c>
+      <c r="B1663">
+        <v>101</v>
+      </c>
+      <c r="C1663" t="s">
+        <v>0</v>
+      </c>
+      <c r="D1663">
+        <v>70490</v>
+      </c>
+      <c r="E1663">
+        <v>180567</v>
+      </c>
+    </row>
+    <row r="1664" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1664" s="1">
+        <v>46324</v>
+      </c>
+      <c r="B1664">
+        <v>101</v>
+      </c>
+      <c r="C1664" t="s">
+        <v>60</v>
+      </c>
+      <c r="D1664">
+        <v>70067</v>
+      </c>
+      <c r="E1664">
+        <v>180586</v>
+      </c>
+    </row>
+    <row r="1665" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1665" s="1">
+        <v>46324</v>
+      </c>
+      <c r="B1665">
+        <v>101</v>
+      </c>
+      <c r="C1665" t="s">
+        <v>256</v>
+      </c>
+      <c r="D1665">
+        <v>70882</v>
+      </c>
+      <c r="E1665">
+        <v>180392</v>
+      </c>
+    </row>
+    <row r="1666" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1666" s="1">
+        <v>46324</v>
+      </c>
+      <c r="B1666">
+        <v>101</v>
+      </c>
+      <c r="C1666" t="s">
+        <v>60</v>
+      </c>
+      <c r="D1666">
+        <v>70699</v>
+      </c>
+      <c r="E1666">
+        <v>180585</v>
+      </c>
+    </row>
+    <row r="1667" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1667" s="1">
+        <v>46324</v>
+      </c>
+      <c r="B1667">
+        <v>101</v>
+      </c>
+      <c r="C1667" t="s">
+        <v>0</v>
+      </c>
+      <c r="D1667">
+        <v>70025</v>
+      </c>
+      <c r="E1667">
+        <v>180573</v>
+      </c>
+    </row>
+    <row r="1668" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1668" s="1">
+        <v>46324</v>
+      </c>
+      <c r="B1668">
+        <v>101</v>
+      </c>
+      <c r="C1668" t="s">
+        <v>23</v>
+      </c>
+      <c r="D1668">
+        <v>71038</v>
+      </c>
+      <c r="E1668">
+        <v>180617</v>
+      </c>
+    </row>
+    <row r="1669" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1669" s="1">
+        <v>46324</v>
+      </c>
+      <c r="B1669">
+        <v>101</v>
+      </c>
+      <c r="C1669" t="s">
+        <v>0</v>
+      </c>
+      <c r="D1669">
+        <v>70105</v>
+      </c>
+      <c r="E1669">
+        <v>180624</v>
+      </c>
+    </row>
+    <row r="1670" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1670" s="1">
+        <v>46324</v>
+      </c>
+      <c r="B1670">
+        <v>101</v>
+      </c>
+      <c r="C1670" t="s">
+        <v>0</v>
+      </c>
+      <c r="E1670">
+        <v>180569</v>
+      </c>
+    </row>
+    <row r="1671" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1671" s="1">
+        <v>46324</v>
+      </c>
+      <c r="B1671">
+        <v>101</v>
+      </c>
+      <c r="C1671" t="s">
+        <v>167</v>
+      </c>
+      <c r="D1671">
+        <v>69573</v>
+      </c>
+      <c r="E1671">
+        <v>180638</v>
+      </c>
+    </row>
+    <row r="1672" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1672" s="1">
+        <v>46324</v>
+      </c>
+      <c r="B1672">
+        <v>101</v>
+      </c>
+      <c r="C1672" t="s">
+        <v>40</v>
+      </c>
+      <c r="D1672">
+        <v>70910</v>
+      </c>
+      <c r="E1672">
+        <v>180622</v>
+      </c>
+    </row>
+    <row r="1673" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1673" s="1">
+        <v>46324</v>
+      </c>
+      <c r="B1673">
+        <v>101</v>
+      </c>
+      <c r="C1673" t="s">
+        <v>23</v>
+      </c>
+      <c r="D1673">
+        <v>69572</v>
+      </c>
+      <c r="E1673">
+        <v>180627</v>
+      </c>
+    </row>
+    <row r="1674" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1674" s="1">
+        <v>46324</v>
+      </c>
+      <c r="B1674">
+        <v>101</v>
+      </c>
+      <c r="C1674" t="s">
+        <v>15</v>
+      </c>
+      <c r="D1674">
+        <v>69824</v>
+      </c>
+      <c r="E1674">
+        <v>180566</v>
+      </c>
+    </row>
+    <row r="1675" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1675" s="1">
+        <v>46324</v>
+      </c>
+      <c r="B1675">
+        <v>101</v>
+      </c>
+      <c r="C1675" t="s">
+        <v>33</v>
+      </c>
+      <c r="E1675">
+        <v>180587</v>
+      </c>
+    </row>
+    <row r="1676" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1676" s="1">
+        <v>46324</v>
+      </c>
+      <c r="B1676">
+        <v>101</v>
+      </c>
+      <c r="C1676" t="s">
+        <v>13</v>
+      </c>
+      <c r="E1676">
+        <v>180599</v>
+      </c>
+    </row>
+    <row r="1677" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1677" s="1">
+        <v>46324</v>
+      </c>
+      <c r="B1677">
+        <v>101</v>
+      </c>
+      <c r="C1677" t="s">
+        <v>271</v>
+      </c>
+      <c r="D1677">
+        <v>69788</v>
+      </c>
+      <c r="E1677">
+        <v>180069</v>
+      </c>
+    </row>
+    <row r="1678" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1678" s="1">
+        <v>46324</v>
+      </c>
+      <c r="B1678">
+        <v>101</v>
+      </c>
+      <c r="C1678" t="s">
+        <v>15</v>
+      </c>
+      <c r="E1678">
+        <v>179394</v>
+      </c>
+    </row>
+    <row r="1679" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1679" s="1">
+        <v>46324</v>
+      </c>
+      <c r="B1679">
+        <v>101</v>
+      </c>
+      <c r="C1679" t="s">
+        <v>147</v>
+      </c>
+      <c r="D1679">
+        <v>70552</v>
+      </c>
+      <c r="E1679">
+        <v>180357</v>
+      </c>
+    </row>
+    <row r="1680" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1680" s="1">
+        <v>46324</v>
+      </c>
+      <c r="B1680">
+        <v>101</v>
+      </c>
+      <c r="C1680" t="s">
+        <v>13</v>
+      </c>
+      <c r="E1680">
+        <v>180643</v>
+      </c>
+    </row>
+    <row r="1681" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1681" s="1">
+        <v>46324</v>
+      </c>
+      <c r="B1681">
+        <v>101</v>
+      </c>
+      <c r="C1681" t="s">
+        <v>16</v>
+      </c>
+      <c r="D1681">
+        <v>69686</v>
+      </c>
+      <c r="E1681">
+        <v>180600</v>
+      </c>
+    </row>
+    <row r="1682" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1682" s="1">
+        <v>46324</v>
+      </c>
+      <c r="B1682">
+        <v>101</v>
+      </c>
+      <c r="C1682" t="s">
+        <v>142</v>
+      </c>
+      <c r="D1682">
+        <v>69791</v>
+      </c>
+      <c r="E1682">
+        <v>180065</v>
+      </c>
+    </row>
+    <row r="1683" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1683" s="1">
+        <v>46324</v>
+      </c>
+      <c r="B1683">
+        <v>101</v>
+      </c>
+      <c r="C1683" t="s">
+        <v>272</v>
+      </c>
+      <c r="D1683">
+        <v>70557</v>
+      </c>
+      <c r="E1683">
+        <v>180439</v>
+      </c>
+    </row>
+    <row r="1684" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1684" s="1">
+        <v>46324</v>
+      </c>
+      <c r="B1684">
+        <v>101</v>
+      </c>
+      <c r="C1684" t="s">
+        <v>13</v>
+      </c>
+      <c r="E1684">
+        <v>180655</v>
+      </c>
+    </row>
+    <row r="1685" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1685" s="1">
+        <v>46324</v>
+      </c>
+      <c r="B1685">
+        <v>101</v>
+      </c>
+      <c r="C1685" t="s">
+        <v>13</v>
+      </c>
+      <c r="D1685">
+        <v>70896</v>
+      </c>
+      <c r="E1685">
+        <v>180654</v>
+      </c>
+    </row>
+    <row r="1686" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1686" s="1">
+        <v>46324</v>
+      </c>
+      <c r="B1686">
+        <v>101</v>
+      </c>
+      <c r="C1686" t="s">
+        <v>16</v>
+      </c>
+      <c r="D1686">
+        <v>70540</v>
+      </c>
+      <c r="E1686">
+        <v>180591</v>
+      </c>
+    </row>
+    <row r="1687" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1687" s="1">
+        <v>46324</v>
+      </c>
+      <c r="B1687">
+        <v>101</v>
+      </c>
+      <c r="C1687" t="s">
+        <v>16</v>
+      </c>
+      <c r="E1687">
+        <v>180658</v>
+      </c>
+    </row>
+    <row r="1688" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1688" s="1">
+        <v>46324</v>
+      </c>
+      <c r="B1688">
+        <v>101</v>
+      </c>
+      <c r="C1688" t="s">
+        <v>200</v>
+      </c>
+      <c r="D1688">
+        <v>70912</v>
+      </c>
+      <c r="E1688">
+        <v>180649</v>
+      </c>
+    </row>
+    <row r="1689" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1689" s="1">
+        <v>46324</v>
+      </c>
+      <c r="B1689">
+        <v>101</v>
+      </c>
+      <c r="C1689" t="s">
+        <v>15</v>
+      </c>
+      <c r="E1689">
+        <v>180601</v>
+      </c>
+    </row>
+    <row r="1690" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1690" s="1">
+        <v>46324</v>
+      </c>
+      <c r="B1690">
+        <v>101</v>
+      </c>
+      <c r="C1690" t="s">
+        <v>13</v>
+      </c>
+      <c r="E1690">
+        <v>180590</v>
+      </c>
+    </row>
+    <row r="1691" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1691" s="1">
+        <v>46324</v>
+      </c>
+      <c r="B1691">
+        <v>101</v>
+      </c>
+      <c r="C1691" t="s">
+        <v>89</v>
+      </c>
+      <c r="D1691">
+        <v>70890</v>
+      </c>
+      <c r="E1691">
+        <v>180651</v>
+      </c>
+    </row>
+    <row r="1692" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1692" s="1">
+        <v>46324</v>
+      </c>
+      <c r="B1692">
+        <v>101</v>
+      </c>
+      <c r="C1692" t="s">
+        <v>273</v>
+      </c>
+      <c r="D1692">
+        <v>70554</v>
+      </c>
+      <c r="E1692">
+        <v>180639</v>
+      </c>
+    </row>
+    <row r="1693" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1693" s="1">
+        <v>46324</v>
+      </c>
+      <c r="B1693">
+        <v>101</v>
+      </c>
+      <c r="C1693" t="s">
+        <v>147</v>
+      </c>
+      <c r="D1693">
+        <v>70938</v>
+      </c>
+      <c r="E1693">
+        <v>180592</v>
+      </c>
+    </row>
+    <row r="1694" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1694" s="1">
+        <v>46324</v>
+      </c>
+      <c r="B1694">
+        <v>101</v>
+      </c>
+      <c r="C1694" t="s">
+        <v>13</v>
+      </c>
+      <c r="E1694">
+        <v>180593</v>
+      </c>
+    </row>
+    <row r="1695" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1695" s="1">
+        <v>46324</v>
+      </c>
+      <c r="B1695">
+        <v>101</v>
+      </c>
+      <c r="C1695" t="s">
+        <v>148</v>
+      </c>
+      <c r="E1695">
+        <v>180641</v>
+      </c>
+    </row>
   </sheetData>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:E719">
     <sortCondition ref="A703:A719"/>
@@ -27384,6 +29514,15 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CED8C53F-6FB3-4BFC-89F0-CAB3146C1FEB}">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetData/>
+  <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5180BF9C-1943-4030-8A1B-6F86FE205C17}">
   <dimension ref="A1:C22"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -27588,7 +29727,7 @@
       </c>
       <c r="B22">
         <f>COUNTIF(Romaneios!A:A,DadosRomaneios!A22)</f>
-        <v>89</v>
+        <v>153</v>
       </c>
     </row>
   </sheetData>

--- a/DadosRomaneios.xlsx
+++ b/DadosRomaneios.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="U:\AcompanhamentoProducao\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0E0D5981-269A-4404-8894-3C77D6C672D7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5AC4D3DC-196D-415A-A52C-DE045F23E809}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{B6976704-8E51-4052-B60A-5847F95A5AE5}"/>
   </bookViews>
@@ -63,7 +63,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1700" uniqueCount="274">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1636" uniqueCount="264">
   <si>
     <t>ALBERT EINSTEIN</t>
   </si>
@@ -845,36 +845,6 @@
     <t>SYNGENTA PROTECAO</t>
   </si>
   <si>
-    <t>TEA RIBEIRAO PRETO</t>
-  </si>
-  <si>
-    <t>HOSP RIBEIRAO PRETO</t>
-  </si>
-  <si>
-    <t>DIAG ALTO BOA VISTA</t>
-  </si>
-  <si>
-    <t>CC RIBEIRAO PRETO</t>
-  </si>
-  <si>
-    <t>HAPCLINICA CAPIVARI</t>
-  </si>
-  <si>
-    <t>DIAG NACOES UNIDAS</t>
-  </si>
-  <si>
-    <t>CLINICA IRACEMAPOLIS</t>
-  </si>
-  <si>
-    <t>CLINICA SERRANA</t>
-  </si>
-  <si>
-    <t>CLINICA MORRO AGUDO</t>
-  </si>
-  <si>
-    <t>CLINICA PIRASSUNUNGA</t>
-  </si>
-  <si>
     <t>CONGREGACAO</t>
   </si>
   <si>
@@ -1264,7 +1234,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BF29A37F-A1D1-4315-91AB-A952895E1E73}">
-  <dimension ref="A1:E1695"/>
+  <dimension ref="A1:E1631"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="12.85546875" bestFit="1" customWidth="1"/>
@@ -27419,41 +27389,41 @@
     </row>
     <row r="1569" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1569" s="1">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="B1569">
         <v>101</v>
       </c>
       <c r="C1569" t="s">
-        <v>191</v>
+        <v>29</v>
       </c>
       <c r="D1569">
-        <v>69169</v>
+        <v>69980</v>
       </c>
       <c r="E1569">
-        <v>178863</v>
+        <v>180433</v>
       </c>
     </row>
     <row r="1570" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1570" s="1">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="B1570">
         <v>101</v>
       </c>
       <c r="C1570" t="s">
-        <v>39</v>
+        <v>85</v>
       </c>
       <c r="D1570">
-        <v>68863</v>
+        <v>70658</v>
       </c>
       <c r="E1570">
-        <v>178667</v>
+        <v>180640</v>
       </c>
     </row>
     <row r="1571" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1571" s="1">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="B1571">
         <v>101</v>
@@ -27462,100 +27432,97 @@
         <v>0</v>
       </c>
       <c r="D1571">
-        <v>69160</v>
+        <v>70889</v>
       </c>
       <c r="E1571">
-        <v>178631</v>
+        <v>180662</v>
       </c>
     </row>
     <row r="1572" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1572" s="1">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="B1572">
         <v>101</v>
       </c>
       <c r="C1572" t="s">
-        <v>260</v>
+        <v>0</v>
       </c>
       <c r="D1572">
-        <v>69509</v>
+        <v>70833</v>
       </c>
       <c r="E1572">
-        <v>178708</v>
+        <v>180468</v>
       </c>
     </row>
     <row r="1573" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1573" s="1">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="B1573">
         <v>101</v>
       </c>
       <c r="C1573" t="s">
-        <v>33</v>
+        <v>0</v>
       </c>
       <c r="D1573">
-        <v>69911</v>
+        <v>69398</v>
       </c>
       <c r="E1573">
-        <v>179002</v>
+        <v>179106</v>
       </c>
     </row>
     <row r="1574" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1574" s="1">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="B1574">
         <v>101</v>
       </c>
       <c r="C1574" t="s">
-        <v>261</v>
+        <v>0</v>
       </c>
       <c r="D1574">
-        <v>69516</v>
+        <v>70107</v>
       </c>
       <c r="E1574">
-        <v>178709</v>
+        <v>180251</v>
       </c>
     </row>
     <row r="1575" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1575" s="1">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="B1575">
         <v>101</v>
       </c>
       <c r="C1575" t="s">
-        <v>262</v>
+        <v>0</v>
       </c>
       <c r="D1575">
-        <v>69506</v>
+        <v>70669</v>
       </c>
       <c r="E1575">
-        <v>178706</v>
+        <v>180267</v>
       </c>
     </row>
     <row r="1576" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1576" s="1">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="B1576">
         <v>101</v>
       </c>
       <c r="C1576" t="s">
-        <v>229</v>
-      </c>
-      <c r="D1576">
-        <v>69681</v>
+        <v>0</v>
       </c>
       <c r="E1576">
-        <v>178765</v>
+        <v>180430</v>
       </c>
     </row>
     <row r="1577" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1577" s="1">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="B1577">
         <v>101</v>
@@ -27564,66 +27531,66 @@
         <v>0</v>
       </c>
       <c r="D1577">
-        <v>69494</v>
+        <v>70834</v>
       </c>
       <c r="E1577">
-        <v>179063</v>
+        <v>180395</v>
       </c>
     </row>
     <row r="1578" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1578" s="1">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="B1578">
         <v>101</v>
       </c>
       <c r="C1578" t="s">
-        <v>263</v>
+        <v>0</v>
       </c>
       <c r="D1578">
-        <v>69507</v>
+        <v>69900</v>
       </c>
       <c r="E1578">
-        <v>178707</v>
+        <v>180396</v>
       </c>
     </row>
     <row r="1579" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1579" s="1">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="B1579">
         <v>101</v>
       </c>
       <c r="C1579" t="s">
-        <v>264</v>
+        <v>0</v>
       </c>
       <c r="D1579">
-        <v>69523</v>
+        <v>70822</v>
       </c>
       <c r="E1579">
-        <v>178710</v>
+        <v>180432</v>
       </c>
     </row>
     <row r="1580" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1580" s="1">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="B1580">
         <v>101</v>
       </c>
       <c r="C1580" t="s">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="D1580">
-        <v>69404</v>
+        <v>70268</v>
       </c>
       <c r="E1580">
-        <v>179115</v>
+        <v>180589</v>
       </c>
     </row>
     <row r="1581" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1581" s="1">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="B1581">
         <v>101</v>
@@ -27632,134 +27599,131 @@
         <v>0</v>
       </c>
       <c r="D1581">
-        <v>69453</v>
+        <v>70106</v>
       </c>
       <c r="E1581">
-        <v>179319</v>
+        <v>180660</v>
       </c>
     </row>
     <row r="1582" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1582" s="1">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="B1582">
         <v>101</v>
       </c>
       <c r="C1582" t="s">
-        <v>191</v>
+        <v>260</v>
       </c>
       <c r="D1582">
-        <v>68977</v>
+        <v>71046</v>
       </c>
       <c r="E1582">
-        <v>178862</v>
+        <v>180656</v>
       </c>
     </row>
     <row r="1583" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1583" s="1">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="B1583">
         <v>101</v>
       </c>
       <c r="C1583" t="s">
-        <v>265</v>
+        <v>20</v>
       </c>
       <c r="D1583">
-        <v>69525</v>
+        <v>69037</v>
       </c>
       <c r="E1583">
-        <v>178705</v>
+        <v>180477</v>
       </c>
     </row>
     <row r="1584" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1584" s="1">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="B1584">
         <v>101</v>
       </c>
       <c r="C1584" t="s">
-        <v>0</v>
-      </c>
-      <c r="D1584">
-        <v>69431</v>
+        <v>20</v>
       </c>
       <c r="E1584">
-        <v>179317</v>
+        <v>180626</v>
       </c>
     </row>
     <row r="1585" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1585" s="1">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="B1585">
         <v>101</v>
       </c>
       <c r="C1585" t="s">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="D1585">
-        <v>69532</v>
+        <v>70249</v>
       </c>
       <c r="E1585">
-        <v>179325</v>
+        <v>180597</v>
       </c>
     </row>
     <row r="1586" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1586" s="1">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="B1586">
         <v>101</v>
       </c>
       <c r="C1586" t="s">
-        <v>204</v>
+        <v>0</v>
       </c>
       <c r="D1586">
-        <v>69651</v>
+        <v>70178</v>
       </c>
       <c r="E1586">
-        <v>179046</v>
+        <v>180623</v>
       </c>
     </row>
     <row r="1587" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1587" s="1">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="B1587">
         <v>101</v>
       </c>
       <c r="C1587" t="s">
-        <v>158</v>
+        <v>45</v>
       </c>
       <c r="D1587">
-        <v>69613</v>
+        <v>69746</v>
       </c>
       <c r="E1587">
-        <v>178877</v>
+        <v>180637</v>
       </c>
     </row>
     <row r="1588" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1588" s="1">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="B1588">
         <v>101</v>
       </c>
       <c r="C1588" t="s">
-        <v>19</v>
+        <v>45</v>
       </c>
       <c r="D1588">
-        <v>69922</v>
+        <v>69914</v>
       </c>
       <c r="E1588">
-        <v>179451</v>
+        <v>180650</v>
       </c>
     </row>
     <row r="1589" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1589" s="1">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="B1589">
         <v>101</v>
@@ -27767,16 +27731,13 @@
       <c r="C1589" t="s">
         <v>0</v>
       </c>
-      <c r="D1589">
-        <v>69864</v>
-      </c>
       <c r="E1589">
-        <v>179302</v>
+        <v>180570</v>
       </c>
     </row>
     <row r="1590" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1590" s="1">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="B1590">
         <v>101</v>
@@ -27785,15 +27746,15 @@
         <v>0</v>
       </c>
       <c r="D1590">
-        <v>69433</v>
+        <v>70493</v>
       </c>
       <c r="E1590">
-        <v>179304</v>
+        <v>180625</v>
       </c>
     </row>
     <row r="1591" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1591" s="1">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="B1591">
         <v>101</v>
@@ -27801,197 +27762,197 @@
       <c r="C1591" t="s">
         <v>0</v>
       </c>
-      <c r="D1591">
-        <v>69419</v>
-      </c>
       <c r="E1591">
-        <v>179064</v>
+        <v>180571</v>
       </c>
     </row>
     <row r="1592" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1592" s="1">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="B1592">
         <v>101</v>
       </c>
       <c r="C1592" t="s">
-        <v>266</v>
+        <v>113</v>
       </c>
       <c r="D1592">
-        <v>69919</v>
+        <v>69717</v>
       </c>
       <c r="E1592">
-        <v>179450</v>
+        <v>180574</v>
       </c>
     </row>
     <row r="1593" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1593" s="1">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="B1593">
         <v>101</v>
       </c>
       <c r="C1593" t="s">
-        <v>0</v>
+        <v>180</v>
       </c>
       <c r="D1593">
-        <v>70032</v>
+        <v>70492</v>
       </c>
       <c r="E1593">
-        <v>179341</v>
+        <v>180631</v>
       </c>
     </row>
     <row r="1594" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1594" s="1">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="B1594">
         <v>101</v>
       </c>
       <c r="C1594" t="s">
-        <v>0</v>
+        <v>111</v>
       </c>
       <c r="D1594">
-        <v>69890</v>
+        <v>69304</v>
       </c>
       <c r="E1594">
-        <v>179308</v>
+        <v>180629</v>
       </c>
     </row>
     <row r="1595" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1595" s="1">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="B1595">
         <v>101</v>
       </c>
       <c r="C1595" t="s">
-        <v>0</v>
+        <v>58</v>
       </c>
       <c r="D1595">
-        <v>69728</v>
+        <v>70933</v>
       </c>
       <c r="E1595">
-        <v>179299</v>
+        <v>180635</v>
       </c>
     </row>
     <row r="1596" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1596" s="1">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="B1596">
         <v>101</v>
       </c>
       <c r="C1596" t="s">
-        <v>267</v>
+        <v>180</v>
       </c>
       <c r="D1596">
-        <v>70136</v>
+        <v>70230</v>
       </c>
       <c r="E1596">
-        <v>179447</v>
+        <v>180582</v>
       </c>
     </row>
     <row r="1597" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1597" s="1">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="B1597">
         <v>101</v>
       </c>
       <c r="C1597" t="s">
-        <v>268</v>
+        <v>45</v>
       </c>
       <c r="D1597">
-        <v>70145</v>
+        <v>70382</v>
       </c>
       <c r="E1597">
-        <v>179454</v>
+        <v>180652</v>
       </c>
     </row>
     <row r="1598" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1598" s="1">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="B1598">
         <v>101</v>
       </c>
       <c r="C1598" t="s">
-        <v>0</v>
-      </c>
-      <c r="D1598">
-        <v>69902</v>
+        <v>60</v>
       </c>
       <c r="E1598">
-        <v>179366</v>
+        <v>180648</v>
       </c>
     </row>
     <row r="1599" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1599" s="1">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="B1599">
         <v>101</v>
       </c>
       <c r="C1599" t="s">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="D1599">
-        <v>69916</v>
+        <v>70490</v>
       </c>
       <c r="E1599">
-        <v>179449</v>
+        <v>180567</v>
       </c>
     </row>
     <row r="1600" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1600" s="1">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="B1600">
         <v>101</v>
       </c>
       <c r="C1600" t="s">
-        <v>0</v>
+        <v>60</v>
+      </c>
+      <c r="D1600">
+        <v>70067</v>
       </c>
       <c r="E1600">
-        <v>179758</v>
+        <v>180586</v>
       </c>
     </row>
     <row r="1601" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1601" s="1">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="B1601">
         <v>101</v>
       </c>
       <c r="C1601" t="s">
-        <v>7</v>
+        <v>256</v>
       </c>
       <c r="D1601">
-        <v>70091</v>
+        <v>70882</v>
       </c>
       <c r="E1601">
-        <v>179487</v>
+        <v>180392</v>
       </c>
     </row>
     <row r="1602" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1602" s="1">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="B1602">
         <v>101</v>
       </c>
       <c r="C1602" t="s">
-        <v>39</v>
+        <v>60</v>
+      </c>
+      <c r="D1602">
+        <v>70699</v>
       </c>
       <c r="E1602">
-        <v>179884</v>
+        <v>180585</v>
       </c>
     </row>
     <row r="1603" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1603" s="1">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="B1603">
         <v>101</v>
@@ -27999,44 +27960,50 @@
       <c r="C1603" t="s">
         <v>0</v>
       </c>
+      <c r="D1603">
+        <v>70025</v>
+      </c>
       <c r="E1603">
-        <v>179559</v>
+        <v>180573</v>
       </c>
     </row>
     <row r="1604" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1604" s="1">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="B1604">
         <v>101</v>
       </c>
       <c r="C1604" t="s">
-        <v>0</v>
+        <v>23</v>
+      </c>
+      <c r="D1604">
+        <v>71038</v>
       </c>
       <c r="E1604">
-        <v>179815</v>
+        <v>180617</v>
       </c>
     </row>
     <row r="1605" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1605" s="1">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="B1605">
         <v>101</v>
       </c>
       <c r="C1605" t="s">
-        <v>183</v>
+        <v>0</v>
       </c>
       <c r="D1605">
-        <v>69361</v>
+        <v>70105</v>
       </c>
       <c r="E1605">
-        <v>179595</v>
+        <v>180624</v>
       </c>
     </row>
     <row r="1606" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1606" s="1">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="B1606">
         <v>101</v>
@@ -28045,1462 +28012,401 @@
         <v>0</v>
       </c>
       <c r="E1606">
-        <v>179804</v>
+        <v>180569</v>
       </c>
     </row>
     <row r="1607" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1607" s="1">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="B1607">
         <v>101</v>
       </c>
       <c r="C1607" t="s">
-        <v>269</v>
+        <v>167</v>
       </c>
       <c r="D1607">
-        <v>70318</v>
+        <v>69573</v>
       </c>
       <c r="E1607">
-        <v>179633</v>
+        <v>180638</v>
       </c>
     </row>
     <row r="1608" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1608" s="1">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="B1608">
         <v>101</v>
       </c>
       <c r="C1608" t="s">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="D1608">
-        <v>70095</v>
+        <v>70910</v>
       </c>
       <c r="E1608">
-        <v>179761</v>
+        <v>180622</v>
       </c>
     </row>
     <row r="1609" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1609" s="1">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="B1609">
         <v>101</v>
       </c>
       <c r="C1609" t="s">
-        <v>0</v>
+        <v>23</v>
+      </c>
+      <c r="D1609">
+        <v>69572</v>
       </c>
       <c r="E1609">
-        <v>179814</v>
+        <v>180627</v>
       </c>
     </row>
     <row r="1610" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1610" s="1">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="B1610">
         <v>101</v>
       </c>
       <c r="C1610" t="s">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="D1610">
-        <v>69725</v>
+        <v>69824</v>
       </c>
       <c r="E1610">
-        <v>179867</v>
+        <v>180566</v>
       </c>
     </row>
     <row r="1611" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1611" s="1">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="B1611">
         <v>101</v>
       </c>
       <c r="C1611" t="s">
-        <v>183</v>
-      </c>
-      <c r="D1611">
-        <v>69362</v>
+        <v>33</v>
       </c>
       <c r="E1611">
-        <v>179598</v>
+        <v>180587</v>
       </c>
     </row>
     <row r="1612" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1612" s="1">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="B1612">
         <v>101</v>
       </c>
       <c r="C1612" t="s">
-        <v>0</v>
-      </c>
-      <c r="D1612">
-        <v>70287</v>
+        <v>13</v>
       </c>
       <c r="E1612">
-        <v>179813</v>
+        <v>180599</v>
       </c>
     </row>
     <row r="1613" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1613" s="1">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="B1613">
         <v>101</v>
       </c>
       <c r="C1613" t="s">
-        <v>0</v>
+        <v>261</v>
       </c>
       <c r="D1613">
-        <v>69845</v>
+        <v>69788</v>
       </c>
       <c r="E1613">
-        <v>179868</v>
+        <v>180069</v>
       </c>
     </row>
     <row r="1614" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1614" s="1">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="B1614">
         <v>101</v>
       </c>
       <c r="C1614" t="s">
-        <v>0</v>
-      </c>
-      <c r="D1614">
-        <v>69866</v>
+        <v>15</v>
       </c>
       <c r="E1614">
-        <v>179869</v>
+        <v>179394</v>
       </c>
     </row>
     <row r="1615" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1615" s="1">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="B1615">
         <v>101</v>
       </c>
       <c r="C1615" t="s">
-        <v>20</v>
+        <v>147</v>
       </c>
       <c r="D1615">
-        <v>70458</v>
+        <v>70552</v>
       </c>
       <c r="E1615">
-        <v>179729</v>
+        <v>180357</v>
       </c>
     </row>
     <row r="1616" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1616" s="1">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="B1616">
         <v>101</v>
       </c>
       <c r="C1616" t="s">
-        <v>0</v>
-      </c>
-      <c r="D1616">
-        <v>70097</v>
+        <v>13</v>
       </c>
       <c r="E1616">
-        <v>179760</v>
+        <v>180643</v>
       </c>
     </row>
     <row r="1617" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1617" s="1">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="B1617">
         <v>101</v>
       </c>
       <c r="C1617" t="s">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="D1617">
-        <v>69882</v>
+        <v>69686</v>
       </c>
       <c r="E1617">
-        <v>179866</v>
+        <v>180600</v>
       </c>
     </row>
     <row r="1618" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1618" s="1">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="B1618">
         <v>101</v>
       </c>
       <c r="C1618" t="s">
-        <v>0</v>
+        <v>142</v>
       </c>
       <c r="D1618">
-        <v>70101</v>
+        <v>69791</v>
       </c>
       <c r="E1618">
-        <v>179811</v>
+        <v>180065</v>
       </c>
     </row>
     <row r="1619" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1619" s="1">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="B1619">
         <v>101</v>
       </c>
       <c r="C1619" t="s">
-        <v>0</v>
+        <v>262</v>
+      </c>
+      <c r="D1619">
+        <v>70557</v>
       </c>
       <c r="E1619">
-        <v>179764</v>
+        <v>180439</v>
       </c>
     </row>
     <row r="1620" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1620" s="1">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="B1620">
         <v>101</v>
       </c>
       <c r="C1620" t="s">
-        <v>0</v>
-      </c>
-      <c r="D1620">
-        <v>70126</v>
+        <v>13</v>
       </c>
       <c r="E1620">
-        <v>179762</v>
+        <v>180655</v>
       </c>
     </row>
     <row r="1621" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1621" s="1">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="B1621">
         <v>101</v>
       </c>
       <c r="C1621" t="s">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="D1621">
-        <v>70098</v>
+        <v>70896</v>
       </c>
       <c r="E1621">
-        <v>179759</v>
+        <v>180654</v>
       </c>
     </row>
     <row r="1622" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1622" s="1">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="B1622">
         <v>101</v>
       </c>
       <c r="C1622" t="s">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="D1622">
-        <v>70179</v>
+        <v>70540</v>
       </c>
       <c r="E1622">
-        <v>179817</v>
+        <v>180591</v>
       </c>
     </row>
     <row r="1623" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1623" s="1">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="B1623">
         <v>101</v>
       </c>
       <c r="C1623" t="s">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="E1623">
-        <v>179816</v>
+        <v>180658</v>
       </c>
     </row>
     <row r="1624" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1624" s="1">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="B1624">
         <v>101</v>
       </c>
       <c r="C1624" t="s">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="D1624">
-        <v>70290</v>
+        <v>70912</v>
       </c>
       <c r="E1624">
-        <v>179809</v>
+        <v>180649</v>
       </c>
     </row>
     <row r="1625" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1625" s="1">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="B1625">
         <v>101</v>
       </c>
       <c r="C1625" t="s">
-        <v>0</v>
-      </c>
-      <c r="D1625">
-        <v>69443</v>
+        <v>15</v>
       </c>
       <c r="E1625">
-        <v>180093</v>
+        <v>180601</v>
       </c>
     </row>
     <row r="1626" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1626" s="1">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="B1626">
         <v>101</v>
       </c>
       <c r="C1626" t="s">
-        <v>0</v>
-      </c>
-      <c r="D1626">
-        <v>69698</v>
+        <v>13</v>
       </c>
       <c r="E1626">
-        <v>179993</v>
+        <v>180590</v>
       </c>
     </row>
     <row r="1627" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1627" s="1">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="B1627">
         <v>101</v>
       </c>
       <c r="C1627" t="s">
-        <v>0</v>
+        <v>89</v>
       </c>
       <c r="D1627">
-        <v>70100</v>
+        <v>70890</v>
       </c>
       <c r="E1627">
-        <v>179763</v>
+        <v>180651</v>
       </c>
     </row>
     <row r="1628" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1628" s="1">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="B1628">
         <v>101</v>
       </c>
       <c r="C1628" t="s">
-        <v>0</v>
+        <v>263</v>
       </c>
       <c r="D1628">
-        <v>70495</v>
+        <v>70554</v>
       </c>
       <c r="E1628">
-        <v>179994</v>
+        <v>180639</v>
       </c>
     </row>
     <row r="1629" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1629" s="1">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="B1629">
         <v>101</v>
       </c>
       <c r="C1629" t="s">
-        <v>0</v>
+        <v>147</v>
       </c>
       <c r="D1629">
-        <v>70124</v>
+        <v>70938</v>
       </c>
       <c r="E1629">
-        <v>179812</v>
+        <v>180592</v>
       </c>
     </row>
     <row r="1630" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1630" s="1">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="B1630">
         <v>101</v>
       </c>
       <c r="C1630" t="s">
-        <v>0</v>
-      </c>
-      <c r="D1630">
-        <v>70222</v>
+        <v>13</v>
       </c>
       <c r="E1630">
-        <v>179806</v>
+        <v>180593</v>
       </c>
     </row>
     <row r="1631" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1631" s="1">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="B1631">
         <v>101</v>
       </c>
       <c r="C1631" t="s">
-        <v>0</v>
-      </c>
-      <c r="D1631">
-        <v>70224</v>
+        <v>148</v>
       </c>
       <c r="E1631">
-        <v>179805</v>
-      </c>
-    </row>
-    <row r="1632" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A1632" s="1">
-        <v>46323</v>
-      </c>
-      <c r="B1632">
-        <v>101</v>
-      </c>
-      <c r="C1632" t="s">
-        <v>0</v>
-      </c>
-      <c r="D1632">
-        <v>69849</v>
-      </c>
-      <c r="E1632">
-        <v>180010</v>
-      </c>
-    </row>
-    <row r="1633" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A1633" s="1">
-        <v>46324</v>
-      </c>
-      <c r="B1633">
-        <v>101</v>
-      </c>
-      <c r="C1633" t="s">
-        <v>29</v>
-      </c>
-      <c r="D1633">
-        <v>69980</v>
-      </c>
-      <c r="E1633">
-        <v>180433</v>
-      </c>
-    </row>
-    <row r="1634" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A1634" s="1">
-        <v>46324</v>
-      </c>
-      <c r="B1634">
-        <v>101</v>
-      </c>
-      <c r="C1634" t="s">
-        <v>85</v>
-      </c>
-      <c r="D1634">
-        <v>70658</v>
-      </c>
-      <c r="E1634">
-        <v>180640</v>
-      </c>
-    </row>
-    <row r="1635" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A1635" s="1">
-        <v>46324</v>
-      </c>
-      <c r="B1635">
-        <v>101</v>
-      </c>
-      <c r="C1635" t="s">
-        <v>0</v>
-      </c>
-      <c r="D1635">
-        <v>70889</v>
-      </c>
-      <c r="E1635">
-        <v>180662</v>
-      </c>
-    </row>
-    <row r="1636" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A1636" s="1">
-        <v>46324</v>
-      </c>
-      <c r="B1636">
-        <v>101</v>
-      </c>
-      <c r="C1636" t="s">
-        <v>0</v>
-      </c>
-      <c r="D1636">
-        <v>70833</v>
-      </c>
-      <c r="E1636">
-        <v>180468</v>
-      </c>
-    </row>
-    <row r="1637" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A1637" s="1">
-        <v>46324</v>
-      </c>
-      <c r="B1637">
-        <v>101</v>
-      </c>
-      <c r="C1637" t="s">
-        <v>0</v>
-      </c>
-      <c r="D1637">
-        <v>69398</v>
-      </c>
-      <c r="E1637">
-        <v>179106</v>
-      </c>
-    </row>
-    <row r="1638" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A1638" s="1">
-        <v>46324</v>
-      </c>
-      <c r="B1638">
-        <v>101</v>
-      </c>
-      <c r="C1638" t="s">
-        <v>0</v>
-      </c>
-      <c r="D1638">
-        <v>70107</v>
-      </c>
-      <c r="E1638">
-        <v>180251</v>
-      </c>
-    </row>
-    <row r="1639" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A1639" s="1">
-        <v>46324</v>
-      </c>
-      <c r="B1639">
-        <v>101</v>
-      </c>
-      <c r="C1639" t="s">
-        <v>0</v>
-      </c>
-      <c r="D1639">
-        <v>70669</v>
-      </c>
-      <c r="E1639">
-        <v>180267</v>
-      </c>
-    </row>
-    <row r="1640" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A1640" s="1">
-        <v>46324</v>
-      </c>
-      <c r="B1640">
-        <v>101</v>
-      </c>
-      <c r="C1640" t="s">
-        <v>0</v>
-      </c>
-      <c r="E1640">
-        <v>180430</v>
-      </c>
-    </row>
-    <row r="1641" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A1641" s="1">
-        <v>46324</v>
-      </c>
-      <c r="B1641">
-        <v>101</v>
-      </c>
-      <c r="C1641" t="s">
-        <v>0</v>
-      </c>
-      <c r="D1641">
-        <v>70834</v>
-      </c>
-      <c r="E1641">
-        <v>180395</v>
-      </c>
-    </row>
-    <row r="1642" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A1642" s="1">
-        <v>46324</v>
-      </c>
-      <c r="B1642">
-        <v>101</v>
-      </c>
-      <c r="C1642" t="s">
-        <v>0</v>
-      </c>
-      <c r="D1642">
-        <v>69900</v>
-      </c>
-      <c r="E1642">
-        <v>180396</v>
-      </c>
-    </row>
-    <row r="1643" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A1643" s="1">
-        <v>46324</v>
-      </c>
-      <c r="B1643">
-        <v>101</v>
-      </c>
-      <c r="C1643" t="s">
-        <v>0</v>
-      </c>
-      <c r="D1643">
-        <v>70822</v>
-      </c>
-      <c r="E1643">
-        <v>180432</v>
-      </c>
-    </row>
-    <row r="1644" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A1644" s="1">
-        <v>46324</v>
-      </c>
-      <c r="B1644">
-        <v>101</v>
-      </c>
-      <c r="C1644" t="s">
-        <v>15</v>
-      </c>
-      <c r="D1644">
-        <v>70268</v>
-      </c>
-      <c r="E1644">
-        <v>180589</v>
-      </c>
-    </row>
-    <row r="1645" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A1645" s="1">
-        <v>46324</v>
-      </c>
-      <c r="B1645">
-        <v>101</v>
-      </c>
-      <c r="C1645" t="s">
-        <v>0</v>
-      </c>
-      <c r="D1645">
-        <v>70106</v>
-      </c>
-      <c r="E1645">
-        <v>180660</v>
-      </c>
-    </row>
-    <row r="1646" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A1646" s="1">
-        <v>46324</v>
-      </c>
-      <c r="B1646">
-        <v>101</v>
-      </c>
-      <c r="C1646" t="s">
-        <v>270</v>
-      </c>
-      <c r="D1646">
-        <v>71046</v>
-      </c>
-      <c r="E1646">
-        <v>180656</v>
-      </c>
-    </row>
-    <row r="1647" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A1647" s="1">
-        <v>46324</v>
-      </c>
-      <c r="B1647">
-        <v>101</v>
-      </c>
-      <c r="C1647" t="s">
-        <v>20</v>
-      </c>
-      <c r="D1647">
-        <v>69037</v>
-      </c>
-      <c r="E1647">
-        <v>180477</v>
-      </c>
-    </row>
-    <row r="1648" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A1648" s="1">
-        <v>46324</v>
-      </c>
-      <c r="B1648">
-        <v>101</v>
-      </c>
-      <c r="C1648" t="s">
-        <v>20</v>
-      </c>
-      <c r="E1648">
-        <v>180626</v>
-      </c>
-    </row>
-    <row r="1649" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A1649" s="1">
-        <v>46324</v>
-      </c>
-      <c r="B1649">
-        <v>101</v>
-      </c>
-      <c r="C1649" t="s">
-        <v>20</v>
-      </c>
-      <c r="D1649">
-        <v>70249</v>
-      </c>
-      <c r="E1649">
-        <v>180597</v>
-      </c>
-    </row>
-    <row r="1650" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A1650" s="1">
-        <v>46324</v>
-      </c>
-      <c r="B1650">
-        <v>101</v>
-      </c>
-      <c r="C1650" t="s">
-        <v>0</v>
-      </c>
-      <c r="D1650">
-        <v>70178</v>
-      </c>
-      <c r="E1650">
-        <v>180623</v>
-      </c>
-    </row>
-    <row r="1651" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A1651" s="1">
-        <v>46324</v>
-      </c>
-      <c r="B1651">
-        <v>101</v>
-      </c>
-      <c r="C1651" t="s">
-        <v>45</v>
-      </c>
-      <c r="D1651">
-        <v>69746</v>
-      </c>
-      <c r="E1651">
-        <v>180637</v>
-      </c>
-    </row>
-    <row r="1652" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A1652" s="1">
-        <v>46324</v>
-      </c>
-      <c r="B1652">
-        <v>101</v>
-      </c>
-      <c r="C1652" t="s">
-        <v>45</v>
-      </c>
-      <c r="D1652">
-        <v>69914</v>
-      </c>
-      <c r="E1652">
-        <v>180650</v>
-      </c>
-    </row>
-    <row r="1653" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A1653" s="1">
-        <v>46324</v>
-      </c>
-      <c r="B1653">
-        <v>101</v>
-      </c>
-      <c r="C1653" t="s">
-        <v>0</v>
-      </c>
-      <c r="E1653">
-        <v>180570</v>
-      </c>
-    </row>
-    <row r="1654" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A1654" s="1">
-        <v>46324</v>
-      </c>
-      <c r="B1654">
-        <v>101</v>
-      </c>
-      <c r="C1654" t="s">
-        <v>0</v>
-      </c>
-      <c r="D1654">
-        <v>70493</v>
-      </c>
-      <c r="E1654">
-        <v>180625</v>
-      </c>
-    </row>
-    <row r="1655" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A1655" s="1">
-        <v>46324</v>
-      </c>
-      <c r="B1655">
-        <v>101</v>
-      </c>
-      <c r="C1655" t="s">
-        <v>0</v>
-      </c>
-      <c r="E1655">
-        <v>180571</v>
-      </c>
-    </row>
-    <row r="1656" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A1656" s="1">
-        <v>46324</v>
-      </c>
-      <c r="B1656">
-        <v>101</v>
-      </c>
-      <c r="C1656" t="s">
-        <v>113</v>
-      </c>
-      <c r="D1656">
-        <v>69717</v>
-      </c>
-      <c r="E1656">
-        <v>180574</v>
-      </c>
-    </row>
-    <row r="1657" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A1657" s="1">
-        <v>46324</v>
-      </c>
-      <c r="B1657">
-        <v>101</v>
-      </c>
-      <c r="C1657" t="s">
-        <v>180</v>
-      </c>
-      <c r="D1657">
-        <v>70492</v>
-      </c>
-      <c r="E1657">
-        <v>180631</v>
-      </c>
-    </row>
-    <row r="1658" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A1658" s="1">
-        <v>46324</v>
-      </c>
-      <c r="B1658">
-        <v>101</v>
-      </c>
-      <c r="C1658" t="s">
-        <v>111</v>
-      </c>
-      <c r="D1658">
-        <v>69304</v>
-      </c>
-      <c r="E1658">
-        <v>180629</v>
-      </c>
-    </row>
-    <row r="1659" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A1659" s="1">
-        <v>46324</v>
-      </c>
-      <c r="B1659">
-        <v>101</v>
-      </c>
-      <c r="C1659" t="s">
-        <v>58</v>
-      </c>
-      <c r="D1659">
-        <v>70933</v>
-      </c>
-      <c r="E1659">
-        <v>180635</v>
-      </c>
-    </row>
-    <row r="1660" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A1660" s="1">
-        <v>46324</v>
-      </c>
-      <c r="B1660">
-        <v>101</v>
-      </c>
-      <c r="C1660" t="s">
-        <v>180</v>
-      </c>
-      <c r="D1660">
-        <v>70230</v>
-      </c>
-      <c r="E1660">
-        <v>180582</v>
-      </c>
-    </row>
-    <row r="1661" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A1661" s="1">
-        <v>46324</v>
-      </c>
-      <c r="B1661">
-        <v>101</v>
-      </c>
-      <c r="C1661" t="s">
-        <v>45</v>
-      </c>
-      <c r="D1661">
-        <v>70382</v>
-      </c>
-      <c r="E1661">
-        <v>180652</v>
-      </c>
-    </row>
-    <row r="1662" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A1662" s="1">
-        <v>46324</v>
-      </c>
-      <c r="B1662">
-        <v>101</v>
-      </c>
-      <c r="C1662" t="s">
-        <v>60</v>
-      </c>
-      <c r="E1662">
-        <v>180648</v>
-      </c>
-    </row>
-    <row r="1663" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A1663" s="1">
-        <v>46324</v>
-      </c>
-      <c r="B1663">
-        <v>101</v>
-      </c>
-      <c r="C1663" t="s">
-        <v>0</v>
-      </c>
-      <c r="D1663">
-        <v>70490</v>
-      </c>
-      <c r="E1663">
-        <v>180567</v>
-      </c>
-    </row>
-    <row r="1664" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A1664" s="1">
-        <v>46324</v>
-      </c>
-      <c r="B1664">
-        <v>101</v>
-      </c>
-      <c r="C1664" t="s">
-        <v>60</v>
-      </c>
-      <c r="D1664">
-        <v>70067</v>
-      </c>
-      <c r="E1664">
-        <v>180586</v>
-      </c>
-    </row>
-    <row r="1665" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A1665" s="1">
-        <v>46324</v>
-      </c>
-      <c r="B1665">
-        <v>101</v>
-      </c>
-      <c r="C1665" t="s">
-        <v>256</v>
-      </c>
-      <c r="D1665">
-        <v>70882</v>
-      </c>
-      <c r="E1665">
-        <v>180392</v>
-      </c>
-    </row>
-    <row r="1666" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A1666" s="1">
-        <v>46324</v>
-      </c>
-      <c r="B1666">
-        <v>101</v>
-      </c>
-      <c r="C1666" t="s">
-        <v>60</v>
-      </c>
-      <c r="D1666">
-        <v>70699</v>
-      </c>
-      <c r="E1666">
-        <v>180585</v>
-      </c>
-    </row>
-    <row r="1667" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A1667" s="1">
-        <v>46324</v>
-      </c>
-      <c r="B1667">
-        <v>101</v>
-      </c>
-      <c r="C1667" t="s">
-        <v>0</v>
-      </c>
-      <c r="D1667">
-        <v>70025</v>
-      </c>
-      <c r="E1667">
-        <v>180573</v>
-      </c>
-    </row>
-    <row r="1668" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A1668" s="1">
-        <v>46324</v>
-      </c>
-      <c r="B1668">
-        <v>101</v>
-      </c>
-      <c r="C1668" t="s">
-        <v>23</v>
-      </c>
-      <c r="D1668">
-        <v>71038</v>
-      </c>
-      <c r="E1668">
-        <v>180617</v>
-      </c>
-    </row>
-    <row r="1669" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A1669" s="1">
-        <v>46324</v>
-      </c>
-      <c r="B1669">
-        <v>101</v>
-      </c>
-      <c r="C1669" t="s">
-        <v>0</v>
-      </c>
-      <c r="D1669">
-        <v>70105</v>
-      </c>
-      <c r="E1669">
-        <v>180624</v>
-      </c>
-    </row>
-    <row r="1670" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A1670" s="1">
-        <v>46324</v>
-      </c>
-      <c r="B1670">
-        <v>101</v>
-      </c>
-      <c r="C1670" t="s">
-        <v>0</v>
-      </c>
-      <c r="E1670">
-        <v>180569</v>
-      </c>
-    </row>
-    <row r="1671" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A1671" s="1">
-        <v>46324</v>
-      </c>
-      <c r="B1671">
-        <v>101</v>
-      </c>
-      <c r="C1671" t="s">
-        <v>167</v>
-      </c>
-      <c r="D1671">
-        <v>69573</v>
-      </c>
-      <c r="E1671">
-        <v>180638</v>
-      </c>
-    </row>
-    <row r="1672" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A1672" s="1">
-        <v>46324</v>
-      </c>
-      <c r="B1672">
-        <v>101</v>
-      </c>
-      <c r="C1672" t="s">
-        <v>40</v>
-      </c>
-      <c r="D1672">
-        <v>70910</v>
-      </c>
-      <c r="E1672">
-        <v>180622</v>
-      </c>
-    </row>
-    <row r="1673" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A1673" s="1">
-        <v>46324</v>
-      </c>
-      <c r="B1673">
-        <v>101</v>
-      </c>
-      <c r="C1673" t="s">
-        <v>23</v>
-      </c>
-      <c r="D1673">
-        <v>69572</v>
-      </c>
-      <c r="E1673">
-        <v>180627</v>
-      </c>
-    </row>
-    <row r="1674" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A1674" s="1">
-        <v>46324</v>
-      </c>
-      <c r="B1674">
-        <v>101</v>
-      </c>
-      <c r="C1674" t="s">
-        <v>15</v>
-      </c>
-      <c r="D1674">
-        <v>69824</v>
-      </c>
-      <c r="E1674">
-        <v>180566</v>
-      </c>
-    </row>
-    <row r="1675" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A1675" s="1">
-        <v>46324</v>
-      </c>
-      <c r="B1675">
-        <v>101</v>
-      </c>
-      <c r="C1675" t="s">
-        <v>33</v>
-      </c>
-      <c r="E1675">
-        <v>180587</v>
-      </c>
-    </row>
-    <row r="1676" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A1676" s="1">
-        <v>46324</v>
-      </c>
-      <c r="B1676">
-        <v>101</v>
-      </c>
-      <c r="C1676" t="s">
-        <v>13</v>
-      </c>
-      <c r="E1676">
-        <v>180599</v>
-      </c>
-    </row>
-    <row r="1677" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A1677" s="1">
-        <v>46324</v>
-      </c>
-      <c r="B1677">
-        <v>101</v>
-      </c>
-      <c r="C1677" t="s">
-        <v>271</v>
-      </c>
-      <c r="D1677">
-        <v>69788</v>
-      </c>
-      <c r="E1677">
-        <v>180069</v>
-      </c>
-    </row>
-    <row r="1678" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A1678" s="1">
-        <v>46324</v>
-      </c>
-      <c r="B1678">
-        <v>101</v>
-      </c>
-      <c r="C1678" t="s">
-        <v>15</v>
-      </c>
-      <c r="E1678">
-        <v>179394</v>
-      </c>
-    </row>
-    <row r="1679" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A1679" s="1">
-        <v>46324</v>
-      </c>
-      <c r="B1679">
-        <v>101</v>
-      </c>
-      <c r="C1679" t="s">
-        <v>147</v>
-      </c>
-      <c r="D1679">
-        <v>70552</v>
-      </c>
-      <c r="E1679">
-        <v>180357</v>
-      </c>
-    </row>
-    <row r="1680" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A1680" s="1">
-        <v>46324</v>
-      </c>
-      <c r="B1680">
-        <v>101</v>
-      </c>
-      <c r="C1680" t="s">
-        <v>13</v>
-      </c>
-      <c r="E1680">
-        <v>180643</v>
-      </c>
-    </row>
-    <row r="1681" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A1681" s="1">
-        <v>46324</v>
-      </c>
-      <c r="B1681">
-        <v>101</v>
-      </c>
-      <c r="C1681" t="s">
-        <v>16</v>
-      </c>
-      <c r="D1681">
-        <v>69686</v>
-      </c>
-      <c r="E1681">
-        <v>180600</v>
-      </c>
-    </row>
-    <row r="1682" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A1682" s="1">
-        <v>46324</v>
-      </c>
-      <c r="B1682">
-        <v>101</v>
-      </c>
-      <c r="C1682" t="s">
-        <v>142</v>
-      </c>
-      <c r="D1682">
-        <v>69791</v>
-      </c>
-      <c r="E1682">
-        <v>180065</v>
-      </c>
-    </row>
-    <row r="1683" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A1683" s="1">
-        <v>46324</v>
-      </c>
-      <c r="B1683">
-        <v>101</v>
-      </c>
-      <c r="C1683" t="s">
-        <v>272</v>
-      </c>
-      <c r="D1683">
-        <v>70557</v>
-      </c>
-      <c r="E1683">
-        <v>180439</v>
-      </c>
-    </row>
-    <row r="1684" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A1684" s="1">
-        <v>46324</v>
-      </c>
-      <c r="B1684">
-        <v>101</v>
-      </c>
-      <c r="C1684" t="s">
-        <v>13</v>
-      </c>
-      <c r="E1684">
-        <v>180655</v>
-      </c>
-    </row>
-    <row r="1685" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A1685" s="1">
-        <v>46324</v>
-      </c>
-      <c r="B1685">
-        <v>101</v>
-      </c>
-      <c r="C1685" t="s">
-        <v>13</v>
-      </c>
-      <c r="D1685">
-        <v>70896</v>
-      </c>
-      <c r="E1685">
-        <v>180654</v>
-      </c>
-    </row>
-    <row r="1686" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A1686" s="1">
-        <v>46324</v>
-      </c>
-      <c r="B1686">
-        <v>101</v>
-      </c>
-      <c r="C1686" t="s">
-        <v>16</v>
-      </c>
-      <c r="D1686">
-        <v>70540</v>
-      </c>
-      <c r="E1686">
-        <v>180591</v>
-      </c>
-    </row>
-    <row r="1687" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A1687" s="1">
-        <v>46324</v>
-      </c>
-      <c r="B1687">
-        <v>101</v>
-      </c>
-      <c r="C1687" t="s">
-        <v>16</v>
-      </c>
-      <c r="E1687">
-        <v>180658</v>
-      </c>
-    </row>
-    <row r="1688" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A1688" s="1">
-        <v>46324</v>
-      </c>
-      <c r="B1688">
-        <v>101</v>
-      </c>
-      <c r="C1688" t="s">
-        <v>200</v>
-      </c>
-      <c r="D1688">
-        <v>70912</v>
-      </c>
-      <c r="E1688">
-        <v>180649</v>
-      </c>
-    </row>
-    <row r="1689" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A1689" s="1">
-        <v>46324</v>
-      </c>
-      <c r="B1689">
-        <v>101</v>
-      </c>
-      <c r="C1689" t="s">
-        <v>15</v>
-      </c>
-      <c r="E1689">
-        <v>180601</v>
-      </c>
-    </row>
-    <row r="1690" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A1690" s="1">
-        <v>46324</v>
-      </c>
-      <c r="B1690">
-        <v>101</v>
-      </c>
-      <c r="C1690" t="s">
-        <v>13</v>
-      </c>
-      <c r="E1690">
-        <v>180590</v>
-      </c>
-    </row>
-    <row r="1691" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A1691" s="1">
-        <v>46324</v>
-      </c>
-      <c r="B1691">
-        <v>101</v>
-      </c>
-      <c r="C1691" t="s">
-        <v>89</v>
-      </c>
-      <c r="D1691">
-        <v>70890</v>
-      </c>
-      <c r="E1691">
-        <v>180651</v>
-      </c>
-    </row>
-    <row r="1692" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A1692" s="1">
-        <v>46324</v>
-      </c>
-      <c r="B1692">
-        <v>101</v>
-      </c>
-      <c r="C1692" t="s">
-        <v>273</v>
-      </c>
-      <c r="D1692">
-        <v>70554</v>
-      </c>
-      <c r="E1692">
-        <v>180639</v>
-      </c>
-    </row>
-    <row r="1693" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A1693" s="1">
-        <v>46324</v>
-      </c>
-      <c r="B1693">
-        <v>101</v>
-      </c>
-      <c r="C1693" t="s">
-        <v>147</v>
-      </c>
-      <c r="D1693">
-        <v>70938</v>
-      </c>
-      <c r="E1693">
-        <v>180592</v>
-      </c>
-    </row>
-    <row r="1694" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A1694" s="1">
-        <v>46324</v>
-      </c>
-      <c r="B1694">
-        <v>101</v>
-      </c>
-      <c r="C1694" t="s">
-        <v>13</v>
-      </c>
-      <c r="E1694">
-        <v>180593</v>
-      </c>
-    </row>
-    <row r="1695" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A1695" s="1">
-        <v>46324</v>
-      </c>
-      <c r="B1695">
-        <v>101</v>
-      </c>
-      <c r="C1695" t="s">
-        <v>148</v>
-      </c>
-      <c r="E1695">
         <v>180641</v>
       </c>
     </row>
@@ -29727,7 +28633,7 @@
       </c>
       <c r="B22">
         <f>COUNTIF(Romaneios!A:A,DadosRomaneios!A22)</f>
-        <v>153</v>
+        <v>89</v>
       </c>
     </row>
   </sheetData>

--- a/DadosRomaneios.xlsx
+++ b/DadosRomaneios.xlsx
@@ -8,14 +8,13 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="U:\AcompanhamentoProducao\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5AC4D3DC-196D-415A-A52C-DE045F23E809}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A50B8077-AF1F-40C3-B93B-D28F8A272DD6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{B6976704-8E51-4052-B60A-5847F95A5AE5}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" activeTab="1" xr2:uid="{B6976704-8E51-4052-B60A-5847F95A5AE5}"/>
   </bookViews>
   <sheets>
     <sheet name="Romaneios" sheetId="2" r:id="rId1"/>
-    <sheet name="Planilha1" sheetId="4" r:id="rId2"/>
-    <sheet name="DadosRomaneios" sheetId="3" r:id="rId3"/>
+    <sheet name="DadosRomaneios" sheetId="3" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -41,7 +40,7 @@
 </file>
 
 <file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
-<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
+<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xlrd="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
   <metadataTypes count="1">
     <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
   </metadataTypes>
@@ -63,7 +62,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1636" uniqueCount="264">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1650" uniqueCount="269">
   <si>
     <t>ALBERT EINSTEIN</t>
   </si>
@@ -856,6 +855,21 @@
   <si>
     <t>CC MADUREIRA</t>
   </si>
+  <si>
+    <t>090149-DGAC</t>
+  </si>
+  <si>
+    <t>DASA 61.486.650/008</t>
+  </si>
+  <si>
+    <t>AME RIO CLARO</t>
+  </si>
+  <si>
+    <t>HOSPITAL ARARAQUARA</t>
+  </si>
+  <si>
+    <t>HOSPITAL FRANCA</t>
+  </si>
 </sst>
 </file>
 
@@ -1234,7 +1248,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BF29A37F-A1D1-4315-91AB-A952895E1E73}">
-  <dimension ref="A1:E1631"/>
+  <dimension ref="A1:E1645"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="12.85546875" bestFit="1" customWidth="1"/>
@@ -28410,6 +28424,244 @@
         <v>180641</v>
       </c>
     </row>
+    <row r="1632" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1632" s="1">
+        <v>46324</v>
+      </c>
+      <c r="B1632">
+        <v>101</v>
+      </c>
+      <c r="C1632" t="s">
+        <v>246</v>
+      </c>
+      <c r="D1632">
+        <v>70578</v>
+      </c>
+      <c r="E1632">
+        <v>180645</v>
+      </c>
+    </row>
+    <row r="1633" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1633" s="1">
+        <v>46324</v>
+      </c>
+      <c r="B1633">
+        <v>101</v>
+      </c>
+      <c r="C1633" t="s">
+        <v>246</v>
+      </c>
+      <c r="D1633">
+        <v>70580</v>
+      </c>
+      <c r="E1633">
+        <v>180646</v>
+      </c>
+    </row>
+    <row r="1634" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1634" s="1">
+        <v>46324</v>
+      </c>
+      <c r="B1634">
+        <v>101</v>
+      </c>
+      <c r="C1634" t="s">
+        <v>7</v>
+      </c>
+      <c r="D1634">
+        <v>70819</v>
+      </c>
+      <c r="E1634">
+        <v>180542</v>
+      </c>
+    </row>
+    <row r="1635" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1635" s="1">
+        <v>46324</v>
+      </c>
+      <c r="B1635">
+        <v>101</v>
+      </c>
+      <c r="C1635" t="s">
+        <v>222</v>
+      </c>
+      <c r="D1635">
+        <v>69985</v>
+      </c>
+      <c r="E1635">
+        <v>180556</v>
+      </c>
+    </row>
+    <row r="1636" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1636" s="1">
+        <v>46324</v>
+      </c>
+      <c r="B1636">
+        <v>101</v>
+      </c>
+      <c r="C1636" t="s">
+        <v>7</v>
+      </c>
+      <c r="D1636">
+        <v>70995</v>
+      </c>
+      <c r="E1636">
+        <v>180494</v>
+      </c>
+    </row>
+    <row r="1637" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1637" s="1">
+        <v>46324</v>
+      </c>
+      <c r="B1637">
+        <v>101</v>
+      </c>
+      <c r="C1637" t="s">
+        <v>264</v>
+      </c>
+      <c r="D1637">
+        <v>70294</v>
+      </c>
+      <c r="E1637">
+        <v>180553</v>
+      </c>
+    </row>
+    <row r="1638" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1638" s="1">
+        <v>46324</v>
+      </c>
+      <c r="B1638">
+        <v>101</v>
+      </c>
+      <c r="C1638" t="s">
+        <v>265</v>
+      </c>
+      <c r="D1638">
+        <v>70698</v>
+      </c>
+      <c r="E1638">
+        <v>180634</v>
+      </c>
+    </row>
+    <row r="1639" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1639" s="1">
+        <v>46324</v>
+      </c>
+      <c r="B1639">
+        <v>101</v>
+      </c>
+      <c r="C1639" t="s">
+        <v>19</v>
+      </c>
+      <c r="D1639">
+        <v>70879</v>
+      </c>
+      <c r="E1639">
+        <v>180595</v>
+      </c>
+    </row>
+    <row r="1640" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1640" s="1">
+        <v>46324</v>
+      </c>
+      <c r="B1640">
+        <v>101</v>
+      </c>
+      <c r="C1640" t="s">
+        <v>266</v>
+      </c>
+      <c r="D1640">
+        <v>70931</v>
+      </c>
+      <c r="E1640">
+        <v>180678</v>
+      </c>
+    </row>
+    <row r="1641" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1641" s="1">
+        <v>46324</v>
+      </c>
+      <c r="B1641">
+        <v>101</v>
+      </c>
+      <c r="C1641" t="s">
+        <v>267</v>
+      </c>
+      <c r="D1641">
+        <v>70880</v>
+      </c>
+      <c r="E1641">
+        <v>180628</v>
+      </c>
+    </row>
+    <row r="1642" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1642" s="1">
+        <v>46324</v>
+      </c>
+      <c r="B1642">
+        <v>101</v>
+      </c>
+      <c r="C1642" t="s">
+        <v>268</v>
+      </c>
+      <c r="D1642">
+        <v>70884</v>
+      </c>
+      <c r="E1642">
+        <v>180583</v>
+      </c>
+    </row>
+    <row r="1643" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1643" s="1">
+        <v>46324</v>
+      </c>
+      <c r="B1643">
+        <v>101</v>
+      </c>
+      <c r="C1643" t="s">
+        <v>148</v>
+      </c>
+      <c r="D1643">
+        <v>70010</v>
+      </c>
+      <c r="E1643">
+        <v>180435</v>
+      </c>
+    </row>
+    <row r="1644" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1644" s="1">
+        <v>46324</v>
+      </c>
+      <c r="B1644">
+        <v>101</v>
+      </c>
+      <c r="C1644" t="s">
+        <v>144</v>
+      </c>
+      <c r="D1644">
+        <v>69800</v>
+      </c>
+      <c r="E1644">
+        <v>180491</v>
+      </c>
+    </row>
+    <row r="1645" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1645" s="1">
+        <v>46324</v>
+      </c>
+      <c r="B1645">
+        <v>101</v>
+      </c>
+      <c r="C1645" t="s">
+        <v>62</v>
+      </c>
+      <c r="D1645">
+        <v>70845</v>
+      </c>
+      <c r="E1645">
+        <v>180387</v>
+      </c>
+    </row>
   </sheetData>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:E719">
     <sortCondition ref="A703:A719"/>
@@ -28420,17 +28672,8 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CED8C53F-6FB3-4BFC-89F0-CAB3146C1FEB}">
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <sheetData/>
-  <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5180BF9C-1943-4030-8A1B-6F86FE205C17}">
-  <dimension ref="A1:C22"/>
+  <dimension ref="A1:C23"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="12.85546875" style="1" bestFit="1" customWidth="1"/>
@@ -28439,7 +28682,7 @@
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="str" cm="1">
-        <f t="array" ref="A1:A22">_xlfn.UNIQUE(Romaneios!A1:A1568)</f>
+        <f t="array" ref="A1:A23">_xlfn.UNIQUE(Romaneios!A1:A1645)</f>
         <v>Dt. Romaneio</v>
       </c>
       <c r="B1" t="s">
@@ -28634,6 +28877,15 @@
       <c r="B22">
         <f>COUNTIF(Romaneios!A:A,DadosRomaneios!A22)</f>
         <v>89</v>
+      </c>
+    </row>
+    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A23" s="1">
+        <v>46324</v>
+      </c>
+      <c r="B23">
+        <f>COUNTIF(Romaneios!A:A,DadosRomaneios!A23)</f>
+        <v>77</v>
       </c>
     </row>
   </sheetData>

--- a/DadosRomaneios.xlsx
+++ b/DadosRomaneios.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="U:\AcompanhamentoProducao\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A50B8077-AF1F-40C3-B93B-D28F8A272DD6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FCFDC095-4DD0-4FC8-A40B-312AC16C187E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" activeTab="1" xr2:uid="{B6976704-8E51-4052-B60A-5847F95A5AE5}"/>
   </bookViews>
@@ -62,7 +62,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1650" uniqueCount="269">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1742" uniqueCount="271">
   <si>
     <t>ALBERT EINSTEIN</t>
   </si>
@@ -870,6 +870,12 @@
   <si>
     <t>HOSPITAL FRANCA</t>
   </si>
+  <si>
+    <t>WURTH SW INDUSTRY</t>
+  </si>
+  <si>
+    <t>DASA RAPOSO</t>
+  </si>
 </sst>
 </file>
 
@@ -1248,7 +1254,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BF29A37F-A1D1-4315-91AB-A952895E1E73}">
-  <dimension ref="A1:E1645"/>
+  <dimension ref="A1:E1737"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="12.85546875" bestFit="1" customWidth="1"/>
@@ -28662,6 +28668,1534 @@
         <v>180387</v>
       </c>
     </row>
+    <row r="1646" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1646" s="1">
+        <v>46324</v>
+      </c>
+      <c r="B1646">
+        <v>101</v>
+      </c>
+      <c r="C1646" t="s">
+        <v>27</v>
+      </c>
+      <c r="D1646">
+        <v>70256</v>
+      </c>
+      <c r="E1646">
+        <v>180732</v>
+      </c>
+    </row>
+    <row r="1647" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1647" s="1">
+        <v>46324</v>
+      </c>
+      <c r="B1647">
+        <v>101</v>
+      </c>
+      <c r="C1647" t="s">
+        <v>159</v>
+      </c>
+      <c r="D1647">
+        <v>66269</v>
+      </c>
+      <c r="E1647">
+        <v>178556</v>
+      </c>
+    </row>
+    <row r="1648" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1648" s="1">
+        <v>46324</v>
+      </c>
+      <c r="B1648">
+        <v>101</v>
+      </c>
+      <c r="C1648" t="s">
+        <v>159</v>
+      </c>
+      <c r="D1648">
+        <v>70311</v>
+      </c>
+      <c r="E1648">
+        <v>180022</v>
+      </c>
+    </row>
+    <row r="1649" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1649" s="1">
+        <v>46324</v>
+      </c>
+      <c r="B1649">
+        <v>101</v>
+      </c>
+      <c r="C1649" t="s">
+        <v>89</v>
+      </c>
+      <c r="D1649">
+        <v>70954</v>
+      </c>
+      <c r="E1649">
+        <v>180661</v>
+      </c>
+    </row>
+    <row r="1650" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1650" s="1">
+        <v>46324</v>
+      </c>
+      <c r="B1650">
+        <v>101</v>
+      </c>
+      <c r="C1650" t="s">
+        <v>159</v>
+      </c>
+      <c r="E1650">
+        <v>180676</v>
+      </c>
+    </row>
+    <row r="1651" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1651" s="1">
+        <v>46324</v>
+      </c>
+      <c r="B1651">
+        <v>101</v>
+      </c>
+      <c r="C1651" t="s">
+        <v>45</v>
+      </c>
+      <c r="D1651">
+        <v>70586</v>
+      </c>
+      <c r="E1651">
+        <v>180722</v>
+      </c>
+    </row>
+    <row r="1652" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1652" s="1">
+        <v>46324</v>
+      </c>
+      <c r="B1652">
+        <v>101</v>
+      </c>
+      <c r="C1652" t="s">
+        <v>9</v>
+      </c>
+      <c r="D1652">
+        <v>70805</v>
+      </c>
+      <c r="E1652">
+        <v>180349</v>
+      </c>
+    </row>
+    <row r="1653" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1653" s="1">
+        <v>46324</v>
+      </c>
+      <c r="B1653">
+        <v>101</v>
+      </c>
+      <c r="C1653" t="s">
+        <v>9</v>
+      </c>
+      <c r="D1653">
+        <v>70784</v>
+      </c>
+      <c r="E1653">
+        <v>180351</v>
+      </c>
+    </row>
+    <row r="1654" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1654" s="1">
+        <v>46324</v>
+      </c>
+      <c r="B1654">
+        <v>101</v>
+      </c>
+      <c r="C1654" t="s">
+        <v>152</v>
+      </c>
+      <c r="D1654">
+        <v>70798</v>
+      </c>
+      <c r="E1654">
+        <v>180313</v>
+      </c>
+    </row>
+    <row r="1655" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1655" s="1">
+        <v>46324</v>
+      </c>
+      <c r="B1655">
+        <v>101</v>
+      </c>
+      <c r="C1655" t="s">
+        <v>152</v>
+      </c>
+      <c r="D1655">
+        <v>70812</v>
+      </c>
+      <c r="E1655">
+        <v>180361</v>
+      </c>
+    </row>
+    <row r="1656" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1656" s="1">
+        <v>46324</v>
+      </c>
+      <c r="B1656">
+        <v>101</v>
+      </c>
+      <c r="C1656" t="s">
+        <v>34</v>
+      </c>
+      <c r="D1656">
+        <v>71002</v>
+      </c>
+      <c r="E1656">
+        <v>180530</v>
+      </c>
+    </row>
+    <row r="1657" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1657" s="1">
+        <v>46324</v>
+      </c>
+      <c r="B1657">
+        <v>101</v>
+      </c>
+      <c r="C1657" t="s">
+        <v>9</v>
+      </c>
+      <c r="D1657">
+        <v>70963</v>
+      </c>
+      <c r="E1657">
+        <v>180498</v>
+      </c>
+    </row>
+    <row r="1658" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1658" s="1">
+        <v>46324</v>
+      </c>
+      <c r="B1658">
+        <v>101</v>
+      </c>
+      <c r="C1658" t="s">
+        <v>9</v>
+      </c>
+      <c r="D1658">
+        <v>70804</v>
+      </c>
+      <c r="E1658">
+        <v>180346</v>
+      </c>
+    </row>
+    <row r="1659" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1659" s="1">
+        <v>46324</v>
+      </c>
+      <c r="B1659">
+        <v>101</v>
+      </c>
+      <c r="C1659" t="s">
+        <v>9</v>
+      </c>
+      <c r="D1659">
+        <v>70785</v>
+      </c>
+      <c r="E1659">
+        <v>180353</v>
+      </c>
+    </row>
+    <row r="1660" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1660" s="1">
+        <v>46324</v>
+      </c>
+      <c r="B1660">
+        <v>101</v>
+      </c>
+      <c r="C1660" t="s">
+        <v>152</v>
+      </c>
+      <c r="D1660">
+        <v>70774</v>
+      </c>
+      <c r="E1660">
+        <v>180403</v>
+      </c>
+    </row>
+    <row r="1661" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1661" s="1">
+        <v>46324</v>
+      </c>
+      <c r="B1661">
+        <v>101</v>
+      </c>
+      <c r="C1661" t="s">
+        <v>9</v>
+      </c>
+      <c r="D1661">
+        <v>70975</v>
+      </c>
+      <c r="E1661">
+        <v>180505</v>
+      </c>
+    </row>
+    <row r="1662" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1662" s="1">
+        <v>46324</v>
+      </c>
+      <c r="B1662">
+        <v>101</v>
+      </c>
+      <c r="C1662" t="s">
+        <v>34</v>
+      </c>
+      <c r="D1662">
+        <v>70974</v>
+      </c>
+      <c r="E1662">
+        <v>180503</v>
+      </c>
+    </row>
+    <row r="1663" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1663" s="1">
+        <v>46324</v>
+      </c>
+      <c r="B1663">
+        <v>101</v>
+      </c>
+      <c r="C1663" t="s">
+        <v>119</v>
+      </c>
+      <c r="D1663">
+        <v>70901</v>
+      </c>
+      <c r="E1663">
+        <v>180368</v>
+      </c>
+    </row>
+    <row r="1664" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1664" s="1">
+        <v>46324</v>
+      </c>
+      <c r="B1664">
+        <v>101</v>
+      </c>
+      <c r="C1664" t="s">
+        <v>9</v>
+      </c>
+      <c r="D1664">
+        <v>71004</v>
+      </c>
+      <c r="E1664">
+        <v>180534</v>
+      </c>
+    </row>
+    <row r="1665" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1665" s="1">
+        <v>46324</v>
+      </c>
+      <c r="B1665">
+        <v>101</v>
+      </c>
+      <c r="C1665" t="s">
+        <v>9</v>
+      </c>
+      <c r="D1665">
+        <v>70981</v>
+      </c>
+      <c r="E1665">
+        <v>180513</v>
+      </c>
+    </row>
+    <row r="1666" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1666" s="1">
+        <v>46324</v>
+      </c>
+      <c r="B1666">
+        <v>101</v>
+      </c>
+      <c r="C1666" t="s">
+        <v>152</v>
+      </c>
+      <c r="D1666">
+        <v>70773</v>
+      </c>
+      <c r="E1666">
+        <v>180404</v>
+      </c>
+    </row>
+    <row r="1667" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1667" s="1">
+        <v>46324</v>
+      </c>
+      <c r="B1667">
+        <v>101</v>
+      </c>
+      <c r="C1667" t="s">
+        <v>152</v>
+      </c>
+      <c r="D1667">
+        <v>70980</v>
+      </c>
+      <c r="E1667">
+        <v>180510</v>
+      </c>
+    </row>
+    <row r="1668" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1668" s="1">
+        <v>46324</v>
+      </c>
+      <c r="B1668">
+        <v>101</v>
+      </c>
+      <c r="C1668" t="s">
+        <v>8</v>
+      </c>
+      <c r="D1668">
+        <v>70966</v>
+      </c>
+      <c r="E1668">
+        <v>180499</v>
+      </c>
+    </row>
+    <row r="1669" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1669" s="1">
+        <v>46324</v>
+      </c>
+      <c r="B1669">
+        <v>101</v>
+      </c>
+      <c r="C1669" t="s">
+        <v>9</v>
+      </c>
+      <c r="D1669">
+        <v>70983</v>
+      </c>
+      <c r="E1669">
+        <v>180519</v>
+      </c>
+    </row>
+    <row r="1670" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1670" s="1">
+        <v>46324</v>
+      </c>
+      <c r="B1670">
+        <v>101</v>
+      </c>
+      <c r="C1670" t="s">
+        <v>152</v>
+      </c>
+      <c r="D1670">
+        <v>70978</v>
+      </c>
+      <c r="E1670">
+        <v>180515</v>
+      </c>
+    </row>
+    <row r="1671" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1671" s="1">
+        <v>46324</v>
+      </c>
+      <c r="B1671">
+        <v>101</v>
+      </c>
+      <c r="C1671" t="s">
+        <v>9</v>
+      </c>
+      <c r="D1671">
+        <v>70976</v>
+      </c>
+      <c r="E1671">
+        <v>180504</v>
+      </c>
+    </row>
+    <row r="1672" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1672" s="1">
+        <v>46324</v>
+      </c>
+      <c r="B1672">
+        <v>101</v>
+      </c>
+      <c r="C1672" t="s">
+        <v>119</v>
+      </c>
+      <c r="D1672">
+        <v>70757</v>
+      </c>
+      <c r="E1672">
+        <v>180428</v>
+      </c>
+    </row>
+    <row r="1673" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1673" s="1">
+        <v>46324</v>
+      </c>
+      <c r="B1673">
+        <v>101</v>
+      </c>
+      <c r="C1673" t="s">
+        <v>9</v>
+      </c>
+      <c r="D1673">
+        <v>71003</v>
+      </c>
+      <c r="E1673">
+        <v>180531</v>
+      </c>
+    </row>
+    <row r="1674" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1674" s="1">
+        <v>46324</v>
+      </c>
+      <c r="B1674">
+        <v>101</v>
+      </c>
+      <c r="C1674" t="s">
+        <v>9</v>
+      </c>
+      <c r="D1674">
+        <v>70964</v>
+      </c>
+      <c r="E1674">
+        <v>180497</v>
+      </c>
+    </row>
+    <row r="1675" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1675" s="1">
+        <v>46324</v>
+      </c>
+      <c r="B1675">
+        <v>101</v>
+      </c>
+      <c r="C1675" t="s">
+        <v>9</v>
+      </c>
+      <c r="D1675">
+        <v>70979</v>
+      </c>
+      <c r="E1675">
+        <v>180517</v>
+      </c>
+    </row>
+    <row r="1676" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1676" s="1">
+        <v>46324</v>
+      </c>
+      <c r="B1676">
+        <v>101</v>
+      </c>
+      <c r="C1676" t="s">
+        <v>119</v>
+      </c>
+      <c r="D1676">
+        <v>70758</v>
+      </c>
+      <c r="E1676">
+        <v>180429</v>
+      </c>
+    </row>
+    <row r="1677" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1677" s="1">
+        <v>46324</v>
+      </c>
+      <c r="B1677">
+        <v>101</v>
+      </c>
+      <c r="C1677" t="s">
+        <v>9</v>
+      </c>
+      <c r="D1677">
+        <v>71005</v>
+      </c>
+      <c r="E1677">
+        <v>180533</v>
+      </c>
+    </row>
+    <row r="1678" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1678" s="1">
+        <v>46324</v>
+      </c>
+      <c r="B1678">
+        <v>101</v>
+      </c>
+      <c r="C1678" t="s">
+        <v>9</v>
+      </c>
+      <c r="D1678">
+        <v>70988</v>
+      </c>
+      <c r="E1678">
+        <v>180523</v>
+      </c>
+    </row>
+    <row r="1679" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1679" s="1">
+        <v>46324</v>
+      </c>
+      <c r="B1679">
+        <v>101</v>
+      </c>
+      <c r="C1679" t="s">
+        <v>9</v>
+      </c>
+      <c r="D1679">
+        <v>70982</v>
+      </c>
+      <c r="E1679">
+        <v>180518</v>
+      </c>
+    </row>
+    <row r="1680" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1680" s="1">
+        <v>46324</v>
+      </c>
+      <c r="B1680">
+        <v>101</v>
+      </c>
+      <c r="C1680" t="s">
+        <v>119</v>
+      </c>
+      <c r="D1680">
+        <v>71006</v>
+      </c>
+      <c r="E1680">
+        <v>180536</v>
+      </c>
+    </row>
+    <row r="1681" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1681" s="1">
+        <v>46324</v>
+      </c>
+      <c r="B1681">
+        <v>101</v>
+      </c>
+      <c r="C1681" t="s">
+        <v>8</v>
+      </c>
+      <c r="D1681">
+        <v>70969</v>
+      </c>
+      <c r="E1681">
+        <v>180500</v>
+      </c>
+    </row>
+    <row r="1682" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1682" s="1">
+        <v>46324</v>
+      </c>
+      <c r="B1682">
+        <v>101</v>
+      </c>
+      <c r="C1682" t="s">
+        <v>9</v>
+      </c>
+      <c r="D1682">
+        <v>70989</v>
+      </c>
+      <c r="E1682">
+        <v>180522</v>
+      </c>
+    </row>
+    <row r="1683" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1683" s="1">
+        <v>46324</v>
+      </c>
+      <c r="B1683">
+        <v>101</v>
+      </c>
+      <c r="C1683" t="s">
+        <v>9</v>
+      </c>
+      <c r="D1683">
+        <v>70984</v>
+      </c>
+      <c r="E1683">
+        <v>180521</v>
+      </c>
+    </row>
+    <row r="1684" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1684" s="1">
+        <v>46324</v>
+      </c>
+      <c r="B1684">
+        <v>101</v>
+      </c>
+      <c r="C1684" t="s">
+        <v>11</v>
+      </c>
+      <c r="D1684">
+        <v>70977</v>
+      </c>
+      <c r="E1684">
+        <v>180508</v>
+      </c>
+    </row>
+    <row r="1685" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1685" s="1">
+        <v>46324</v>
+      </c>
+      <c r="B1685">
+        <v>101</v>
+      </c>
+      <c r="C1685" t="s">
+        <v>9</v>
+      </c>
+      <c r="D1685">
+        <v>70985</v>
+      </c>
+      <c r="E1685">
+        <v>180520</v>
+      </c>
+    </row>
+    <row r="1686" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1686" s="1">
+        <v>46324</v>
+      </c>
+      <c r="B1686">
+        <v>101</v>
+      </c>
+      <c r="C1686" t="s">
+        <v>9</v>
+      </c>
+      <c r="D1686">
+        <v>70996</v>
+      </c>
+      <c r="E1686">
+        <v>180532</v>
+      </c>
+    </row>
+    <row r="1687" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1687" s="1">
+        <v>46324</v>
+      </c>
+      <c r="B1687">
+        <v>101</v>
+      </c>
+      <c r="C1687" t="s">
+        <v>9</v>
+      </c>
+      <c r="D1687">
+        <v>70997</v>
+      </c>
+      <c r="E1687">
+        <v>180525</v>
+      </c>
+    </row>
+    <row r="1688" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1688" s="1">
+        <v>46324</v>
+      </c>
+      <c r="B1688">
+        <v>101</v>
+      </c>
+      <c r="C1688" t="s">
+        <v>8</v>
+      </c>
+      <c r="D1688">
+        <v>70973</v>
+      </c>
+      <c r="E1688">
+        <v>180502</v>
+      </c>
+    </row>
+    <row r="1689" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1689" s="1">
+        <v>46324</v>
+      </c>
+      <c r="B1689">
+        <v>101</v>
+      </c>
+      <c r="C1689" t="s">
+        <v>8</v>
+      </c>
+      <c r="D1689">
+        <v>70998</v>
+      </c>
+      <c r="E1689">
+        <v>180526</v>
+      </c>
+    </row>
+    <row r="1690" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1690" s="1">
+        <v>46324</v>
+      </c>
+      <c r="B1690">
+        <v>101</v>
+      </c>
+      <c r="C1690" t="s">
+        <v>119</v>
+      </c>
+      <c r="D1690">
+        <v>71007</v>
+      </c>
+      <c r="E1690">
+        <v>180535</v>
+      </c>
+    </row>
+    <row r="1691" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1691" s="1">
+        <v>46324</v>
+      </c>
+      <c r="B1691">
+        <v>101</v>
+      </c>
+      <c r="C1691" t="s">
+        <v>71</v>
+      </c>
+      <c r="E1691">
+        <v>180819</v>
+      </c>
+    </row>
+    <row r="1692" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1692" s="1">
+        <v>46325</v>
+      </c>
+      <c r="B1692">
+        <v>101</v>
+      </c>
+      <c r="C1692" t="s">
+        <v>227</v>
+      </c>
+      <c r="E1692">
+        <v>180339</v>
+      </c>
+    </row>
+    <row r="1693" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1693" s="1">
+        <v>46325</v>
+      </c>
+      <c r="B1693">
+        <v>101</v>
+      </c>
+      <c r="C1693" t="s">
+        <v>173</v>
+      </c>
+      <c r="D1693">
+        <v>70243</v>
+      </c>
+      <c r="E1693">
+        <v>180828</v>
+      </c>
+    </row>
+    <row r="1694" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1694" s="1">
+        <v>46325</v>
+      </c>
+      <c r="B1694">
+        <v>101</v>
+      </c>
+      <c r="C1694" t="s">
+        <v>173</v>
+      </c>
+      <c r="E1694">
+        <v>180397</v>
+      </c>
+    </row>
+    <row r="1695" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1695" s="1">
+        <v>46325</v>
+      </c>
+      <c r="B1695">
+        <v>101</v>
+      </c>
+      <c r="C1695" t="s">
+        <v>97</v>
+      </c>
+      <c r="D1695">
+        <v>70885</v>
+      </c>
+      <c r="E1695">
+        <v>180677</v>
+      </c>
+    </row>
+    <row r="1696" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1696" s="1">
+        <v>46325</v>
+      </c>
+      <c r="B1696">
+        <v>101</v>
+      </c>
+      <c r="C1696" t="s">
+        <v>229</v>
+      </c>
+      <c r="D1696">
+        <v>70255</v>
+      </c>
+      <c r="E1696">
+        <v>180514</v>
+      </c>
+    </row>
+    <row r="1697" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1697" s="1">
+        <v>46325</v>
+      </c>
+      <c r="B1697">
+        <v>101</v>
+      </c>
+      <c r="C1697" t="s">
+        <v>40</v>
+      </c>
+      <c r="D1697">
+        <v>70910</v>
+      </c>
+      <c r="E1697">
+        <v>180622</v>
+      </c>
+    </row>
+    <row r="1698" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1698" s="1">
+        <v>46325</v>
+      </c>
+      <c r="B1698">
+        <v>101</v>
+      </c>
+      <c r="C1698" t="s">
+        <v>40</v>
+      </c>
+      <c r="D1698">
+        <v>71082</v>
+      </c>
+      <c r="E1698">
+        <v>180811</v>
+      </c>
+    </row>
+    <row r="1699" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1699" s="1">
+        <v>46325</v>
+      </c>
+      <c r="B1699">
+        <v>101</v>
+      </c>
+      <c r="C1699" t="s">
+        <v>167</v>
+      </c>
+      <c r="D1699">
+        <v>71066</v>
+      </c>
+      <c r="E1699">
+        <v>180735</v>
+      </c>
+    </row>
+    <row r="1700" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1700" s="1">
+        <v>46325</v>
+      </c>
+      <c r="B1700">
+        <v>101</v>
+      </c>
+      <c r="C1700" t="s">
+        <v>45</v>
+      </c>
+      <c r="D1700">
+        <v>70930</v>
+      </c>
+      <c r="E1700">
+        <v>180733</v>
+      </c>
+    </row>
+    <row r="1701" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1701" s="1">
+        <v>46325</v>
+      </c>
+      <c r="B1701">
+        <v>101</v>
+      </c>
+      <c r="C1701" t="s">
+        <v>24</v>
+      </c>
+      <c r="E1701">
+        <v>180813</v>
+      </c>
+    </row>
+    <row r="1702" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1702" s="1">
+        <v>46325</v>
+      </c>
+      <c r="B1702">
+        <v>101</v>
+      </c>
+      <c r="C1702" t="s">
+        <v>24</v>
+      </c>
+      <c r="D1702">
+        <v>71123</v>
+      </c>
+      <c r="E1702">
+        <v>180834</v>
+      </c>
+    </row>
+    <row r="1703" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1703" s="1">
+        <v>46325</v>
+      </c>
+      <c r="B1703">
+        <v>101</v>
+      </c>
+      <c r="C1703" t="s">
+        <v>15</v>
+      </c>
+      <c r="D1703">
+        <v>71060</v>
+      </c>
+      <c r="E1703">
+        <v>180830</v>
+      </c>
+    </row>
+    <row r="1704" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1704" s="1">
+        <v>46325</v>
+      </c>
+      <c r="B1704">
+        <v>101</v>
+      </c>
+      <c r="C1704" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1704">
+        <v>70877</v>
+      </c>
+      <c r="E1704">
+        <v>180341</v>
+      </c>
+    </row>
+    <row r="1705" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1705" s="1">
+        <v>46325</v>
+      </c>
+      <c r="B1705">
+        <v>101</v>
+      </c>
+      <c r="C1705" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1705">
+        <v>69185</v>
+      </c>
+      <c r="E1705">
+        <v>180506</v>
+      </c>
+    </row>
+    <row r="1706" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1706" s="1">
+        <v>46325</v>
+      </c>
+      <c r="B1706">
+        <v>101</v>
+      </c>
+      <c r="C1706" t="s">
+        <v>98</v>
+      </c>
+      <c r="D1706">
+        <v>71019</v>
+      </c>
+      <c r="E1706">
+        <v>180825</v>
+      </c>
+    </row>
+    <row r="1707" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1707" s="1">
+        <v>46325</v>
+      </c>
+      <c r="B1707">
+        <v>101</v>
+      </c>
+      <c r="C1707" t="s">
+        <v>80</v>
+      </c>
+      <c r="D1707">
+        <v>65955</v>
+      </c>
+      <c r="E1707">
+        <v>180718</v>
+      </c>
+    </row>
+    <row r="1708" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1708" s="1">
+        <v>46325</v>
+      </c>
+      <c r="B1708">
+        <v>101</v>
+      </c>
+      <c r="C1708" t="s">
+        <v>46</v>
+      </c>
+      <c r="D1708">
+        <v>71133</v>
+      </c>
+      <c r="E1708">
+        <v>180799</v>
+      </c>
+    </row>
+    <row r="1709" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1709" s="1">
+        <v>46325</v>
+      </c>
+      <c r="B1709">
+        <v>101</v>
+      </c>
+      <c r="C1709" t="s">
+        <v>269</v>
+      </c>
+      <c r="D1709">
+        <v>66634</v>
+      </c>
+      <c r="E1709">
+        <v>180804</v>
+      </c>
+    </row>
+    <row r="1710" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1710" s="1">
+        <v>46325</v>
+      </c>
+      <c r="B1710">
+        <v>101</v>
+      </c>
+      <c r="C1710" t="s">
+        <v>235</v>
+      </c>
+      <c r="E1710">
+        <v>180838</v>
+      </c>
+    </row>
+    <row r="1711" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1711" s="1">
+        <v>46325</v>
+      </c>
+      <c r="B1711">
+        <v>101</v>
+      </c>
+      <c r="C1711" t="s">
+        <v>235</v>
+      </c>
+      <c r="D1711">
+        <v>70001</v>
+      </c>
+      <c r="E1711">
+        <v>180814</v>
+      </c>
+    </row>
+    <row r="1712" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1712" s="1">
+        <v>46325</v>
+      </c>
+      <c r="B1712">
+        <v>101</v>
+      </c>
+      <c r="C1712" t="s">
+        <v>270</v>
+      </c>
+      <c r="D1712">
+        <v>71064</v>
+      </c>
+      <c r="E1712">
+        <v>180826</v>
+      </c>
+    </row>
+    <row r="1713" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1713" s="1">
+        <v>46325</v>
+      </c>
+      <c r="B1713">
+        <v>101</v>
+      </c>
+      <c r="C1713" t="s">
+        <v>23</v>
+      </c>
+      <c r="E1713">
+        <v>180831</v>
+      </c>
+    </row>
+    <row r="1714" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1714" s="1">
+        <v>46325</v>
+      </c>
+      <c r="B1714">
+        <v>101</v>
+      </c>
+      <c r="C1714" t="s">
+        <v>23</v>
+      </c>
+      <c r="E1714">
+        <v>180840</v>
+      </c>
+    </row>
+    <row r="1715" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1715" s="1">
+        <v>46325</v>
+      </c>
+      <c r="B1715">
+        <v>101</v>
+      </c>
+      <c r="C1715" t="s">
+        <v>23</v>
+      </c>
+      <c r="D1715">
+        <v>71131</v>
+      </c>
+      <c r="E1715">
+        <v>180808</v>
+      </c>
+    </row>
+    <row r="1716" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1716" s="1">
+        <v>46325</v>
+      </c>
+      <c r="B1716">
+        <v>101</v>
+      </c>
+      <c r="C1716" t="s">
+        <v>23</v>
+      </c>
+      <c r="E1716">
+        <v>180815</v>
+      </c>
+    </row>
+    <row r="1717" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1717" s="1">
+        <v>46325</v>
+      </c>
+      <c r="B1717">
+        <v>101</v>
+      </c>
+      <c r="C1717" t="s">
+        <v>23</v>
+      </c>
+      <c r="D1717">
+        <v>70644</v>
+      </c>
+      <c r="E1717">
+        <v>180836</v>
+      </c>
+    </row>
+    <row r="1718" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1718" s="1">
+        <v>46325</v>
+      </c>
+      <c r="B1718">
+        <v>101</v>
+      </c>
+      <c r="C1718" t="s">
+        <v>23</v>
+      </c>
+      <c r="D1718">
+        <v>69416</v>
+      </c>
+      <c r="E1718">
+        <v>180835</v>
+      </c>
+    </row>
+    <row r="1719" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1719" s="1">
+        <v>46325</v>
+      </c>
+      <c r="B1719">
+        <v>101</v>
+      </c>
+      <c r="C1719" t="s">
+        <v>23</v>
+      </c>
+      <c r="D1719">
+        <v>70941</v>
+      </c>
+      <c r="E1719">
+        <v>180824</v>
+      </c>
+    </row>
+    <row r="1720" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1720" s="1">
+        <v>46325</v>
+      </c>
+      <c r="B1720">
+        <v>101</v>
+      </c>
+      <c r="C1720" t="s">
+        <v>23</v>
+      </c>
+      <c r="D1720">
+        <v>69571</v>
+      </c>
+      <c r="E1720">
+        <v>180730</v>
+      </c>
+    </row>
+    <row r="1721" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1721" s="1">
+        <v>46325</v>
+      </c>
+      <c r="B1721">
+        <v>101</v>
+      </c>
+      <c r="C1721" t="s">
+        <v>23</v>
+      </c>
+      <c r="D1721">
+        <v>70048</v>
+      </c>
+      <c r="E1721">
+        <v>180833</v>
+      </c>
+    </row>
+    <row r="1722" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1722" s="1">
+        <v>46325</v>
+      </c>
+      <c r="B1722">
+        <v>101</v>
+      </c>
+      <c r="C1722" t="s">
+        <v>36</v>
+      </c>
+      <c r="D1722">
+        <v>71055</v>
+      </c>
+      <c r="E1722">
+        <v>180793</v>
+      </c>
+    </row>
+    <row r="1723" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1723" s="1">
+        <v>46325</v>
+      </c>
+      <c r="B1723">
+        <v>101</v>
+      </c>
+      <c r="C1723" t="s">
+        <v>89</v>
+      </c>
+      <c r="D1723">
+        <v>71042</v>
+      </c>
+      <c r="E1723">
+        <v>180843</v>
+      </c>
+    </row>
+    <row r="1724" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1724" s="1">
+        <v>46325</v>
+      </c>
+      <c r="B1724">
+        <v>101</v>
+      </c>
+      <c r="C1724" t="s">
+        <v>22</v>
+      </c>
+      <c r="D1724">
+        <v>70924</v>
+      </c>
+      <c r="E1724">
+        <v>180726</v>
+      </c>
+    </row>
+    <row r="1725" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1725" s="1">
+        <v>46325</v>
+      </c>
+      <c r="B1725">
+        <v>101</v>
+      </c>
+      <c r="C1725" t="s">
+        <v>108</v>
+      </c>
+      <c r="E1725">
+        <v>180817</v>
+      </c>
+    </row>
+    <row r="1726" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1726" s="1">
+        <v>46325</v>
+      </c>
+      <c r="B1726">
+        <v>101</v>
+      </c>
+      <c r="C1726" t="s">
+        <v>85</v>
+      </c>
+      <c r="D1726">
+        <v>70917</v>
+      </c>
+      <c r="E1726">
+        <v>180805</v>
+      </c>
+    </row>
+    <row r="1727" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1727" s="1">
+        <v>46325</v>
+      </c>
+      <c r="B1727">
+        <v>101</v>
+      </c>
+      <c r="C1727" t="s">
+        <v>23</v>
+      </c>
+      <c r="D1727">
+        <v>70502</v>
+      </c>
+      <c r="E1727">
+        <v>180837</v>
+      </c>
+    </row>
+    <row r="1728" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1728" s="1">
+        <v>46325</v>
+      </c>
+      <c r="B1728">
+        <v>101</v>
+      </c>
+      <c r="C1728" t="s">
+        <v>39</v>
+      </c>
+      <c r="D1728">
+        <v>71056</v>
+      </c>
+      <c r="E1728">
+        <v>180734</v>
+      </c>
+    </row>
+    <row r="1729" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1729" s="1">
+        <v>46325</v>
+      </c>
+      <c r="B1729">
+        <v>101</v>
+      </c>
+      <c r="C1729" t="s">
+        <v>107</v>
+      </c>
+      <c r="D1729">
+        <v>70972</v>
+      </c>
+      <c r="E1729">
+        <v>180737</v>
+      </c>
+    </row>
+    <row r="1730" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1730" s="1">
+        <v>46325</v>
+      </c>
+      <c r="B1730">
+        <v>101</v>
+      </c>
+      <c r="C1730" t="s">
+        <v>23</v>
+      </c>
+      <c r="D1730">
+        <v>70463</v>
+      </c>
+      <c r="E1730">
+        <v>180794</v>
+      </c>
+    </row>
+    <row r="1731" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1731" s="1">
+        <v>46325</v>
+      </c>
+      <c r="B1731">
+        <v>101</v>
+      </c>
+      <c r="C1731" t="s">
+        <v>26</v>
+      </c>
+      <c r="D1731">
+        <v>70862</v>
+      </c>
+      <c r="E1731">
+        <v>180798</v>
+      </c>
+    </row>
+    <row r="1732" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1732" s="1">
+        <v>46325</v>
+      </c>
+      <c r="B1732">
+        <v>101</v>
+      </c>
+      <c r="C1732" t="s">
+        <v>26</v>
+      </c>
+      <c r="D1732">
+        <v>70858</v>
+      </c>
+      <c r="E1732">
+        <v>180679</v>
+      </c>
+    </row>
+    <row r="1733" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1733" s="1">
+        <v>46325</v>
+      </c>
+      <c r="B1733">
+        <v>101</v>
+      </c>
+      <c r="C1733" t="s">
+        <v>56</v>
+      </c>
+      <c r="D1733">
+        <v>69584</v>
+      </c>
+      <c r="E1733">
+        <v>180723</v>
+      </c>
+    </row>
+    <row r="1734" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1734" s="1">
+        <v>46325</v>
+      </c>
+      <c r="B1734">
+        <v>101</v>
+      </c>
+      <c r="C1734" t="s">
+        <v>45</v>
+      </c>
+      <c r="E1734">
+        <v>180816</v>
+      </c>
+    </row>
+    <row r="1735" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1735" s="1">
+        <v>46325</v>
+      </c>
+      <c r="B1735">
+        <v>101</v>
+      </c>
+      <c r="C1735" t="s">
+        <v>19</v>
+      </c>
+      <c r="E1735">
+        <v>180806</v>
+      </c>
+    </row>
+    <row r="1736" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1736" s="1">
+        <v>46325</v>
+      </c>
+      <c r="B1736">
+        <v>101</v>
+      </c>
+      <c r="C1736" t="s">
+        <v>19</v>
+      </c>
+      <c r="D1736">
+        <v>67069</v>
+      </c>
+      <c r="E1736">
+        <v>180738</v>
+      </c>
+    </row>
+    <row r="1737" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1737" s="1">
+        <v>46325</v>
+      </c>
+      <c r="B1737">
+        <v>101</v>
+      </c>
+      <c r="C1737" t="s">
+        <v>19</v>
+      </c>
+      <c r="D1737">
+        <v>70940</v>
+      </c>
+      <c r="E1737">
+        <v>180720</v>
+      </c>
+    </row>
   </sheetData>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:E719">
     <sortCondition ref="A703:A719"/>
@@ -28673,7 +30207,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5180BF9C-1943-4030-8A1B-6F86FE205C17}">
-  <dimension ref="A1:C23"/>
+  <dimension ref="A1:C24"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="12.85546875" style="1" bestFit="1" customWidth="1"/>
@@ -28682,7 +30216,7 @@
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="str" cm="1">
-        <f t="array" ref="A1:A23">_xlfn.UNIQUE(Romaneios!A1:A1645)</f>
+        <f t="array" ref="A1:A24">_xlfn.UNIQUE(Romaneios!A1:A1737)</f>
         <v>Dt. Romaneio</v>
       </c>
       <c r="B1" t="s">
@@ -28885,7 +30419,16 @@
       </c>
       <c r="B23">
         <f>COUNTIF(Romaneios!A:A,DadosRomaneios!A23)</f>
-        <v>77</v>
+        <v>123</v>
+      </c>
+    </row>
+    <row r="24" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A24" s="1">
+        <v>46325</v>
+      </c>
+      <c r="B24">
+        <f>COUNTIF(Romaneios!A:A,DadosRomaneios!A24)</f>
+        <v>46</v>
       </c>
     </row>
   </sheetData>
